--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="327">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -94,6 +94,9 @@
     <t/>
   </si>
   <si>
+    <t>Tarea Terminada</t>
+  </si>
+  <si>
     <t>1215727723381461</t>
   </si>
   <si>
@@ -107,9 +110,6 @@
   </si>
   <si>
     <t>Alta</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215727723447838</t>
@@ -167,111 +167,122 @@
     <t>Ingenieria Basica Motor</t>
   </si>
   <si>
-    <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
+    <t>Motor de Stock Código 350012</t>
   </si>
   <si>
     <t>propuesta motor,Ingenieria Jefe de proyecto:,Analisis de costeo</t>
   </si>
   <si>
+    <t>1215727792543713</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Definición Rodete ZVN 1-9:
+        Alabe s/ plano 4999.01
+        Código 300000
+        Rodete de placas s/plano 4999.00
+        Z8 N590
+        Calaje y consumo: hgutierrez@zitron.com por favor tu apoyo.
+</t>
+  </si>
+  <si>
+    <t>propuesta alabes,Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta nucleo rodeteOT 4360</t>
+  </si>
+  <si>
+    <t>1215727792546176</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215727792546198</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1215727332551584</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta motor,propuesta alabes,propuesta Corte Laser OT 43164360,propuesta nucleo rodeteOT 4360</t>
+  </si>
+  <si>
+    <t>1215727792562799</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor OT 4360</t>
+  </si>
+  <si>
+    <t>1215727723502427</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Definición Rodete ZVN 1-9:
+        Alabe s/ plano 4999.01
+        Código 300000
+        Rodete de placas s/plano 4999.00
+        Z8 N590
+</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe OT 4316</t>
+  </si>
+  <si>
+    <t>1215728035784425</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodeteOT 4360</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete OT 4316</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215728035784447</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT 43164360</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4360</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
-    <t>1215727792543713</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Selección de Rodete:
-        Rodete de placas s/plano 3073.00
-        Alabe s/ plano 3073.01
-        Z8 N600
-        Código 300003
-        hgutierrez@zitron.com, tu apoyo con la definición de calaje.
-</t>
-  </si>
-  <si>
-    <t>propuesta alabes,Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta nucleo rodeteOT 4360</t>
-  </si>
-  <si>
-    <t>1215727792546176</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215727792546198</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1215727332551584</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta motor,propuesta alabes,propuesta Corte Laser OT 43164360,propuesta nucleo rodeteOT 4360</t>
-  </si>
-  <si>
-    <t>1215727792562799</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor OT 4360</t>
-  </si>
-  <si>
-    <t>1215727723502427</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe OT 4316</t>
-  </si>
-  <si>
-    <t>1215728035784425</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodeteOT 4360</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete OT 4316</t>
-  </si>
-  <si>
-    <t>1215728035784447</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT 43164360</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4360</t>
-  </si>
-  <si>
     <t>1215727831264658</t>
   </si>
   <si>
@@ -323,16 +334,16 @@
     <t>Generación OC Alabe OT 4316,Fabricación Alabe OT 4316</t>
   </si>
   <si>
+    <t>1215727792616534</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe OT 4316</t>
+  </si>
+  <si>
+    <t>Alabe OT 4360,Fabricación Alabe OT 4316</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>1215727792616534</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4316</t>
-  </si>
-  <si>
-    <t>Alabe OT 4360,Fabricación Alabe OT 4316</t>
   </si>
   <si>
     <t>1215727792616554</t>
@@ -1058,6 +1069,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF62d26f"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
@@ -1074,11 +1090,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFeec300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF62d26f"/>
       </patternFill>
     </fill>
   </fills>
@@ -1139,8 +1150,8 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1633,9 +1644,11 @@
       <c r="B4" s="5">
         <v>46188.634159629626</v>
       </c>
-      <c r="C4" s="6"/>
+      <c r="C4" s="5">
+        <v>46188.91968755787</v>
+      </c>
       <c r="D4" s="5">
-        <v>46188.64390645833</v>
+        <v>46188.91970172454</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1670,70 +1683,76 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
+      <c r="T4" s="6">
+        <v>1</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="9">
+        <v>46188.634310856476</v>
+      </c>
+      <c r="C5" s="9">
+        <v>46188.919674178236</v>
+      </c>
+      <c r="D5" s="9">
+        <v>46188.91968832176</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="9">
+        <v>46176</v>
+      </c>
+      <c r="J5" s="9">
+        <v>46176</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>46176</v>
+      </c>
+      <c r="R5" s="9">
+        <v>46176</v>
+      </c>
+      <c r="S5" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" s="10">
+        <v>1</v>
+      </c>
+      <c r="U5" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" s="8">
-        <v>46188.634310856476</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8">
-        <v>46188.67335834491</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="8">
-        <v>46176</v>
-      </c>
-      <c r="J5" s="8">
-        <v>46176</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>46176</v>
-      </c>
-      <c r="R5" s="8">
-        <v>46176</v>
-      </c>
-      <c r="S5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T5" s="9">
-        <v>0</v>
-      </c>
-      <c r="U5" s="11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1743,9 +1762,11 @@
       <c r="B6" s="5">
         <v>46188.63431648148</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="5">
+        <v>46188.919543298616</v>
+      </c>
       <c r="D6" s="5">
-        <v>46188.67335453704</v>
+        <v>46188.91956144676</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1754,10 +1775,10 @@
         <v>26</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="5">
         <v>46176</v>
@@ -1789,77 +1810,79 @@
       <c r="R6" s="5">
         <v>46176</v>
       </c>
-      <c r="S6" s="10" t="s">
+      <c r="S6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" s="6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46188.63432182871</v>
+      </c>
+      <c r="C7" s="9">
+        <v>46188.91959428241</v>
+      </c>
+      <c r="D7" s="9">
+        <v>46188.9196094213</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="T6" s="6">
-        <v>0</v>
-      </c>
-      <c r="U6" s="11" t="s">
+      <c r="I7" s="9">
+        <v>46176</v>
+      </c>
+      <c r="J7" s="9">
+        <v>46176</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>46176</v>
+      </c>
+      <c r="R7" s="9">
+        <v>46176</v>
+      </c>
+      <c r="S7" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="8">
-        <v>46188.63432182871</v>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8">
-        <v>46188.67335145833</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="8">
-        <v>46176</v>
-      </c>
-      <c r="J7" s="8">
-        <v>46176</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>46176</v>
-      </c>
-      <c r="R7" s="8">
-        <v>46176</v>
-      </c>
-      <c r="S7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T7" s="9">
-        <v>0</v>
-      </c>
-      <c r="U7" s="11" t="s">
-        <v>32</v>
+      <c r="T7" s="10">
+        <v>1</v>
+      </c>
+      <c r="U7" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -1869,9 +1892,11 @@
       <c r="B8" s="5">
         <v>46188.634326643514</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="5">
+        <v>46188.919635115744</v>
+      </c>
       <c r="D8" s="5">
-        <v>46188.67334635417</v>
+        <v>46188.91965210648</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1880,10 +1905,10 @@
         <v>26</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="5">
         <v>46176</v>
@@ -1915,62 +1940,68 @@
       <c r="R8" s="5">
         <v>46176</v>
       </c>
-      <c r="S8" s="10" t="s">
-        <v>31</v>
+      <c r="S8" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T8" s="6">
+        <v>1</v>
+      </c>
+      <c r="U8" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46188.634165474534</v>
+      </c>
+      <c r="C9" s="9">
+        <v>46188.92057981482</v>
+      </c>
+      <c r="D9" s="9">
+        <v>46188.92059026621</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="U8" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="8">
-        <v>46188.634165474534</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="8">
-        <v>46188.64617423611</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="9" t="s">
+      <c r="N9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="P9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
+      <c r="P9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10">
+        <v>1</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1979,9 +2010,11 @@
       <c r="B10" s="5">
         <v>46188.63433173611</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46188.920111388885</v>
+      </c>
       <c r="D10" s="5">
-        <v>46188.67342688657</v>
+        <v>46188.920113182874</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -1990,10 +2023,10 @@
         <v>26</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="5">
         <v>46177</v>
@@ -2025,101 +2058,105 @@
       <c r="R10" s="5">
         <v>46178</v>
       </c>
-      <c r="S10" s="10" t="s">
+      <c r="S10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T10" s="6">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="9">
+        <v>46188.63434310185</v>
+      </c>
+      <c r="C11" s="9">
+        <v>46188.91974537037</v>
+      </c>
+      <c r="D11" s="9">
+        <v>46188.92032122685</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="8">
-        <v>46188.63434310185</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8">
-        <v>46188.67342364583</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="I11" s="9">
+        <v>46177</v>
+      </c>
+      <c r="J11" s="9">
+        <v>46178</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="8">
+      <c r="M11" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="9">
         <v>46177</v>
       </c>
-      <c r="J11" s="8">
+      <c r="R11" s="9">
         <v>46178</v>
       </c>
-      <c r="K11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>46177</v>
-      </c>
-      <c r="R11" s="8">
-        <v>46178</v>
-      </c>
-      <c r="S11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T11" s="9">
-        <v>0</v>
-      </c>
-      <c r="U11" s="10" t="s">
-        <v>49</v>
+      <c r="S11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="10">
+        <v>1</v>
+      </c>
+      <c r="U11" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="5">
         <v>46188.63435032408</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46188.92048497685</v>
+      </c>
       <c r="D12" s="5">
-        <v>46188.67342074074</v>
+        <v>46188.92050125</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="5">
         <v>46177</v>
@@ -2143,7 +2180,7 @@
         <v>36</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q12" s="5">
         <v>46177</v>
@@ -2151,92 +2188,94 @@
       <c r="R12" s="5">
         <v>46185</v>
       </c>
-      <c r="S12" s="10" t="s">
+      <c r="S12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T12" s="6">
+        <v>1</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="9">
+        <v>46188.634356759256</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46188.920564201384</v>
+      </c>
+      <c r="D13" s="9">
+        <v>46188.92057991898</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="8">
-        <v>46188.634356759256</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="8">
-        <v>46188.67341725694</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="I13" s="9">
+        <v>46177</v>
+      </c>
+      <c r="J13" s="9">
+        <v>46185</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="O13" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="8">
+      <c r="P13" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q13" s="9">
         <v>46177</v>
       </c>
-      <c r="J13" s="8">
+      <c r="R13" s="9">
         <v>46185</v>
       </c>
-      <c r="K13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>46177</v>
-      </c>
-      <c r="R13" s="8">
-        <v>46185</v>
-      </c>
-      <c r="S13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T13" s="9">
-        <v>0</v>
-      </c>
-      <c r="U13" s="10" t="s">
-        <v>49</v>
+      <c r="S13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T13" s="10">
+        <v>1</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" s="5">
         <v>46188.634170000005</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46188.65327028935</v>
+        <v>46188.921342905094</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2260,7 +2299,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2272,90 +2311,94 @@
       <c r="U14" s="6"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="9">
+        <v>46188.63436615741</v>
+      </c>
+      <c r="C15" s="9">
+        <v>46188.92065792824</v>
+      </c>
+      <c r="D15" s="9">
+        <v>46188.9208512037</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="8">
-        <v>46188.63436615741</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8">
-        <v>46188.67348193287</v>
-      </c>
-      <c r="E15" s="9" t="s">
+      <c r="F15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="9">
+        <v>46181</v>
+      </c>
+      <c r="J15" s="9">
+        <v>46182</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="8">
+      <c r="Q15" s="9">
         <v>46181</v>
       </c>
-      <c r="J15" s="8">
+      <c r="R15" s="9">
         <v>46182</v>
       </c>
-      <c r="K15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="O15" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>46181</v>
-      </c>
-      <c r="R15" s="8">
-        <v>46182</v>
-      </c>
-      <c r="S15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T15" s="9">
-        <v>0</v>
-      </c>
-      <c r="U15" s="10" t="s">
-        <v>49</v>
+      <c r="S15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" s="10">
+        <v>1</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="5">
         <v>46188.63437259259</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5">
+        <v>46188.9213359375</v>
+      </c>
       <c r="D16" s="5">
-        <v>46188.67347890046</v>
+        <v>46188.92135230324</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I16" s="5">
         <v>46181</v>
@@ -2367,16 +2410,16 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>69</v>
@@ -2387,82 +2430,82 @@
       <c r="R16" s="5">
         <v>46182</v>
       </c>
-      <c r="S16" s="10" t="s">
-        <v>31</v>
+      <c r="S16" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T16" s="6">
+        <v>1</v>
+      </c>
+      <c r="U16" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46188.63437929398</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9">
+        <v>46188.91976528935</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I17" s="9">
+        <v>46181</v>
+      </c>
+      <c r="J17" s="9">
+        <v>46182</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O17" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="P17" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>46211</v>
+      </c>
+      <c r="R17" s="9">
+        <v>46182</v>
+      </c>
+      <c r="S17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T17" s="10">
         <v>0</v>
       </c>
-      <c r="U16" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="8">
-        <v>46188.63437929398</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="8">
-        <v>46188.67352045139</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I17" s="8">
-        <v>46181</v>
-      </c>
-      <c r="J17" s="8">
-        <v>46182</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="O17" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="P17" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>46211</v>
-      </c>
-      <c r="R17" s="8">
-        <v>46182</v>
-      </c>
-      <c r="S17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T17" s="9">
-        <v>0</v>
-      </c>
-      <c r="U17" s="10" t="s">
-        <v>49</v>
+      <c r="U17" s="12" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46188.63438636574</v>
@@ -2472,16 +2515,16 @@
         <v>46188.673596319444</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46211</v>
@@ -2499,13 +2542,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46211</v>
@@ -2513,82 +2556,82 @@
       <c r="R18" s="5">
         <v>46212</v>
       </c>
-      <c r="S18" s="10" t="s">
-        <v>31</v>
+      <c r="S18" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="10" t="s">
-        <v>49</v>
+      <c r="U18" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="8">
+      <c r="A19" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="9">
         <v>46188.634392708336</v>
       </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8">
+      <c r="C19" s="10"/>
+      <c r="D19" s="9">
         <v>46188.67359288194</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I19" s="9">
+        <v>46211</v>
+      </c>
+      <c r="J19" s="9">
+        <v>46212</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P19" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>46211</v>
+      </c>
+      <c r="R19" s="9">
+        <v>46212</v>
+      </c>
+      <c r="S19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" s="10">
+        <v>0</v>
+      </c>
+      <c r="U19" s="11" t="s">
         <v>81</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I19" s="8">
-        <v>46211</v>
-      </c>
-      <c r="J19" s="8">
-        <v>46212</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>46211</v>
-      </c>
-      <c r="R19" s="8">
-        <v>46212</v>
-      </c>
-      <c r="S19" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T19" s="9">
-        <v>0</v>
-      </c>
-      <c r="U19" s="10" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46188.63439828704</v>
@@ -2598,16 +2641,16 @@
         <v>46188.67358973379</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46211</v>
@@ -2625,13 +2668,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46211</v>
@@ -2639,82 +2682,82 @@
       <c r="R20" s="5">
         <v>46212</v>
       </c>
-      <c r="S20" s="10" t="s">
-        <v>31</v>
+      <c r="S20" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="10" t="s">
-        <v>49</v>
+      <c r="U20" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="8">
+      <c r="A21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="9">
         <v>46188.634403055556</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="8">
+      <c r="C21" s="10"/>
+      <c r="D21" s="9">
         <v>46188.673584675926</v>
       </c>
-      <c r="E21" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="9" t="s">
+      <c r="E21" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I21" s="8">
+      <c r="H21" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21" s="9">
         <v>46211</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="9">
         <v>46212</v>
       </c>
-      <c r="K21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q21" s="8">
+      <c r="K21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="O21" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P21" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q21" s="9">
         <v>46211</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="9">
         <v>46212</v>
       </c>
-      <c r="S21" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T21" s="9">
+      <c r="S21" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="10" t="s">
-        <v>49</v>
+      <c r="U21" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46188.634174861116</v>
@@ -2724,7 +2767,7 @@
         <v>46188.65473270833</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2748,7 +2791,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2760,90 +2803,90 @@
       <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" s="9">
+        <v>46188.63440866898</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="9">
+        <v>46189.16963417824</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I23" s="9">
+        <v>46183</v>
+      </c>
+      <c r="J23" s="9">
+        <v>46188</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="8">
-        <v>46188.63440866898</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="8">
-        <v>46188.67370075232</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23" s="8">
+      <c r="O23" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="P23" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q23" s="9">
         <v>46183</v>
       </c>
-      <c r="J23" s="8">
+      <c r="R23" s="9">
         <v>46188</v>
       </c>
-      <c r="K23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>46183</v>
-      </c>
-      <c r="R23" s="8">
-        <v>46188</v>
-      </c>
-      <c r="S23" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T23" s="9">
+      <c r="S23" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="T23" s="10">
         <v>0</v>
       </c>
-      <c r="U23" s="10" t="s">
-        <v>49</v>
+      <c r="U23" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46188.63441429398</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46188.673676770835</v>
+        <v>46188.92134424769</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I24" s="5">
         <v>46183</v>
@@ -2861,88 +2904,88 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
-      <c r="S24" s="12" t="s">
-        <v>97</v>
+      <c r="S24" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="10" t="s">
-        <v>49</v>
+      <c r="U24" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="8">
+      <c r="A25" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="9">
         <v>46188.63442</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="8">
+      <c r="C25" s="10"/>
+      <c r="D25" s="9">
         <v>46188.67367325231</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="9">
+        <v>46185</v>
+      </c>
+      <c r="J25" s="9">
+        <v>46188</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="P25" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I25" s="8">
-        <v>46185</v>
-      </c>
-      <c r="J25" s="8">
-        <v>46188</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="9"/>
-      <c r="S25" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T25" s="9">
+      <c r="T25" s="10">
         <v>0</v>
       </c>
-      <c r="U25" s="10" t="s">
-        <v>49</v>
+      <c r="U25" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
@@ -2952,16 +2995,16 @@
         <v>46188.67380942129</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -2979,13 +3022,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="5">
         <v>46183</v>
@@ -2993,78 +3036,78 @@
       <c r="R26" s="5">
         <v>46204</v>
       </c>
-      <c r="S26" s="12" t="s">
-        <v>97</v>
+      <c r="S26" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
-      <c r="U26" s="10" t="s">
-        <v>49</v>
+      <c r="U26" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="9">
+        <v>46188.634431805556</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9">
+        <v>46188.67377717592</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I27" s="9">
+        <v>46183</v>
+      </c>
+      <c r="J27" s="9">
+        <v>46184</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="8">
-        <v>46188.634431805556</v>
-      </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="8">
-        <v>46188.67377717592</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I27" s="8">
-        <v>46183</v>
-      </c>
-      <c r="J27" s="8">
-        <v>46184</v>
-      </c>
-      <c r="K27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="O27" s="9" t="s">
+      <c r="O27" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="P27" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T27" s="9">
+      <c r="P27" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T27" s="10">
         <v>0</v>
       </c>
-      <c r="U27" s="10" t="s">
-        <v>49</v>
+      <c r="U27" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3074,16 +3117,16 @@
         <v>46188.67377366898</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3101,111 +3144,111 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
-      <c r="S28" s="12" t="s">
-        <v>97</v>
+      <c r="S28" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="10" t="s">
-        <v>49</v>
+      <c r="U28" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29" s="8">
+      <c r="A29" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="9">
         <v>46188.63444313657</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="8">
+      <c r="C29" s="10"/>
+      <c r="D29" s="9">
         <v>46188.67394298611</v>
       </c>
-      <c r="E29" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I29" s="8">
+      <c r="E29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I29" s="9">
         <v>46183</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="9">
         <v>46220</v>
       </c>
-      <c r="K29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q29" s="8">
+      <c r="K29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="O29" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="P29" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q29" s="9">
         <v>46183</v>
       </c>
-      <c r="R29" s="8">
+      <c r="R29" s="9">
         <v>46220</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T29" s="9">
+      <c r="S29" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T29" s="10">
         <v>0</v>
       </c>
-      <c r="U29" s="10" t="s">
-        <v>49</v>
+      <c r="U29" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63444855324</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.673913900464</v>
+        <v>46188.92066599537</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I30" s="5">
         <v>46183</v>
@@ -3223,88 +3266,88 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
-      <c r="S30" s="12" t="s">
-        <v>97</v>
+      <c r="S30" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="10" t="s">
-        <v>49</v>
+      <c r="U30" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="9">
+        <v>46188.63445415509</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="9">
+        <v>46188.673910219906</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I31" s="9">
+        <v>46192</v>
+      </c>
+      <c r="J31" s="9">
+        <v>46220</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="O31" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="8">
-        <v>46188.63445415509</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="8">
-        <v>46188.673910219906</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I31" s="8">
-        <v>46192</v>
-      </c>
-      <c r="J31" s="8">
-        <v>46220</v>
-      </c>
-      <c r="K31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="9"/>
-      <c r="S31" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T31" s="9">
+      <c r="P31" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T31" s="10">
         <v>0</v>
       </c>
-      <c r="U31" s="10" t="s">
-        <v>49</v>
+      <c r="U31" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63450900463</v>
@@ -3314,16 +3357,16 @@
         <v>46188.67390592593</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I32" s="5">
         <v>46192</v>
@@ -3341,92 +3384,92 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
-      <c r="S32" s="12" t="s">
-        <v>97</v>
+      <c r="S32" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="10" t="s">
-        <v>49</v>
+      <c r="U32" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33" s="8">
+      <c r="A33" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B33" s="9">
         <v>46188.63451584491</v>
       </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="8">
+      <c r="C33" s="10"/>
+      <c r="D33" s="9">
         <v>46188.674114560185</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="H33" s="9" t="s">
+      <c r="E33" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="I33" s="8">
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I33" s="9">
         <v>46213</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="9">
         <v>46225</v>
       </c>
-      <c r="K33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="P33" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q33" s="8">
+      <c r="K33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="O33" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="P33" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q33" s="9">
         <v>46213</v>
       </c>
-      <c r="R33" s="8">
+      <c r="R33" s="9">
         <v>46225</v>
       </c>
-      <c r="S33" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T33" s="9">
+      <c r="S33" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T33" s="10">
         <v>0</v>
       </c>
-      <c r="U33" s="10" t="s">
-        <v>49</v>
+      <c r="U33" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63452219908</v>
@@ -3436,16 +3479,16 @@
         <v>46188.67407226852</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46213</v>
@@ -3463,88 +3506,88 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
-      <c r="S34" s="12" t="s">
-        <v>97</v>
+      <c r="S34" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="10" t="s">
-        <v>49</v>
+      <c r="U34" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="9">
+        <v>46188.634528194445</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="9">
+        <v>46188.6740696412</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I35" s="9">
+        <v>46217</v>
+      </c>
+      <c r="J35" s="9">
+        <v>46225</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="O35" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="B35" s="8">
-        <v>46188.634528194445</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="8">
-        <v>46188.6740696412</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="I35" s="8">
-        <v>46217</v>
-      </c>
-      <c r="J35" s="8">
-        <v>46225</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T35" s="9">
+      <c r="P35" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T35" s="10">
         <v>0</v>
       </c>
-      <c r="U35" s="10" t="s">
-        <v>49</v>
+      <c r="U35" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63453408565</v>
@@ -3554,16 +3597,16 @@
         <v>46188.67423875</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3581,10 +3624,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3595,72 +3638,72 @@
       <c r="R36" s="5">
         <v>46225</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>97</v>
+      <c r="S36" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="10" t="s">
-        <v>49</v>
+      <c r="U36" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" s="9">
+        <v>46188.634538252314</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="9">
+        <v>46188.674186689816</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I37" s="9">
+        <v>46213</v>
+      </c>
+      <c r="J37" s="9">
+        <v>46216</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B37" s="8">
-        <v>46188.634538252314</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="8">
-        <v>46188.674186689816</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="I37" s="8">
-        <v>46213</v>
-      </c>
-      <c r="J37" s="8">
-        <v>46216</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="P37" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-      <c r="U37" s="9"/>
+      <c r="O37" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="P37" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63454329861</v>
@@ -3670,16 +3713,16 @@
         <v>46188.674183877316</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46217</v>
@@ -3697,13 +3740,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3712,71 +3755,71 @@
       <c r="U38" s="6"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B39" s="8">
+      <c r="A39" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B39" s="9">
         <v>46188.63454804398</v>
       </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="8">
+      <c r="C39" s="10"/>
+      <c r="D39" s="9">
         <v>46188.674703854165</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H39" s="9" t="s">
+      <c r="E39" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="I39" s="8">
+      <c r="F39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="I39" s="9">
         <v>46213</v>
       </c>
-      <c r="J39" s="8">
+      <c r="J39" s="9">
         <v>46253</v>
       </c>
-      <c r="K39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q39" s="8">
+      <c r="K39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="O39" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="P39" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q39" s="9">
         <v>46213</v>
       </c>
-      <c r="R39" s="8">
+      <c r="R39" s="9">
         <v>46253</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T39" s="9">
+      <c r="S39" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T39" s="10">
         <v>0</v>
       </c>
-      <c r="U39" s="10" t="s">
-        <v>49</v>
+      <c r="U39" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63455278936</v>
@@ -3786,16 +3829,16 @@
         <v>46188.67435018519</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3813,13 +3856,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3828,61 +3871,61 @@
       <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B41" s="8">
+      <c r="A41" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B41" s="9">
         <v>46188.63455811342</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="8">
+      <c r="C41" s="10"/>
+      <c r="D41" s="9">
         <v>46188.67434657407</v>
       </c>
-      <c r="E41" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H41" s="9" t="s">
+      <c r="E41" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="I41" s="9">
+        <v>46224</v>
+      </c>
+      <c r="J41" s="9">
+        <v>46252</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="I41" s="8">
-        <v>46224</v>
-      </c>
-      <c r="J41" s="8">
-        <v>46252</v>
-      </c>
-      <c r="K41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="O41" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="P41" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q41" s="9"/>
-      <c r="R41" s="9"/>
-      <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-      <c r="U41" s="9"/>
+      <c r="O41" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="P41" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63456381945</v>
@@ -3892,16 +3935,16 @@
         <v>46188.674648472224</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46253</v>
@@ -3919,10 +3962,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3934,71 +3977,71 @@
       <c r="U42" s="6"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B43" s="8">
+      <c r="A43" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B43" s="9">
         <v>46188.63456738426</v>
       </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="8">
+      <c r="C43" s="10"/>
+      <c r="D43" s="9">
         <v>46188.67687303241</v>
       </c>
-      <c r="E43" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="I43" s="8">
+      <c r="E43" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I43" s="9">
         <v>46213</v>
       </c>
-      <c r="J43" s="8">
+      <c r="J43" s="9">
         <v>46225</v>
       </c>
-      <c r="K43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="P43" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q43" s="8">
+      <c r="K43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="O43" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="P43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q43" s="9">
         <v>46213</v>
       </c>
-      <c r="R43" s="8">
+      <c r="R43" s="9">
         <v>46225</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T43" s="9">
+      <c r="S43" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T43" s="10">
         <v>0</v>
       </c>
-      <c r="U43" s="10" t="s">
-        <v>49</v>
+      <c r="U43" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46188.63457166667</v>
@@ -4008,16 +4051,16 @@
         <v>46188.67683644676</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46213</v>
@@ -4035,13 +4078,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4050,61 +4093,61 @@
       <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="B45" s="8">
+      <c r="A45" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" s="9">
         <v>46188.634576701385</v>
       </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="8">
+      <c r="C45" s="10"/>
+      <c r="D45" s="9">
         <v>46188.67683361111</v>
       </c>
-      <c r="E45" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="I45" s="8">
+      <c r="E45" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I45" s="9">
         <v>46217</v>
       </c>
-      <c r="J45" s="8">
+      <c r="J45" s="9">
         <v>46225</v>
       </c>
-      <c r="K45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="P45" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q45" s="9"/>
-      <c r="R45" s="9"/>
-      <c r="S45" s="9"/>
-      <c r="T45" s="9"/>
-      <c r="U45" s="9"/>
+      <c r="K45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="O45" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="P45" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63417921297</v>
@@ -4114,7 +4157,7 @@
         <v>46188.676957083335</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4138,7 +4181,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4150,71 +4193,71 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B47" s="9">
+        <v>46188.63458247685</v>
+      </c>
+      <c r="C47" s="10"/>
+      <c r="D47" s="9">
+        <v>46188.9205047338</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="I47" s="9">
+        <v>46188</v>
+      </c>
+      <c r="J47" s="9">
+        <v>46192</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="B47" s="8">
-        <v>46188.63458247685</v>
-      </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="8">
-        <v>46188.67693771991</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="I47" s="8">
+      <c r="O47" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="P47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q47" s="9">
         <v>46188</v>
       </c>
-      <c r="J47" s="8">
+      <c r="R47" s="9">
         <v>46192</v>
       </c>
-      <c r="K47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="O47" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="P47" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q47" s="8">
-        <v>46188</v>
-      </c>
-      <c r="R47" s="8">
-        <v>46192</v>
-      </c>
-      <c r="S47" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T47" s="9">
+      <c r="S47" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T47" s="10">
         <v>0</v>
       </c>
-      <c r="U47" s="10" t="s">
-        <v>49</v>
+      <c r="U47" s="12" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46188.634588587964</v>
@@ -4224,16 +4267,16 @@
         <v>46188.6769350463</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46203</v>
@@ -4251,13 +4294,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46203</v>
@@ -4265,82 +4308,82 @@
       <c r="R48" s="5">
         <v>46209</v>
       </c>
-      <c r="S48" s="12" t="s">
-        <v>97</v>
+      <c r="S48" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="10" t="s">
-        <v>49</v>
+      <c r="U48" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B49" s="8">
+      <c r="A49" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B49" s="9">
         <v>46188.63459497685</v>
       </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="8">
+      <c r="C49" s="10"/>
+      <c r="D49" s="9">
         <v>46188.67693108796</v>
       </c>
-      <c r="E49" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="I49" s="8">
+      <c r="E49" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="I49" s="9">
         <v>46210</v>
       </c>
-      <c r="J49" s="8">
+      <c r="J49" s="9">
         <v>46210</v>
       </c>
-      <c r="K49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="O49" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="P49" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q49" s="8">
+      <c r="K49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="O49" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q49" s="9">
         <v>46210</v>
       </c>
-      <c r="R49" s="8">
+      <c r="R49" s="9">
         <v>46210</v>
       </c>
-      <c r="S49" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T49" s="9">
+      <c r="S49" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T49" s="10">
         <v>0</v>
       </c>
-      <c r="U49" s="10" t="s">
-        <v>49</v>
+      <c r="U49" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63460983796</v>
@@ -4350,16 +4393,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I50" s="5">
         <v>46259</v>
@@ -4377,10 +4420,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4391,72 +4434,72 @@
       <c r="R50" s="5">
         <v>46259</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>97</v>
+      <c r="S50" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="10" t="s">
-        <v>49</v>
+      <c r="U50" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" s="9">
+        <v>46188.634613946764</v>
+      </c>
+      <c r="C51" s="10"/>
+      <c r="D51" s="9">
+        <v>46188.677066122684</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B51" s="8">
-        <v>46188.634613946764</v>
-      </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="8">
-        <v>46188.677066122684</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="H51" s="9" t="s">
+      <c r="I51" s="9">
+        <v>46259</v>
+      </c>
+      <c r="J51" s="9">
+        <v>46259</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="I51" s="8">
-        <v>46259</v>
-      </c>
-      <c r="J51" s="8">
-        <v>46259</v>
-      </c>
-      <c r="K51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q51" s="9"/>
-      <c r="R51" s="9"/>
-      <c r="S51" s="9"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
+      <c r="O51" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="P51" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46188.63461840278</v>
@@ -4466,16 +4509,16 @@
         <v>46188.67706284722</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46259</v>
@@ -4493,13 +4536,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4508,55 +4551,55 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B53" s="8">
+      <c r="A53" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B53" s="9">
         <v>46188.63467295139</v>
       </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="8">
+      <c r="C53" s="10"/>
+      <c r="D53" s="9">
         <v>46188.660341678245</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="F53" s="9" t="s">
+      <c r="E53" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="F53" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="9"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" s="9" t="s">
+      <c r="G53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="P53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q53" s="9"/>
-      <c r="R53" s="9"/>
-      <c r="S53" s="9"/>
-      <c r="T53" s="9"/>
-      <c r="U53" s="9"/>
+      <c r="N53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O53" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63467763889</v>
@@ -4566,16 +4609,16 @@
         <v>46188.67723120371</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4593,13 +4636,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4607,82 +4650,82 @@
       <c r="R54" s="5">
         <v>46227</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>97</v>
+      <c r="S54" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
-      <c r="U54" s="10" t="s">
-        <v>49</v>
+      <c r="U54" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="B55" s="8">
+      <c r="A55" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B55" s="9">
         <v>46188.634684942124</v>
       </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="8">
+      <c r="C55" s="10"/>
+      <c r="D55" s="9">
         <v>46188.67731989583</v>
       </c>
-      <c r="E55" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="I55" s="8">
+      <c r="E55" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="I55" s="9">
         <v>46230</v>
       </c>
-      <c r="J55" s="8">
+      <c r="J55" s="9">
         <v>46231</v>
       </c>
-      <c r="K55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q55" s="8">
+      <c r="K55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="O55" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="P55" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q55" s="9">
         <v>46230</v>
       </c>
-      <c r="R55" s="8">
+      <c r="R55" s="9">
         <v>46231</v>
       </c>
-      <c r="S55" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T55" s="9">
+      <c r="S55" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T55" s="10">
         <v>0</v>
       </c>
-      <c r="U55" s="10" t="s">
-        <v>49</v>
+      <c r="U55" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46188.634692962965</v>
@@ -4692,16 +4735,16 @@
         <v>46188.67722799769</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I56" s="5">
         <v>46226</v>
@@ -4719,13 +4762,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q56" s="5">
         <v>46226</v>
@@ -4733,82 +4776,82 @@
       <c r="R56" s="5">
         <v>46227</v>
       </c>
-      <c r="S56" s="12" t="s">
-        <v>97</v>
+      <c r="S56" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
       </c>
-      <c r="U56" s="10" t="s">
-        <v>49</v>
+      <c r="U56" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B57" s="9">
+        <v>46188.63469954861</v>
+      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="9">
+        <v>46188.67731701389</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="I57" s="9">
+        <v>46230</v>
+      </c>
+      <c r="J57" s="9">
+        <v>46231</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="O57" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="B57" s="8">
-        <v>46188.63469954861</v>
-      </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="8">
-        <v>46188.67731701389</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="I57" s="8">
+      <c r="P57" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q57" s="9">
         <v>46230</v>
       </c>
-      <c r="J57" s="8">
+      <c r="R57" s="9">
         <v>46231</v>
       </c>
-      <c r="K57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q57" s="8">
-        <v>46230</v>
-      </c>
-      <c r="R57" s="8">
-        <v>46231</v>
-      </c>
-      <c r="S57" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T57" s="9">
+      <c r="S57" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T57" s="10">
         <v>0</v>
       </c>
-      <c r="U57" s="10" t="s">
-        <v>49</v>
+      <c r="U57" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63470560186</v>
@@ -4818,16 +4861,16 @@
         <v>46188.677224942134</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I58" s="5">
         <v>46226</v>
@@ -4845,13 +4888,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q58" s="5">
         <v>46226</v>
@@ -4859,82 +4902,82 @@
       <c r="R58" s="5">
         <v>46227</v>
       </c>
-      <c r="S58" s="12" t="s">
-        <v>97</v>
+      <c r="S58" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T58" s="6">
         <v>0</v>
       </c>
-      <c r="U58" s="10" t="s">
-        <v>49</v>
+      <c r="U58" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B59" s="9">
+        <v>46188.63471155093</v>
+      </c>
+      <c r="C59" s="10"/>
+      <c r="D59" s="9">
+        <v>46188.67731351852</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="I59" s="9">
+        <v>46230</v>
+      </c>
+      <c r="J59" s="9">
+        <v>46231</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="O59" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B59" s="8">
-        <v>46188.63471155093</v>
-      </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="8">
-        <v>46188.67731351852</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="I59" s="8">
+      <c r="P59" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q59" s="9">
         <v>46230</v>
       </c>
-      <c r="J59" s="8">
+      <c r="R59" s="9">
         <v>46231</v>
       </c>
-      <c r="K59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="O59" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q59" s="8">
-        <v>46230</v>
-      </c>
-      <c r="R59" s="8">
-        <v>46231</v>
-      </c>
-      <c r="S59" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T59" s="9">
+      <c r="S59" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T59" s="10">
         <v>0</v>
       </c>
-      <c r="U59" s="10" t="s">
-        <v>49</v>
+      <c r="U59" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63471731481</v>
@@ -4944,7 +4987,7 @@
         <v>46188.662660393515</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -4968,7 +5011,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -4980,71 +5023,71 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B61" s="9">
+        <v>46188.63472107639</v>
+      </c>
+      <c r="C61" s="10"/>
+      <c r="D61" s="9">
+        <v>46188.677743113425</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I61" s="9">
+        <v>46232</v>
+      </c>
+      <c r="J61" s="9">
+        <v>46234</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="B61" s="8">
-        <v>46188.63472107639</v>
-      </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="8">
-        <v>46188.677743113425</v>
-      </c>
-      <c r="E61" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I61" s="8">
+      <c r="O61" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P61" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q61" s="9">
         <v>46232</v>
       </c>
-      <c r="J61" s="8">
+      <c r="R61" s="9">
         <v>46234</v>
       </c>
-      <c r="K61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="P61" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q61" s="8">
-        <v>46232</v>
-      </c>
-      <c r="R61" s="8">
-        <v>46234</v>
-      </c>
-      <c r="S61" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T61" s="9">
+      <c r="S61" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T61" s="10">
         <v>0</v>
       </c>
-      <c r="U61" s="10" t="s">
-        <v>49</v>
+      <c r="U61" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63473258102</v>
@@ -5054,16 +5097,16 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I62" s="5">
         <v>46232</v>
@@ -5081,13 +5124,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5096,61 +5139,61 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B63" s="8">
+      <c r="A63" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B63" s="9">
         <v>46188.63474121528</v>
       </c>
-      <c r="C63" s="9"/>
-      <c r="D63" s="8">
+      <c r="C63" s="10"/>
+      <c r="D63" s="9">
         <v>46188.677461087966</v>
       </c>
-      <c r="E63" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H63" s="9" t="s">
+      <c r="E63" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I63" s="9">
+        <v>46232</v>
+      </c>
+      <c r="J63" s="9">
+        <v>46234</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="I63" s="8">
-        <v>46232</v>
-      </c>
-      <c r="J63" s="8">
-        <v>46234</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="O63" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="P63" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q63" s="9"/>
-      <c r="R63" s="9"/>
-      <c r="S63" s="9"/>
-      <c r="T63" s="9"/>
-      <c r="U63" s="9"/>
+      <c r="O63" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="P63" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
+      <c r="S63" s="10"/>
+      <c r="T63" s="10"/>
+      <c r="U63" s="10"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B64" s="5">
         <v>46188.63477284722</v>
@@ -5160,16 +5203,16 @@
         <v>46188.67773935186</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I64" s="5">
         <v>46237</v>
@@ -5187,13 +5230,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q64" s="5">
         <v>46237</v>
@@ -5201,72 +5244,72 @@
       <c r="R64" s="5">
         <v>46241</v>
       </c>
-      <c r="S64" s="12" t="s">
-        <v>97</v>
+      <c r="S64" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="10" t="s">
-        <v>49</v>
+      <c r="U64" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="B65" s="8">
+      <c r="A65" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B65" s="9">
         <v>46188.63477877315</v>
       </c>
-      <c r="C65" s="9"/>
-      <c r="D65" s="8">
+      <c r="C65" s="10"/>
+      <c r="D65" s="9">
         <v>46188.677545659724</v>
       </c>
-      <c r="E65" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I65" s="8">
+      <c r="E65" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I65" s="9">
         <v>46237</v>
       </c>
-      <c r="J65" s="8">
+      <c r="J65" s="9">
         <v>46241</v>
       </c>
-      <c r="K65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="O65" s="9" t="s">
+      <c r="K65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="P65" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q65" s="9"/>
-      <c r="R65" s="9"/>
-      <c r="S65" s="9"/>
-      <c r="T65" s="9"/>
-      <c r="U65" s="9"/>
+      <c r="O65" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="P65" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63478605324</v>
@@ -5276,16 +5319,16 @@
         <v>46188.67754284722</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I66" s="5">
         <v>46237</v>
@@ -5303,13 +5346,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5318,71 +5361,71 @@
       <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B67" s="8">
+      <c r="A67" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B67" s="9">
         <v>46188.63485537037</v>
       </c>
-      <c r="C67" s="9"/>
-      <c r="D67" s="8">
+      <c r="C67" s="10"/>
+      <c r="D67" s="9">
         <v>46188.67780341435</v>
       </c>
-      <c r="E67" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="I67" s="8">
+      <c r="E67" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="F67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="I67" s="9">
         <v>46244</v>
       </c>
-      <c r="J67" s="8">
+      <c r="J67" s="9">
         <v>46244</v>
       </c>
-      <c r="K67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="O67" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q67" s="8">
+      <c r="K67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="O67" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P67" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q67" s="9">
         <v>46244</v>
       </c>
-      <c r="R67" s="8">
+      <c r="R67" s="9">
         <v>46244</v>
       </c>
-      <c r="S67" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T67" s="9">
+      <c r="S67" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T67" s="10">
         <v>0</v>
       </c>
-      <c r="U67" s="10" t="s">
-        <v>49</v>
+      <c r="U67" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B68" s="5">
         <v>46188.634861805556</v>
@@ -5392,16 +5435,16 @@
         <v>46188.677654756946</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I68" s="5">
         <v>46244</v>
@@ -5419,13 +5462,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5434,61 +5477,61 @@
       <c r="U68" s="6"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B69" s="8">
+      <c r="A69" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B69" s="9">
         <v>46188.63486881944</v>
       </c>
-      <c r="C69" s="9"/>
-      <c r="D69" s="8">
+      <c r="C69" s="10"/>
+      <c r="D69" s="9">
         <v>46188.67765203703</v>
       </c>
-      <c r="E69" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="I69" s="8">
+      <c r="E69" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="I69" s="9">
         <v>46244</v>
       </c>
-      <c r="J69" s="8">
+      <c r="J69" s="9">
         <v>46244</v>
       </c>
-      <c r="K69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="O69" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="P69" s="9" t="s">
+      <c r="K69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="Q69" s="9"/>
-      <c r="R69" s="9"/>
-      <c r="S69" s="9"/>
-      <c r="T69" s="9"/>
-      <c r="U69" s="9"/>
+      <c r="O69" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="P69" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
+      <c r="S69" s="10"/>
+      <c r="T69" s="10"/>
+      <c r="U69" s="10"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B70" s="5">
         <v>46188.63489331018</v>
@@ -5498,7 +5541,7 @@
         <v>46188.664478900464</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5522,7 +5565,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5534,90 +5577,90 @@
       <c r="U70" s="6"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B71" s="8">
+      <c r="A71" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="B71" s="9">
         <v>46188.634903391205</v>
       </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="8">
+      <c r="C71" s="10"/>
+      <c r="D71" s="9">
         <v>46188.677911018516</v>
       </c>
-      <c r="E71" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="I71" s="8">
+      <c r="E71" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="I71" s="9">
         <v>46205</v>
       </c>
-      <c r="J71" s="8">
+      <c r="J71" s="9">
         <v>46205</v>
       </c>
-      <c r="K71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="O71" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q71" s="8">
+      <c r="K71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="O71" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="P71" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q71" s="9">
         <v>46205</v>
       </c>
-      <c r="R71" s="8">
+      <c r="R71" s="9">
         <v>46205</v>
       </c>
-      <c r="S71" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T71" s="9">
+      <c r="S71" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T71" s="10">
         <v>0</v>
       </c>
-      <c r="U71" s="10" t="s">
-        <v>49</v>
+      <c r="U71" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46188.6349100463</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.67790753472</v>
+        <v>46189.174127997685</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I72" s="5">
         <v>46189</v>
@@ -5635,13 +5678,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q72" s="5">
         <v>46189</v>
@@ -5649,82 +5692,82 @@
       <c r="R72" s="5">
         <v>46189</v>
       </c>
-      <c r="S72" s="11" t="s">
-        <v>241</v>
+      <c r="S72" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="10" t="s">
-        <v>49</v>
+      <c r="U72" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B73" s="8">
+      <c r="A73" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B73" s="9">
         <v>46188.6349165162</v>
       </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="8">
+      <c r="C73" s="10"/>
+      <c r="D73" s="9">
         <v>46188.677904247685</v>
       </c>
-      <c r="E73" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="I73" s="8">
+      <c r="E73" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="I73" s="9">
         <v>46223</v>
       </c>
-      <c r="J73" s="8">
+      <c r="J73" s="9">
         <v>46223</v>
       </c>
-      <c r="K73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q73" s="8">
+      <c r="K73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="O73" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q73" s="9">
         <v>46223</v>
       </c>
-      <c r="R73" s="8">
+      <c r="R73" s="9">
         <v>46223</v>
       </c>
-      <c r="S73" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T73" s="9">
+      <c r="S73" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T73" s="10">
         <v>0</v>
       </c>
-      <c r="U73" s="10" t="s">
-        <v>49</v>
+      <c r="U73" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46188.634922916666</v>
@@ -5734,16 +5777,16 @@
         <v>46188.67789931713</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I74" s="5">
         <v>46254</v>
@@ -5761,13 +5804,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q74" s="5">
         <v>46254</v>
@@ -5775,66 +5818,66 @@
       <c r="R74" s="5">
         <v>46254</v>
       </c>
-      <c r="S74" s="12" t="s">
-        <v>97</v>
+      <c r="S74" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="U74" s="10" t="s">
-        <v>49</v>
+      <c r="U74" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B75" s="8">
+      <c r="A75" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B75" s="9">
         <v>46188.63492795139</v>
       </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="8">
+      <c r="C75" s="10"/>
+      <c r="D75" s="9">
         <v>46188.66851157407</v>
       </c>
-      <c r="E75" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="F75" s="9" t="s">
+      <c r="E75" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="F75" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9"/>
-      <c r="K75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" s="9" t="s">
+      <c r="G75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H75" s="10"/>
+      <c r="I75" s="10"/>
+      <c r="J75" s="10"/>
+      <c r="K75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O75" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="P75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q75" s="9"/>
-      <c r="R75" s="9"/>
-      <c r="S75" s="9"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
+      <c r="N75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O75" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
+      <c r="S75" s="10"/>
+      <c r="T75" s="10"/>
+      <c r="U75" s="10"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B76" s="5">
         <v>46188.63493152778</v>
@@ -5844,7 +5887,7 @@
         <v>46188.67802387731</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5871,13 +5914,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q76" s="5">
         <v>46245</v>
@@ -5885,72 +5928,72 @@
       <c r="R76" s="5">
         <v>46251</v>
       </c>
-      <c r="S76" s="12" t="s">
-        <v>97</v>
+      <c r="S76" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
       </c>
-      <c r="U76" s="10" t="s">
-        <v>49</v>
+      <c r="U76" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B77" s="9">
+        <v>46188.63494034723</v>
+      </c>
+      <c r="C77" s="10"/>
+      <c r="D77" s="9">
+        <v>46188.677983657406</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I77" s="9">
+        <v>46245</v>
+      </c>
+      <c r="J77" s="9">
+        <v>46251</v>
+      </c>
+      <c r="K77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="B77" s="8">
-        <v>46188.63494034723</v>
-      </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="8">
-        <v>46188.677983657406</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I77" s="8">
-        <v>46245</v>
-      </c>
-      <c r="J77" s="8">
-        <v>46251</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="P77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q77" s="9"/>
-      <c r="R77" s="9"/>
-      <c r="S77" s="9"/>
-      <c r="T77" s="9"/>
-      <c r="U77" s="9"/>
+      <c r="O77" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="P77" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
+      <c r="S77" s="10"/>
+      <c r="T77" s="10"/>
+      <c r="U77" s="10"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B78" s="5">
         <v>46188.634945150465</v>
@@ -5960,7 +6003,7 @@
         <v>46188.677980567125</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5987,10 +6030,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6002,71 +6045,71 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="B79" s="8">
+      <c r="A79" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B79" s="9">
         <v>46188.634963668985</v>
       </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="8">
+      <c r="C79" s="10"/>
+      <c r="D79" s="9">
         <v>46188.67832872685</v>
       </c>
-      <c r="E79" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="9" t="s">
+      <c r="E79" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H79" s="9" t="s">
+      <c r="H79" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I79" s="8">
+      <c r="I79" s="9">
         <v>46252</v>
       </c>
-      <c r="J79" s="8">
+      <c r="J79" s="9">
         <v>46252</v>
       </c>
-      <c r="K79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N79" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q79" s="8">
+      <c r="K79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="O79" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P79" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q79" s="9">
         <v>46252</v>
       </c>
-      <c r="R79" s="8">
+      <c r="R79" s="9">
         <v>46252</v>
       </c>
-      <c r="S79" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T79" s="9">
+      <c r="S79" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T79" s="10">
         <v>0</v>
       </c>
-      <c r="U79" s="10" t="s">
-        <v>49</v>
+      <c r="U79" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B80" s="5">
         <v>46188.63496887732</v>
@@ -6076,7 +6119,7 @@
         <v>46188.678293923615</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6103,13 +6146,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6118,61 +6161,61 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
+      <c r="A81" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B81" s="9">
+        <v>46188.63498112268</v>
+      </c>
+      <c r="C81" s="10"/>
+      <c r="D81" s="9">
+        <v>46188.678290868054</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I81" s="9">
+        <v>46252</v>
+      </c>
+      <c r="J81" s="9">
+        <v>46252</v>
+      </c>
+      <c r="K81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N81" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="O81" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B81" s="8">
-        <v>46188.63498112268</v>
-      </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="8">
-        <v>46188.678290868054</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I81" s="8">
-        <v>46252</v>
-      </c>
-      <c r="J81" s="8">
-        <v>46252</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q81" s="9"/>
-      <c r="R81" s="9"/>
-      <c r="S81" s="9"/>
-      <c r="T81" s="9"/>
-      <c r="U81" s="9"/>
+      <c r="P81" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
+      <c r="S81" s="10"/>
+      <c r="T81" s="10"/>
+      <c r="U81" s="10"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B82" s="5">
         <v>46188.635046296295</v>
@@ -6182,7 +6225,7 @@
         <v>46188.67895050926</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6209,13 +6252,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q82" s="5">
         <v>46253</v>
@@ -6223,72 +6266,72 @@
       <c r="R82" s="5">
         <v>46253</v>
       </c>
-      <c r="S82" s="12" t="s">
-        <v>97</v>
+      <c r="S82" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
-      <c r="U82" s="10" t="s">
-        <v>49</v>
+      <c r="U82" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="B83" s="8">
+      <c r="A83" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B83" s="9">
         <v>46188.63505403935</v>
       </c>
-      <c r="C83" s="9"/>
-      <c r="D83" s="8">
+      <c r="C83" s="10"/>
+      <c r="D83" s="9">
         <v>46188.67891099537</v>
       </c>
-      <c r="E83" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="9" t="s">
+      <c r="E83" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H83" s="9" t="s">
+      <c r="H83" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I83" s="8">
+      <c r="I83" s="9">
         <v>46253</v>
       </c>
-      <c r="J83" s="8">
+      <c r="J83" s="9">
         <v>46253</v>
       </c>
-      <c r="K83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="O83" s="9" t="s">
+      <c r="K83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="P83" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q83" s="9"/>
-      <c r="R83" s="9"/>
-      <c r="S83" s="9"/>
-      <c r="T83" s="9"/>
-      <c r="U83" s="9"/>
+      <c r="O83" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="P83" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
+      <c r="S83" s="10"/>
+      <c r="T83" s="10"/>
+      <c r="U83" s="10"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B84" s="5">
         <v>46188.63506813657</v>
@@ -6298,7 +6341,7 @@
         <v>46188.678908194444</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6325,13 +6368,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6340,71 +6383,71 @@
       <c r="U84" s="6"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="B85" s="8">
+      <c r="A85" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B85" s="9">
         <v>46188.63509704861</v>
       </c>
-      <c r="C85" s="9"/>
-      <c r="D85" s="8">
+      <c r="C85" s="10"/>
+      <c r="D85" s="9">
         <v>46188.67906003472</v>
       </c>
-      <c r="E85" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="9" t="s">
+      <c r="E85" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H85" s="9" t="s">
+      <c r="H85" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I85" s="8">
+      <c r="I85" s="9">
         <v>46224</v>
       </c>
-      <c r="J85" s="8">
+      <c r="J85" s="9">
         <v>46224</v>
       </c>
-      <c r="K85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="O85" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="P85" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q85" s="8">
+      <c r="K85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="O85" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P85" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q85" s="9">
         <v>46224</v>
       </c>
-      <c r="R85" s="8">
+      <c r="R85" s="9">
         <v>46224</v>
       </c>
-      <c r="S85" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T85" s="9">
+      <c r="S85" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T85" s="10">
         <v>0</v>
       </c>
-      <c r="U85" s="10" t="s">
-        <v>49</v>
+      <c r="U85" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B86" s="5">
         <v>46188.635102939814</v>
@@ -6414,7 +6457,7 @@
         <v>46188.67902152777</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6441,13 +6484,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6456,61 +6499,61 @@
       <c r="U86" s="6"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
+      <c r="A87" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="B87" s="9">
+        <v>46188.63510991898</v>
+      </c>
+      <c r="C87" s="10"/>
+      <c r="D87" s="9">
+        <v>46188.67901871528</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I87" s="9">
+        <v>46224</v>
+      </c>
+      <c r="J87" s="9">
+        <v>46224</v>
+      </c>
+      <c r="K87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="O87" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="B87" s="8">
-        <v>46188.63510991898</v>
-      </c>
-      <c r="C87" s="9"/>
-      <c r="D87" s="8">
-        <v>46188.67901871528</v>
-      </c>
-      <c r="E87" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I87" s="8">
-        <v>46224</v>
-      </c>
-      <c r="J87" s="8">
-        <v>46224</v>
-      </c>
-      <c r="K87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="O87" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="P87" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q87" s="9"/>
-      <c r="R87" s="9"/>
-      <c r="S87" s="9"/>
-      <c r="T87" s="9"/>
-      <c r="U87" s="9"/>
+      <c r="P87" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="10"/>
+      <c r="S87" s="10"/>
+      <c r="T87" s="10"/>
+      <c r="U87" s="10"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B88" s="5">
         <v>46188.63513603009</v>
@@ -6520,7 +6563,7 @@
         <v>46188.6792096875</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6547,13 +6590,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q88" s="5">
         <v>46258</v>
@@ -6561,70 +6604,70 @@
       <c r="R88" s="5">
         <v>46258</v>
       </c>
-      <c r="S88" s="12" t="s">
-        <v>97</v>
+      <c r="S88" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="U88" s="10" t="s">
-        <v>49</v>
+      <c r="U88" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="B89" s="9">
+        <v>46188.63514172454</v>
+      </c>
+      <c r="C89" s="10"/>
+      <c r="D89" s="9">
+        <v>46188.679159583335</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I89" s="10"/>
+      <c r="J89" s="9">
+        <v>46258</v>
+      </c>
+      <c r="K89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B89" s="8">
-        <v>46188.63514172454</v>
-      </c>
-      <c r="C89" s="9"/>
-      <c r="D89" s="8">
-        <v>46188.679159583335</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I89" s="9"/>
-      <c r="J89" s="8">
-        <v>46258</v>
-      </c>
-      <c r="K89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="P89" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q89" s="9"/>
-      <c r="R89" s="9"/>
-      <c r="S89" s="9"/>
-      <c r="T89" s="9"/>
-      <c r="U89" s="9"/>
+      <c r="O89" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P89" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10"/>
+      <c r="S89" s="10"/>
+      <c r="T89" s="10"/>
+      <c r="U89" s="10"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B90" s="5">
         <v>46188.63514853009</v>
@@ -6634,7 +6677,7 @@
         <v>46188.6791566551</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6659,13 +6702,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6674,71 +6717,71 @@
       <c r="U90" s="6"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="B91" s="8">
+      <c r="A91" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B91" s="9">
         <v>46188.63521115741</v>
       </c>
-      <c r="C91" s="9"/>
-      <c r="D91" s="8">
+      <c r="C91" s="10"/>
+      <c r="D91" s="9">
         <v>46188.68062993056</v>
       </c>
-      <c r="E91" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="9" t="s">
+      <c r="E91" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H91" s="9" t="s">
+      <c r="H91" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I91" s="8">
+      <c r="I91" s="9">
         <v>46260</v>
       </c>
-      <c r="J91" s="8">
+      <c r="J91" s="9">
         <v>46260</v>
       </c>
-      <c r="K91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N91" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="O91" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="P91" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q91" s="8">
+      <c r="K91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="O91" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P91" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q91" s="9">
         <v>46260</v>
       </c>
-      <c r="R91" s="8">
+      <c r="R91" s="9">
         <v>46260</v>
       </c>
-      <c r="S91" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T91" s="9">
+      <c r="S91" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T91" s="10">
         <v>0</v>
       </c>
-      <c r="U91" s="10" t="s">
-        <v>49</v>
+      <c r="U91" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B92" s="5">
         <v>46188.63521795139</v>
@@ -6748,7 +6791,7 @@
         <v>46188.68070547454</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6775,13 +6818,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6790,61 +6833,61 @@
       <c r="U92" s="6"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="B93" s="8">
+      <c r="A93" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B93" s="9">
         <v>46188.635222916666</v>
       </c>
-      <c r="C93" s="9"/>
-      <c r="D93" s="8">
+      <c r="C93" s="10"/>
+      <c r="D93" s="9">
         <v>46188.680702488426</v>
       </c>
-      <c r="E93" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" s="9" t="s">
+      <c r="E93" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H93" s="9" t="s">
+      <c r="H93" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I93" s="8">
+      <c r="I93" s="9">
         <v>46260</v>
       </c>
-      <c r="J93" s="8">
+      <c r="J93" s="9">
         <v>46260</v>
       </c>
-      <c r="K93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N93" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="O93" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q93" s="9"/>
-      <c r="R93" s="9"/>
-      <c r="S93" s="9"/>
-      <c r="T93" s="9"/>
-      <c r="U93" s="9"/>
+      <c r="K93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M93" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N93" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="O93" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P93" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="10"/>
+      <c r="T93" s="10"/>
+      <c r="U93" s="10"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B94" s="5">
         <v>46188.635247199076</v>
@@ -6854,7 +6897,7 @@
         <v>46188.67010366898</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>25</v>
@@ -6878,7 +6921,7 @@
         <v>26</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>26</v>
@@ -6890,71 +6933,71 @@
       <c r="U94" s="6"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
+      <c r="A95" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B95" s="9">
+        <v>46188.635250844905</v>
+      </c>
+      <c r="C95" s="10"/>
+      <c r="D95" s="9">
+        <v>46188.68085204861</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="I95" s="9">
+        <v>46261</v>
+      </c>
+      <c r="J95" s="9">
+        <v>46261</v>
+      </c>
+      <c r="K95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M95" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N95" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B95" s="8">
-        <v>46188.635250844905</v>
-      </c>
-      <c r="C95" s="9"/>
-      <c r="D95" s="8">
-        <v>46188.68085204861</v>
-      </c>
-      <c r="E95" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="I95" s="8">
+      <c r="O95" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="P95" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q95" s="9">
         <v>46261</v>
       </c>
-      <c r="J95" s="8">
+      <c r="R95" s="9">
         <v>46261</v>
       </c>
-      <c r="K95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N95" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q95" s="8">
-        <v>46261</v>
-      </c>
-      <c r="R95" s="8">
-        <v>46261</v>
-      </c>
-      <c r="S95" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T95" s="9">
+      <c r="S95" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T95" s="10">
         <v>0</v>
       </c>
-      <c r="U95" s="10" t="s">
-        <v>49</v>
+      <c r="U95" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B96" s="5">
         <v>46188.63525673611</v>
@@ -6964,16 +7007,16 @@
         <v>46188.68080148148</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I96" s="5">
         <v>46261</v>
@@ -6991,13 +7034,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7006,61 +7049,61 @@
       <c r="U96" s="6"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B97" s="8">
+      <c r="A97" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B97" s="9">
         <v>46188.635261689815</v>
       </c>
-      <c r="C97" s="9"/>
-      <c r="D97" s="8">
+      <c r="C97" s="10"/>
+      <c r="D97" s="9">
         <v>46188.680797928246</v>
       </c>
-      <c r="E97" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="H97" s="9" t="s">
+      <c r="E97" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="I97" s="9">
+        <v>46261</v>
+      </c>
+      <c r="J97" s="9">
+        <v>46261</v>
+      </c>
+      <c r="K97" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L97" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="I97" s="8">
-        <v>46261</v>
-      </c>
-      <c r="J97" s="8">
-        <v>46261</v>
-      </c>
-      <c r="K97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N97" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="O97" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q97" s="9"/>
-      <c r="R97" s="9"/>
-      <c r="S97" s="9"/>
-      <c r="T97" s="9"/>
-      <c r="U97" s="9"/>
+      <c r="O97" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P97" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q97" s="10"/>
+      <c r="R97" s="10"/>
+      <c r="S97" s="10"/>
+      <c r="T97" s="10"/>
+      <c r="U97" s="10"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B98" s="5">
         <v>46188.635279375</v>
@@ -7070,7 +7113,7 @@
         <v>46188.68118097223</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7097,13 +7140,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q98" s="5">
         <v>46262</v>
@@ -7111,70 +7154,70 @@
       <c r="R98" s="5">
         <v>46262</v>
       </c>
-      <c r="S98" s="12" t="s">
-        <v>97</v>
+      <c r="S98" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
-      <c r="U98" s="10" t="s">
-        <v>49</v>
+      <c r="U98" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B99" s="8">
+      <c r="A99" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B99" s="9">
         <v>46188.63528446759</v>
       </c>
-      <c r="C99" s="9"/>
-      <c r="D99" s="8">
+      <c r="C99" s="10"/>
+      <c r="D99" s="9">
         <v>46188.68112704861</v>
       </c>
-      <c r="E99" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G99" s="9" t="s">
+      <c r="E99" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H99" s="9" t="s">
+      <c r="H99" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I99" s="9"/>
-      <c r="J99" s="8">
+      <c r="I99" s="10"/>
+      <c r="J99" s="9">
         <v>46262</v>
       </c>
-      <c r="K99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N99" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="O99" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="P99" s="9" t="s">
+      <c r="K99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="Q99" s="9"/>
-      <c r="R99" s="9"/>
-      <c r="S99" s="9"/>
-      <c r="T99" s="9"/>
-      <c r="U99" s="9"/>
+      <c r="O99" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P99" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="10"/>
+      <c r="S99" s="10"/>
+      <c r="T99" s="10"/>
+      <c r="U99" s="10"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B100" s="5">
         <v>46188.6352894213</v>
@@ -7184,7 +7227,7 @@
         <v>46188.68112425926</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7209,13 +7252,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7224,71 +7267,71 @@
       <c r="U100" s="6"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A101" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="B101" s="8">
+      <c r="A101" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B101" s="9">
         <v>46188.63530922454</v>
       </c>
-      <c r="C101" s="9"/>
-      <c r="D101" s="8">
+      <c r="C101" s="10"/>
+      <c r="D101" s="9">
         <v>46188.68135644676</v>
       </c>
-      <c r="E101" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I101" s="8">
+      <c r="E101" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I101" s="9">
         <v>46265</v>
       </c>
-      <c r="J101" s="8">
+      <c r="J101" s="9">
         <v>46265</v>
       </c>
-      <c r="K101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N101" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="O101" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q101" s="8">
+      <c r="K101" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L101" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M101" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N101" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="O101" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P101" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q101" s="9">
         <v>46265</v>
       </c>
-      <c r="R101" s="8">
+      <c r="R101" s="9">
         <v>46265</v>
       </c>
-      <c r="S101" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T101" s="9">
+      <c r="S101" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T101" s="10">
         <v>0</v>
       </c>
-      <c r="U101" s="10" t="s">
-        <v>49</v>
+      <c r="U101" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B102" s="5">
         <v>46188.63531412037</v>
@@ -7298,16 +7341,16 @@
         <v>46188.681314560185</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -7323,13 +7366,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7338,59 +7381,59 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B103" s="8">
+      <c r="A103" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="B103" s="9">
         <v>46188.63532239583</v>
       </c>
-      <c r="C103" s="9"/>
-      <c r="D103" s="8">
+      <c r="C103" s="10"/>
+      <c r="D103" s="9">
         <v>46188.68131152778</v>
       </c>
-      <c r="E103" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I103" s="9"/>
-      <c r="J103" s="8">
+      <c r="E103" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I103" s="10"/>
+      <c r="J103" s="9">
         <v>46265</v>
       </c>
-      <c r="K103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N103" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="O103" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="P103" s="9" t="s">
+      <c r="K103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M103" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N103" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="Q103" s="9"/>
-      <c r="R103" s="9"/>
-      <c r="S103" s="9"/>
-      <c r="T103" s="9"/>
-      <c r="U103" s="9"/>
+      <c r="O103" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P103" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q103" s="10"/>
+      <c r="R103" s="10"/>
+      <c r="S103" s="10"/>
+      <c r="T103" s="10"/>
+      <c r="U103" s="10"/>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B104" s="5">
         <v>46188.63538068287</v>
@@ -7400,16 +7443,16 @@
         <v>46188.68149567129</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I104" s="5">
         <v>46266</v>
@@ -7427,13 +7470,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q104" s="5">
         <v>46266</v>
@@ -7441,72 +7484,72 @@
       <c r="R104" s="5">
         <v>46266</v>
       </c>
-      <c r="S104" s="12" t="s">
-        <v>97</v>
+      <c r="S104" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
-      <c r="U104" s="10" t="s">
-        <v>49</v>
+      <c r="U104" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
+      <c r="A105" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B105" s="9">
+        <v>46188.6353874537</v>
+      </c>
+      <c r="C105" s="10"/>
+      <c r="D105" s="9">
+        <v>46188.68144886574</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I105" s="9">
+        <v>46266</v>
+      </c>
+      <c r="J105" s="9">
+        <v>46266</v>
+      </c>
+      <c r="K105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N105" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B105" s="8">
-        <v>46188.6353874537</v>
-      </c>
-      <c r="C105" s="9"/>
-      <c r="D105" s="8">
-        <v>46188.68144886574</v>
-      </c>
-      <c r="E105" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G105" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="I105" s="8">
-        <v>46266</v>
-      </c>
-      <c r="J105" s="8">
-        <v>46266</v>
-      </c>
-      <c r="K105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N105" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="O105" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="P105" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q105" s="9"/>
-      <c r="R105" s="9"/>
-      <c r="S105" s="9"/>
-      <c r="T105" s="9"/>
-      <c r="U105" s="9"/>
+      <c r="O105" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P105" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q105" s="10"/>
+      <c r="R105" s="10"/>
+      <c r="S105" s="10"/>
+      <c r="T105" s="10"/>
+      <c r="U105" s="10"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B106" s="5">
         <v>46188.63539206018</v>
@@ -7516,16 +7559,16 @@
         <v>46188.681445636576</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I106" s="5">
         <v>46266</v>
@@ -7543,13 +7586,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7558,55 +7601,55 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="B107" s="8">
+      <c r="A107" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="B107" s="9">
         <v>46188.635410682866</v>
       </c>
-      <c r="C107" s="9"/>
-      <c r="D107" s="8">
+      <c r="C107" s="10"/>
+      <c r="D107" s="9">
         <v>46188.67123894676</v>
       </c>
-      <c r="E107" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="F107" s="9" t="s">
+      <c r="E107" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F107" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="9"/>
-      <c r="I107" s="9"/>
-      <c r="J107" s="9"/>
-      <c r="K107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M107" s="9" t="s">
+      <c r="G107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H107" s="10"/>
+      <c r="I107" s="10"/>
+      <c r="J107" s="10"/>
+      <c r="K107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M107" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="N107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O107" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="P107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q107" s="9"/>
-      <c r="R107" s="9"/>
-      <c r="S107" s="9"/>
-      <c r="T107" s="9"/>
-      <c r="U107" s="9"/>
+      <c r="N107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O107" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="P107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q107" s="10"/>
+      <c r="R107" s="10"/>
+      <c r="S107" s="10"/>
+      <c r="T107" s="10"/>
+      <c r="U107" s="10"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B108" s="5">
         <v>46188.635413993055</v>
@@ -7616,16 +7659,16 @@
         <v>46188.68161465278</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I108" s="5">
         <v>46267</v>
@@ -7643,13 +7686,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q108" s="5">
         <v>46267</v>
@@ -7657,77 +7700,77 @@
       <c r="R108" s="5">
         <v>46275</v>
       </c>
-      <c r="S108" s="12" t="s">
-        <v>97</v>
+      <c r="S108" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="T108" s="6">
         <v>0</v>
       </c>
-      <c r="U108" s="10" t="s">
-        <v>49</v>
+      <c r="U108" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="B109" s="8">
+      <c r="A109" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B109" s="9">
         <v>46188.63541944444</v>
       </c>
-      <c r="C109" s="9"/>
-      <c r="D109" s="8">
-        <v>46188.68165633101</v>
-      </c>
-      <c r="E109" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="F109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G109" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="I109" s="8">
+      <c r="C109" s="10"/>
+      <c r="D109" s="9">
+        <v>46188.920573842595</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="I109" s="9">
         <v>46267</v>
       </c>
-      <c r="J109" s="8">
+      <c r="J109" s="9">
         <v>46275</v>
       </c>
-      <c r="K109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N109" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="O109" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="P109" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q109" s="8">
+      <c r="K109" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L109" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M109" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N109" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="O109" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="P109" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q109" s="9">
         <v>46267</v>
       </c>
-      <c r="R109" s="8">
+      <c r="R109" s="9">
         <v>46275</v>
       </c>
-      <c r="S109" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="T109" s="9">
+      <c r="S109" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="T109" s="10">
         <v>0</v>
       </c>
-      <c r="U109" s="10" t="s">
-        <v>49</v>
+      <c r="U109" s="11" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="314">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -227,7 +227,7 @@
     <t>propuesta motor</t>
   </si>
   <si>
-    <t>Propuesta compras:,Generación OC motor OT 4360</t>
+    <t>Propuesta compras:,motor 4360</t>
   </si>
   <si>
     <t>1215727723502427</t>
@@ -244,7 +244,7 @@
 </t>
   </si>
   <si>
-    <t>Propuesta compras:,Generación OC Alabe OT 4316</t>
+    <t>Propuesta compras:,Alabe 4360</t>
   </si>
   <si>
     <t>1215728035784425</t>
@@ -310,19 +310,49 @@
     <t>Generacion OC Fabricación Externa OT 4360</t>
   </si>
   <si>
+    <t>1215771707606671</t>
+  </si>
+  <si>
+    <t>Reserva producción</t>
+  </si>
+  <si>
+    <t>motor 4360,Alabe 4360</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1215771707606683</t>
+  </si>
+  <si>
+    <t>motor 4360</t>
+  </si>
+  <si>
+    <t>Reserva producción,Recepcionx motor</t>
+  </si>
+  <si>
+    <t>1215771707606685</t>
+  </si>
+  <si>
+    <t>Alabe 4360</t>
+  </si>
+  <si>
+    <t>Reserva producción,Recepcionx Alabe</t>
+  </si>
+  <si>
     <t>1215727332551586</t>
   </si>
   <si>
     <t>Compras:</t>
   </si>
   <si>
-    <t>Materiales corte Laser OT 4360,Motor OT 4360,Alabe OT 4360,rodete OT 4360</t>
-  </si>
-  <si>
-    <t>1215728035806415</t>
-  </si>
-  <si>
-    <t>Alabe OT 4360</t>
+    <t>Materiales corte Laser OT 4360,rodete OT 4360</t>
+  </si>
+  <si>
+    <t>1215728035819291</t>
+  </si>
+  <si>
+    <t>rodete OT 4360</t>
   </si>
   <si>
     <t>Eliana</t>
@@ -331,36 +361,6 @@
     <t>ecarico@zitron.com</t>
   </si>
   <si>
-    <t>Generación OC Alabe OT 4316,Fabricación Alabe OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792616534</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe OT 4316</t>
-  </si>
-  <si>
-    <t>Alabe OT 4360,Fabricación Alabe OT 4316</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1215727792616554</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe OT 4316</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Alabe OT 4360</t>
-  </si>
-  <si>
-    <t>1215728035819291</t>
-  </si>
-  <si>
-    <t>rodete OT 4360</t>
-  </si>
-  <si>
     <t>Generación OC Rodete OT 4316,Fabricación Rodete OT 4316</t>
   </si>
   <si>
@@ -382,42 +382,6 @@
     <t>Recepcion Rodete,rodete OT 4360</t>
   </si>
   <si>
-    <t>1215727792650140</t>
-  </si>
-  <si>
-    <t>Motor OT 4360</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4360,Generación OC motor OT 4360,Fabricación motor OT 4360</t>
-  </si>
-  <si>
-    <t>1215727792650157</t>
-  </si>
-  <si>
-    <t>Generación OC motor OT 4360</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4360,Motor OT 4360,Fabricación motor OT 4360</t>
-  </si>
-  <si>
-    <t>1215727939683120</t>
-  </si>
-  <si>
-    <t>Fabricación motor OT 4360</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Motor OT 4360</t>
-  </si>
-  <si>
-    <t>1215727723568457</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor OT 4360</t>
-  </si>
-  <si>
-    <t>Motor OT 4360,Planos definitivos</t>
-  </si>
-  <si>
     <t>1215727723568477</t>
   </si>
   <si>
@@ -571,9 +535,6 @@
     <t>Planos definitivos</t>
   </si>
   <si>
-    <t>Planos preliminar,Planos motor proveedor OT 4360</t>
-  </si>
-  <si>
     <t>Ingenieria y diseñoo:,check planos</t>
   </si>
   <si>
@@ -751,7 +712,7 @@
     <t>1215727940067011</t>
   </si>
   <si>
-    <t>Recepcion Alabe,Recepcion motor,Recepcion Rodete</t>
+    <t>Recepcionx Alabe,Recepcionx motor,Recepcion Rodete</t>
   </si>
   <si>
     <t>1215727940078553</t>
@@ -763,7 +724,7 @@
     <t>1215727940078575</t>
   </si>
   <si>
-    <t>Recepcion Alabe</t>
+    <t>Recepcionx Alabe</t>
   </si>
   <si>
     <t>Media</t>
@@ -772,7 +733,7 @@
     <t>1215727793148813</t>
   </si>
   <si>
-    <t>Recepcion motor</t>
+    <t>Recepcionx motor</t>
   </si>
   <si>
     <t>1215728036191110</t>
@@ -820,7 +781,7 @@
     <t>1215727940112407</t>
   </si>
   <si>
-    <t>Recepcion Alabe,check planos</t>
+    <t>Recepcionx Alabe,check planos</t>
   </si>
   <si>
     <t>Montaje Alabe,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
@@ -859,7 +820,7 @@
     <t>1215728008590051</t>
   </si>
   <si>
-    <t>Recepcion motor,check planos</t>
+    <t>Recepcionx motor,check planos</t>
   </si>
   <si>
     <t>Montaje motor,OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
@@ -1539,7 +1500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U109"/>
+  <dimension ref="A1:U105"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2321,7 +2282,7 @@
         <v>46188.92065792824</v>
       </c>
       <c r="D15" s="9">
-        <v>46188.9208512037</v>
+        <v>46189.814397685186</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2386,7 +2347,7 @@
         <v>46188.9213359375</v>
       </c>
       <c r="D16" s="5">
-        <v>46188.92135230324</v>
+        <v>46189.814421944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2760,11 +2721,11 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46188.634174861116</v>
+        <v>46189.78075929398</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46188.65473270833</v>
+        <v>46189.814552916665</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2798,32 +2759,38 @@
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
+      <c r="S22" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T22" s="6">
+        <v>0</v>
+      </c>
+      <c r="U22" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46188.63440866898</v>
+        <v>46189.81187604167</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46189.16963417824</v>
+        <v>46189.81491765047</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="I23" s="9">
         <v>46183</v>
@@ -2844,10 +2811,10 @@
         <v>92</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="Q23" s="9">
         <v>46183</v>
@@ -2867,32 +2834,32 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46188.63441429398</v>
+        <v>46189.8120440162</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46188.92134424769</v>
+        <v>46189.8148409375</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="I24" s="5">
         <v>46183</v>
       </c>
       <c r="J24" s="5">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>26</v>
@@ -2904,18 +2871,22 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
+      </c>
+      <c r="Q24" s="5">
+        <v>46183</v>
+      </c>
+      <c r="R24" s="5">
+        <v>46188</v>
+      </c>
+      <c r="S24" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
@@ -2926,33 +2897,27 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.63442</v>
+        <v>46188.634174861116</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46188.67367325231</v>
+        <v>46189.78281247686</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="I25" s="9">
-        <v>46185</v>
-      </c>
-      <c r="J25" s="9">
-        <v>46188</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
       <c r="K25" s="10" t="s">
         <v>26</v>
       </c>
@@ -2960,32 +2925,26 @@
         <v>26</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
-      <c r="S25" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T25" s="10">
-        <v>0</v>
-      </c>
-      <c r="U25" s="11" t="s">
-        <v>81</v>
-      </c>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
@@ -2995,16 +2954,16 @@
         <v>46188.67380942129</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -3022,13 +2981,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="Q26" s="5">
         <v>46183</v>
@@ -3037,7 +2996,7 @@
         <v>46204</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -3064,10 +3023,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3085,7 +3044,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>71</v>
@@ -3096,7 +3055,7 @@
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
@@ -3123,10 +3082,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3144,7 +3103,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>110</v>
@@ -3155,7 +3114,7 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
@@ -3169,11 +3128,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.63444313657</v>
+        <v>46188.63451584491</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46188.67394298611</v>
+        <v>46188.674114560185</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3182,16 +3141,16 @@
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="I29" s="9">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="J29" s="9">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>26</v>
@@ -3203,22 +3162,22 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="Q29" s="9">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="R29" s="9">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
@@ -3229,32 +3188,32 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.63444855324</v>
+        <v>46188.63452219908</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.92066599537</v>
+        <v>46188.67407226852</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="I30" s="5">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="J30" s="5">
-        <v>46191</v>
+        <v>46216</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>26</v>
@@ -3269,15 +3228,15 @@
         <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3288,32 +3247,32 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.63445415509</v>
+        <v>46188.634528194445</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46188.673910219906</v>
+        <v>46188.6740696412</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="I31" s="9">
-        <v>46192</v>
+        <v>46217</v>
       </c>
       <c r="J31" s="9">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="K31" s="10" t="s">
         <v>26</v>
@@ -3328,15 +3287,15 @@
         <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
@@ -3347,32 +3306,32 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.63450900463</v>
+        <v>46188.63453408565</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46188.67390592593</v>
+        <v>46188.67423875</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="I32" s="5">
-        <v>46192</v>
+        <v>46213</v>
       </c>
       <c r="J32" s="5">
-        <v>46202</v>
+        <v>46225</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
@@ -3384,18 +3343,22 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>46213</v>
+      </c>
+      <c r="R32" s="5">
+        <v>46225</v>
+      </c>
       <c r="S32" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -3406,32 +3369,32 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.63451584491</v>
+        <v>46188.634538252314</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46188.674114560185</v>
+        <v>46188.674186689816</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
       </c>
       <c r="J33" s="9">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>26</v>
@@ -3443,117 +3406,101 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q33" s="9">
-        <v>46213</v>
-      </c>
-      <c r="R33" s="9">
-        <v>46225</v>
-      </c>
-      <c r="S33" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.63452219908</v>
+        <v>46188.63454329861</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46188.67407226852</v>
+        <v>46188.674183877316</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="I34" s="5">
+        <v>46217</v>
+      </c>
+      <c r="J34" s="5">
+        <v>46225</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="P34" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I34" s="5">
-        <v>46213</v>
-      </c>
-      <c r="J34" s="5">
-        <v>46216</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="O34" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="P34" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
-      <c r="S34" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T34" s="6">
-        <v>0</v>
-      </c>
-      <c r="U34" s="11" t="s">
-        <v>81</v>
-      </c>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.634528194445</v>
+        <v>46188.63454804398</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46188.6740696412</v>
+        <v>46188.674703854165</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>129</v>
-      </c>
       <c r="H35" s="10" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I35" s="9">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="J35" s="9">
-        <v>46225</v>
+        <v>46253</v>
       </c>
       <c r="K35" s="10" t="s">
         <v>26</v>
@@ -3565,18 +3512,22 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>46213</v>
+      </c>
+      <c r="R35" s="9">
+        <v>46253</v>
+      </c>
       <c r="S35" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
@@ -3587,32 +3538,32 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.63453408565</v>
+        <v>46188.63455278936</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46188.67423875</v>
+        <v>46188.67435018519</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
       </c>
       <c r="J36" s="5">
-        <v>46225</v>
+        <v>46223</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>26</v>
@@ -3624,58 +3575,48 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="P36" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="P36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q36" s="5">
-        <v>46213</v>
-      </c>
-      <c r="R36" s="5">
-        <v>46225</v>
-      </c>
-      <c r="S36" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T36" s="6">
-        <v>0</v>
-      </c>
-      <c r="U36" s="11" t="s">
-        <v>81</v>
-      </c>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.634538252314</v>
+        <v>46188.63455811342</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46188.674186689816</v>
+        <v>46188.67434657407</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I37" s="9">
-        <v>46213</v>
+        <v>46224</v>
       </c>
       <c r="J37" s="9">
-        <v>46216</v>
+        <v>46252</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>26</v>
@@ -3687,13 +3628,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3703,32 +3644,32 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.63454329861</v>
+        <v>46188.63456381945</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46188.674183877316</v>
+        <v>46188.674648472224</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="I38" s="5">
-        <v>46217</v>
+        <v>46253</v>
       </c>
       <c r="J38" s="5">
-        <v>46225</v>
+        <v>46253</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>26</v>
@@ -3740,13 +3681,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3756,32 +3697,32 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.63454804398</v>
+        <v>46188.63456738426</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46188.674703854165</v>
+        <v>46188.67687303241</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
       </c>
       <c r="J39" s="9">
-        <v>46253</v>
+        <v>46225</v>
       </c>
       <c r="K39" s="10" t="s">
         <v>26</v>
@@ -3793,7 +3734,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>150</v>
@@ -3805,10 +3746,10 @@
         <v>46213</v>
       </c>
       <c r="R39" s="9">
-        <v>46253</v>
+        <v>46225</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
@@ -3822,29 +3763,29 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.63455278936</v>
+        <v>46188.63457166667</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46188.67435018519</v>
+        <v>46188.67683644676</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
       </c>
       <c r="J40" s="5">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -3856,10 +3797,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>152</v>
@@ -3875,11 +3816,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.63455811342</v>
+        <v>46188.634576701385</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46188.67434657407</v>
+        <v>46188.67683361111</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -3888,31 +3829,31 @@
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="H41" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="I41" s="9">
+        <v>46217</v>
+      </c>
+      <c r="J41" s="9">
+        <v>46225</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="I41" s="9">
-        <v>46224</v>
-      </c>
-      <c r="J41" s="9">
-        <v>46252</v>
-      </c>
-      <c r="K41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" s="10" t="s">
-        <v>147</v>
-      </c>
       <c r="O41" s="10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>155</v>
@@ -3928,44 +3869,38 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.63456381945</v>
+        <v>46188.63417921297</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46188.674648472224</v>
+        <v>46188.676957083335</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I42" s="5">
-        <v>46253</v>
-      </c>
-      <c r="J42" s="5">
-        <v>46253</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3978,32 +3913,32 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.63456738426</v>
+        <v>46188.63458247685</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46188.67687303241</v>
+        <v>46188.9205047338</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>129</v>
-      </c>
       <c r="H43" s="10" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="I43" s="9">
-        <v>46213</v>
+        <v>46188</v>
       </c>
       <c r="J43" s="9">
-        <v>46225</v>
+        <v>46192</v>
       </c>
       <c r="K43" s="10" t="s">
         <v>26</v>
@@ -4015,58 +3950,58 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="9">
-        <v>46213</v>
+        <v>46188</v>
       </c>
       <c r="R43" s="9">
-        <v>46225</v>
+        <v>46192</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
       </c>
-      <c r="U43" s="11" t="s">
-        <v>81</v>
+      <c r="U43" s="12" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.63457166667</v>
+        <v>46188.634588587964</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46188.67683644676</v>
+        <v>46189.78047149305</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="I44" s="5">
-        <v>46213</v>
+        <v>46203</v>
       </c>
       <c r="J44" s="5">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
@@ -4078,48 +4013,58 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6"/>
-      <c r="T44" s="6"/>
-      <c r="U44" s="6"/>
+        <v>166</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>46203</v>
+      </c>
+      <c r="R44" s="5">
+        <v>46209</v>
+      </c>
+      <c r="S44" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T44" s="6">
+        <v>0</v>
+      </c>
+      <c r="U44" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.634576701385</v>
+        <v>46188.63459497685</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46188.67683361111</v>
+        <v>46188.67693108796</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="I45" s="9">
-        <v>46217</v>
+        <v>46210</v>
       </c>
       <c r="J45" s="9">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="K45" s="10" t="s">
         <v>26</v>
@@ -4131,43 +4076,59 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="10"/>
-      <c r="S45" s="10"/>
-      <c r="T45" s="10"/>
-      <c r="U45" s="10"/>
+        <v>168</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>46210</v>
+      </c>
+      <c r="R45" s="9">
+        <v>46210</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T45" s="10">
+        <v>0</v>
+      </c>
+      <c r="U45" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.63417921297</v>
+        <v>46188.63460983796</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.676957083335</v>
+        <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
+        <v>171</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="I46" s="5">
+        <v>46259</v>
+      </c>
+      <c r="J46" s="5">
+        <v>46259</v>
+      </c>
       <c r="K46" s="6" t="s">
         <v>26</v>
       </c>
@@ -4175,51 +4136,61 @@
         <v>26</v>
       </c>
       <c r="M46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q46" s="5">
+        <v>46259</v>
+      </c>
+      <c r="R46" s="5">
+        <v>46259</v>
+      </c>
+      <c r="S46" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T46" s="6">
         <v>0</v>
       </c>
-      <c r="N46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="P46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+      <c r="U46" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.63458247685</v>
+        <v>46188.634613946764</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46188.9205047338</v>
+        <v>46188.677066122684</v>
       </c>
       <c r="E47" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>174</v>
-      </c>
       <c r="I47" s="9">
-        <v>46188</v>
+        <v>46259</v>
       </c>
       <c r="J47" s="9">
-        <v>46192</v>
+        <v>46259</v>
       </c>
       <c r="K47" s="10" t="s">
         <v>26</v>
@@ -4231,122 +4202,96 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q47" s="9">
-        <v>46188</v>
-      </c>
-      <c r="R47" s="9">
-        <v>46192</v>
-      </c>
-      <c r="S47" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T47" s="10">
-        <v>0</v>
-      </c>
-      <c r="U47" s="12" t="s">
-        <v>74</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.634588587964</v>
+        <v>46188.63461840278</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46188.6769350463</v>
+        <v>46188.67706284722</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="I48" s="5">
+        <v>46259</v>
+      </c>
+      <c r="J48" s="5">
+        <v>46259</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="I48" s="5">
-        <v>46203</v>
-      </c>
-      <c r="J48" s="5">
-        <v>46209</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q48" s="5">
-        <v>46203</v>
-      </c>
-      <c r="R48" s="5">
-        <v>46209</v>
-      </c>
-      <c r="S48" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T48" s="6">
-        <v>0</v>
-      </c>
-      <c r="U48" s="11" t="s">
-        <v>81</v>
-      </c>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6"/>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.63459497685</v>
+        <v>46188.63467295139</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.67693108796</v>
+        <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I49" s="9">
-        <v>46210</v>
-      </c>
-      <c r="J49" s="9">
-        <v>46210</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
       <c r="K49" s="10" t="s">
         <v>26</v>
       </c>
@@ -4354,43 +4299,33 @@
         <v>26</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>169</v>
+        <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q49" s="9">
-        <v>46210</v>
-      </c>
-      <c r="R49" s="9">
-        <v>46210</v>
-      </c>
-      <c r="S49" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T49" s="10">
-        <v>0</v>
-      </c>
-      <c r="U49" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>182</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.63460983796</v>
+        <v>46188.63467763889</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46188.677102754635</v>
+        <v>46188.67723120371</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>183</v>
@@ -4405,10 +4340,10 @@
         <v>185</v>
       </c>
       <c r="I50" s="5">
-        <v>46259</v>
+        <v>46226</v>
       </c>
       <c r="J50" s="5">
-        <v>46259</v>
+        <v>46227</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>26</v>
@@ -4420,22 +4355,22 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="P50" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="Q50" s="5">
-        <v>46259</v>
+        <v>46226</v>
       </c>
       <c r="R50" s="5">
-        <v>46259</v>
+        <v>46227</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4449,11 +4384,11 @@
         <v>187</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.634613946764</v>
+        <v>46188.634684942124</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.677066122684</v>
+        <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>188</v>
@@ -4462,16 +4397,16 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="I51" s="9">
-        <v>46259</v>
+        <v>46230</v>
       </c>
       <c r="J51" s="9">
-        <v>46259</v>
+        <v>46231</v>
       </c>
       <c r="K51" s="10" t="s">
         <v>26</v>
@@ -4483,7 +4418,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>189</v>
@@ -4491,25 +4426,35 @@
       <c r="P51" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10"/>
-      <c r="T51" s="10"/>
-      <c r="U51" s="10"/>
+      <c r="Q51" s="9">
+        <v>46230</v>
+      </c>
+      <c r="R51" s="9">
+        <v>46231</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T51" s="10">
+        <v>0</v>
+      </c>
+      <c r="U51" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>191</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.63461840278</v>
+        <v>46188.634692962965</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46188.67706284722</v>
+        <v>46188.67722799769</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4521,10 +4466,10 @@
         <v>185</v>
       </c>
       <c r="I52" s="5">
-        <v>46259</v>
+        <v>46226</v>
       </c>
       <c r="J52" s="5">
-        <v>46259</v>
+        <v>46227</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>26</v>
@@ -4536,43 +4481,59 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>188</v>
+        <v>132</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="6"/>
+        <v>193</v>
+      </c>
+      <c r="Q52" s="5">
+        <v>46226</v>
+      </c>
+      <c r="R52" s="5">
+        <v>46227</v>
+      </c>
+      <c r="S52" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T52" s="6">
+        <v>0</v>
+      </c>
+      <c r="U52" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.63467295139</v>
+        <v>46188.63469954861</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.660341678245</v>
+        <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
+        <v>146</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="I53" s="9">
+        <v>46230</v>
+      </c>
+      <c r="J53" s="9">
+        <v>46231</v>
+      </c>
       <c r="K53" s="10" t="s">
         <v>26</v>
       </c>
@@ -4580,45 +4541,55 @@
         <v>26</v>
       </c>
       <c r="M53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="O53" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="P53" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q53" s="9">
+        <v>46230</v>
+      </c>
+      <c r="R53" s="9">
+        <v>46231</v>
+      </c>
+      <c r="S53" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T53" s="10">
         <v>0</v>
       </c>
-      <c r="N53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="P53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
+      <c r="U53" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.63467763889</v>
+        <v>46188.63470560186</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46188.67723120371</v>
+        <v>46188.677224942134</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4636,13 +4607,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4651,7 +4622,7 @@
         <v>46227</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4662,26 +4633,26 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.634684942124</v>
+        <v>46188.63471155093</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.67731989583</v>
+        <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4699,13 +4670,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4714,7 +4685,7 @@
         <v>46231</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4725,33 +4696,27 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.634692962965</v>
+        <v>46188.63471731481</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.67722799769</v>
+        <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="I56" s="5">
-        <v>46226</v>
-      </c>
-      <c r="J56" s="5">
-        <v>46227</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
       <c r="K56" s="6" t="s">
         <v>26</v>
       </c>
@@ -4759,61 +4724,51 @@
         <v>26</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q56" s="5">
-        <v>46226</v>
-      </c>
-      <c r="R56" s="5">
-        <v>46227</v>
-      </c>
-      <c r="S56" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T56" s="6">
-        <v>0</v>
-      </c>
-      <c r="U56" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6"/>
+      <c r="T56" s="6"/>
+      <c r="U56" s="6"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.63469954861</v>
+        <v>46188.63472107639</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.67731701389</v>
+        <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>159</v>
+        <v>206</v>
       </c>
       <c r="I57" s="9">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="J57" s="9">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="K57" s="10" t="s">
         <v>26</v>
@@ -4825,22 +4780,22 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="Q57" s="9">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="R57" s="9">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
@@ -4851,32 +4806,32 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.63470560186</v>
+        <v>46188.63473258102</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.677224942134</v>
+        <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="I58" s="5">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="J58" s="5">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>26</v>
@@ -4888,116 +4843,102 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q58" s="5">
-        <v>46226</v>
-      </c>
-      <c r="R58" s="5">
-        <v>46227</v>
-      </c>
-      <c r="S58" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T58" s="6">
-        <v>0</v>
-      </c>
-      <c r="U58" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="6"/>
+      <c r="U58" s="6"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.63471155093</v>
+        <v>46188.63474121528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.67731351852</v>
+        <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I59" s="9">
+        <v>46232</v>
+      </c>
+      <c r="J59" s="9">
+        <v>46234</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="O59" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="I59" s="9">
-        <v>46230</v>
-      </c>
-      <c r="J59" s="9">
-        <v>46231</v>
-      </c>
-      <c r="K59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="O59" s="10" t="s">
-        <v>210</v>
-      </c>
       <c r="P59" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q59" s="9">
-        <v>46230</v>
-      </c>
-      <c r="R59" s="9">
-        <v>46231</v>
-      </c>
-      <c r="S59" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T59" s="10">
-        <v>0</v>
-      </c>
-      <c r="U59" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>213</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.63471731481</v>
+        <v>46188.63477284722</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.662660393515</v>
+        <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>214</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
+        <v>205</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="I60" s="5">
+        <v>46237</v>
+      </c>
+      <c r="J60" s="5">
+        <v>46241</v>
+      </c>
       <c r="K60" s="6" t="s">
         <v>26</v>
       </c>
@@ -5005,51 +4946,61 @@
         <v>26</v>
       </c>
       <c r="M60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q60" s="5">
+        <v>46237</v>
+      </c>
+      <c r="R60" s="5">
+        <v>46241</v>
+      </c>
+      <c r="S60" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T60" s="6">
         <v>0</v>
       </c>
-      <c r="N60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="6"/>
-      <c r="S60" s="6"/>
-      <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
+      <c r="U60" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.63472107639</v>
+        <v>46188.63477877315</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46188.677743113425</v>
+        <v>46188.677545659724</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I61" s="9">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="J61" s="9">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="K61" s="10" t="s">
         <v>26</v>
@@ -5064,55 +5015,45 @@
         <v>214</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q61" s="9">
-        <v>46232</v>
-      </c>
-      <c r="R61" s="9">
-        <v>46234</v>
-      </c>
-      <c r="S61" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T61" s="10">
-        <v>0</v>
-      </c>
-      <c r="U61" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="10"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.63473258102</v>
+        <v>46188.63478605324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46188.677464444445</v>
+        <v>46188.67754284722</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I62" s="5">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="J62" s="5">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>26</v>
@@ -5124,13 +5065,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5140,32 +5081,32 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.63474121528</v>
+        <v>46188.63485537037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.677461087966</v>
+        <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>219</v>
+        <v>147</v>
       </c>
       <c r="I63" s="9">
-        <v>46232</v>
+        <v>46244</v>
       </c>
       <c r="J63" s="9">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="K63" s="10" t="s">
         <v>26</v>
@@ -5177,48 +5118,58 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q63" s="10"/>
-      <c r="R63" s="10"/>
-      <c r="S63" s="10"/>
-      <c r="T63" s="10"/>
-      <c r="U63" s="10"/>
+        <v>201</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>46244</v>
+      </c>
+      <c r="R63" s="9">
+        <v>46244</v>
+      </c>
+      <c r="S63" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T63" s="10">
+        <v>0</v>
+      </c>
+      <c r="U63" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.63477284722</v>
+        <v>46188.634861805556</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46188.67773935186</v>
+        <v>46188.677654756946</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>227</v>
+        <v>175</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>147</v>
       </c>
       <c r="I64" s="5">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J64" s="5">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
@@ -5230,58 +5181,48 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q64" s="5">
-        <v>46237</v>
-      </c>
-      <c r="R64" s="5">
-        <v>46241</v>
-      </c>
-      <c r="S64" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T64" s="6">
-        <v>0</v>
-      </c>
-      <c r="U64" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.63477877315</v>
+        <v>46188.63486881944</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46188.677545659724</v>
+        <v>46188.67765203703</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>219</v>
+        <v>147</v>
       </c>
       <c r="I65" s="9">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J65" s="9">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K65" s="10" t="s">
         <v>26</v>
@@ -5293,13 +5234,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5309,33 +5250,27 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.63478605324</v>
+        <v>46188.63489331018</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46188.67754284722</v>
+        <v>46188.664478900464</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I66" s="5">
-        <v>46237</v>
-      </c>
-      <c r="J66" s="5">
-        <v>46241</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
       <c r="K66" s="6" t="s">
         <v>26</v>
       </c>
@@ -5343,16 +5278,16 @@
         <v>26</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>227</v>
+        <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>230</v>
+        <v>26</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5362,32 +5297,32 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.63485537037</v>
+        <v>46188.634903391205</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46188.67780341435</v>
+        <v>46188.677911018516</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="I67" s="9">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="J67" s="9">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="K67" s="10" t="s">
         <v>26</v>
@@ -5399,22 +5334,22 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="Q67" s="9">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="R67" s="9">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="S67" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5425,32 +5360,32 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.634861805556</v>
+        <v>46188.6349100463</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46188.677654756946</v>
+        <v>46189.81484074074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="I68" s="5">
-        <v>46244</v>
+        <v>46189</v>
       </c>
       <c r="J68" s="5">
-        <v>46244</v>
+        <v>46189</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
@@ -5462,48 +5397,58 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>229</v>
+        <v>99</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+        <v>190</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>46189</v>
+      </c>
+      <c r="R68" s="5">
+        <v>46189</v>
+      </c>
+      <c r="S68" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="T68" s="6">
+        <v>0</v>
+      </c>
+      <c r="U68" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.63486881944</v>
+        <v>46188.6349165162</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46188.67765203703</v>
+        <v>46189.81491748843</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="I69" s="9">
-        <v>46244</v>
+        <v>46223</v>
       </c>
       <c r="J69" s="9">
-        <v>46244</v>
+        <v>46223</v>
       </c>
       <c r="K69" s="10" t="s">
         <v>26</v>
@@ -5515,43 +5460,59 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>229</v>
+        <v>96</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q69" s="10"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="10"/>
-      <c r="T69" s="10"/>
-      <c r="U69" s="10"/>
+        <v>190</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>46223</v>
+      </c>
+      <c r="R69" s="9">
+        <v>46223</v>
+      </c>
+      <c r="S69" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T69" s="10">
+        <v>0</v>
+      </c>
+      <c r="U69" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.63489331018</v>
+        <v>46188.634922916666</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46188.664478900464</v>
+        <v>46188.67789931713</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
+        <v>184</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="I70" s="5">
+        <v>46254</v>
+      </c>
+      <c r="J70" s="5">
+        <v>46254</v>
+      </c>
       <c r="K70" s="6" t="s">
         <v>26</v>
       </c>
@@ -5559,52 +5520,56 @@
         <v>26</v>
       </c>
       <c r="M70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>46254</v>
+      </c>
+      <c r="R70" s="5">
+        <v>46254</v>
+      </c>
+      <c r="S70" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T70" s="6">
         <v>0</v>
       </c>
-      <c r="N70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O70" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="6"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
+      <c r="U70" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.634903391205</v>
+        <v>46188.63492795139</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46188.677911018516</v>
+        <v>46188.66851157407</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="I71" s="9">
-        <v>46205</v>
-      </c>
-      <c r="J71" s="9">
-        <v>46205</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H71" s="10"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
       <c r="K71" s="10" t="s">
         <v>26</v>
       </c>
@@ -5612,61 +5577,51 @@
         <v>26</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>193</v>
+        <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>113</v>
+        <v>238</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q71" s="9">
-        <v>46205</v>
-      </c>
-      <c r="R71" s="9">
-        <v>46205</v>
-      </c>
-      <c r="S71" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T71" s="10">
-        <v>0</v>
-      </c>
-      <c r="U71" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
+      <c r="S71" s="10"/>
+      <c r="T71" s="10"/>
+      <c r="U71" s="10"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.6349100463</v>
+        <v>46188.63493152778</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46189.174127997685</v>
+        <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="I72" s="5">
-        <v>46189</v>
+        <v>46245</v>
       </c>
       <c r="J72" s="5">
-        <v>46189</v>
+        <v>46251</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>26</v>
@@ -5678,22 +5633,22 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>193</v>
+        <v>237</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>104</v>
+        <v>241</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="Q72" s="5">
-        <v>46189</v>
+        <v>46245</v>
       </c>
       <c r="R72" s="5">
-        <v>46189</v>
-      </c>
-      <c r="S72" s="12" t="s">
-        <v>243</v>
+        <v>46251</v>
+      </c>
+      <c r="S72" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5704,32 +5659,32 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.6349165162</v>
+        <v>46188.63494034723</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.677904247685</v>
+        <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="I73" s="9">
-        <v>46223</v>
+        <v>46245</v>
       </c>
       <c r="J73" s="9">
-        <v>46223</v>
+        <v>46251</v>
       </c>
       <c r="K73" s="10" t="s">
         <v>26</v>
@@ -5741,58 +5696,48 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q73" s="9">
-        <v>46223</v>
-      </c>
-      <c r="R73" s="9">
-        <v>46223</v>
-      </c>
-      <c r="S73" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T73" s="10">
-        <v>0</v>
-      </c>
-      <c r="U73" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
+      <c r="S73" s="10"/>
+      <c r="T73" s="10"/>
+      <c r="U73" s="10"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.634922916666</v>
+        <v>46188.634945150465</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.67789931713</v>
+        <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>247</v>
+        <v>175</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>197</v>
+        <v>72</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="I74" s="5">
-        <v>46254</v>
+        <v>46245</v>
       </c>
       <c r="J74" s="5">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
@@ -5804,53 +5749,49 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>154</v>
+        <v>243</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>46254</v>
-      </c>
-      <c r="R74" s="5">
-        <v>46254</v>
-      </c>
-      <c r="S74" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="6"/>
+      <c r="T74" s="6"/>
+      <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.63492795139</v>
+        <v>46188.634963668985</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46188.66851157407</v>
+        <v>46188.67832872685</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
+        <v>72</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I75" s="9">
+        <v>46252</v>
+      </c>
+      <c r="J75" s="9">
+        <v>46252</v>
+      </c>
       <c r="K75" s="10" t="s">
         <v>26</v>
       </c>
@@ -5858,36 +5799,46 @@
         <v>26</v>
       </c>
       <c r="M75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="O75" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q75" s="9">
+        <v>46252</v>
+      </c>
+      <c r="R75" s="9">
+        <v>46252</v>
+      </c>
+      <c r="S75" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T75" s="10">
         <v>0</v>
       </c>
-      <c r="N75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O75" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q75" s="10"/>
-      <c r="R75" s="10"/>
-      <c r="S75" s="10"/>
-      <c r="T75" s="10"/>
-      <c r="U75" s="10"/>
+      <c r="U75" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.63493152778</v>
+        <v>46188.63496887732</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46188.67802387731</v>
+        <v>46188.678293923615</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5899,10 +5850,10 @@
         <v>72</v>
       </c>
       <c r="I76" s="5">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="J76" s="5">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
@@ -5914,43 +5865,33 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q76" s="5">
-        <v>46245</v>
-      </c>
-      <c r="R76" s="5">
-        <v>46251</v>
-      </c>
-      <c r="S76" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.63494034723</v>
+        <v>46188.63498112268</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46188.677983657406</v>
+        <v>46188.678290868054</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5962,10 +5903,10 @@
         <v>72</v>
       </c>
       <c r="I77" s="9">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="J77" s="9">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="K77" s="10" t="s">
         <v>26</v>
@@ -5977,13 +5918,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>26</v>
+        <v>251</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5993,17 +5934,17 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.634945150465</v>
+        <v>46188.635046296295</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.677980567125</v>
+        <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>188</v>
+        <v>253</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6015,10 +5956,10 @@
         <v>72</v>
       </c>
       <c r="I78" s="5">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="J78" s="5">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>26</v>
@@ -6030,33 +5971,43 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
+        <v>237</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>46253</v>
+      </c>
+      <c r="R78" s="5">
+        <v>46253</v>
+      </c>
+      <c r="S78" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T78" s="6">
+        <v>0</v>
+      </c>
+      <c r="U78" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.634963668985</v>
+        <v>46188.63505403935</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46188.67832872685</v>
+        <v>46188.67891099537</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6068,10 +6019,10 @@
         <v>72</v>
       </c>
       <c r="I79" s="9">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="J79" s="9">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="K79" s="10" t="s">
         <v>26</v>
@@ -6083,43 +6034,33 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>186</v>
+        <v>255</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q79" s="9">
-        <v>46252</v>
-      </c>
-      <c r="R79" s="9">
-        <v>46252</v>
-      </c>
-      <c r="S79" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T79" s="10">
-        <v>0</v>
-      </c>
-      <c r="U79" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
+      <c r="S79" s="10"/>
+      <c r="T79" s="10"/>
+      <c r="U79" s="10"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.63496887732</v>
+        <v>46188.63506813657</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46188.678293923615</v>
+        <v>46188.678908194444</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6131,10 +6072,10 @@
         <v>72</v>
       </c>
       <c r="I80" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="J80" s="5">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -6146,13 +6087,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6162,17 +6103,17 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.63498112268</v>
+        <v>46188.63509704861</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.678290868054</v>
+        <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>188</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6184,10 +6125,10 @@
         <v>72</v>
       </c>
       <c r="I81" s="9">
-        <v>46252</v>
+        <v>46224</v>
       </c>
       <c r="J81" s="9">
-        <v>46252</v>
+        <v>46224</v>
       </c>
       <c r="K81" s="10" t="s">
         <v>26</v>
@@ -6199,33 +6140,43 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="10"/>
-      <c r="T81" s="10"/>
-      <c r="U81" s="10"/>
+        <v>237</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>46224</v>
+      </c>
+      <c r="R81" s="9">
+        <v>46224</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T81" s="10">
+        <v>0</v>
+      </c>
+      <c r="U81" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.635046296295</v>
+        <v>46188.635102939814</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46188.67895050926</v>
+        <v>46188.67902152777</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>266</v>
+        <v>175</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6237,10 +6188,10 @@
         <v>72</v>
       </c>
       <c r="I82" s="5">
-        <v>46253</v>
+        <v>46224</v>
       </c>
       <c r="J82" s="5">
-        <v>46253</v>
+        <v>46224</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>26</v>
@@ -6252,43 +6203,33 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>186</v>
+        <v>261</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q82" s="5">
-        <v>46253</v>
-      </c>
-      <c r="R82" s="5">
-        <v>46253</v>
-      </c>
-      <c r="S82" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T82" s="6">
-        <v>0</v>
-      </c>
-      <c r="U82" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="Q82" s="6"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="6"/>
+      <c r="T82" s="6"/>
+      <c r="U82" s="6"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.63505403935</v>
+        <v>46188.63510991898</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46188.67891099537</v>
+        <v>46188.67901871528</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6300,10 +6241,10 @@
         <v>72</v>
       </c>
       <c r="I83" s="9">
-        <v>46253</v>
+        <v>46224</v>
       </c>
       <c r="J83" s="9">
-        <v>46253</v>
+        <v>46224</v>
       </c>
       <c r="K83" s="10" t="s">
         <v>26</v>
@@ -6315,13 +6256,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6331,17 +6272,17 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.63506813657</v>
+        <v>46188.63513603009</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.678908194444</v>
+        <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>188</v>
+        <v>266</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6353,10 +6294,10 @@
         <v>72</v>
       </c>
       <c r="I84" s="5">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="J84" s="5">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>26</v>
@@ -6368,33 +6309,43 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
+        <v>237</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>46258</v>
+      </c>
+      <c r="R84" s="5">
+        <v>46258</v>
+      </c>
+      <c r="S84" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T84" s="6">
+        <v>0</v>
+      </c>
+      <c r="U84" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.63509704861</v>
+        <v>46188.63514172454</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46188.67906003472</v>
+        <v>46188.679159583335</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>272</v>
+        <v>176</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6405,11 +6356,9 @@
       <c r="H85" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I85" s="9">
-        <v>46224</v>
-      </c>
+      <c r="I85" s="10"/>
       <c r="J85" s="9">
-        <v>46224</v>
+        <v>46258</v>
       </c>
       <c r="K85" s="10" t="s">
         <v>26</v>
@@ -6421,43 +6370,33 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q85" s="9">
-        <v>46224</v>
-      </c>
-      <c r="R85" s="9">
-        <v>46224</v>
-      </c>
-      <c r="S85" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T85" s="10">
-        <v>0</v>
-      </c>
-      <c r="U85" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
+      <c r="T85" s="10"/>
+      <c r="U85" s="10"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.635102939814</v>
+        <v>46188.63514853009</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46188.67902152777</v>
+        <v>46188.6791566551</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6468,11 +6407,9 @@
       <c r="H86" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I86" s="5">
-        <v>46224</v>
-      </c>
+      <c r="I86" s="6"/>
       <c r="J86" s="5">
-        <v>46224</v>
+        <v>46258</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>26</v>
@@ -6484,13 +6421,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>274</v>
+        <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6500,17 +6437,17 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.63510991898</v>
+        <v>46188.63521115741</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46188.67901871528</v>
+        <v>46188.68062993056</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>188</v>
+        <v>272</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6522,10 +6459,10 @@
         <v>72</v>
       </c>
       <c r="I87" s="9">
-        <v>46224</v>
+        <v>46260</v>
       </c>
       <c r="J87" s="9">
-        <v>46224</v>
+        <v>46260</v>
       </c>
       <c r="K87" s="10" t="s">
         <v>26</v>
@@ -6537,33 +6474,43 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>274</v>
+        <v>173</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q87" s="10"/>
-      <c r="R87" s="10"/>
-      <c r="S87" s="10"/>
-      <c r="T87" s="10"/>
-      <c r="U87" s="10"/>
+        <v>273</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>46260</v>
+      </c>
+      <c r="R87" s="9">
+        <v>46260</v>
+      </c>
+      <c r="S87" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T87" s="10">
+        <v>0</v>
+      </c>
+      <c r="U87" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.63513603009</v>
+        <v>46188.63521795139</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46188.6792096875</v>
+        <v>46188.68070547454</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6575,10 +6522,10 @@
         <v>72</v>
       </c>
       <c r="I88" s="5">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="J88" s="5">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
@@ -6590,43 +6537,33 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>280</v>
+        <v>175</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q88" s="5">
-        <v>46258</v>
-      </c>
-      <c r="R88" s="5">
-        <v>46258</v>
-      </c>
-      <c r="S88" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="6"/>
+      <c r="T88" s="6"/>
+      <c r="U88" s="6"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.63514172454</v>
+        <v>46188.635222916666</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.679159583335</v>
+        <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6637,9 +6574,11 @@
       <c r="H89" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I89" s="10"/>
+      <c r="I89" s="9">
+        <v>46260</v>
+      </c>
       <c r="J89" s="9">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="K89" s="10" t="s">
         <v>26</v>
@@ -6651,13 +6590,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6667,31 +6606,27 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.63514853009</v>
+        <v>46188.635247199076</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.6791566551</v>
+        <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>188</v>
+        <v>278</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>72</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
       <c r="I90" s="6"/>
-      <c r="J90" s="5">
-        <v>46258</v>
-      </c>
+      <c r="J90" s="6"/>
       <c r="K90" s="6" t="s">
         <v>26</v>
       </c>
@@ -6699,16 +6634,16 @@
         <v>26</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O90" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="O90" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="P90" s="6" t="s">
-        <v>282</v>
+        <v>26</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6718,32 +6653,32 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.63521115741</v>
+        <v>46188.635250844905</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.68062993056</v>
+        <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>72</v>
+        <v>282</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>72</v>
+        <v>283</v>
       </c>
       <c r="I91" s="9">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="J91" s="9">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="K91" s="10" t="s">
         <v>26</v>
@@ -6755,22 +6690,22 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>186</v>
+        <v>284</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="Q91" s="9">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="R91" s="9">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
@@ -6781,32 +6716,32 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.63521795139</v>
+        <v>46188.63525673611</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46188.68070547454</v>
+        <v>46188.68080148148</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>72</v>
+        <v>282</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>72</v>
+        <v>283</v>
       </c>
       <c r="I92" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="J92" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>26</v>
@@ -6818,13 +6753,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6834,32 +6769,32 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.635222916666</v>
+        <v>46188.635261689815</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46188.680702488426</v>
+        <v>46188.680797928246</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>72</v>
+        <v>282</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>72</v>
+        <v>283</v>
       </c>
       <c r="I93" s="9">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="J93" s="9">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="K93" s="10" t="s">
         <v>26</v>
@@ -6871,13 +6806,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6887,27 +6822,33 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.635247199076</v>
+        <v>46188.635279375</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.67010366898</v>
+        <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
+        <v>72</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I94" s="5">
+        <v>46262</v>
+      </c>
+      <c r="J94" s="5">
+        <v>46262</v>
+      </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
       </c>
@@ -6915,51 +6856,59 @@
         <v>26</v>
       </c>
       <c r="M94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>46262</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46262</v>
+      </c>
+      <c r="S94" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="N94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+      <c r="U94" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.635250844905</v>
+        <v>46188.63528446759</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46188.68085204861</v>
+        <v>46188.68112704861</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>294</v>
+        <v>175</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>295</v>
+        <v>72</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="I95" s="9">
-        <v>46261</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I95" s="10"/>
       <c r="J95" s="9">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="K95" s="10" t="s">
         <v>26</v>
@@ -6971,58 +6920,46 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>297</v>
+        <v>175</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="Q95" s="9">
-        <v>46261</v>
-      </c>
-      <c r="R95" s="9">
-        <v>46261</v>
-      </c>
-      <c r="S95" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T95" s="10">
-        <v>0</v>
-      </c>
-      <c r="U95" s="11" t="s">
-        <v>81</v>
-      </c>
+      <c r="Q95" s="10"/>
+      <c r="R95" s="10"/>
+      <c r="S95" s="10"/>
+      <c r="T95" s="10"/>
+      <c r="U95" s="10"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.63525673611</v>
+        <v>46188.6352894213</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46188.68080148148</v>
+        <v>46188.68112425926</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>295</v>
+        <v>72</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="I96" s="5">
-        <v>46261</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I96" s="6"/>
       <c r="J96" s="5">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>26</v>
@@ -7034,13 +6971,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7050,32 +6987,32 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.635261689815</v>
+        <v>46188.63530922454</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.680797928246</v>
+        <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>188</v>
+        <v>295</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>295</v>
+        <v>205</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>296</v>
+        <v>206</v>
       </c>
       <c r="I97" s="9">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="J97" s="9">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="K97" s="10" t="s">
         <v>26</v>
@@ -7087,48 +7024,56 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q97" s="10"/>
-      <c r="R97" s="10"/>
-      <c r="S97" s="10"/>
-      <c r="T97" s="10"/>
-      <c r="U97" s="10"/>
+        <v>278</v>
+      </c>
+      <c r="Q97" s="9">
+        <v>46265</v>
+      </c>
+      <c r="R97" s="9">
+        <v>46265</v>
+      </c>
+      <c r="S97" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T97" s="10">
+        <v>0</v>
+      </c>
+      <c r="U97" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.635279375</v>
+        <v>46188.63531412037</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46188.68118097223</v>
+        <v>46188.681314560185</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>302</v>
+        <v>175</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="I98" s="5">
-        <v>46262</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="I98" s="6"/>
       <c r="J98" s="5">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>26</v>
@@ -7140,56 +7085,46 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q98" s="5">
-        <v>46262</v>
-      </c>
-      <c r="R98" s="5">
-        <v>46262</v>
-      </c>
-      <c r="S98" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="Q98" s="6"/>
+      <c r="R98" s="6"/>
+      <c r="S98" s="6"/>
+      <c r="T98" s="6"/>
+      <c r="U98" s="6"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.63528446759</v>
+        <v>46188.63532239583</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46188.68112704861</v>
+        <v>46188.68131152778</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>72</v>
+        <v>206</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="K99" s="10" t="s">
         <v>26</v>
@@ -7201,13 +7136,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7217,30 +7152,32 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.6352894213</v>
+        <v>46188.63538068287</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.68112425926</v>
+        <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>188</v>
+        <v>300</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="I100" s="6"/>
+        <v>206</v>
+      </c>
+      <c r="I100" s="5">
+        <v>46266</v>
+      </c>
       <c r="J100" s="5">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>26</v>
@@ -7252,48 +7189,58 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="6"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="6"/>
-      <c r="U100" s="6"/>
+        <v>301</v>
+      </c>
+      <c r="Q100" s="5">
+        <v>46266</v>
+      </c>
+      <c r="R100" s="5">
+        <v>46266</v>
+      </c>
+      <c r="S100" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T100" s="6">
+        <v>0</v>
+      </c>
+      <c r="U100" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.63530922454</v>
+        <v>46188.6353874537</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46188.68135644676</v>
+        <v>46188.68144886574</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>308</v>
+        <v>175</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I101" s="9">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="J101" s="9">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="K101" s="10" t="s">
         <v>26</v>
@@ -7305,56 +7252,48 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q101" s="9">
-        <v>46265</v>
-      </c>
-      <c r="R101" s="9">
-        <v>46265</v>
-      </c>
-      <c r="S101" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T101" s="10">
-        <v>0</v>
-      </c>
-      <c r="U101" s="11" t="s">
-        <v>81</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="Q101" s="10"/>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
+      <c r="T101" s="10"/>
+      <c r="U101" s="10"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.63531412037</v>
+        <v>46188.63539206018</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46188.681314560185</v>
+        <v>46188.681445636576</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I102" s="6"/>
+        <v>206</v>
+      </c>
+      <c r="I102" s="5">
+        <v>46266</v>
+      </c>
       <c r="J102" s="5">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>26</v>
@@ -7366,13 +7305,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7382,31 +7321,27 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.63532239583</v>
+        <v>46188.635410682866</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.68131152778</v>
+        <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>188</v>
+        <v>305</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>219</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="10"/>
       <c r="I103" s="10"/>
-      <c r="J103" s="9">
-        <v>46265</v>
-      </c>
+      <c r="J103" s="10"/>
       <c r="K103" s="10" t="s">
         <v>26</v>
       </c>
@@ -7414,16 +7349,16 @@
         <v>26</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>308</v>
+        <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>188</v>
+        <v>306</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>310</v>
+        <v>26</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7433,32 +7368,32 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.63538068287</v>
+        <v>46188.635413993055</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.68149567129</v>
+        <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>218</v>
+        <v>309</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>219</v>
+        <v>310</v>
       </c>
       <c r="I104" s="5">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="J104" s="5">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>26</v>
@@ -7470,22 +7405,22 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>186</v>
+        <v>300</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="Q104" s="5">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="R104" s="5">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
@@ -7496,32 +7431,32 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.6353874537</v>
+        <v>46188.63541944444</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.68144886574</v>
+        <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>188</v>
+        <v>312</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
       <c r="I105" s="9">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="J105" s="9">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="K105" s="10" t="s">
         <v>26</v>
@@ -7533,243 +7468,27 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="O105" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="O105" s="10" t="s">
-        <v>188</v>
-      </c>
       <c r="P105" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q105" s="10"/>
-      <c r="R105" s="10"/>
-      <c r="S105" s="10"/>
-      <c r="T105" s="10"/>
-      <c r="U105" s="10"/>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B106" s="5">
-        <v>46188.63539206018</v>
-      </c>
-      <c r="C106" s="6"/>
-      <c r="D106" s="5">
-        <v>46188.681445636576</v>
-      </c>
-      <c r="E106" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G106" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="I106" s="5">
-        <v>46266</v>
-      </c>
-      <c r="J106" s="5">
-        <v>46266</v>
-      </c>
-      <c r="K106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N106" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="O106" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="6"/>
-      <c r="S106" s="6"/>
-      <c r="T106" s="6"/>
-      <c r="U106" s="6"/>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A107" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="B107" s="9">
-        <v>46188.635410682866</v>
-      </c>
-      <c r="C107" s="10"/>
-      <c r="D107" s="9">
-        <v>46188.67123894676</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="F107" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="10"/>
-      <c r="I107" s="10"/>
-      <c r="J107" s="10"/>
-      <c r="K107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M107" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q105" s="9">
+        <v>46267</v>
+      </c>
+      <c r="R105" s="9">
+        <v>46275</v>
+      </c>
+      <c r="S105" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="T105" s="10">
         <v>0</v>
       </c>
-      <c r="N107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O107" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="P107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q107" s="10"/>
-      <c r="R107" s="10"/>
-      <c r="S107" s="10"/>
-      <c r="T107" s="10"/>
-      <c r="U107" s="10"/>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B108" s="5">
-        <v>46188.635413993055</v>
-      </c>
-      <c r="C108" s="6"/>
-      <c r="D108" s="5">
-        <v>46188.68161465278</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="I108" s="5">
-        <v>46267</v>
-      </c>
-      <c r="J108" s="5">
-        <v>46275</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N108" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q108" s="5">
-        <v>46267</v>
-      </c>
-      <c r="R108" s="5">
-        <v>46275</v>
-      </c>
-      <c r="S108" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T108" s="6">
-        <v>0</v>
-      </c>
-      <c r="U108" s="11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A109" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="B109" s="9">
-        <v>46188.63541944444</v>
-      </c>
-      <c r="C109" s="10"/>
-      <c r="D109" s="9">
-        <v>46188.920573842595</v>
-      </c>
-      <c r="E109" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="F109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G109" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="I109" s="9">
-        <v>46267</v>
-      </c>
-      <c r="J109" s="9">
-        <v>46275</v>
-      </c>
-      <c r="K109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N109" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="O109" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="P109" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="Q109" s="9">
-        <v>46267</v>
-      </c>
-      <c r="R109" s="9">
-        <v>46275</v>
-      </c>
-      <c r="S109" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="T109" s="10">
-        <v>0</v>
-      </c>
-      <c r="U109" s="11" t="s">
+      <c r="U105" s="11" t="s">
         <v>81</v>
       </c>
     </row>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -227,7 +227,7 @@
     <t>propuesta motor</t>
   </si>
   <si>
-    <t>Propuesta compras:,motor 4360</t>
+    <t>Propuesta compras:,motor ot 4360</t>
   </si>
   <si>
     <t>1215727723502427</t>
@@ -244,7 +244,7 @@
 </t>
   </si>
   <si>
-    <t>Propuesta compras:,Alabe 4360</t>
+    <t>Propuesta compras:,Alabe  ot 4360</t>
   </si>
   <si>
     <t>1215728035784425</t>
@@ -316,7 +316,7 @@
     <t>Reserva producción</t>
   </si>
   <si>
-    <t>motor 4360,Alabe 4360</t>
+    <t>motor ot 4360,Alabe  ot 4360</t>
   </si>
   <si>
     <t>Baja</t>
@@ -325,7 +325,7 @@
     <t>1215771707606683</t>
   </si>
   <si>
-    <t>motor 4360</t>
+    <t>motor ot 4360</t>
   </si>
   <si>
     <t>Reserva producción,Recepcionx motor</t>
@@ -334,7 +334,7 @@
     <t>1215771707606685</t>
   </si>
   <si>
-    <t>Alabe 4360</t>
+    <t>Alabe  ot 4360</t>
   </si>
   <si>
     <t>Reserva producción,Recepcionx Alabe</t>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46189.81491765047</v>
+        <v>46189.89213912037</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46189.8148409375</v>
+        <v>46189.89217115741</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="313">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -725,9 +725,6 @@
   </si>
   <si>
     <t>Recepcionx Alabe</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215727793148813</t>
@@ -5367,7 +5364,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46189.81484074074</v>
+        <v>46190.17849086806</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>229</v>
@@ -5411,8 +5408,8 @@
       <c r="R68" s="5">
         <v>46189</v>
       </c>
-      <c r="S68" s="12" t="s">
-        <v>230</v>
+      <c r="S68" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -5423,7 +5420,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
@@ -5433,7 +5430,7 @@
         <v>46189.81491748843</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5486,7 +5483,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5496,7 +5493,7 @@
         <v>46188.67789931713</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5529,7 +5526,7 @@
         <v>142</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5549,7 +5546,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5559,7 +5556,7 @@
         <v>46188.66851157407</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5583,7 +5580,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5596,7 +5593,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
@@ -5606,7 +5603,7 @@
         <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5633,13 +5630,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5659,7 +5656,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B73" s="9">
         <v>46188.63494034723</v>
@@ -5696,10 +5693,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5712,7 +5709,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B74" s="5">
         <v>46188.634945150465</v>
@@ -5749,10 +5746,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5765,7 +5762,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46188.634963668985</v>
@@ -5775,7 +5772,7 @@
         <v>46188.67832872685</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5802,13 +5799,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>173</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5828,7 +5825,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46188.63496887732</v>
@@ -5865,13 +5862,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5881,7 +5878,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B77" s="9">
         <v>46188.63498112268</v>
@@ -5918,13 +5915,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5934,7 +5931,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46188.635046296295</v>
@@ -5944,7 +5941,7 @@
         <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5971,13 +5968,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -5997,7 +5994,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46188.63505403935</v>
@@ -6034,13 +6031,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6050,7 +6047,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46188.63506813657</v>
@@ -6087,13 +6084,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6103,7 +6100,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46188.63509704861</v>
@@ -6113,7 +6110,7 @@
         <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6140,13 +6137,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>173</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6166,7 +6163,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46188.635102939814</v>
@@ -6203,13 +6200,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6219,7 +6216,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B83" s="9">
         <v>46188.63510991898</v>
@@ -6256,13 +6253,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6272,7 +6269,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B84" s="5">
         <v>46188.63513603009</v>
@@ -6282,7 +6279,7 @@
         <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6309,13 +6306,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6335,7 +6332,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B85" s="9">
         <v>46188.63514172454</v>
@@ -6370,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>175</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6386,7 +6383,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B86" s="5">
         <v>46188.63514853009</v>
@@ -6421,13 +6418,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6437,7 +6434,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B87" s="9">
         <v>46188.63521115741</v>
@@ -6447,7 +6444,7 @@
         <v>46188.68062993056</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6474,13 +6471,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>173</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q87" s="9">
         <v>46260</v>
@@ -6500,7 +6497,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46188.63521795139</v>
@@ -6537,13 +6534,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6553,7 +6550,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B89" s="9">
         <v>46188.635222916666</v>
@@ -6590,13 +6587,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>175</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6606,7 +6603,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B90" s="5">
         <v>46188.635247199076</v>
@@ -6616,7 +6613,7 @@
         <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6640,7 +6637,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6653,7 +6650,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B91" s="9">
         <v>46188.635250844905</v>
@@ -6663,16 +6660,16 @@
         <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="10" t="s">
+      <c r="H91" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="I91" s="9">
         <v>46261</v>
@@ -6690,13 +6687,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q91" s="9">
         <v>46261</v>
@@ -6716,7 +6713,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B92" s="5">
         <v>46188.63525673611</v>
@@ -6732,10 +6729,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>283</v>
       </c>
       <c r="I92" s="5">
         <v>46261</v>
@@ -6753,13 +6750,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6769,7 +6766,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B93" s="9">
         <v>46188.635261689815</v>
@@ -6785,10 +6782,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="I93" s="9">
         <v>46261</v>
@@ -6806,13 +6803,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>175</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6822,7 +6819,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B94" s="5">
         <v>46188.635279375</v>
@@ -6832,7 +6829,7 @@
         <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6859,13 +6856,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q94" s="5">
         <v>46262</v>
@@ -6885,7 +6882,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B95" s="9">
         <v>46188.63528446759</v>
@@ -6920,13 +6917,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>175</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6936,7 +6933,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B96" s="5">
         <v>46188.6352894213</v>
@@ -6971,13 +6968,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6987,7 +6984,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B97" s="9">
         <v>46188.63530922454</v>
@@ -6997,7 +6994,7 @@
         <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7024,13 +7021,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>173</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q97" s="9">
         <v>46265</v>
@@ -7050,7 +7047,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B98" s="5">
         <v>46188.63531412037</v>
@@ -7085,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7101,7 +7098,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B99" s="9">
         <v>46188.63532239583</v>
@@ -7136,13 +7133,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>175</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7152,7 +7149,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B100" s="5">
         <v>46188.63538068287</v>
@@ -7162,7 +7159,7 @@
         <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7189,13 +7186,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>173</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q100" s="5">
         <v>46266</v>
@@ -7215,7 +7212,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B101" s="9">
         <v>46188.6353874537</v>
@@ -7252,13 +7249,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>175</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7268,7 +7265,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46188.63539206018</v>
@@ -7305,13 +7302,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7321,7 +7318,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B103" s="9">
         <v>46188.635410682866</v>
@@ -7331,7 +7328,7 @@
         <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7355,7 +7352,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7368,7 +7365,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B104" s="5">
         <v>46188.635413993055</v>
@@ -7378,16 +7375,16 @@
         <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G104" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="F104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G104" s="6" t="s">
+      <c r="H104" s="6" t="s">
         <v>309</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>310</v>
       </c>
       <c r="I104" s="5">
         <v>46267</v>
@@ -7405,13 +7402,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q104" s="5">
         <v>46267</v>
@@ -7431,7 +7428,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
@@ -7441,7 +7438,7 @@
         <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7468,13 +7465,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q105" s="9">
         <v>46267</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -3917,7 +3917,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46188.9205047338</v>
+        <v>46192.1790090625</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -3917,7 +3917,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46192.1790090625</v>
+        <v>46193.184916238424</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -3961,8 +3961,8 @@
       <c r="R43" s="9">
         <v>46192</v>
       </c>
-      <c r="S43" s="7" t="s">
-        <v>94</v>
+      <c r="S43" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -3870,7 +3870,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46188.676957083335</v>
+        <v>46196.52482885416</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3915,9 +3915,11 @@
       <c r="B43" s="9">
         <v>46188.63458247685</v>
       </c>
-      <c r="C43" s="10"/>
+      <c r="C43" s="9">
+        <v>46196.52481820602</v>
+      </c>
       <c r="D43" s="9">
-        <v>46193.184916238424</v>
+        <v>46196.52483686343</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -3965,10 +3967,10 @@
         <v>32</v>
       </c>
       <c r="T43" s="10">
-        <v>0</v>
-      </c>
-      <c r="U43" s="12" t="s">
-        <v>74</v>
+        <v>1</v>
+      </c>
+      <c r="U43" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -3980,7 +3982,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46189.78047149305</v>
+        <v>46196.52483783565</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4030,8 +4032,8 @@
       <c r="T44" s="6">
         <v>0</v>
       </c>
-      <c r="U44" s="11" t="s">
-        <v>81</v>
+      <c r="U44" s="12" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="314">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Generación OC Rodete OT 4316,Fabricación Rodete OT 4316</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215728035819308</t>
@@ -2948,7 +2951,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46188.67380942129</v>
+        <v>46197.177845300925</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -2992,8 +2995,8 @@
       <c r="R26" s="5">
         <v>46204</v>
       </c>
-      <c r="S26" s="7" t="s">
-        <v>94</v>
+      <c r="S26" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -3004,7 +3007,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46188.634431805556</v>
@@ -3014,7 +3017,7 @@
         <v>46188.67377717592</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3047,7 +3050,7 @@
         <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3063,7 +3066,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3073,7 +3076,7 @@
         <v>46188.67377366898</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3103,10 +3106,10 @@
         <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3122,7 +3125,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3132,16 +3135,16 @@
         <v>46188.674114560185</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3162,7 +3165,7 @@
         <v>102</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>102</v>
@@ -3185,7 +3188,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3195,16 +3198,16 @@
         <v>46188.67407226852</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3222,13 +3225,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3244,7 +3247,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3254,16 +3257,16 @@
         <v>46188.6740696412</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3281,13 +3284,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3303,7 +3306,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3313,16 +3316,16 @@
         <v>46188.67423875</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3343,7 +3346,7 @@
         <v>102</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3366,7 +3369,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3382,10 +3385,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3403,13 +3406,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>83</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3419,7 +3422,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3429,16 +3432,16 @@
         <v>46188.674183877316</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3456,13 +3459,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3472,7 +3475,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3482,16 +3485,16 @@
         <v>46188.674703854165</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3512,7 +3515,7 @@
         <v>102</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3535,7 +3538,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3551,10 +3554,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3572,13 +3575,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>89</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3588,7 +3591,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3598,16 +3601,16 @@
         <v>46188.67434657407</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3625,13 +3628,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>90</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3641,7 +3644,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3651,16 +3654,16 @@
         <v>46188.674648472224</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3678,10 +3681,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3694,7 +3697,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3704,16 +3707,16 @@
         <v>46188.67687303241</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3734,7 +3737,7 @@
         <v>102</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3757,7 +3760,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3773,10 +3776,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3794,13 +3797,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3810,7 +3813,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3820,16 +3823,16 @@
         <v>46188.67683361111</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3847,13 +3850,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>87</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3863,7 +3866,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3873,7 +3876,7 @@
         <v>46196.52482885416</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3897,7 +3900,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3910,7 +3913,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -3922,16 +3925,16 @@
         <v>46196.52483686343</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -3949,13 +3952,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>54</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -3975,7 +3978,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -3985,16 +3988,16 @@
         <v>46196.52483783565</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4012,13 +4015,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4038,7 +4041,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4054,10 +4057,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4075,13 +4078,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4101,7 +4104,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4111,16 +4114,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4138,10 +4141,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4164,7 +4167,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4174,16 +4177,16 @@
         <v>46188.677066122684</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4201,13 +4204,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4217,7 +4220,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4227,16 +4230,16 @@
         <v>46188.67706284722</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4254,13 +4257,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4270,7 +4273,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4280,7 +4283,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4304,7 +4307,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4317,7 +4320,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4327,16 +4330,16 @@
         <v>46188.67723120371</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4354,13 +4357,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4380,7 +4383,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46188.634684942124</v>
@@ -4390,16 +4393,16 @@
         <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4417,13 +4420,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4443,7 +4446,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46188.634692962965</v>
@@ -4453,16 +4456,16 @@
         <v>46188.67722799769</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4480,13 +4483,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4506,7 +4509,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46188.63469954861</v>
@@ -4516,16 +4519,16 @@
         <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4543,13 +4546,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4569,7 +4572,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63470560186</v>
@@ -4579,16 +4582,16 @@
         <v>46188.677224942134</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4606,13 +4609,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4632,7 +4635,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46188.63471155093</v>
@@ -4642,16 +4645,16 @@
         <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4669,13 +4672,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4695,7 +4698,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46188.63471731481</v>
@@ -4705,7 +4708,7 @@
         <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4729,7 +4732,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4742,7 +4745,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46188.63472107639</v>
@@ -4752,16 +4755,16 @@
         <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4779,13 +4782,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4805,7 +4808,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63473258102</v>
@@ -4815,16 +4818,16 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4842,13 +4845,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4858,7 +4861,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B59" s="9">
         <v>46188.63474121528</v>
@@ -4868,16 +4871,16 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -4895,13 +4898,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4911,7 +4914,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63477284722</v>
@@ -4921,16 +4924,16 @@
         <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -4948,13 +4951,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -4974,7 +4977,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B61" s="9">
         <v>46188.63477877315</v>
@@ -4984,16 +4987,16 @@
         <v>46188.677545659724</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5011,13 +5014,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5027,7 +5030,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63478605324</v>
@@ -5037,16 +5040,16 @@
         <v>46188.67754284722</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5064,13 +5067,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5080,7 +5083,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46188.63485537037</v>
@@ -5090,16 +5093,16 @@
         <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5117,13 +5120,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5143,7 +5146,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46188.634861805556</v>
@@ -5153,16 +5156,16 @@
         <v>46188.677654756946</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5180,13 +5183,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5196,7 +5199,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B65" s="9">
         <v>46188.63486881944</v>
@@ -5206,16 +5209,16 @@
         <v>46188.67765203703</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5233,13 +5236,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5249,7 +5252,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63489331018</v>
@@ -5259,7 +5262,7 @@
         <v>46188.664478900464</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5283,7 +5286,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5296,7 +5299,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B67" s="9">
         <v>46188.634903391205</v>
@@ -5306,16 +5309,16 @@
         <v>46188.677911018516</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5333,13 +5336,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5359,7 +5362,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B68" s="5">
         <v>46188.6349100463</v>
@@ -5369,16 +5372,16 @@
         <v>46190.17849086806</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5396,13 +5399,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>99</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5422,7 +5425,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
@@ -5432,16 +5435,16 @@
         <v>46189.81491748843</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5459,13 +5462,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>96</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5485,7 +5488,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5495,16 +5498,16 @@
         <v>46188.67789931713</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5522,13 +5525,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5548,7 +5551,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5558,7 +5561,7 @@
         <v>46188.66851157407</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5582,7 +5585,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5595,7 +5598,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
@@ -5605,7 +5608,7 @@
         <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5632,13 +5635,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5658,7 +5661,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
         <v>46188.63494034723</v>
@@ -5668,7 +5671,7 @@
         <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5695,10 +5698,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5711,7 +5714,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46188.634945150465</v>
@@ -5721,7 +5724,7 @@
         <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5748,10 +5751,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5764,7 +5767,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
         <v>46188.634963668985</v>
@@ -5774,7 +5777,7 @@
         <v>46188.67832872685</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5801,13 +5804,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5827,7 +5830,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46188.63496887732</v>
@@ -5837,7 +5840,7 @@
         <v>46188.678293923615</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5864,13 +5867,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5880,7 +5883,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" s="9">
         <v>46188.63498112268</v>
@@ -5890,7 +5893,7 @@
         <v>46188.678290868054</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5917,13 +5920,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5933,7 +5936,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
         <v>46188.635046296295</v>
@@ -5943,7 +5946,7 @@
         <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5970,13 +5973,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -5996,7 +5999,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B79" s="9">
         <v>46188.63505403935</v>
@@ -6006,7 +6009,7 @@
         <v>46188.67891099537</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6033,13 +6036,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6049,7 +6052,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46188.63506813657</v>
@@ -6059,7 +6062,7 @@
         <v>46188.678908194444</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6086,13 +6089,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6102,7 +6105,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46188.63509704861</v>
@@ -6112,7 +6115,7 @@
         <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6139,13 +6142,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6165,7 +6168,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46188.635102939814</v>
@@ -6175,7 +6178,7 @@
         <v>46188.67902152777</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6202,13 +6205,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6218,7 +6221,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
         <v>46188.63510991898</v>
@@ -6228,7 +6231,7 @@
         <v>46188.67901871528</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6255,13 +6258,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6271,7 +6274,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B84" s="5">
         <v>46188.63513603009</v>
@@ -6281,7 +6284,7 @@
         <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6308,13 +6311,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6334,7 +6337,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B85" s="9">
         <v>46188.63514172454</v>
@@ -6344,7 +6347,7 @@
         <v>46188.679159583335</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6369,13 +6372,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6385,7 +6388,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46188.63514853009</v>
@@ -6395,7 +6398,7 @@
         <v>46188.6791566551</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6420,13 +6423,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6436,7 +6439,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B87" s="9">
         <v>46188.63521115741</v>
@@ -6446,7 +6449,7 @@
         <v>46188.68062993056</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6473,13 +6476,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="9">
         <v>46260</v>
@@ -6499,7 +6502,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46188.63521795139</v>
@@ -6509,7 +6512,7 @@
         <v>46188.68070547454</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6536,13 +6539,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6552,7 +6555,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="9">
         <v>46188.635222916666</v>
@@ -6562,7 +6565,7 @@
         <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6589,13 +6592,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6605,7 +6608,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46188.635247199076</v>
@@ -6615,7 +6618,7 @@
         <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6639,7 +6642,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6652,7 +6655,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
         <v>46188.635250844905</v>
@@ -6662,16 +6665,16 @@
         <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I91" s="9">
         <v>46261</v>
@@ -6689,13 +6692,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q91" s="9">
         <v>46261</v>
@@ -6715,7 +6718,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B92" s="5">
         <v>46188.63525673611</v>
@@ -6725,16 +6728,16 @@
         <v>46188.68080148148</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I92" s="5">
         <v>46261</v>
@@ -6752,13 +6755,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6768,7 +6771,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B93" s="9">
         <v>46188.635261689815</v>
@@ -6778,16 +6781,16 @@
         <v>46188.680797928246</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I93" s="9">
         <v>46261</v>
@@ -6805,13 +6808,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6821,7 +6824,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B94" s="5">
         <v>46188.635279375</v>
@@ -6831,7 +6834,7 @@
         <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6858,13 +6861,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q94" s="5">
         <v>46262</v>
@@ -6884,7 +6887,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B95" s="9">
         <v>46188.63528446759</v>
@@ -6894,7 +6897,7 @@
         <v>46188.68112704861</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6919,13 +6922,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6935,7 +6938,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B96" s="5">
         <v>46188.6352894213</v>
@@ -6945,7 +6948,7 @@
         <v>46188.68112425926</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6970,13 +6973,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -6986,7 +6989,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B97" s="9">
         <v>46188.63530922454</v>
@@ -6996,16 +6999,16 @@
         <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7023,13 +7026,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q97" s="9">
         <v>46265</v>
@@ -7049,7 +7052,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B98" s="5">
         <v>46188.63531412037</v>
@@ -7059,16 +7062,16 @@
         <v>46188.681314560185</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7084,13 +7087,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7100,7 +7103,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B99" s="9">
         <v>46188.63532239583</v>
@@ -7110,16 +7113,16 @@
         <v>46188.68131152778</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
@@ -7135,13 +7138,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7151,7 +7154,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
         <v>46188.63538068287</v>
@@ -7161,16 +7164,16 @@
         <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7188,13 +7191,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q100" s="5">
         <v>46266</v>
@@ -7214,7 +7217,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B101" s="9">
         <v>46188.6353874537</v>
@@ -7224,16 +7227,16 @@
         <v>46188.68144886574</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7251,13 +7254,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7267,7 +7270,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B102" s="5">
         <v>46188.63539206018</v>
@@ -7277,16 +7280,16 @@
         <v>46188.681445636576</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>
@@ -7304,13 +7307,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7320,7 +7323,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B103" s="9">
         <v>46188.635410682866</v>
@@ -7330,7 +7333,7 @@
         <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7354,7 +7357,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7367,7 +7370,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B104" s="5">
         <v>46188.635413993055</v>
@@ -7377,16 +7380,16 @@
         <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I104" s="5">
         <v>46267</v>
@@ -7404,13 +7407,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q104" s="5">
         <v>46267</v>
@@ -7430,7 +7433,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
@@ -7440,16 +7443,16 @@
         <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>
@@ -7467,13 +7470,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q105" s="9">
         <v>46267</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -259,286 +259,286 @@
     <t>Propuesta compras:,Generación OC Rodete OT 4316</t>
   </si>
   <si>
+    <t>1215728035784447</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser OT 43164360</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4360</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1215727831264658</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4360</t>
+  </si>
+  <si>
+    <t>1215727831264670</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215728035806401</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4360</t>
+  </si>
+  <si>
+    <t>1215771707606671</t>
+  </si>
+  <si>
+    <t>Reserva producción</t>
+  </si>
+  <si>
+    <t>motor ot 4360,Alabe  ot 4360</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1215771707606683</t>
+  </si>
+  <si>
+    <t>motor ot 4360</t>
+  </si>
+  <si>
+    <t>Reserva producción,Recepcionx motor</t>
+  </si>
+  <si>
+    <t>1215771707606685</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4360</t>
+  </si>
+  <si>
+    <t>Reserva producción,Recepcionx Alabe</t>
+  </si>
+  <si>
+    <t>1215727332551586</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4360,rodete OT 4360</t>
+  </si>
+  <si>
+    <t>1215728035819291</t>
+  </si>
+  <si>
+    <t>rodete OT 4360</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4316,Fabricación Rodete OT 4316</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1215728035819308</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4316</t>
+  </si>
+  <si>
+    <t>rodete OT 4360,Fabricación Rodete OT 4316</t>
+  </si>
+  <si>
+    <t>1215728035829709</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4316</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,rodete OT 4360</t>
+  </si>
+  <si>
+    <t>1215727723568477</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4360</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>1215727831363866</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>1215727831363886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4360,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215727831373407</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>1215727831373419</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>1215727723641751</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1215727723641768</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4360,Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t>1215727939764035</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4360,Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t>1215727939764052</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4360,Control de calidad fabricación externa  OT 4360,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215727939776448</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215727939776460</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215727792775028</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215727792775045</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1215727332551588</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215727939795692</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1215727939795714</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215728035784447</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser OT 43164360</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC materiales corte Laser OT 4360</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215727831264658</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4360</t>
-  </si>
-  <si>
-    <t>1215727831264670</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215728035806401</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4360</t>
-  </si>
-  <si>
-    <t>1215771707606671</t>
-  </si>
-  <si>
-    <t>Reserva producción</t>
-  </si>
-  <si>
-    <t>motor ot 4360,Alabe  ot 4360</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1215771707606683</t>
-  </si>
-  <si>
-    <t>motor ot 4360</t>
-  </si>
-  <si>
-    <t>Reserva producción,Recepcionx motor</t>
-  </si>
-  <si>
-    <t>1215771707606685</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4360</t>
-  </si>
-  <si>
-    <t>Reserva producción,Recepcionx Alabe</t>
-  </si>
-  <si>
-    <t>1215727332551586</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4360,rodete OT 4360</t>
-  </si>
-  <si>
-    <t>1215728035819291</t>
-  </si>
-  <si>
-    <t>rodete OT 4360</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4316,Fabricación Rodete OT 4316</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1215728035819308</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4316</t>
-  </si>
-  <si>
-    <t>rodete OT 4360,Fabricación Rodete OT 4316</t>
-  </si>
-  <si>
-    <t>1215728035829709</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4316</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,rodete OT 4360</t>
-  </si>
-  <si>
-    <t>1215727723568477</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4360</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>1215727831363866</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>1215727831363886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4360,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215727831373407</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>1215727831373419</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>1215727723641751</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1215727723641768</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4360,Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t>1215727939764035</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4360,Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t>1215727939764052</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4360,Control de calidad fabricación externa  OT 4360,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215727939776448</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215727939776460</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792775028</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792775045</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1215727332551588</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215727939795692</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1215727939795714</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
   </si>
   <si>
     <t>1215727792809496</t>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46188.921342905094</v>
+        <v>46197.58646723379</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2408,9 +2408,11 @@
       <c r="B17" s="9">
         <v>46188.63437929398</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="9">
+        <v>46197.58646039352</v>
+      </c>
       <c r="D17" s="9">
-        <v>46188.91976528935</v>
+        <v>46197.586479687496</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2458,15 +2460,15 @@
         <v>32</v>
       </c>
       <c r="T17" s="10">
-        <v>0</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>74</v>
+        <v>1</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46188.63438636574</v>
@@ -2476,16 +2478,16 @@
         <v>46188.673596319444</v>
       </c>
       <c r="E18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46211</v>
@@ -2506,10 +2508,10 @@
         <v>61</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46211</v>
@@ -2524,12 +2526,12 @@
         <v>0</v>
       </c>
       <c r="U18" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46188.634392708336</v>
@@ -2539,16 +2541,16 @@
         <v>46188.67359288194</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I19" s="9">
         <v>46211</v>
@@ -2569,10 +2571,10 @@
         <v>61</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="9">
         <v>46211</v>
@@ -2587,12 +2589,12 @@
         <v>0</v>
       </c>
       <c r="U19" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46188.63439828704</v>
@@ -2602,16 +2604,16 @@
         <v>46188.67358973379</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46211</v>
@@ -2632,10 +2634,10 @@
         <v>61</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46211</v>
@@ -2650,12 +2652,12 @@
         <v>0</v>
       </c>
       <c r="U20" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
         <v>46188.634403055556</v>
@@ -2665,16 +2667,16 @@
         <v>46188.673584675926</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="I21" s="9">
         <v>46211</v>
@@ -2695,10 +2697,10 @@
         <v>61</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="9">
         <v>46211</v>
@@ -2713,22 +2715,24 @@
         <v>0</v>
       </c>
       <c r="U21" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46189.78075929398</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5">
+        <v>46197.58662379629</v>
+      </c>
       <c r="D22" s="5">
-        <v>46189.814552916665</v>
+        <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2752,7 +2756,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2760,28 +2764,30 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="11" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U22" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46189.81187604167</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46197.586606770834</v>
+      </c>
       <c r="D23" s="9">
-        <v>46189.89213912037</v>
+        <v>46197.586624143514</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2808,13 +2814,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>64</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="9">
         <v>46183</v>
@@ -2826,25 +2832,27 @@
         <v>32</v>
       </c>
       <c r="T23" s="10">
-        <v>0</v>
-      </c>
-      <c r="U23" s="11" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46189.8120440162</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46197.58654909722</v>
+      </c>
       <c r="D24" s="5">
-        <v>46189.89217115741</v>
+        <v>46197.586567060185</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2871,13 +2879,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="5">
         <v>46183</v>
@@ -2889,15 +2897,15 @@
         <v>32</v>
       </c>
       <c r="T24" s="6">
-        <v>0</v>
-      </c>
-      <c r="U24" s="11" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U24" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25" s="9">
         <v>46188.634174861116</v>
@@ -2907,7 +2915,7 @@
         <v>46189.78281247686</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -2931,7 +2939,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -2944,7 +2952,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
@@ -2954,16 +2962,16 @@
         <v>46197.177845300925</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -2981,13 +2989,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q26" s="5">
         <v>46183</v>
@@ -2996,37 +3004,37 @@
         <v>46204</v>
       </c>
       <c r="S26" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46188.634431805556</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46188.67377717592</v>
+        <v>46197.586468877314</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>107</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3044,29 +3052,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3076,16 +3084,16 @@
         <v>46188.67377366898</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3103,29 +3111,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3135,16 +3143,16 @@
         <v>46188.674114560185</v>
       </c>
       <c r="E29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="10" t="s">
+      <c r="H29" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3162,13 +3170,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q29" s="9">
         <v>46213</v>
@@ -3177,18 +3185,18 @@
         <v>46225</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3198,16 +3206,16 @@
         <v>46188.67407226852</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3225,29 +3233,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3257,16 +3265,16 @@
         <v>46188.6740696412</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3284,29 +3292,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3316,16 +3324,16 @@
         <v>46188.67423875</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3343,10 +3351,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3358,18 +3366,18 @@
         <v>46225</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3379,16 +3387,16 @@
         <v>46188.674186689816</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3406,13 +3414,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3422,7 +3430,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3432,16 +3440,16 @@
         <v>46188.674183877316</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3459,13 +3467,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3475,7 +3483,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3485,16 +3493,16 @@
         <v>46188.674703854165</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3512,10 +3520,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3527,18 +3535,18 @@
         <v>46253</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3548,16 +3556,16 @@
         <v>46188.67435018519</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3575,13 +3583,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3591,7 +3599,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3601,16 +3609,16 @@
         <v>46188.67434657407</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3628,13 +3636,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3644,7 +3652,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3654,16 +3662,16 @@
         <v>46188.674648472224</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3681,10 +3689,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3697,7 +3705,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3707,16 +3715,16 @@
         <v>46188.67687303241</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3734,10 +3742,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3749,18 +3757,18 @@
         <v>46225</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3770,16 +3778,16 @@
         <v>46188.67683644676</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3797,13 +3805,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3813,7 +3821,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3823,16 +3831,16 @@
         <v>46188.67683361111</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3850,13 +3858,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3866,7 +3874,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3876,7 +3884,7 @@
         <v>46196.52482885416</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3900,7 +3908,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3913,7 +3921,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -3925,16 +3933,16 @@
         <v>46196.52483686343</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -3952,13 +3960,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>54</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -3978,7 +3986,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -3988,16 +3996,16 @@
         <v>46196.52483783565</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4015,13 +4023,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4030,13 +4038,13 @@
         <v>46209</v>
       </c>
       <c r="S44" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="12" t="s">
-        <v>74</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4051,16 +4059,16 @@
         <v>46188.67693108796</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4078,10 +4086,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>169</v>
@@ -4093,13 +4101,13 @@
         <v>46210</v>
       </c>
       <c r="S45" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4141,7 +4149,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>174</v>
@@ -4156,13 +4164,13 @@
         <v>46259</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4360,7 +4368,7 @@
         <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>187</v>
@@ -4372,13 +4380,13 @@
         <v>46227</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4399,10 +4407,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4435,13 +4443,13 @@
         <v>46231</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4486,7 +4494,7 @@
         <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>194</v>
@@ -4498,13 +4506,13 @@
         <v>46227</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4525,10 +4533,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4561,13 +4569,13 @@
         <v>46231</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4612,7 +4620,7 @@
         <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>199</v>
@@ -4624,13 +4632,13 @@
         <v>46227</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4651,10 +4659,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4687,13 +4695,13 @@
         <v>46231</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4797,13 +4805,13 @@
         <v>46234</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4966,13 +4974,13 @@
         <v>46241</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5099,10 +5107,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5135,13 +5143,13 @@
         <v>46244</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5162,10 +5170,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5215,10 +5223,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5339,7 +5347,7 @@
         <v>181</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>191</v>
@@ -5351,13 +5359,13 @@
         <v>46205</v>
       </c>
       <c r="S67" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5369,7 +5377,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46190.17849086806</v>
+        <v>46197.586557766204</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>230</v>
@@ -5402,7 +5410,7 @@
         <v>181</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>191</v>
@@ -5420,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>74</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5432,7 +5440,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46189.81491748843</v>
+        <v>46197.58661731481</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>232</v>
@@ -5465,7 +5473,7 @@
         <v>181</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>191</v>
@@ -5477,13 +5485,13 @@
         <v>46223</v>
       </c>
       <c r="S69" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>74</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5528,7 +5536,7 @@
         <v>181</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>235</v>
@@ -5540,13 +5548,13 @@
         <v>46254</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5558,7 +5566,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46188.66851157407</v>
+        <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>237</v>
@@ -5650,13 +5658,13 @@
         <v>46251</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5772,9 +5780,11 @@
       <c r="B75" s="9">
         <v>46188.634963668985</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="9">
+        <v>46197.58704829861</v>
+      </c>
       <c r="D75" s="9">
-        <v>46188.67832872685</v>
+        <v>46197.58706070602</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>246</v>
@@ -5819,13 +5829,13 @@
         <v>46252</v>
       </c>
       <c r="S75" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T75" s="10">
-        <v>0</v>
-      </c>
-      <c r="U75" s="11" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U75" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -5835,9 +5845,11 @@
       <c r="B76" s="5">
         <v>46188.63496887732</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46197.58695519676</v>
+      </c>
       <c r="D76" s="5">
-        <v>46188.678293923615</v>
+        <v>46197.586956666666</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>176</v>
@@ -5888,9 +5900,11 @@
       <c r="B77" s="9">
         <v>46188.63498112268</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="9">
+        <v>46197.587035335644</v>
+      </c>
       <c r="D77" s="9">
-        <v>46188.678290868054</v>
+        <v>46197.587036770834</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>176</v>
@@ -5988,13 +6002,13 @@
         <v>46253</v>
       </c>
       <c r="S78" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6006,7 +6020,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46188.67891099537</v>
+        <v>46197.586961747686</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>176</v>
@@ -6059,7 +6073,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46188.678908194444</v>
+        <v>46197.58704049769</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>176</v>
@@ -6157,13 +6171,13 @@
         <v>46224</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6326,13 +6340,13 @@
         <v>46258</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6491,13 +6505,13 @@
         <v>46260</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6707,13 +6721,13 @@
         <v>46261</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6876,13 +6890,13 @@
         <v>46262</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7041,13 +7055,13 @@
         <v>46265</v>
       </c>
       <c r="S97" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7206,13 +7220,13 @@
         <v>46266</v>
       </c>
       <c r="S100" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7422,13 +7436,13 @@
         <v>46275</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7485,13 +7499,13 @@
         <v>46275</v>
       </c>
       <c r="S105" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -1603,13 +1603,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46188.634159629626</v>
+        <v>46188.46749296296</v>
       </c>
       <c r="C4" s="5">
-        <v>46188.91968755787</v>
+        <v>46188.75302089121</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.91970172454</v>
+        <v>46188.753035057875</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1656,13 +1656,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46188.634310856476</v>
+        <v>46188.46764418982</v>
       </c>
       <c r="C5" s="9">
-        <v>46188.919674178236</v>
+        <v>46188.75300751158</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.91968832176</v>
+        <v>46188.753021655095</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1721,13 +1721,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46188.63431648148</v>
+        <v>46188.46764981482</v>
       </c>
       <c r="C6" s="5">
-        <v>46188.919543298616</v>
+        <v>46188.752876631945</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.91956144676</v>
+        <v>46188.75289478009</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1786,13 +1786,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="9">
-        <v>46188.63432182871</v>
+        <v>46188.467655162036</v>
       </c>
       <c r="C7" s="9">
-        <v>46188.91959428241</v>
+        <v>46188.752927615744</v>
       </c>
       <c r="D7" s="9">
-        <v>46188.9196094213</v>
+        <v>46188.752942754625</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>36</v>
@@ -1851,13 +1851,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46188.634326643514</v>
+        <v>46188.46765997686</v>
       </c>
       <c r="C8" s="5">
-        <v>46188.919635115744</v>
+        <v>46188.75296844907</v>
       </c>
       <c r="D8" s="5">
-        <v>46188.91965210648</v>
+        <v>46188.752985439816</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1916,13 +1916,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46188.634165474534</v>
+        <v>46188.46749880787</v>
       </c>
       <c r="C9" s="9">
-        <v>46188.92057981482</v>
+        <v>46188.753913148146</v>
       </c>
       <c r="D9" s="9">
-        <v>46188.92059026621</v>
+        <v>46188.753923599535</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -1969,13 +1969,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46188.63433173611</v>
+        <v>46188.467665069446</v>
       </c>
       <c r="C10" s="5">
-        <v>46188.920111388885</v>
+        <v>46188.75344472222</v>
       </c>
       <c r="D10" s="5">
-        <v>46188.920113182874</v>
+        <v>46188.7534465162</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2034,13 +2034,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46188.63434310185</v>
+        <v>46188.46767643519</v>
       </c>
       <c r="C11" s="9">
-        <v>46188.91974537037</v>
+        <v>46188.7530787037</v>
       </c>
       <c r="D11" s="9">
-        <v>46188.92032122685</v>
+        <v>46188.75365456019</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2099,13 +2099,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46188.63435032408</v>
+        <v>46188.46768365741</v>
       </c>
       <c r="C12" s="5">
-        <v>46188.92048497685</v>
+        <v>46188.753818310186</v>
       </c>
       <c r="D12" s="5">
-        <v>46188.92050125</v>
+        <v>46188.75383458333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2164,13 +2164,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="9">
-        <v>46188.634356759256</v>
+        <v>46188.46769009259</v>
       </c>
       <c r="C13" s="9">
-        <v>46188.920564201384</v>
+        <v>46188.75389753473</v>
       </c>
       <c r="D13" s="9">
-        <v>46188.92057991898</v>
+        <v>46188.753913252316</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2229,11 +2229,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46188.634170000005</v>
+        <v>46188.46750333333</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.58646723379</v>
+        <v>46197.41980056713</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2276,13 +2276,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46188.63436615741</v>
+        <v>46188.46769949074</v>
       </c>
       <c r="C15" s="9">
-        <v>46188.92065792824</v>
+        <v>46188.753991261576</v>
       </c>
       <c r="D15" s="9">
-        <v>46189.814397685186</v>
+        <v>46189.647731018515</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2341,13 +2341,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46188.63437259259</v>
+        <v>46188.46770592593</v>
       </c>
       <c r="C16" s="5">
-        <v>46188.9213359375</v>
+        <v>46188.754669270835</v>
       </c>
       <c r="D16" s="5">
-        <v>46189.814421944444</v>
+        <v>46189.64775527778</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2406,13 +2406,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46188.63437929398</v>
+        <v>46188.467712627316</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.58646039352</v>
+        <v>46197.41979372685</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.586479687496</v>
+        <v>46197.41981302084</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2471,11 +2471,11 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46188.63438636574</v>
+        <v>46188.467719699074</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46188.673596319444</v>
+        <v>46188.50692965278</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2534,11 +2534,11 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46188.634392708336</v>
+        <v>46188.467726041665</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46188.67359288194</v>
+        <v>46188.50692621528</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2597,11 +2597,11 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46188.63439828704</v>
+        <v>46188.467731620374</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46188.67358973379</v>
+        <v>46188.50692306713</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2660,11 +2660,11 @@
         <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46188.634403055556</v>
+        <v>46188.46773638889</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46188.673584675926</v>
+        <v>46188.506918009254</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2723,13 +2723,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46189.78075929398</v>
+        <v>46189.614092627315</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.58662379629</v>
+        <v>46197.419957129634</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.58663670139</v>
+        <v>46197.41997003472</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2778,13 +2778,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46189.81187604167</v>
+        <v>46189.645209375</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.586606770834</v>
+        <v>46197.41994010417</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.586624143514</v>
+        <v>46197.41995747686</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -2843,13 +2843,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46189.8120440162</v>
+        <v>46189.64537734954</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.58654909722</v>
+        <v>46197.41988243056</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.586567060185</v>
+        <v>46197.41990039352</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2908,11 +2908,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.634174861116</v>
+        <v>46188.467508194444</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46189.78281247686</v>
+        <v>46189.616145810185</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -2955,11 +2955,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46188.63442598379</v>
+        <v>46188.46775931713</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.177845300925</v>
+        <v>46197.01117863426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -3018,11 +3018,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46188.634431805556</v>
+        <v>46188.46776513889</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.586468877314</v>
+        <v>46197.41980221064</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3077,11 +3077,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46188.63443740741</v>
+        <v>46188.46777074074</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46188.67377366898</v>
+        <v>46188.50710700231</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3136,11 +3136,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.63451584491</v>
+        <v>46188.46784917824</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46188.674114560185</v>
+        <v>46188.50744789352</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3199,11 +3199,11 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.63452219908</v>
+        <v>46188.467855532406</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.67407226852</v>
+        <v>46188.50740560185</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3258,11 +3258,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.634528194445</v>
+        <v>46188.46786152778</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46188.6740696412</v>
+        <v>46188.50740297454</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3317,11 +3317,11 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.63453408565</v>
+        <v>46188.46786741898</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46188.67423875</v>
+        <v>46188.507572083334</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3380,11 +3380,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.634538252314</v>
+        <v>46188.46787158565</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46188.674186689816</v>
+        <v>46188.50752002315</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>83</v>
@@ -3433,11 +3433,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.63454329861</v>
+        <v>46188.46787663194</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46188.674183877316</v>
+        <v>46188.507517210644</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3486,11 +3486,11 @@
         <v>134</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.63454804398</v>
+        <v>46188.46788137731</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46188.674703854165</v>
+        <v>46188.5080371875</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>135</v>
@@ -3549,11 +3549,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.63455278936</v>
+        <v>46188.467886122686</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46188.67435018519</v>
+        <v>46188.50768351852</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>89</v>
@@ -3602,11 +3602,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.63455811342</v>
+        <v>46188.46789144676</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46188.67434657407</v>
+        <v>46188.50767990741</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3655,11 +3655,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.63456381945</v>
+        <v>46188.467897152776</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46188.674648472224</v>
+        <v>46188.50798180555</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3708,11 +3708,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.63456738426</v>
+        <v>46188.46790071759</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46188.67687303241</v>
+        <v>46188.51020636574</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3771,11 +3771,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.63457166667</v>
+        <v>46188.467905</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46188.67683644676</v>
+        <v>46188.51016978009</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>86</v>
@@ -3824,11 +3824,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.634576701385</v>
+        <v>46188.46791003473</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46188.67683361111</v>
+        <v>46188.51016694444</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -3877,11 +3877,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.63417921297</v>
+        <v>46188.467512546296</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.52482885416</v>
+        <v>46196.3581621875</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3924,13 +3924,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.63458247685</v>
+        <v>46188.467915810186</v>
       </c>
       <c r="C43" s="9">
-        <v>46196.52481820602</v>
+        <v>46196.35815153935</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.52483686343</v>
+        <v>46196.35817019676</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -3989,11 +3989,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.634588587964</v>
+        <v>46188.4679219213</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46196.52483783565</v>
+        <v>46196.35817116898</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4052,11 +4052,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.63459497685</v>
+        <v>46188.46792831019</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46188.67693108796</v>
+        <v>46188.5102644213</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4115,11 +4115,11 @@
         <v>170</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.63460983796</v>
+        <v>46188.4679431713</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.677102754635</v>
+        <v>46188.51043608796</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4178,11 +4178,11 @@
         <v>175</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.634613946764</v>
+        <v>46188.46794728009</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46188.677066122684</v>
+        <v>46188.51039945602</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>176</v>
@@ -4231,11 +4231,11 @@
         <v>179</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.63461840278</v>
+        <v>46188.46795173611</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46188.67706284722</v>
+        <v>46188.51039618056</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4284,11 +4284,11 @@
         <v>180</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.63467295139</v>
+        <v>46188.46800628472</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.660341678245</v>
+        <v>46188.493675011574</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>181</v>
@@ -4331,11 +4331,11 @@
         <v>183</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.63467763889</v>
+        <v>46188.468010972225</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46188.67723120371</v>
+        <v>46188.510564537035</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4394,11 +4394,11 @@
         <v>188</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.634684942124</v>
+        <v>46188.46801827547</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.67731989583</v>
+        <v>46188.51065322917</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>189</v>
@@ -4457,11 +4457,11 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.634692962965</v>
+        <v>46188.468026296294</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46188.67722799769</v>
+        <v>46188.510561331015</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4520,11 +4520,11 @@
         <v>195</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.63469954861</v>
+        <v>46188.468032881945</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.67731701389</v>
+        <v>46188.51065034722</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>196</v>
@@ -4583,11 +4583,11 @@
         <v>197</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.63470560186</v>
+        <v>46188.468038935185</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46188.677224942134</v>
+        <v>46188.51055827546</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>198</v>
@@ -4646,11 +4646,11 @@
         <v>200</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.63471155093</v>
+        <v>46188.468044884256</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.67731351852</v>
+        <v>46188.51064685185</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>199</v>
@@ -4709,11 +4709,11 @@
         <v>201</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.63471731481</v>
+        <v>46188.46805064815</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.662660393515</v>
+        <v>46188.49599372685</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>202</v>
@@ -4756,11 +4756,11 @@
         <v>204</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.63472107639</v>
+        <v>46188.46805440972</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.677743113425</v>
+        <v>46188.51107644676</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>205</v>
@@ -4819,11 +4819,11 @@
         <v>208</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.63473258102</v>
+        <v>46188.46806591435</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.677464444445</v>
+        <v>46188.51079777778</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>176</v>
@@ -4872,11 +4872,11 @@
         <v>211</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.63474121528</v>
+        <v>46188.46807454861</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.677461087966</v>
+        <v>46188.510794421294</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>176</v>
@@ -4925,11 +4925,11 @@
         <v>214</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.63477284722</v>
+        <v>46188.46810618056</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.67773935186</v>
+        <v>46188.511072685185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>215</v>
@@ -4988,11 +4988,11 @@
         <v>216</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.63477877315</v>
+        <v>46188.46811210648</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46188.677545659724</v>
+        <v>46188.51087899305</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>176</v>
@@ -5041,11 +5041,11 @@
         <v>219</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.63478605324</v>
+        <v>46188.46811938657</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46188.67754284722</v>
+        <v>46188.51087618056</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>176</v>
@@ -5094,11 +5094,11 @@
         <v>220</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.63485537037</v>
+        <v>46188.4681887037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.67780341435</v>
+        <v>46188.511136747686</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>221</v>
@@ -5157,11 +5157,11 @@
         <v>222</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.634861805556</v>
+        <v>46188.46819513889</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46188.677654756946</v>
+        <v>46188.510988090275</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>176</v>
@@ -5210,11 +5210,11 @@
         <v>224</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.63486881944</v>
+        <v>46188.46820215278</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46188.67765203703</v>
+        <v>46188.51098537037</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>176</v>
@@ -5263,11 +5263,11 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.63489331018</v>
+        <v>46188.46822664352</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46188.664478900464</v>
+        <v>46188.49781223379</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>181</v>
@@ -5310,11 +5310,11 @@
         <v>227</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.634903391205</v>
+        <v>46188.46823672454</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46188.677911018516</v>
+        <v>46188.51124435185</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>228</v>
@@ -5373,11 +5373,11 @@
         <v>229</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.6349100463</v>
+        <v>46188.468243379626</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.586557766204</v>
+        <v>46197.41989109953</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>230</v>
@@ -5436,11 +5436,11 @@
         <v>231</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.6349165162</v>
+        <v>46188.46824984954</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.58661731481</v>
+        <v>46197.41995064815</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>232</v>
@@ -5499,11 +5499,11 @@
         <v>233</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.634922916666</v>
+        <v>46188.468256249995</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46188.67789931713</v>
+        <v>46188.51123265046</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>234</v>
@@ -5562,11 +5562,11 @@
         <v>236</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.63492795139</v>
+        <v>46188.468261284725</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.58705803241</v>
+        <v>46197.42039136574</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>237</v>
@@ -5609,11 +5609,11 @@
         <v>239</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.63493152778</v>
+        <v>46188.46826486111</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.67802387731</v>
+        <v>46188.51135721065</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>240</v>
@@ -5672,11 +5672,11 @@
         <v>242</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.63494034723</v>
+        <v>46188.468273680555</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.677983657406</v>
+        <v>46188.51131699074</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>176</v>
@@ -5725,11 +5725,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.634945150465</v>
+        <v>46188.46827848379</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.677980567125</v>
+        <v>46188.51131390047</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>176</v>
@@ -5778,13 +5778,13 @@
         <v>245</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.634963668985</v>
+        <v>46188.46829700231</v>
       </c>
       <c r="C75" s="9">
-        <v>46197.58704829861</v>
+        <v>46197.42038163195</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.58706070602</v>
+        <v>46197.42039403935</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>246</v>
@@ -5843,13 +5843,13 @@
         <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.63496887732</v>
+        <v>46188.46830221065</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.58695519676</v>
+        <v>46197.42028853009</v>
       </c>
       <c r="D76" s="5">
-        <v>46197.586956666666</v>
+        <v>46197.420289999995</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>176</v>
@@ -5898,13 +5898,13 @@
         <v>250</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.63498112268</v>
+        <v>46188.46831445602</v>
       </c>
       <c r="C77" s="9">
-        <v>46197.587035335644</v>
+        <v>46197.42036866898</v>
       </c>
       <c r="D77" s="9">
-        <v>46197.587036770834</v>
+        <v>46197.42037010417</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>176</v>
@@ -5953,11 +5953,11 @@
         <v>252</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.635046296295</v>
+        <v>46188.46837962963</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.67895050926</v>
+        <v>46188.51228384259</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>253</v>
@@ -6016,11 +6016,11 @@
         <v>254</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.63505403935</v>
+        <v>46188.46838737269</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.586961747686</v>
+        <v>46197.420295081014</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>176</v>
@@ -6069,11 +6069,11 @@
         <v>256</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.63506813657</v>
+        <v>46188.46840146991</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46197.58704049769</v>
+        <v>46197.42037383102</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>176</v>
@@ -6122,11 +6122,11 @@
         <v>258</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.63509704861</v>
+        <v>46188.468430381945</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.67906003472</v>
+        <v>46188.51239336806</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>259</v>
@@ -6185,11 +6185,11 @@
         <v>260</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.635102939814</v>
+        <v>46188.46843627315</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46188.67902152777</v>
+        <v>46188.512354861115</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>176</v>
@@ -6238,11 +6238,11 @@
         <v>263</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.63510991898</v>
+        <v>46188.46844325231</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46188.67901871528</v>
+        <v>46188.51235204861</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>176</v>
@@ -6291,11 +6291,11 @@
         <v>265</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.63513603009</v>
+        <v>46188.468469363426</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.6792096875</v>
+        <v>46188.51254302083</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>266</v>
@@ -6354,11 +6354,11 @@
         <v>268</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.63514172454</v>
+        <v>46188.468475057874</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46188.679159583335</v>
+        <v>46188.51249291666</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>177</v>
@@ -6405,11 +6405,11 @@
         <v>270</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.63514853009</v>
+        <v>46188.46848186343</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46188.6791566551</v>
+        <v>46188.512489988425</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>176</v>
@@ -6456,11 +6456,11 @@
         <v>271</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.63521115741</v>
+        <v>46188.46854449074</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46188.68062993056</v>
+        <v>46188.51396326389</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>272</v>
@@ -6519,11 +6519,11 @@
         <v>274</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.63521795139</v>
+        <v>46188.46855128472</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46188.68070547454</v>
+        <v>46188.51403880787</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>176</v>
@@ -6572,11 +6572,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.635222916666</v>
+        <v>46188.46855625</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.680702488426</v>
+        <v>46188.51403582176</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>176</v>
@@ -6625,11 +6625,11 @@
         <v>277</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.635247199076</v>
+        <v>46188.46858053241</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.67010366898</v>
+        <v>46188.50343700231</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>278</v>
@@ -6672,11 +6672,11 @@
         <v>280</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.635250844905</v>
+        <v>46188.46858417824</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.68085204861</v>
+        <v>46188.514185381944</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>281</v>
@@ -6735,11 +6735,11 @@
         <v>285</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.63525673611</v>
+        <v>46188.468590069446</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46188.68080148148</v>
+        <v>46188.51413481482</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>176</v>
@@ -6788,11 +6788,11 @@
         <v>287</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.635261689815</v>
+        <v>46188.46859502315</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46188.680797928246</v>
+        <v>46188.514131261574</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>176</v>
@@ -6841,11 +6841,11 @@
         <v>288</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.635279375</v>
+        <v>46188.46861270833</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.68118097223</v>
+        <v>46188.514514305556</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>289</v>
@@ -6904,11 +6904,11 @@
         <v>290</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.63528446759</v>
+        <v>46188.46861780093</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46188.68112704861</v>
+        <v>46188.51446038194</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>176</v>
@@ -6955,11 +6955,11 @@
         <v>292</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.6352894213</v>
+        <v>46188.46862275463</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46188.68112425926</v>
+        <v>46188.514457592595</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>176</v>
@@ -7006,11 +7006,11 @@
         <v>294</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.63530922454</v>
+        <v>46188.46864255787</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.68135644676</v>
+        <v>46188.51468978009</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>295</v>
@@ -7069,11 +7069,11 @@
         <v>296</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.63531412037</v>
+        <v>46188.4686474537</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46188.681314560185</v>
+        <v>46188.51464789352</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>176</v>
@@ -7120,11 +7120,11 @@
         <v>298</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.63532239583</v>
+        <v>46188.46865572917</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46188.68131152778</v>
+        <v>46188.51464486111</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>176</v>
@@ -7171,11 +7171,11 @@
         <v>299</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.63538068287</v>
+        <v>46188.4687140162</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.68149567129</v>
+        <v>46188.514829004635</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>300</v>
@@ -7234,11 +7234,11 @@
         <v>302</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.6353874537</v>
+        <v>46188.46872078704</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46188.68144886574</v>
+        <v>46188.514782199076</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>176</v>
@@ -7287,11 +7287,11 @@
         <v>303</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.63539206018</v>
+        <v>46188.46872539352</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46188.681445636576</v>
+        <v>46188.51477896991</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>176</v>
@@ -7340,11 +7340,11 @@
         <v>304</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.635410682866</v>
+        <v>46188.46874401621</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.67123894676</v>
+        <v>46188.50457228009</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>305</v>
@@ -7387,11 +7387,11 @@
         <v>307</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.635413993055</v>
+        <v>46188.46874732639</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.68161465278</v>
+        <v>46188.514947986114</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>308</v>
@@ -7450,11 +7450,11 @@
         <v>311</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.63541944444</v>
+        <v>46188.46875277778</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.920573842595</v>
+        <v>46188.753907175924</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>312</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="316">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -520,28 +520,34 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1215727939795714</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215727792809496</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1215727939795714</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215727792809496</t>
   </si>
   <si>
     <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 43164360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
@@ -1603,13 +1609,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46188.46749296296</v>
+        <v>46188.634159629626</v>
       </c>
       <c r="C4" s="5">
-        <v>46188.75302089121</v>
+        <v>46188.91968755787</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.753035057875</v>
+        <v>46188.91970172454</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1656,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46188.46764418982</v>
+        <v>46188.634310856476</v>
       </c>
       <c r="C5" s="9">
-        <v>46188.75300751158</v>
+        <v>46188.919674178236</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.753021655095</v>
+        <v>46188.91968832176</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1721,13 +1727,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46188.46764981482</v>
+        <v>46188.63431648148</v>
       </c>
       <c r="C6" s="5">
-        <v>46188.752876631945</v>
+        <v>46188.919543298616</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.75289478009</v>
+        <v>46188.91956144676</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1786,13 +1792,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="9">
-        <v>46188.467655162036</v>
+        <v>46188.63432182871</v>
       </c>
       <c r="C7" s="9">
-        <v>46188.752927615744</v>
+        <v>46188.91959428241</v>
       </c>
       <c r="D7" s="9">
-        <v>46188.752942754625</v>
+        <v>46188.9196094213</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>36</v>
@@ -1851,13 +1857,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46188.46765997686</v>
+        <v>46188.634326643514</v>
       </c>
       <c r="C8" s="5">
-        <v>46188.75296844907</v>
+        <v>46188.919635115744</v>
       </c>
       <c r="D8" s="5">
-        <v>46188.752985439816</v>
+        <v>46188.91965210648</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1916,13 +1922,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46188.46749880787</v>
+        <v>46188.634165474534</v>
       </c>
       <c r="C9" s="9">
-        <v>46188.753913148146</v>
+        <v>46188.92057981482</v>
       </c>
       <c r="D9" s="9">
-        <v>46188.753923599535</v>
+        <v>46188.92059026621</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -1969,13 +1975,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46188.467665069446</v>
+        <v>46188.63433173611</v>
       </c>
       <c r="C10" s="5">
-        <v>46188.75344472222</v>
+        <v>46188.920111388885</v>
       </c>
       <c r="D10" s="5">
-        <v>46188.7534465162</v>
+        <v>46188.920113182874</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2034,13 +2040,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46188.46767643519</v>
+        <v>46188.63434310185</v>
       </c>
       <c r="C11" s="9">
-        <v>46188.7530787037</v>
+        <v>46188.91974537037</v>
       </c>
       <c r="D11" s="9">
-        <v>46188.75365456019</v>
+        <v>46188.92032122685</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2099,13 +2105,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46188.46768365741</v>
+        <v>46188.63435032408</v>
       </c>
       <c r="C12" s="5">
-        <v>46188.753818310186</v>
+        <v>46188.92048497685</v>
       </c>
       <c r="D12" s="5">
-        <v>46188.75383458333</v>
+        <v>46188.92050125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2164,13 +2170,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="9">
-        <v>46188.46769009259</v>
+        <v>46188.634356759256</v>
       </c>
       <c r="C13" s="9">
-        <v>46188.75389753473</v>
+        <v>46188.920564201384</v>
       </c>
       <c r="D13" s="9">
-        <v>46188.753913252316</v>
+        <v>46188.92057991898</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2229,11 +2235,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46188.46750333333</v>
+        <v>46188.634170000005</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.41980056713</v>
+        <v>46197.58646723379</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2276,13 +2282,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46188.46769949074</v>
+        <v>46188.63436615741</v>
       </c>
       <c r="C15" s="9">
-        <v>46188.753991261576</v>
+        <v>46188.92065792824</v>
       </c>
       <c r="D15" s="9">
-        <v>46189.647731018515</v>
+        <v>46189.814397685186</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2341,13 +2347,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46188.46770592593</v>
+        <v>46188.63437259259</v>
       </c>
       <c r="C16" s="5">
-        <v>46188.754669270835</v>
+        <v>46188.9213359375</v>
       </c>
       <c r="D16" s="5">
-        <v>46189.64775527778</v>
+        <v>46189.814421944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2406,13 +2412,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46188.467712627316</v>
+        <v>46188.63437929398</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.41979372685</v>
+        <v>46197.58646039352</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.41981302084</v>
+        <v>46197.586479687496</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2471,11 +2477,11 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46188.467719699074</v>
+        <v>46188.63438636574</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46188.50692965278</v>
+        <v>46188.673596319444</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2534,11 +2540,11 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46188.467726041665</v>
+        <v>46188.634392708336</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46188.50692621528</v>
+        <v>46188.67359288194</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2597,11 +2603,11 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46188.467731620374</v>
+        <v>46188.63439828704</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46188.50692306713</v>
+        <v>46188.67358973379</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2660,11 +2666,11 @@
         <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46188.46773638889</v>
+        <v>46188.634403055556</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46188.506918009254</v>
+        <v>46188.673584675926</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2723,13 +2729,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46189.614092627315</v>
+        <v>46189.78075929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.419957129634</v>
+        <v>46197.58662379629</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.41997003472</v>
+        <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2778,13 +2784,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46189.645209375</v>
+        <v>46189.81187604167</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.41994010417</v>
+        <v>46197.586606770834</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.41995747686</v>
+        <v>46197.586624143514</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -2843,13 +2849,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46189.64537734954</v>
+        <v>46189.8120440162</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.41988243056</v>
+        <v>46197.58654909722</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.41990039352</v>
+        <v>46197.586567060185</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2908,11 +2914,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.467508194444</v>
+        <v>46188.634174861116</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46189.616145810185</v>
+        <v>46189.78281247686</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -2955,11 +2961,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46188.46775931713</v>
+        <v>46188.63442598379</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.01117863426</v>
+        <v>46197.177845300925</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -3018,11 +3024,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46188.46776513889</v>
+        <v>46188.634431805556</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.41980221064</v>
+        <v>46197.586468877314</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3077,11 +3083,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46188.46777074074</v>
+        <v>46188.63443740741</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46188.50710700231</v>
+        <v>46188.67377366898</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3136,11 +3142,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.46784917824</v>
+        <v>46188.63451584491</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46188.50744789352</v>
+        <v>46188.674114560185</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3199,11 +3205,11 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.467855532406</v>
+        <v>46188.63452219908</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.50740560185</v>
+        <v>46188.67407226852</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3258,11 +3264,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.46786152778</v>
+        <v>46188.634528194445</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46188.50740297454</v>
+        <v>46188.6740696412</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3317,11 +3323,11 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.46786741898</v>
+        <v>46188.63453408565</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46188.507572083334</v>
+        <v>46188.67423875</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3380,11 +3386,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.46787158565</v>
+        <v>46188.634538252314</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46188.50752002315</v>
+        <v>46188.674186689816</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>83</v>
@@ -3433,11 +3439,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.46787663194</v>
+        <v>46188.63454329861</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46188.507517210644</v>
+        <v>46188.674183877316</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3486,11 +3492,11 @@
         <v>134</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.46788137731</v>
+        <v>46188.63454804398</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46188.5080371875</v>
+        <v>46188.674703854165</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>135</v>
@@ -3549,11 +3555,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.467886122686</v>
+        <v>46188.63455278936</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46188.50768351852</v>
+        <v>46188.67435018519</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>89</v>
@@ -3602,11 +3608,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.46789144676</v>
+        <v>46188.63455811342</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46188.50767990741</v>
+        <v>46188.67434657407</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3655,11 +3661,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.467897152776</v>
+        <v>46188.63456381945</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46188.50798180555</v>
+        <v>46188.674648472224</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3708,11 +3714,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.46790071759</v>
+        <v>46188.63456738426</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46188.51020636574</v>
+        <v>46188.67687303241</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3771,11 +3777,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.467905</v>
+        <v>46188.63457166667</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46188.51016978009</v>
+        <v>46188.67683644676</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>86</v>
@@ -3824,11 +3830,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.46791003473</v>
+        <v>46188.634576701385</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46188.51016694444</v>
+        <v>46188.67683361111</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -3877,11 +3883,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.467512546296</v>
+        <v>46188.63417921297</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.3581621875</v>
+        <v>46196.52482885416</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3924,13 +3930,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.467915810186</v>
+        <v>46188.63458247685</v>
       </c>
       <c r="C43" s="9">
-        <v>46196.35815153935</v>
+        <v>46196.52481820602</v>
       </c>
       <c r="D43" s="9">
-        <v>46196.35817019676</v>
+        <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -3989,11 +3995,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.4679219213</v>
+        <v>46188.634588587964</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46196.35817116898</v>
+        <v>46197.716253356484</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4052,11 +4058,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.46792831019</v>
+        <v>46188.63459497685</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46188.5102644213</v>
+        <v>46188.67693108796</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4065,10 +4071,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4092,7 +4098,7 @@
         <v>165</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4112,26 +4118,26 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.4679431713</v>
+        <v>46188.63460983796</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.51043608796</v>
+        <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4152,7 +4158,7 @@
         <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4175,26 +4181,26 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.46794728009</v>
+        <v>46188.634613946764</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46188.51039945602</v>
+        <v>46188.677066122684</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4212,13 +4218,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4228,26 +4234,26 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.46795173611</v>
+        <v>46188.63461840278</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46188.51039618056</v>
+        <v>46188.67706284722</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4265,13 +4271,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4281,17 +4287,17 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.46800628472</v>
+        <v>46188.63467295139</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.493675011574</v>
+        <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4315,7 +4321,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4328,26 +4334,26 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.468010972225</v>
+        <v>46188.63467763889</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46188.510564537035</v>
+        <v>46188.67723120371</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4365,13 +4371,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>124</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4391,17 +4397,17 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.46801827547</v>
+        <v>46188.634684942124</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.51065322917</v>
+        <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4428,13 +4434,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4454,26 +4460,26 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.468026296294</v>
+        <v>46188.634692962965</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46188.510561331015</v>
+        <v>46188.67722799769</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4491,13 +4497,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>132</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4517,17 +4523,17 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.468032881945</v>
+        <v>46188.63469954861</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.51065034722</v>
+        <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4554,13 +4560,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4580,26 +4586,26 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.468038935185</v>
+        <v>46188.63470560186</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46188.51055827546</v>
+        <v>46188.677224942134</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4617,13 +4623,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>154</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4643,17 +4649,17 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.468044884256</v>
+        <v>46188.63471155093</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.51064685185</v>
+        <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4680,13 +4686,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4706,17 +4712,17 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.46805064815</v>
+        <v>46188.63471731481</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.49599372685</v>
+        <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4740,7 +4746,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4753,26 +4759,26 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.46805440972</v>
+        <v>46188.63472107639</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.51107644676</v>
+        <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4790,13 +4796,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4816,26 +4822,26 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.46806591435</v>
+        <v>46188.63473258102</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.51079777778</v>
+        <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4853,13 +4859,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4869,26 +4875,26 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.46807454861</v>
+        <v>46188.63474121528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.510794421294</v>
+        <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -4906,13 +4912,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4922,26 +4928,26 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.46810618056</v>
+        <v>46188.63477284722</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.511072685185</v>
+        <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -4959,13 +4965,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -4985,26 +4991,26 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.46811210648</v>
+        <v>46188.63477877315</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46188.51087899305</v>
+        <v>46188.677545659724</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5022,13 +5028,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5038,26 +5044,26 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.46811938657</v>
+        <v>46188.63478605324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46188.51087618056</v>
+        <v>46188.67754284722</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5075,13 +5081,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5091,17 +5097,17 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.4681887037</v>
+        <v>46188.63485537037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.511136747686</v>
+        <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5128,13 +5134,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5154,17 +5160,17 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.46819513889</v>
+        <v>46188.634861805556</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46188.510988090275</v>
+        <v>46188.677654756946</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5191,13 +5197,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5207,17 +5213,17 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.46820215278</v>
+        <v>46188.63486881944</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46188.51098537037</v>
+        <v>46188.67765203703</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5244,13 +5250,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5260,17 +5266,17 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.46822664352</v>
+        <v>46188.63489331018</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46188.49781223379</v>
+        <v>46188.664478900464</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5294,7 +5300,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5307,26 +5313,26 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.46823672454</v>
+        <v>46188.634903391205</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46188.51124435185</v>
+        <v>46188.677911018516</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5344,13 +5350,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>113</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5370,26 +5376,26 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.468243379626</v>
+        <v>46188.6349100463</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.41989109953</v>
+        <v>46197.586557766204</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5407,13 +5413,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5433,26 +5439,26 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.46824984954</v>
+        <v>46188.6349165162</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.41995064815</v>
+        <v>46197.58661731481</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5470,13 +5476,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>95</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5496,26 +5502,26 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.468256249995</v>
+        <v>46188.634922916666</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46188.51123265046</v>
+        <v>46188.67789931713</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5533,13 +5539,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>142</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5559,17 +5565,17 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.468261284725</v>
+        <v>46188.63492795139</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.42039136574</v>
+        <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5593,7 +5599,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5606,17 +5612,17 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.46826486111</v>
+        <v>46188.63493152778</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.51135721065</v>
+        <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5643,13 +5649,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5669,17 +5675,17 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.468273680555</v>
+        <v>46188.63494034723</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.51131699074</v>
+        <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5706,10 +5712,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5722,17 +5728,17 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.46827848379</v>
+        <v>46188.634945150465</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.51131390047</v>
+        <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5759,10 +5765,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5775,19 +5781,19 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.46829700231</v>
+        <v>46188.634963668985</v>
       </c>
       <c r="C75" s="9">
-        <v>46197.42038163195</v>
+        <v>46197.58704829861</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.42039403935</v>
+        <v>46197.58706070602</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5814,13 +5820,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5840,19 +5846,19 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.46830221065</v>
+        <v>46188.63496887732</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.42028853009</v>
+        <v>46197.58695519676</v>
       </c>
       <c r="D76" s="5">
-        <v>46197.420289999995</v>
+        <v>46197.586956666666</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5879,13 +5885,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5895,19 +5901,19 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.46831445602</v>
+        <v>46188.63498112268</v>
       </c>
       <c r="C77" s="9">
-        <v>46197.42036866898</v>
+        <v>46197.587035335644</v>
       </c>
       <c r="D77" s="9">
-        <v>46197.42037010417</v>
+        <v>46197.587036770834</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5934,13 +5940,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5950,17 +5956,17 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.46837962963</v>
+        <v>46188.635046296295</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.51228384259</v>
+        <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5987,13 +5993,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -6013,17 +6019,17 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.46838737269</v>
+        <v>46188.63505403935</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.420295081014</v>
+        <v>46197.586961747686</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6050,13 +6056,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O79" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="P79" s="10" t="s">
         <v>255</v>
-      </c>
-      <c r="P79" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6066,17 +6072,17 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.46840146991</v>
+        <v>46188.63506813657</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46197.42037383102</v>
+        <v>46197.58704049769</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6103,13 +6109,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6119,17 +6125,17 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.468430381945</v>
+        <v>46188.63509704861</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.51239336806</v>
+        <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6156,13 +6162,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6182,17 +6188,17 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.46843627315</v>
+        <v>46188.635102939814</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46188.512354861115</v>
+        <v>46188.67902152777</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6219,13 +6225,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6235,17 +6241,17 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.46844325231</v>
+        <v>46188.63510991898</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46188.51235204861</v>
+        <v>46188.67901871528</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6272,13 +6278,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6288,17 +6294,17 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.468469363426</v>
+        <v>46188.63513603009</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.51254302083</v>
+        <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6325,13 +6331,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6351,17 +6357,17 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.468475057874</v>
+        <v>46188.63514172454</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46188.51249291666</v>
+        <v>46188.679159583335</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6386,13 +6392,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6402,17 +6408,17 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.46848186343</v>
+        <v>46188.63514853009</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46188.512489988425</v>
+        <v>46188.6791566551</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6437,13 +6443,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6453,17 +6459,17 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.46854449074</v>
+        <v>46188.63521115741</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46188.51396326389</v>
+        <v>46188.68062993056</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6490,13 +6496,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="9">
         <v>46260</v>
@@ -6516,17 +6522,17 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.46855128472</v>
+        <v>46188.63521795139</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46188.51403880787</v>
+        <v>46188.68070547454</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6553,13 +6559,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6569,17 +6575,17 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.46855625</v>
+        <v>46188.635222916666</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.51403582176</v>
+        <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6606,13 +6612,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6622,17 +6628,17 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.46858053241</v>
+        <v>46188.635247199076</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.50343700231</v>
+        <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6656,7 +6662,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6669,26 +6675,26 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.46858417824</v>
+        <v>46188.635250844905</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.514185381944</v>
+        <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I91" s="9">
         <v>46261</v>
@@ -6706,13 +6712,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q91" s="9">
         <v>46261</v>
@@ -6732,26 +6738,26 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.468590069446</v>
+        <v>46188.63525673611</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46188.51413481482</v>
+        <v>46188.68080148148</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I92" s="5">
         <v>46261</v>
@@ -6769,13 +6775,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6785,26 +6791,26 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.46859502315</v>
+        <v>46188.635261689815</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46188.514131261574</v>
+        <v>46188.680797928246</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I93" s="9">
         <v>46261</v>
@@ -6822,13 +6828,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6838,17 +6844,17 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.46861270833</v>
+        <v>46188.635279375</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.514514305556</v>
+        <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6875,13 +6881,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q94" s="5">
         <v>46262</v>
@@ -6901,17 +6907,17 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.46861780093</v>
+        <v>46188.63528446759</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46188.51446038194</v>
+        <v>46188.68112704861</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6936,13 +6942,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6952,17 +6958,17 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.46862275463</v>
+        <v>46188.6352894213</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46188.514457592595</v>
+        <v>46188.68112425926</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -6987,13 +6993,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7003,26 +7009,26 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.46864255787</v>
+        <v>46188.63530922454</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.51468978009</v>
+        <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7040,13 +7046,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q97" s="9">
         <v>46265</v>
@@ -7066,26 +7072,26 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.4686474537</v>
+        <v>46188.63531412037</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46188.51464789352</v>
+        <v>46188.681314560185</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I98" s="6"/>
       <c r="J98" s="5">
@@ -7101,13 +7107,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7117,26 +7123,26 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.46865572917</v>
+        <v>46188.63532239583</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46188.51464486111</v>
+        <v>46188.68131152778</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I99" s="10"/>
       <c r="J99" s="9">
@@ -7152,13 +7158,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7168,26 +7174,26 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.4687140162</v>
+        <v>46188.63538068287</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.514829004635</v>
+        <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7205,13 +7211,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q100" s="5">
         <v>46266</v>
@@ -7231,26 +7237,26 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.46872078704</v>
+        <v>46188.6353874537</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46188.514782199076</v>
+        <v>46188.68144886574</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7268,13 +7274,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7284,26 +7290,26 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.46872539352</v>
+        <v>46188.63539206018</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46188.51477896991</v>
+        <v>46188.681445636576</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>
@@ -7321,13 +7327,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7337,17 +7343,17 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.46874401621</v>
+        <v>46188.635410682866</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.50457228009</v>
+        <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7371,7 +7377,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7384,26 +7390,26 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.46874732639</v>
+        <v>46188.635413993055</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.514947986114</v>
+        <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="I104" s="5">
         <v>46267</v>
@@ -7421,13 +7427,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q104" s="5">
         <v>46267</v>
@@ -7447,26 +7453,26 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.46875277778</v>
+        <v>46188.63541944444</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.753907175924</v>
+        <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>
@@ -7484,13 +7490,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q105" s="9">
         <v>46267</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -1609,13 +1609,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46188.634159629626</v>
+        <v>46188.46749296296</v>
       </c>
       <c r="C4" s="5">
-        <v>46188.91968755787</v>
+        <v>46188.75302089121</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.91970172454</v>
+        <v>46188.753035057875</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1662,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46188.634310856476</v>
+        <v>46188.46764418982</v>
       </c>
       <c r="C5" s="9">
-        <v>46188.919674178236</v>
+        <v>46188.75300751158</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.91968832176</v>
+        <v>46188.753021655095</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1727,13 +1727,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46188.63431648148</v>
+        <v>46188.46764981482</v>
       </c>
       <c r="C6" s="5">
-        <v>46188.919543298616</v>
+        <v>46188.752876631945</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.91956144676</v>
+        <v>46188.75289478009</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1792,13 +1792,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="9">
-        <v>46188.63432182871</v>
+        <v>46188.467655162036</v>
       </c>
       <c r="C7" s="9">
-        <v>46188.91959428241</v>
+        <v>46188.752927615744</v>
       </c>
       <c r="D7" s="9">
-        <v>46188.9196094213</v>
+        <v>46188.752942754625</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>36</v>
@@ -1857,13 +1857,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46188.634326643514</v>
+        <v>46188.46765997686</v>
       </c>
       <c r="C8" s="5">
-        <v>46188.919635115744</v>
+        <v>46188.75296844907</v>
       </c>
       <c r="D8" s="5">
-        <v>46188.91965210648</v>
+        <v>46188.752985439816</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1922,13 +1922,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46188.634165474534</v>
+        <v>46188.46749880787</v>
       </c>
       <c r="C9" s="9">
-        <v>46188.92057981482</v>
+        <v>46188.753913148146</v>
       </c>
       <c r="D9" s="9">
-        <v>46188.92059026621</v>
+        <v>46188.753923599535</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -1975,13 +1975,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46188.63433173611</v>
+        <v>46188.467665069446</v>
       </c>
       <c r="C10" s="5">
-        <v>46188.920111388885</v>
+        <v>46188.75344472222</v>
       </c>
       <c r="D10" s="5">
-        <v>46188.920113182874</v>
+        <v>46188.7534465162</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2040,13 +2040,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46188.63434310185</v>
+        <v>46188.46767643519</v>
       </c>
       <c r="C11" s="9">
-        <v>46188.91974537037</v>
+        <v>46188.7530787037</v>
       </c>
       <c r="D11" s="9">
-        <v>46188.92032122685</v>
+        <v>46188.75365456019</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2105,13 +2105,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46188.63435032408</v>
+        <v>46188.46768365741</v>
       </c>
       <c r="C12" s="5">
-        <v>46188.92048497685</v>
+        <v>46188.753818310186</v>
       </c>
       <c r="D12" s="5">
-        <v>46188.92050125</v>
+        <v>46188.75383458333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2170,13 +2170,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="9">
-        <v>46188.634356759256</v>
+        <v>46188.46769009259</v>
       </c>
       <c r="C13" s="9">
-        <v>46188.920564201384</v>
+        <v>46188.75389753473</v>
       </c>
       <c r="D13" s="9">
-        <v>46188.92057991898</v>
+        <v>46188.753913252316</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2235,11 +2235,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46188.634170000005</v>
+        <v>46188.46750333333</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.58646723379</v>
+        <v>46197.41980056713</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2282,13 +2282,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46188.63436615741</v>
+        <v>46188.46769949074</v>
       </c>
       <c r="C15" s="9">
-        <v>46188.92065792824</v>
+        <v>46188.753991261576</v>
       </c>
       <c r="D15" s="9">
-        <v>46189.814397685186</v>
+        <v>46189.647731018515</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2347,13 +2347,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46188.63437259259</v>
+        <v>46188.46770592593</v>
       </c>
       <c r="C16" s="5">
-        <v>46188.9213359375</v>
+        <v>46188.754669270835</v>
       </c>
       <c r="D16" s="5">
-        <v>46189.814421944444</v>
+        <v>46189.64775527778</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2412,13 +2412,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46188.63437929398</v>
+        <v>46188.467712627316</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.58646039352</v>
+        <v>46197.41979372685</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.586479687496</v>
+        <v>46197.41981302084</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2477,11 +2477,11 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46188.63438636574</v>
+        <v>46188.467719699074</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46188.673596319444</v>
+        <v>46188.50692965278</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2540,11 +2540,11 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46188.634392708336</v>
+        <v>46188.467726041665</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46188.67359288194</v>
+        <v>46188.50692621528</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2603,11 +2603,11 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46188.63439828704</v>
+        <v>46188.467731620374</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46188.67358973379</v>
+        <v>46188.50692306713</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2666,11 +2666,11 @@
         <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46188.634403055556</v>
+        <v>46188.46773638889</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46188.673584675926</v>
+        <v>46188.506918009254</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2729,13 +2729,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46189.78075929398</v>
+        <v>46189.614092627315</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.58662379629</v>
+        <v>46197.419957129634</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.58663670139</v>
+        <v>46197.41997003472</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2784,13 +2784,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46189.81187604167</v>
+        <v>46189.645209375</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.586606770834</v>
+        <v>46197.41994010417</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.586624143514</v>
+        <v>46197.41995747686</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -2849,13 +2849,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46189.8120440162</v>
+        <v>46189.64537734954</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.58654909722</v>
+        <v>46197.41988243056</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.586567060185</v>
+        <v>46197.41990039352</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2914,11 +2914,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.634174861116</v>
+        <v>46188.467508194444</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46189.78281247686</v>
+        <v>46189.616145810185</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -2961,11 +2961,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46188.63442598379</v>
+        <v>46188.46775931713</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.177845300925</v>
+        <v>46197.01117863426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -3024,11 +3024,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46188.634431805556</v>
+        <v>46188.46776513889</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.586468877314</v>
+        <v>46197.41980221064</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3083,11 +3083,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46188.63443740741</v>
+        <v>46188.46777074074</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46188.67377366898</v>
+        <v>46188.50710700231</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3142,11 +3142,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.63451584491</v>
+        <v>46188.46784917824</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46188.674114560185</v>
+        <v>46188.50744789352</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3205,11 +3205,11 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.63452219908</v>
+        <v>46188.467855532406</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.67407226852</v>
+        <v>46188.50740560185</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3264,11 +3264,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.634528194445</v>
+        <v>46188.46786152778</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46188.6740696412</v>
+        <v>46188.50740297454</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3323,11 +3323,11 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.63453408565</v>
+        <v>46188.46786741898</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46188.67423875</v>
+        <v>46188.507572083334</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3386,11 +3386,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.634538252314</v>
+        <v>46188.46787158565</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46188.674186689816</v>
+        <v>46188.50752002315</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>83</v>
@@ -3439,11 +3439,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.63454329861</v>
+        <v>46188.46787663194</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46188.674183877316</v>
+        <v>46188.507517210644</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3492,11 +3492,11 @@
         <v>134</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.63454804398</v>
+        <v>46188.46788137731</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46188.674703854165</v>
+        <v>46188.5080371875</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>135</v>
@@ -3555,11 +3555,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.63455278936</v>
+        <v>46188.467886122686</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46188.67435018519</v>
+        <v>46188.50768351852</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>89</v>
@@ -3608,11 +3608,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.63455811342</v>
+        <v>46188.46789144676</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46188.67434657407</v>
+        <v>46188.50767990741</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3661,11 +3661,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.63456381945</v>
+        <v>46188.467897152776</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46188.674648472224</v>
+        <v>46188.50798180555</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3714,11 +3714,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.63456738426</v>
+        <v>46188.46790071759</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46188.67687303241</v>
+        <v>46188.51020636574</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3777,11 +3777,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.63457166667</v>
+        <v>46188.467905</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46188.67683644676</v>
+        <v>46188.51016978009</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>86</v>
@@ -3830,11 +3830,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.634576701385</v>
+        <v>46188.46791003473</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46188.67683361111</v>
+        <v>46188.51016694444</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -3883,11 +3883,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.63417921297</v>
+        <v>46188.467512546296</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.52482885416</v>
+        <v>46196.3581621875</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3930,13 +3930,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.63458247685</v>
+        <v>46188.467915810186</v>
       </c>
       <c r="C43" s="9">
-        <v>46196.52481820602</v>
+        <v>46196.35815153935</v>
       </c>
       <c r="D43" s="9">
-        <v>46197.71623851852</v>
+        <v>46197.54957185185</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -3995,11 +3995,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.634588587964</v>
+        <v>46188.4679219213</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46197.716253356484</v>
+        <v>46197.54958668981</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4058,11 +4058,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.63459497685</v>
+        <v>46188.46792831019</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46188.67693108796</v>
+        <v>46188.5102644213</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4121,11 +4121,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.63460983796</v>
+        <v>46188.4679431713</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.677102754635</v>
+        <v>46188.51043608796</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4184,11 +4184,11 @@
         <v>177</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.634613946764</v>
+        <v>46188.46794728009</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46188.677066122684</v>
+        <v>46188.51039945602</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>178</v>
@@ -4237,11 +4237,11 @@
         <v>181</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.63461840278</v>
+        <v>46188.46795173611</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46188.67706284722</v>
+        <v>46188.51039618056</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4290,11 +4290,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.63467295139</v>
+        <v>46188.46800628472</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.660341678245</v>
+        <v>46188.493675011574</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4337,11 +4337,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.63467763889</v>
+        <v>46188.468010972225</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46188.67723120371</v>
+        <v>46188.510564537035</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4400,11 +4400,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.634684942124</v>
+        <v>46188.46801827547</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.67731989583</v>
+        <v>46188.51065322917</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4463,11 +4463,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.634692962965</v>
+        <v>46188.468026296294</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46188.67722799769</v>
+        <v>46188.510561331015</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4526,11 +4526,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.63469954861</v>
+        <v>46188.468032881945</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.67731701389</v>
+        <v>46188.51065034722</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4589,11 +4589,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.63470560186</v>
+        <v>46188.468038935185</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46188.677224942134</v>
+        <v>46188.51055827546</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4652,11 +4652,11 @@
         <v>202</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.63471155093</v>
+        <v>46188.468044884256</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.67731351852</v>
+        <v>46188.51064685185</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4715,11 +4715,11 @@
         <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.63471731481</v>
+        <v>46188.46805064815</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.662660393515</v>
+        <v>46188.49599372685</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -4762,11 +4762,11 @@
         <v>206</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.63472107639</v>
+        <v>46188.46805440972</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.677743113425</v>
+        <v>46188.51107644676</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>207</v>
@@ -4825,11 +4825,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.63473258102</v>
+        <v>46188.46806591435</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.677464444445</v>
+        <v>46188.51079777778</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>178</v>
@@ -4878,11 +4878,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.63474121528</v>
+        <v>46188.46807454861</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.677461087966</v>
+        <v>46188.510794421294</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>178</v>
@@ -4931,11 +4931,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.63477284722</v>
+        <v>46188.46810618056</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.67773935186</v>
+        <v>46188.511072685185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -4994,11 +4994,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.63477877315</v>
+        <v>46188.46811210648</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46188.677545659724</v>
+        <v>46188.51087899305</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>178</v>
@@ -5047,11 +5047,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.63478605324</v>
+        <v>46188.46811938657</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46188.67754284722</v>
+        <v>46188.51087618056</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>178</v>
@@ -5100,11 +5100,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.63485537037</v>
+        <v>46188.4681887037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.67780341435</v>
+        <v>46188.511136747686</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5163,11 +5163,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.634861805556</v>
+        <v>46188.46819513889</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46188.677654756946</v>
+        <v>46188.510988090275</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>178</v>
@@ -5216,11 +5216,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.63486881944</v>
+        <v>46188.46820215278</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46188.67765203703</v>
+        <v>46188.51098537037</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>178</v>
@@ -5269,11 +5269,11 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.63489331018</v>
+        <v>46188.46822664352</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46188.664478900464</v>
+        <v>46188.49781223379</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>183</v>
@@ -5316,11 +5316,11 @@
         <v>229</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.634903391205</v>
+        <v>46188.46823672454</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46188.677911018516</v>
+        <v>46188.51124435185</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5379,11 +5379,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.6349100463</v>
+        <v>46188.468243379626</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.586557766204</v>
+        <v>46197.41989109953</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5442,11 +5442,11 @@
         <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.6349165162</v>
+        <v>46188.46824984954</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.58661731481</v>
+        <v>46197.41995064815</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>
@@ -5505,11 +5505,11 @@
         <v>235</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.634922916666</v>
+        <v>46188.468256249995</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46188.67789931713</v>
+        <v>46188.51123265046</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5568,11 +5568,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.63492795139</v>
+        <v>46188.468261284725</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.58705803241</v>
+        <v>46197.42039136574</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>239</v>
@@ -5615,11 +5615,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.63493152778</v>
+        <v>46188.46826486111</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.67802387731</v>
+        <v>46188.51135721065</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5678,11 +5678,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.63494034723</v>
+        <v>46188.468273680555</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.677983657406</v>
+        <v>46188.51131699074</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>178</v>
@@ -5731,11 +5731,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.634945150465</v>
+        <v>46188.46827848379</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.677980567125</v>
+        <v>46188.51131390047</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>178</v>
@@ -5784,13 +5784,13 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.634963668985</v>
+        <v>46188.46829700231</v>
       </c>
       <c r="C75" s="9">
-        <v>46197.58704829861</v>
+        <v>46197.42038163195</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.58706070602</v>
+        <v>46197.42039403935</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5849,13 +5849,13 @@
         <v>249</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.63496887732</v>
+        <v>46188.46830221065</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.58695519676</v>
+        <v>46197.42028853009</v>
       </c>
       <c r="D76" s="5">
-        <v>46197.586956666666</v>
+        <v>46197.420289999995</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>178</v>
@@ -5904,13 +5904,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.63498112268</v>
+        <v>46188.46831445602</v>
       </c>
       <c r="C77" s="9">
-        <v>46197.587035335644</v>
+        <v>46197.42036866898</v>
       </c>
       <c r="D77" s="9">
-        <v>46197.587036770834</v>
+        <v>46197.42037010417</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>178</v>
@@ -5959,11 +5959,11 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.635046296295</v>
+        <v>46188.46837962963</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.67895050926</v>
+        <v>46188.51228384259</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6022,11 +6022,11 @@
         <v>256</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.63505403935</v>
+        <v>46188.46838737269</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.586961747686</v>
+        <v>46197.420295081014</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>178</v>
@@ -6075,11 +6075,11 @@
         <v>258</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.63506813657</v>
+        <v>46188.46840146991</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46197.58704049769</v>
+        <v>46197.42037383102</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>178</v>
@@ -6128,11 +6128,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.63509704861</v>
+        <v>46188.468430381945</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.67906003472</v>
+        <v>46188.51239336806</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6191,11 +6191,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.635102939814</v>
+        <v>46188.46843627315</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46188.67902152777</v>
+        <v>46188.512354861115</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>178</v>
@@ -6244,11 +6244,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.63510991898</v>
+        <v>46188.46844325231</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46188.67901871528</v>
+        <v>46188.51235204861</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>178</v>
@@ -6297,11 +6297,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.63513603009</v>
+        <v>46188.468469363426</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.6792096875</v>
+        <v>46188.51254302083</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6360,11 +6360,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.63514172454</v>
+        <v>46188.468475057874</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46188.679159583335</v>
+        <v>46188.51249291666</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>179</v>
@@ -6411,11 +6411,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.63514853009</v>
+        <v>46188.46848186343</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46188.6791566551</v>
+        <v>46188.512489988425</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>178</v>
@@ -6462,11 +6462,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.63521115741</v>
+        <v>46188.46854449074</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46188.68062993056</v>
+        <v>46188.51396326389</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6525,11 +6525,11 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.63521795139</v>
+        <v>46188.46855128472</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46188.68070547454</v>
+        <v>46188.51403880787</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>178</v>
@@ -6578,11 +6578,11 @@
         <v>278</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.635222916666</v>
+        <v>46188.46855625</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.680702488426</v>
+        <v>46188.51403582176</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>178</v>
@@ -6631,11 +6631,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.635247199076</v>
+        <v>46188.46858053241</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.67010366898</v>
+        <v>46188.50343700231</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -6678,11 +6678,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.635250844905</v>
+        <v>46188.46858417824</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.68085204861</v>
+        <v>46188.514185381944</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>283</v>
@@ -6741,11 +6741,11 @@
         <v>287</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.63525673611</v>
+        <v>46188.468590069446</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46188.68080148148</v>
+        <v>46188.51413481482</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>178</v>
@@ -6794,11 +6794,11 @@
         <v>289</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.635261689815</v>
+        <v>46188.46859502315</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46188.680797928246</v>
+        <v>46188.514131261574</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>178</v>
@@ -6847,11 +6847,11 @@
         <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.635279375</v>
+        <v>46188.46861270833</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.68118097223</v>
+        <v>46188.514514305556</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -6910,11 +6910,11 @@
         <v>292</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.63528446759</v>
+        <v>46188.46861780093</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46188.68112704861</v>
+        <v>46188.51446038194</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>178</v>
@@ -6961,11 +6961,11 @@
         <v>294</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.6352894213</v>
+        <v>46188.46862275463</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46188.68112425926</v>
+        <v>46188.514457592595</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>178</v>
@@ -7012,11 +7012,11 @@
         <v>296</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.63530922454</v>
+        <v>46188.46864255787</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.68135644676</v>
+        <v>46188.51468978009</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>297</v>
@@ -7075,11 +7075,11 @@
         <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.63531412037</v>
+        <v>46188.4686474537</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46188.681314560185</v>
+        <v>46188.51464789352</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>178</v>
@@ -7126,11 +7126,11 @@
         <v>300</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.63532239583</v>
+        <v>46188.46865572917</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46188.68131152778</v>
+        <v>46188.51464486111</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>178</v>
@@ -7177,11 +7177,11 @@
         <v>301</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.63538068287</v>
+        <v>46188.4687140162</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.68149567129</v>
+        <v>46188.514829004635</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>302</v>
@@ -7240,11 +7240,11 @@
         <v>304</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.6353874537</v>
+        <v>46188.46872078704</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46188.68144886574</v>
+        <v>46188.514782199076</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>178</v>
@@ -7293,11 +7293,11 @@
         <v>305</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.63539206018</v>
+        <v>46188.46872539352</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46188.681445636576</v>
+        <v>46188.51477896991</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>178</v>
@@ -7346,11 +7346,11 @@
         <v>306</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.635410682866</v>
+        <v>46188.46874401621</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.67123894676</v>
+        <v>46188.50457228009</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>307</v>
@@ -7393,11 +7393,11 @@
         <v>309</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.635413993055</v>
+        <v>46188.46874732639</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.68161465278</v>
+        <v>46188.514947986114</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>310</v>
@@ -7456,11 +7456,11 @@
         <v>313</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.63541944444</v>
+        <v>46188.46875277778</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.920573842595</v>
+        <v>46188.753907175924</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>314</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -1609,13 +1609,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46188.46749296296</v>
+        <v>46188.634159629626</v>
       </c>
       <c r="C4" s="5">
-        <v>46188.75302089121</v>
+        <v>46188.91968755787</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.753035057875</v>
+        <v>46188.91970172454</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1662,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46188.46764418982</v>
+        <v>46188.634310856476</v>
       </c>
       <c r="C5" s="9">
-        <v>46188.75300751158</v>
+        <v>46188.919674178236</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.753021655095</v>
+        <v>46188.91968832176</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1727,13 +1727,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46188.46764981482</v>
+        <v>46188.63431648148</v>
       </c>
       <c r="C6" s="5">
-        <v>46188.752876631945</v>
+        <v>46188.919543298616</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.75289478009</v>
+        <v>46188.91956144676</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1792,13 +1792,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="9">
-        <v>46188.467655162036</v>
+        <v>46188.63432182871</v>
       </c>
       <c r="C7" s="9">
-        <v>46188.752927615744</v>
+        <v>46188.91959428241</v>
       </c>
       <c r="D7" s="9">
-        <v>46188.752942754625</v>
+        <v>46188.9196094213</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>36</v>
@@ -1857,13 +1857,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46188.46765997686</v>
+        <v>46188.634326643514</v>
       </c>
       <c r="C8" s="5">
-        <v>46188.75296844907</v>
+        <v>46188.919635115744</v>
       </c>
       <c r="D8" s="5">
-        <v>46188.752985439816</v>
+        <v>46188.91965210648</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1922,13 +1922,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46188.46749880787</v>
+        <v>46188.634165474534</v>
       </c>
       <c r="C9" s="9">
-        <v>46188.753913148146</v>
+        <v>46188.92057981482</v>
       </c>
       <c r="D9" s="9">
-        <v>46188.753923599535</v>
+        <v>46188.92059026621</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -1975,13 +1975,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46188.467665069446</v>
+        <v>46188.63433173611</v>
       </c>
       <c r="C10" s="5">
-        <v>46188.75344472222</v>
+        <v>46188.920111388885</v>
       </c>
       <c r="D10" s="5">
-        <v>46188.7534465162</v>
+        <v>46188.920113182874</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2040,13 +2040,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46188.46767643519</v>
+        <v>46188.63434310185</v>
       </c>
       <c r="C11" s="9">
-        <v>46188.7530787037</v>
+        <v>46188.91974537037</v>
       </c>
       <c r="D11" s="9">
-        <v>46188.75365456019</v>
+        <v>46188.92032122685</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2105,13 +2105,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46188.46768365741</v>
+        <v>46188.63435032408</v>
       </c>
       <c r="C12" s="5">
-        <v>46188.753818310186</v>
+        <v>46188.92048497685</v>
       </c>
       <c r="D12" s="5">
-        <v>46188.75383458333</v>
+        <v>46188.92050125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2170,13 +2170,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="9">
-        <v>46188.46769009259</v>
+        <v>46188.634356759256</v>
       </c>
       <c r="C13" s="9">
-        <v>46188.75389753473</v>
+        <v>46188.920564201384</v>
       </c>
       <c r="D13" s="9">
-        <v>46188.753913252316</v>
+        <v>46188.92057991898</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2235,11 +2235,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46188.46750333333</v>
+        <v>46188.634170000005</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.41980056713</v>
+        <v>46197.58646723379</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2282,13 +2282,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46188.46769949074</v>
+        <v>46188.63436615741</v>
       </c>
       <c r="C15" s="9">
-        <v>46188.753991261576</v>
+        <v>46188.92065792824</v>
       </c>
       <c r="D15" s="9">
-        <v>46189.647731018515</v>
+        <v>46189.814397685186</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2347,13 +2347,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46188.46770592593</v>
+        <v>46188.63437259259</v>
       </c>
       <c r="C16" s="5">
-        <v>46188.754669270835</v>
+        <v>46188.9213359375</v>
       </c>
       <c r="D16" s="5">
-        <v>46189.64775527778</v>
+        <v>46189.814421944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2412,13 +2412,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46188.467712627316</v>
+        <v>46188.63437929398</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.41979372685</v>
+        <v>46197.58646039352</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.41981302084</v>
+        <v>46197.586479687496</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2477,11 +2477,11 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46188.467719699074</v>
+        <v>46188.63438636574</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46188.50692965278</v>
+        <v>46188.673596319444</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2540,11 +2540,11 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46188.467726041665</v>
+        <v>46188.634392708336</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46188.50692621528</v>
+        <v>46188.67359288194</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2603,11 +2603,11 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46188.467731620374</v>
+        <v>46188.63439828704</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46188.50692306713</v>
+        <v>46188.67358973379</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2666,11 +2666,11 @@
         <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46188.46773638889</v>
+        <v>46188.634403055556</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46188.506918009254</v>
+        <v>46188.673584675926</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2729,13 +2729,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46189.614092627315</v>
+        <v>46189.78075929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.419957129634</v>
+        <v>46197.58662379629</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.41997003472</v>
+        <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2784,13 +2784,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46189.645209375</v>
+        <v>46189.81187604167</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.41994010417</v>
+        <v>46197.586606770834</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.41995747686</v>
+        <v>46197.586624143514</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -2849,13 +2849,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46189.64537734954</v>
+        <v>46189.8120440162</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.41988243056</v>
+        <v>46197.58654909722</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.41990039352</v>
+        <v>46197.586567060185</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2914,11 +2914,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.467508194444</v>
+        <v>46188.634174861116</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46189.616145810185</v>
+        <v>46189.78281247686</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -2961,11 +2961,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46188.46775931713</v>
+        <v>46188.63442598379</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.01117863426</v>
+        <v>46197.177845300925</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -3024,11 +3024,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46188.46776513889</v>
+        <v>46188.634431805556</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.41980221064</v>
+        <v>46197.586468877314</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3083,11 +3083,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46188.46777074074</v>
+        <v>46188.63443740741</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46188.50710700231</v>
+        <v>46188.67377366898</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3142,11 +3142,11 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.46784917824</v>
+        <v>46188.63451584491</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46188.50744789352</v>
+        <v>46188.674114560185</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3205,11 +3205,11 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.467855532406</v>
+        <v>46188.63452219908</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.50740560185</v>
+        <v>46188.67407226852</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3264,11 +3264,11 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.46786152778</v>
+        <v>46188.634528194445</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46188.50740297454</v>
+        <v>46188.6740696412</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3323,11 +3323,11 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.46786741898</v>
+        <v>46188.63453408565</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46188.507572083334</v>
+        <v>46188.67423875</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3386,11 +3386,11 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.46787158565</v>
+        <v>46188.634538252314</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46188.50752002315</v>
+        <v>46188.674186689816</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>83</v>
@@ -3439,11 +3439,11 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.46787663194</v>
+        <v>46188.63454329861</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46188.507517210644</v>
+        <v>46188.674183877316</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3492,11 +3492,11 @@
         <v>134</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.46788137731</v>
+        <v>46188.63454804398</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46188.5080371875</v>
+        <v>46188.674703854165</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>135</v>
@@ -3555,11 +3555,11 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.467886122686</v>
+        <v>46188.63455278936</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46188.50768351852</v>
+        <v>46188.67435018519</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>89</v>
@@ -3608,11 +3608,11 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.46789144676</v>
+        <v>46188.63455811342</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46188.50767990741</v>
+        <v>46188.67434657407</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3661,11 +3661,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.467897152776</v>
+        <v>46188.63456381945</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46188.50798180555</v>
+        <v>46188.674648472224</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3714,11 +3714,11 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.46790071759</v>
+        <v>46188.63456738426</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46188.51020636574</v>
+        <v>46188.67687303241</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3777,11 +3777,11 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.467905</v>
+        <v>46188.63457166667</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46188.51016978009</v>
+        <v>46188.67683644676</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>86</v>
@@ -3830,11 +3830,11 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.46791003473</v>
+        <v>46188.634576701385</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46188.51016694444</v>
+        <v>46188.67683361111</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -3883,11 +3883,11 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.467512546296</v>
+        <v>46188.63417921297</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.3581621875</v>
+        <v>46196.52482885416</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3930,13 +3930,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.467915810186</v>
+        <v>46188.63458247685</v>
       </c>
       <c r="C43" s="9">
-        <v>46196.35815153935</v>
+        <v>46196.52481820602</v>
       </c>
       <c r="D43" s="9">
-        <v>46197.54957185185</v>
+        <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -3995,11 +3995,11 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.4679219213</v>
+        <v>46188.634588587964</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46197.54958668981</v>
+        <v>46197.716253356484</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4058,11 +4058,11 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.46792831019</v>
+        <v>46188.63459497685</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46188.5102644213</v>
+        <v>46188.67693108796</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4121,11 +4121,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.4679431713</v>
+        <v>46188.63460983796</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.51043608796</v>
+        <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4184,11 +4184,11 @@
         <v>177</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.46794728009</v>
+        <v>46188.634613946764</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46188.51039945602</v>
+        <v>46188.677066122684</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>178</v>
@@ -4237,11 +4237,11 @@
         <v>181</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.46795173611</v>
+        <v>46188.63461840278</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46188.51039618056</v>
+        <v>46188.67706284722</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4290,11 +4290,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.46800628472</v>
+        <v>46188.63467295139</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.493675011574</v>
+        <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4337,11 +4337,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.468010972225</v>
+        <v>46188.63467763889</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46188.510564537035</v>
+        <v>46188.67723120371</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4400,11 +4400,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.46801827547</v>
+        <v>46188.634684942124</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.51065322917</v>
+        <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4463,11 +4463,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.468026296294</v>
+        <v>46188.634692962965</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46188.510561331015</v>
+        <v>46188.67722799769</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4526,11 +4526,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.468032881945</v>
+        <v>46188.63469954861</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.51065034722</v>
+        <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4589,11 +4589,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.468038935185</v>
+        <v>46188.63470560186</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46188.51055827546</v>
+        <v>46188.677224942134</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4652,11 +4652,11 @@
         <v>202</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.468044884256</v>
+        <v>46188.63471155093</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.51064685185</v>
+        <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4715,11 +4715,11 @@
         <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.46805064815</v>
+        <v>46188.63471731481</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.49599372685</v>
+        <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -4762,11 +4762,11 @@
         <v>206</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.46805440972</v>
+        <v>46188.63472107639</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.51107644676</v>
+        <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>207</v>
@@ -4825,11 +4825,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.46806591435</v>
+        <v>46188.63473258102</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.51079777778</v>
+        <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>178</v>
@@ -4878,11 +4878,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.46807454861</v>
+        <v>46188.63474121528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.510794421294</v>
+        <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>178</v>
@@ -4931,11 +4931,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.46810618056</v>
+        <v>46188.63477284722</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.511072685185</v>
+        <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -4994,11 +4994,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.46811210648</v>
+        <v>46188.63477877315</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46188.51087899305</v>
+        <v>46188.677545659724</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>178</v>
@@ -5047,11 +5047,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.46811938657</v>
+        <v>46188.63478605324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46188.51087618056</v>
+        <v>46188.67754284722</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>178</v>
@@ -5100,11 +5100,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.4681887037</v>
+        <v>46188.63485537037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.511136747686</v>
+        <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5163,11 +5163,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.46819513889</v>
+        <v>46188.634861805556</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46188.510988090275</v>
+        <v>46188.677654756946</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>178</v>
@@ -5216,11 +5216,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.46820215278</v>
+        <v>46188.63486881944</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46188.51098537037</v>
+        <v>46188.67765203703</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>178</v>
@@ -5269,11 +5269,11 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.46822664352</v>
+        <v>46188.63489331018</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46188.49781223379</v>
+        <v>46188.664478900464</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>183</v>
@@ -5316,11 +5316,11 @@
         <v>229</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.46823672454</v>
+        <v>46188.634903391205</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46188.51124435185</v>
+        <v>46188.677911018516</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5379,11 +5379,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.468243379626</v>
+        <v>46188.6349100463</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.41989109953</v>
+        <v>46197.586557766204</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5442,11 +5442,11 @@
         <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.46824984954</v>
+        <v>46188.6349165162</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.41995064815</v>
+        <v>46197.58661731481</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>
@@ -5505,11 +5505,11 @@
         <v>235</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.468256249995</v>
+        <v>46188.634922916666</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46188.51123265046</v>
+        <v>46188.67789931713</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5568,11 +5568,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.468261284725</v>
+        <v>46188.63492795139</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.42039136574</v>
+        <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>239</v>
@@ -5615,11 +5615,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.46826486111</v>
+        <v>46188.63493152778</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.51135721065</v>
+        <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5678,11 +5678,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.468273680555</v>
+        <v>46188.63494034723</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.51131699074</v>
+        <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>178</v>
@@ -5731,11 +5731,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.46827848379</v>
+        <v>46188.634945150465</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.51131390047</v>
+        <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>178</v>
@@ -5784,13 +5784,13 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.46829700231</v>
+        <v>46188.634963668985</v>
       </c>
       <c r="C75" s="9">
-        <v>46197.42038163195</v>
+        <v>46197.58704829861</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.42039403935</v>
+        <v>46197.58706070602</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5849,13 +5849,13 @@
         <v>249</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.46830221065</v>
+        <v>46188.63496887732</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.42028853009</v>
+        <v>46197.58695519676</v>
       </c>
       <c r="D76" s="5">
-        <v>46197.420289999995</v>
+        <v>46197.586956666666</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>178</v>
@@ -5904,13 +5904,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.46831445602</v>
+        <v>46188.63498112268</v>
       </c>
       <c r="C77" s="9">
-        <v>46197.42036866898</v>
+        <v>46197.587035335644</v>
       </c>
       <c r="D77" s="9">
-        <v>46197.42037010417</v>
+        <v>46197.587036770834</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>178</v>
@@ -5959,11 +5959,11 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.46837962963</v>
+        <v>46188.635046296295</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.51228384259</v>
+        <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6022,11 +6022,11 @@
         <v>256</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.46838737269</v>
+        <v>46188.63505403935</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.420295081014</v>
+        <v>46197.586961747686</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>178</v>
@@ -6075,11 +6075,11 @@
         <v>258</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.46840146991</v>
+        <v>46188.63506813657</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46197.42037383102</v>
+        <v>46197.58704049769</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>178</v>
@@ -6128,11 +6128,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.468430381945</v>
+        <v>46188.63509704861</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.51239336806</v>
+        <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6191,11 +6191,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.46843627315</v>
+        <v>46188.635102939814</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46188.512354861115</v>
+        <v>46188.67902152777</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>178</v>
@@ -6244,11 +6244,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.46844325231</v>
+        <v>46188.63510991898</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46188.51235204861</v>
+        <v>46188.67901871528</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>178</v>
@@ -6297,11 +6297,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.468469363426</v>
+        <v>46188.63513603009</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.51254302083</v>
+        <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6360,11 +6360,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.468475057874</v>
+        <v>46188.63514172454</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46188.51249291666</v>
+        <v>46188.679159583335</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>179</v>
@@ -6411,11 +6411,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.46848186343</v>
+        <v>46188.63514853009</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46188.512489988425</v>
+        <v>46188.6791566551</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>178</v>
@@ -6462,11 +6462,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.46854449074</v>
+        <v>46188.63521115741</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46188.51396326389</v>
+        <v>46188.68062993056</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6525,11 +6525,11 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.46855128472</v>
+        <v>46188.63521795139</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46188.51403880787</v>
+        <v>46188.68070547454</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>178</v>
@@ -6578,11 +6578,11 @@
         <v>278</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.46855625</v>
+        <v>46188.635222916666</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.51403582176</v>
+        <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>178</v>
@@ -6631,11 +6631,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.46858053241</v>
+        <v>46188.635247199076</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.50343700231</v>
+        <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -6678,11 +6678,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.46858417824</v>
+        <v>46188.635250844905</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.514185381944</v>
+        <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>283</v>
@@ -6741,11 +6741,11 @@
         <v>287</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.468590069446</v>
+        <v>46188.63525673611</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46188.51413481482</v>
+        <v>46188.68080148148</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>178</v>
@@ -6794,11 +6794,11 @@
         <v>289</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.46859502315</v>
+        <v>46188.635261689815</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46188.514131261574</v>
+        <v>46188.680797928246</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>178</v>
@@ -6847,11 +6847,11 @@
         <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.46861270833</v>
+        <v>46188.635279375</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.514514305556</v>
+        <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -6910,11 +6910,11 @@
         <v>292</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.46861780093</v>
+        <v>46188.63528446759</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46188.51446038194</v>
+        <v>46188.68112704861</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>178</v>
@@ -6961,11 +6961,11 @@
         <v>294</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.46862275463</v>
+        <v>46188.6352894213</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46188.514457592595</v>
+        <v>46188.68112425926</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>178</v>
@@ -7012,11 +7012,11 @@
         <v>296</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.46864255787</v>
+        <v>46188.63530922454</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.51468978009</v>
+        <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>297</v>
@@ -7075,11 +7075,11 @@
         <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.4686474537</v>
+        <v>46188.63531412037</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46188.51464789352</v>
+        <v>46188.681314560185</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>178</v>
@@ -7126,11 +7126,11 @@
         <v>300</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.46865572917</v>
+        <v>46188.63532239583</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46188.51464486111</v>
+        <v>46188.68131152778</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>178</v>
@@ -7177,11 +7177,11 @@
         <v>301</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.4687140162</v>
+        <v>46188.63538068287</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.514829004635</v>
+        <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>302</v>
@@ -7240,11 +7240,11 @@
         <v>304</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.46872078704</v>
+        <v>46188.6353874537</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46188.514782199076</v>
+        <v>46188.68144886574</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>178</v>
@@ -7293,11 +7293,11 @@
         <v>305</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.46872539352</v>
+        <v>46188.63539206018</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46188.51477896991</v>
+        <v>46188.681445636576</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>178</v>
@@ -7346,11 +7346,11 @@
         <v>306</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.46874401621</v>
+        <v>46188.635410682866</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.50457228009</v>
+        <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>307</v>
@@ -7393,11 +7393,11 @@
         <v>309</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.46874732639</v>
+        <v>46188.635413993055</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.514947986114</v>
+        <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>310</v>
@@ -7456,11 +7456,11 @@
         <v>313</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.46875277778</v>
+        <v>46188.63541944444</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.753907175924</v>
+        <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>314</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="316">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -277,93 +277,96 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4360</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215727831264658</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4360</t>
+  </si>
+  <si>
+    <t>1215727831264670</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215728035806401</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4360</t>
+  </si>
+  <si>
+    <t>1215771707606671</t>
+  </si>
+  <si>
+    <t>Reserva producción</t>
+  </si>
+  <si>
+    <t>motor ot 4360,Alabe  ot 4360</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1215771707606683</t>
+  </si>
+  <si>
+    <t>motor ot 4360</t>
+  </si>
+  <si>
+    <t>Reserva producción,Recepcionx motor</t>
+  </si>
+  <si>
+    <t>1215771707606685</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4360</t>
+  </si>
+  <si>
+    <t>Reserva producción,Recepcionx Alabe</t>
+  </si>
+  <si>
+    <t>1215727332551586</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4360,rodete OT 4360</t>
+  </si>
+  <si>
+    <t>1215728035819291</t>
+  </si>
+  <si>
+    <t>rodete OT 4360</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4316,Fabricación Rodete OT 4316</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
-    <t>1215727831264658</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4360</t>
-  </si>
-  <si>
-    <t>1215727831264670</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215728035806401</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4360</t>
-  </si>
-  <si>
-    <t>1215771707606671</t>
-  </si>
-  <si>
-    <t>Reserva producción</t>
-  </si>
-  <si>
-    <t>motor ot 4360,Alabe  ot 4360</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1215771707606683</t>
-  </si>
-  <si>
-    <t>motor ot 4360</t>
-  </si>
-  <si>
-    <t>Reserva producción,Recepcionx motor</t>
-  </si>
-  <si>
-    <t>1215771707606685</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4360</t>
-  </si>
-  <si>
-    <t>Reserva producción,Recepcionx Alabe</t>
-  </si>
-  <si>
-    <t>1215727332551586</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4360,rodete OT 4360</t>
-  </si>
-  <si>
-    <t>1215728035819291</t>
-  </si>
-  <si>
-    <t>rodete OT 4360</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4316,Fabricación Rodete OT 4316</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>1215728035819308</t>
   </si>
   <si>
@@ -536,9 +539,6 @@
   </si>
   <si>
     <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215727792809496</t>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46188.673596319444</v>
+        <v>46198.50798766204</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2531,7 +2531,7 @@
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="11" t="s">
+      <c r="U18" s="12" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46188.67359288194</v>
+        <v>46198.507987627316</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2594,7 +2594,7 @@
       <c r="T19" s="10">
         <v>0</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="U19" s="12" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46188.67358973379</v>
+        <v>46198.50798822917</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2657,7 +2657,7 @@
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="11" t="s">
+      <c r="U20" s="12" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46188.673584675926</v>
+        <v>46198.50798766204</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2720,7 +2720,7 @@
       <c r="T21" s="10">
         <v>0</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="U21" s="12" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="9">
         <v>46188.634431805556</v>
@@ -3031,7 +3031,7 @@
         <v>46197.586468877314</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3064,7 +3064,7 @@
         <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3075,12 +3075,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3090,7 +3090,7 @@
         <v>46188.67377366898</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3120,10 +3120,10 @@
         <v>104</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3134,12 +3134,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3149,16 +3149,16 @@
         <v>46188.674114560185</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3179,7 +3179,7 @@
         <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>101</v>
@@ -3197,12 +3197,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3212,16 +3212,16 @@
         <v>46188.67407226852</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3239,13 +3239,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3256,12 +3256,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3271,16 +3271,16 @@
         <v>46188.6740696412</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3298,13 +3298,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3315,12 +3315,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3330,16 +3330,16 @@
         <v>46188.67423875</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3360,7 +3360,7 @@
         <v>101</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3378,12 +3378,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3399,10 +3399,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3420,13 +3420,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3436,7 +3436,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3446,16 +3446,16 @@
         <v>46188.674183877316</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3473,13 +3473,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3499,16 +3499,16 @@
         <v>46188.674703854165</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3529,7 +3529,7 @@
         <v>101</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3547,12 +3547,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3568,10 +3568,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3589,13 +3589,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3605,7 +3605,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3615,16 +3615,16 @@
         <v>46188.67434657407</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3642,13 +3642,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3658,7 +3658,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3668,16 +3668,16 @@
         <v>46188.674648472224</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3695,10 +3695,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3721,16 +3721,16 @@
         <v>46188.67687303241</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3751,7 +3751,7 @@
         <v>101</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3769,12 +3769,12 @@
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3790,10 +3790,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3811,13 +3811,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3827,7 +3827,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3837,16 +3837,16 @@
         <v>46188.67683361111</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3864,13 +3864,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3880,17 +3880,17 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46196.52482885416</v>
+        <v>46198.5079131713</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3914,7 +3914,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3923,11 +3923,13 @@
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
       <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
+      <c r="U42" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -3939,16 +3941,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -3966,13 +3968,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>54</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -3992,26 +3994,28 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46198.50789115741</v>
+      </c>
       <c r="D44" s="5">
-        <v>46197.716253356484</v>
+        <v>46198.50791363426</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4029,13 +4033,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4047,10 +4051,10 @@
         <v>93</v>
       </c>
       <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="12" t="s">
-        <v>167</v>
+        <v>1</v>
+      </c>
+      <c r="U44" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4060,9 +4064,11 @@
       <c r="B45" s="9">
         <v>46188.63459497685</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46198.50795378472</v>
+      </c>
       <c r="D45" s="9">
-        <v>46188.67693108796</v>
+        <v>46198.50797135416</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4092,10 +4098,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>171</v>
@@ -4110,10 +4116,10 @@
         <v>93</v>
       </c>
       <c r="T45" s="10">
-        <v>0</v>
-      </c>
-      <c r="U45" s="11" t="s">
-        <v>80</v>
+        <v>1</v>
+      </c>
+      <c r="U45" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4155,7 +4161,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>176</v>
@@ -4176,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4374,7 +4380,7 @@
         <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>189</v>
@@ -4392,7 +4398,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4413,10 +4419,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4455,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4500,7 +4506,7 @@
         <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>196</v>
@@ -4518,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4539,10 +4545,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4581,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4626,7 +4632,7 @@
         <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>201</v>
@@ -4644,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4665,10 +4671,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4707,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4817,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4986,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -4998,7 +5004,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46188.677545659724</v>
+        <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>178</v>
@@ -5051,7 +5057,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46188.67754284722</v>
+        <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>178</v>
@@ -5113,10 +5119,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5155,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5167,7 +5173,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46188.677654756946</v>
+        <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>178</v>
@@ -5176,10 +5182,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5220,7 +5226,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46188.67765203703</v>
+        <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>178</v>
@@ -5229,10 +5235,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5320,7 +5326,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46188.677911018516</v>
+        <v>46198.16853090278</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5353,7 +5359,7 @@
         <v>183</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>193</v>
@@ -5364,14 +5370,14 @@
       <c r="R67" s="9">
         <v>46205</v>
       </c>
-      <c r="S67" s="7" t="s">
-        <v>93</v>
+      <c r="S67" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5434,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>167</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5497,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>167</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5542,7 +5548,7 @@
         <v>183</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>237</v>
@@ -5560,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5670,7 +5676,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5855,7 +5861,7 @@
         <v>46197.58695519676</v>
       </c>
       <c r="D76" s="5">
-        <v>46197.586956666666</v>
+        <v>46198.507974444445</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>178</v>
@@ -5910,7 +5916,7 @@
         <v>46197.587035335644</v>
       </c>
       <c r="D77" s="9">
-        <v>46197.587036770834</v>
+        <v>46198.50797810185</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>178</v>
@@ -6014,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6026,7 +6032,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46197.586961747686</v>
+        <v>46198.50797702547</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>178</v>
@@ -6079,7 +6085,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46197.58704049769</v>
+        <v>46198.507975162036</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>178</v>
@@ -6183,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6195,7 +6201,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46188.67902152777</v>
+        <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>178</v>
@@ -6248,7 +6254,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46188.67901871528</v>
+        <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>178</v>
@@ -6352,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6517,7 +6523,7 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6733,7 +6739,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6902,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7067,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7232,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7448,7 +7454,7 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7511,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -1609,13 +1609,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46188.634159629626</v>
+        <v>46188.46749296296</v>
       </c>
       <c r="C4" s="5">
-        <v>46188.91968755787</v>
+        <v>46188.75302089121</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.91970172454</v>
+        <v>46188.753035057875</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1662,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46188.634310856476</v>
+        <v>46188.46764418982</v>
       </c>
       <c r="C5" s="9">
-        <v>46188.919674178236</v>
+        <v>46188.75300751158</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.91968832176</v>
+        <v>46188.753021655095</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1727,13 +1727,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46188.63431648148</v>
+        <v>46188.46764981482</v>
       </c>
       <c r="C6" s="5">
-        <v>46188.919543298616</v>
+        <v>46188.752876631945</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.91956144676</v>
+        <v>46188.75289478009</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1792,13 +1792,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="9">
-        <v>46188.63432182871</v>
+        <v>46188.467655162036</v>
       </c>
       <c r="C7" s="9">
-        <v>46188.91959428241</v>
+        <v>46188.752927615744</v>
       </c>
       <c r="D7" s="9">
-        <v>46188.9196094213</v>
+        <v>46188.752942754625</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>36</v>
@@ -1857,13 +1857,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46188.634326643514</v>
+        <v>46188.46765997686</v>
       </c>
       <c r="C8" s="5">
-        <v>46188.919635115744</v>
+        <v>46188.75296844907</v>
       </c>
       <c r="D8" s="5">
-        <v>46188.91965210648</v>
+        <v>46188.752985439816</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1922,13 +1922,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46188.634165474534</v>
+        <v>46188.46749880787</v>
       </c>
       <c r="C9" s="9">
-        <v>46188.92057981482</v>
+        <v>46188.753913148146</v>
       </c>
       <c r="D9" s="9">
-        <v>46188.92059026621</v>
+        <v>46188.753923599535</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -1975,13 +1975,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46188.63433173611</v>
+        <v>46188.467665069446</v>
       </c>
       <c r="C10" s="5">
-        <v>46188.920111388885</v>
+        <v>46188.75344472222</v>
       </c>
       <c r="D10" s="5">
-        <v>46188.920113182874</v>
+        <v>46188.7534465162</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2040,13 +2040,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46188.63434310185</v>
+        <v>46188.46767643519</v>
       </c>
       <c r="C11" s="9">
-        <v>46188.91974537037</v>
+        <v>46188.7530787037</v>
       </c>
       <c r="D11" s="9">
-        <v>46188.92032122685</v>
+        <v>46188.75365456019</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2105,13 +2105,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46188.63435032408</v>
+        <v>46188.46768365741</v>
       </c>
       <c r="C12" s="5">
-        <v>46188.92048497685</v>
+        <v>46188.753818310186</v>
       </c>
       <c r="D12" s="5">
-        <v>46188.92050125</v>
+        <v>46188.75383458333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2170,13 +2170,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="9">
-        <v>46188.634356759256</v>
+        <v>46188.46769009259</v>
       </c>
       <c r="C13" s="9">
-        <v>46188.920564201384</v>
+        <v>46188.75389753473</v>
       </c>
       <c r="D13" s="9">
-        <v>46188.92057991898</v>
+        <v>46188.753913252316</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2235,11 +2235,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46188.634170000005</v>
+        <v>46188.46750333333</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.58646723379</v>
+        <v>46197.41980056713</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2282,13 +2282,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46188.63436615741</v>
+        <v>46188.46769949074</v>
       </c>
       <c r="C15" s="9">
-        <v>46188.92065792824</v>
+        <v>46188.753991261576</v>
       </c>
       <c r="D15" s="9">
-        <v>46189.814397685186</v>
+        <v>46189.647731018515</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2347,13 +2347,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46188.63437259259</v>
+        <v>46188.46770592593</v>
       </c>
       <c r="C16" s="5">
-        <v>46188.9213359375</v>
+        <v>46188.754669270835</v>
       </c>
       <c r="D16" s="5">
-        <v>46189.814421944444</v>
+        <v>46189.64775527778</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2412,13 +2412,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46188.63437929398</v>
+        <v>46188.467712627316</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.58646039352</v>
+        <v>46197.41979372685</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.586479687496</v>
+        <v>46197.41981302084</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2477,11 +2477,11 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46188.63438636574</v>
+        <v>46188.467719699074</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.50798766204</v>
+        <v>46198.34132099537</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2540,11 +2540,11 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46188.634392708336</v>
+        <v>46188.467726041665</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46198.507987627316</v>
+        <v>46198.34132096065</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2603,11 +2603,11 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46188.63439828704</v>
+        <v>46188.467731620374</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.50798822917</v>
+        <v>46198.341321562504</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2666,11 +2666,11 @@
         <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46188.634403055556</v>
+        <v>46188.46773638889</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.50798766204</v>
+        <v>46198.34132099537</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2729,13 +2729,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46189.78075929398</v>
+        <v>46189.614092627315</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.58662379629</v>
+        <v>46197.419957129634</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.58663670139</v>
+        <v>46197.41997003472</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2784,13 +2784,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46189.81187604167</v>
+        <v>46189.645209375</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.586606770834</v>
+        <v>46197.41994010417</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.586624143514</v>
+        <v>46197.41995747686</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -2849,13 +2849,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46189.8120440162</v>
+        <v>46189.64537734954</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.58654909722</v>
+        <v>46197.41988243056</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.586567060185</v>
+        <v>46197.41990039352</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2914,11 +2914,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.634174861116</v>
+        <v>46188.467508194444</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46189.78281247686</v>
+        <v>46189.616145810185</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -2961,11 +2961,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46188.63442598379</v>
+        <v>46188.46775931713</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.177845300925</v>
+        <v>46197.01117863426</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -3024,11 +3024,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46188.634431805556</v>
+        <v>46188.46776513889</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.586468877314</v>
+        <v>46197.41980221064</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3083,11 +3083,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46188.63443740741</v>
+        <v>46188.46777074074</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46188.67377366898</v>
+        <v>46188.50710700231</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3142,11 +3142,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.63451584491</v>
+        <v>46188.46784917824</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46188.674114560185</v>
+        <v>46188.50744789352</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3205,11 +3205,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.63452219908</v>
+        <v>46188.467855532406</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.67407226852</v>
+        <v>46188.50740560185</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3264,11 +3264,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.634528194445</v>
+        <v>46188.46786152778</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46188.6740696412</v>
+        <v>46188.50740297454</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3323,11 +3323,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.63453408565</v>
+        <v>46188.46786741898</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46188.67423875</v>
+        <v>46188.507572083334</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3386,11 +3386,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.634538252314</v>
+        <v>46188.46787158565</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46188.674186689816</v>
+        <v>46188.50752002315</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>83</v>
@@ -3439,11 +3439,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.63454329861</v>
+        <v>46188.46787663194</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46188.674183877316</v>
+        <v>46188.507517210644</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3492,11 +3492,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.63454804398</v>
+        <v>46188.46788137731</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46188.674703854165</v>
+        <v>46188.5080371875</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -3555,11 +3555,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.63455278936</v>
+        <v>46188.467886122686</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46188.67435018519</v>
+        <v>46188.50768351852</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>89</v>
@@ -3608,11 +3608,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.63455811342</v>
+        <v>46188.46789144676</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46188.67434657407</v>
+        <v>46188.50767990741</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3661,11 +3661,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.63456381945</v>
+        <v>46188.467897152776</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46188.674648472224</v>
+        <v>46188.50798180555</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3714,11 +3714,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.63456738426</v>
+        <v>46188.46790071759</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46188.67687303241</v>
+        <v>46188.51020636574</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3777,11 +3777,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.63457166667</v>
+        <v>46188.467905</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46188.67683644676</v>
+        <v>46188.51016978009</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>86</v>
@@ -3830,11 +3830,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.634576701385</v>
+        <v>46188.46791003473</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46188.67683361111</v>
+        <v>46188.51016694444</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -3883,11 +3883,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.63417921297</v>
+        <v>46188.467512546296</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46198.5079131713</v>
+        <v>46198.34124650463</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3932,13 +3932,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.63458247685</v>
+        <v>46188.467915810186</v>
       </c>
       <c r="C43" s="9">
-        <v>46196.52481820602</v>
+        <v>46196.35815153935</v>
       </c>
       <c r="D43" s="9">
-        <v>46197.71623851852</v>
+        <v>46197.54957185185</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -3997,13 +3997,13 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.634588587964</v>
+        <v>46188.4679219213</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.50789115741</v>
+        <v>46198.34122449074</v>
       </c>
       <c r="D44" s="5">
-        <v>46198.50791363426</v>
+        <v>46198.3412469676</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>166</v>
@@ -4062,13 +4062,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.63459497685</v>
+        <v>46188.46792831019</v>
       </c>
       <c r="C45" s="9">
-        <v>46198.50795378472</v>
+        <v>46198.341287118055</v>
       </c>
       <c r="D45" s="9">
-        <v>46198.50797135416</v>
+        <v>46198.3413046875</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4127,11 +4127,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.63460983796</v>
+        <v>46188.4679431713</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.677102754635</v>
+        <v>46188.51043608796</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4190,11 +4190,11 @@
         <v>177</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.634613946764</v>
+        <v>46188.46794728009</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46188.677066122684</v>
+        <v>46188.51039945602</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>178</v>
@@ -4243,11 +4243,11 @@
         <v>181</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.63461840278</v>
+        <v>46188.46795173611</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46188.67706284722</v>
+        <v>46188.51039618056</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4296,11 +4296,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.63467295139</v>
+        <v>46188.46800628472</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.660341678245</v>
+        <v>46188.493675011574</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4343,11 +4343,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.63467763889</v>
+        <v>46188.468010972225</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46188.67723120371</v>
+        <v>46188.510564537035</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4406,11 +4406,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.634684942124</v>
+        <v>46188.46801827547</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.67731989583</v>
+        <v>46188.51065322917</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4469,11 +4469,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.634692962965</v>
+        <v>46188.468026296294</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46188.67722799769</v>
+        <v>46188.510561331015</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4532,11 +4532,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.63469954861</v>
+        <v>46188.468032881945</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.67731701389</v>
+        <v>46188.51065034722</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4595,11 +4595,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.63470560186</v>
+        <v>46188.468038935185</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46188.677224942134</v>
+        <v>46188.51055827546</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4658,11 +4658,11 @@
         <v>202</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.63471155093</v>
+        <v>46188.468044884256</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.67731351852</v>
+        <v>46188.51064685185</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4721,11 +4721,11 @@
         <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.63471731481</v>
+        <v>46188.46805064815</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.662660393515</v>
+        <v>46188.49599372685</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -4768,11 +4768,11 @@
         <v>206</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.63472107639</v>
+        <v>46188.46805440972</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.677743113425</v>
+        <v>46188.51107644676</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>207</v>
@@ -4831,11 +4831,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.63473258102</v>
+        <v>46188.46806591435</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.677464444445</v>
+        <v>46188.51079777778</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>178</v>
@@ -4884,11 +4884,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.63474121528</v>
+        <v>46188.46807454861</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.677461087966</v>
+        <v>46188.510794421294</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>178</v>
@@ -4937,11 +4937,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.63477284722</v>
+        <v>46188.46810618056</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.67773935186</v>
+        <v>46188.511072685185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5000,11 +5000,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.63477877315</v>
+        <v>46188.46811210648</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46198.507975775465</v>
+        <v>46198.3413091088</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>178</v>
@@ -5053,11 +5053,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.63478605324</v>
+        <v>46188.46811938657</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.50797630787</v>
+        <v>46198.341309641204</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>178</v>
@@ -5106,11 +5106,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.63485537037</v>
+        <v>46188.4681887037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.67780341435</v>
+        <v>46188.511136747686</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5169,11 +5169,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.634861805556</v>
+        <v>46188.46819513889</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46198.507973761574</v>
+        <v>46198.3413070949</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>178</v>
@@ -5222,11 +5222,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.63486881944</v>
+        <v>46188.46820215278</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46198.507963055556</v>
+        <v>46198.341296388884</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>178</v>
@@ -5275,11 +5275,11 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.63489331018</v>
+        <v>46188.46822664352</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46188.664478900464</v>
+        <v>46188.49781223379</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>183</v>
@@ -5322,11 +5322,11 @@
         <v>229</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.634903391205</v>
+        <v>46188.46823672454</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46198.16853090278</v>
+        <v>46198.00186423611</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5385,11 +5385,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.6349100463</v>
+        <v>46188.468243379626</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.586557766204</v>
+        <v>46197.41989109953</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5448,11 +5448,11 @@
         <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.6349165162</v>
+        <v>46188.46824984954</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.58661731481</v>
+        <v>46197.41995064815</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>
@@ -5511,11 +5511,11 @@
         <v>235</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.634922916666</v>
+        <v>46188.468256249995</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46188.67789931713</v>
+        <v>46188.51123265046</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5574,11 +5574,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.63492795139</v>
+        <v>46188.468261284725</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.58705803241</v>
+        <v>46197.42039136574</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>239</v>
@@ -5621,11 +5621,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.63493152778</v>
+        <v>46188.46826486111</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.67802387731</v>
+        <v>46188.51135721065</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5684,11 +5684,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.63494034723</v>
+        <v>46188.468273680555</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.677983657406</v>
+        <v>46188.51131699074</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>178</v>
@@ -5737,11 +5737,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.634945150465</v>
+        <v>46188.46827848379</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.677980567125</v>
+        <v>46188.51131390047</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>178</v>
@@ -5790,13 +5790,13 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.634963668985</v>
+        <v>46188.46829700231</v>
       </c>
       <c r="C75" s="9">
-        <v>46197.58704829861</v>
+        <v>46197.42038163195</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.58706070602</v>
+        <v>46197.42039403935</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5855,13 +5855,13 @@
         <v>249</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.63496887732</v>
+        <v>46188.46830221065</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.58695519676</v>
+        <v>46197.42028853009</v>
       </c>
       <c r="D76" s="5">
-        <v>46198.507974444445</v>
+        <v>46198.34130777778</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>178</v>
@@ -5910,13 +5910,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.63498112268</v>
+        <v>46188.46831445602</v>
       </c>
       <c r="C77" s="9">
-        <v>46197.587035335644</v>
+        <v>46197.42036866898</v>
       </c>
       <c r="D77" s="9">
-        <v>46198.50797810185</v>
+        <v>46198.341311435186</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>178</v>
@@ -5965,11 +5965,11 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.635046296295</v>
+        <v>46188.46837962963</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.67895050926</v>
+        <v>46188.51228384259</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6028,11 +6028,11 @@
         <v>256</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.63505403935</v>
+        <v>46188.46838737269</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.50797702547</v>
+        <v>46198.341310358795</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>178</v>
@@ -6081,11 +6081,11 @@
         <v>258</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.63506813657</v>
+        <v>46188.46840146991</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.507975162036</v>
+        <v>46198.34130849537</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>178</v>
@@ -6134,11 +6134,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.63509704861</v>
+        <v>46188.468430381945</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.67906003472</v>
+        <v>46188.51239336806</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6197,11 +6197,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.635102939814</v>
+        <v>46188.46843627315</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.50797759259</v>
+        <v>46198.34131092593</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>178</v>
@@ -6250,11 +6250,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.63510991898</v>
+        <v>46188.46844325231</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46198.50796203704</v>
+        <v>46198.34129537037</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>178</v>
@@ -6303,11 +6303,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.63513603009</v>
+        <v>46188.468469363426</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.6792096875</v>
+        <v>46188.51254302083</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6366,11 +6366,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.63514172454</v>
+        <v>46188.468475057874</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46188.679159583335</v>
+        <v>46188.51249291666</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>179</v>
@@ -6417,11 +6417,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.63514853009</v>
+        <v>46188.46848186343</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46188.6791566551</v>
+        <v>46188.512489988425</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>178</v>
@@ -6468,11 +6468,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.63521115741</v>
+        <v>46188.46854449074</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46188.68062993056</v>
+        <v>46188.51396326389</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6531,11 +6531,11 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.63521795139</v>
+        <v>46188.46855128472</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46188.68070547454</v>
+        <v>46188.51403880787</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>178</v>
@@ -6584,11 +6584,11 @@
         <v>278</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.635222916666</v>
+        <v>46188.46855625</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.680702488426</v>
+        <v>46188.51403582176</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>178</v>
@@ -6637,11 +6637,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.635247199076</v>
+        <v>46188.46858053241</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.67010366898</v>
+        <v>46188.50343700231</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -6684,11 +6684,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.635250844905</v>
+        <v>46188.46858417824</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.68085204861</v>
+        <v>46188.514185381944</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>283</v>
@@ -6747,11 +6747,11 @@
         <v>287</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.63525673611</v>
+        <v>46188.468590069446</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46188.68080148148</v>
+        <v>46188.51413481482</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>178</v>
@@ -6800,11 +6800,11 @@
         <v>289</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.635261689815</v>
+        <v>46188.46859502315</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46188.680797928246</v>
+        <v>46188.514131261574</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>178</v>
@@ -6853,11 +6853,11 @@
         <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.635279375</v>
+        <v>46188.46861270833</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.68118097223</v>
+        <v>46188.514514305556</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -6916,11 +6916,11 @@
         <v>292</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.63528446759</v>
+        <v>46188.46861780093</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46188.68112704861</v>
+        <v>46188.51446038194</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>178</v>
@@ -6967,11 +6967,11 @@
         <v>294</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.6352894213</v>
+        <v>46188.46862275463</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46188.68112425926</v>
+        <v>46188.514457592595</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>178</v>
@@ -7018,11 +7018,11 @@
         <v>296</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.63530922454</v>
+        <v>46188.46864255787</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.68135644676</v>
+        <v>46188.51468978009</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>297</v>
@@ -7081,11 +7081,11 @@
         <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.63531412037</v>
+        <v>46188.4686474537</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46188.681314560185</v>
+        <v>46188.51464789352</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>178</v>
@@ -7132,11 +7132,11 @@
         <v>300</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.63532239583</v>
+        <v>46188.46865572917</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46188.68131152778</v>
+        <v>46188.51464486111</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>178</v>
@@ -7183,11 +7183,11 @@
         <v>301</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.63538068287</v>
+        <v>46188.4687140162</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.68149567129</v>
+        <v>46188.514829004635</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>302</v>
@@ -7246,11 +7246,11 @@
         <v>304</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.6353874537</v>
+        <v>46188.46872078704</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46188.68144886574</v>
+        <v>46188.514782199076</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>178</v>
@@ -7299,11 +7299,11 @@
         <v>305</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.63539206018</v>
+        <v>46188.46872539352</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46188.681445636576</v>
+        <v>46188.51477896991</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>178</v>
@@ -7352,11 +7352,11 @@
         <v>306</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.635410682866</v>
+        <v>46188.46874401621</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.67123894676</v>
+        <v>46188.50457228009</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>307</v>
@@ -7399,11 +7399,11 @@
         <v>309</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.635413993055</v>
+        <v>46188.46874732639</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.68161465278</v>
+        <v>46188.514947986114</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>310</v>
@@ -7462,11 +7462,11 @@
         <v>313</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.63541944444</v>
+        <v>46188.46875277778</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.920573842595</v>
+        <v>46188.753907175924</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>314</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -1609,13 +1609,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46188.46749296296</v>
+        <v>46188.634159629626</v>
       </c>
       <c r="C4" s="5">
-        <v>46188.75302089121</v>
+        <v>46188.91968755787</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.753035057875</v>
+        <v>46188.91970172454</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1662,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46188.46764418982</v>
+        <v>46188.634310856476</v>
       </c>
       <c r="C5" s="9">
-        <v>46188.75300751158</v>
+        <v>46188.919674178236</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.753021655095</v>
+        <v>46188.91968832176</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1727,13 +1727,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46188.46764981482</v>
+        <v>46188.63431648148</v>
       </c>
       <c r="C6" s="5">
-        <v>46188.752876631945</v>
+        <v>46188.919543298616</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.75289478009</v>
+        <v>46188.91956144676</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1792,13 +1792,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="9">
-        <v>46188.467655162036</v>
+        <v>46188.63432182871</v>
       </c>
       <c r="C7" s="9">
-        <v>46188.752927615744</v>
+        <v>46188.91959428241</v>
       </c>
       <c r="D7" s="9">
-        <v>46188.752942754625</v>
+        <v>46188.9196094213</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>36</v>
@@ -1857,13 +1857,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46188.46765997686</v>
+        <v>46188.634326643514</v>
       </c>
       <c r="C8" s="5">
-        <v>46188.75296844907</v>
+        <v>46188.919635115744</v>
       </c>
       <c r="D8" s="5">
-        <v>46188.752985439816</v>
+        <v>46188.91965210648</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1922,13 +1922,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46188.46749880787</v>
+        <v>46188.634165474534</v>
       </c>
       <c r="C9" s="9">
-        <v>46188.753913148146</v>
+        <v>46188.92057981482</v>
       </c>
       <c r="D9" s="9">
-        <v>46188.753923599535</v>
+        <v>46188.92059026621</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -1975,13 +1975,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46188.467665069446</v>
+        <v>46188.63433173611</v>
       </c>
       <c r="C10" s="5">
-        <v>46188.75344472222</v>
+        <v>46188.920111388885</v>
       </c>
       <c r="D10" s="5">
-        <v>46188.7534465162</v>
+        <v>46188.920113182874</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2040,13 +2040,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46188.46767643519</v>
+        <v>46188.63434310185</v>
       </c>
       <c r="C11" s="9">
-        <v>46188.7530787037</v>
+        <v>46188.91974537037</v>
       </c>
       <c r="D11" s="9">
-        <v>46188.75365456019</v>
+        <v>46188.92032122685</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2105,13 +2105,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46188.46768365741</v>
+        <v>46188.63435032408</v>
       </c>
       <c r="C12" s="5">
-        <v>46188.753818310186</v>
+        <v>46188.92048497685</v>
       </c>
       <c r="D12" s="5">
-        <v>46188.75383458333</v>
+        <v>46188.92050125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2170,13 +2170,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="9">
-        <v>46188.46769009259</v>
+        <v>46188.634356759256</v>
       </c>
       <c r="C13" s="9">
-        <v>46188.75389753473</v>
+        <v>46188.920564201384</v>
       </c>
       <c r="D13" s="9">
-        <v>46188.753913252316</v>
+        <v>46188.92057991898</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2235,11 +2235,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46188.46750333333</v>
+        <v>46188.634170000005</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.41980056713</v>
+        <v>46197.58646723379</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2282,13 +2282,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46188.46769949074</v>
+        <v>46188.63436615741</v>
       </c>
       <c r="C15" s="9">
-        <v>46188.753991261576</v>
+        <v>46188.92065792824</v>
       </c>
       <c r="D15" s="9">
-        <v>46189.647731018515</v>
+        <v>46189.814397685186</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2347,13 +2347,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46188.46770592593</v>
+        <v>46188.63437259259</v>
       </c>
       <c r="C16" s="5">
-        <v>46188.754669270835</v>
+        <v>46188.9213359375</v>
       </c>
       <c r="D16" s="5">
-        <v>46189.64775527778</v>
+        <v>46189.814421944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2412,13 +2412,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46188.467712627316</v>
+        <v>46188.63437929398</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.41979372685</v>
+        <v>46197.58646039352</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.41981302084</v>
+        <v>46197.586479687496</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2477,11 +2477,11 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46188.467719699074</v>
+        <v>46188.63438636574</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.34132099537</v>
+        <v>46198.50798766204</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2540,11 +2540,11 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46188.467726041665</v>
+        <v>46188.634392708336</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46198.34132096065</v>
+        <v>46198.507987627316</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2603,11 +2603,11 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46188.467731620374</v>
+        <v>46188.63439828704</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.341321562504</v>
+        <v>46198.50798822917</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2666,11 +2666,11 @@
         <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46188.46773638889</v>
+        <v>46188.634403055556</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.34132099537</v>
+        <v>46198.50798766204</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2729,13 +2729,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46189.614092627315</v>
+        <v>46189.78075929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.419957129634</v>
+        <v>46197.58662379629</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.41997003472</v>
+        <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2784,13 +2784,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46189.645209375</v>
+        <v>46189.81187604167</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.41994010417</v>
+        <v>46197.586606770834</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.41995747686</v>
+        <v>46197.586624143514</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -2849,13 +2849,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46189.64537734954</v>
+        <v>46189.8120440162</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.41988243056</v>
+        <v>46197.58654909722</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.41990039352</v>
+        <v>46197.586567060185</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2914,11 +2914,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.467508194444</v>
+        <v>46188.634174861116</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46189.616145810185</v>
+        <v>46189.78281247686</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -2961,11 +2961,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46188.46775931713</v>
+        <v>46188.63442598379</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.01117863426</v>
+        <v>46197.177845300925</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -3024,11 +3024,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46188.46776513889</v>
+        <v>46188.634431805556</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.41980221064</v>
+        <v>46197.586468877314</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3083,11 +3083,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46188.46777074074</v>
+        <v>46188.63443740741</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46188.50710700231</v>
+        <v>46188.67377366898</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3142,11 +3142,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.46784917824</v>
+        <v>46188.63451584491</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46188.50744789352</v>
+        <v>46188.674114560185</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3205,11 +3205,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.467855532406</v>
+        <v>46188.63452219908</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.50740560185</v>
+        <v>46188.67407226852</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3264,11 +3264,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.46786152778</v>
+        <v>46188.634528194445</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46188.50740297454</v>
+        <v>46188.6740696412</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3323,11 +3323,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.46786741898</v>
+        <v>46188.63453408565</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46188.507572083334</v>
+        <v>46188.67423875</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3386,11 +3386,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.46787158565</v>
+        <v>46188.634538252314</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46188.50752002315</v>
+        <v>46188.674186689816</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>83</v>
@@ -3439,11 +3439,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.46787663194</v>
+        <v>46188.63454329861</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46188.507517210644</v>
+        <v>46188.674183877316</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3492,11 +3492,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.46788137731</v>
+        <v>46188.63454804398</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46188.5080371875</v>
+        <v>46188.674703854165</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -3555,11 +3555,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.467886122686</v>
+        <v>46188.63455278936</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46188.50768351852</v>
+        <v>46188.67435018519</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>89</v>
@@ -3608,11 +3608,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.46789144676</v>
+        <v>46188.63455811342</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46188.50767990741</v>
+        <v>46188.67434657407</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3661,11 +3661,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.467897152776</v>
+        <v>46188.63456381945</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46188.50798180555</v>
+        <v>46188.674648472224</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3714,11 +3714,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.46790071759</v>
+        <v>46188.63456738426</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46188.51020636574</v>
+        <v>46188.67687303241</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3777,11 +3777,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.467905</v>
+        <v>46188.63457166667</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46188.51016978009</v>
+        <v>46188.67683644676</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>86</v>
@@ -3830,11 +3830,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.46791003473</v>
+        <v>46188.634576701385</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46188.51016694444</v>
+        <v>46188.67683361111</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -3883,11 +3883,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.467512546296</v>
+        <v>46188.63417921297</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46198.34124650463</v>
+        <v>46198.5079131713</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3932,13 +3932,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.467915810186</v>
+        <v>46188.63458247685</v>
       </c>
       <c r="C43" s="9">
-        <v>46196.35815153935</v>
+        <v>46196.52481820602</v>
       </c>
       <c r="D43" s="9">
-        <v>46197.54957185185</v>
+        <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -3997,13 +3997,13 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.4679219213</v>
+        <v>46188.634588587964</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.34122449074</v>
+        <v>46198.50789115741</v>
       </c>
       <c r="D44" s="5">
-        <v>46198.3412469676</v>
+        <v>46198.50791363426</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>166</v>
@@ -4062,13 +4062,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.46792831019</v>
+        <v>46188.63459497685</v>
       </c>
       <c r="C45" s="9">
-        <v>46198.341287118055</v>
+        <v>46198.50795378472</v>
       </c>
       <c r="D45" s="9">
-        <v>46198.3413046875</v>
+        <v>46198.50797135416</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4127,11 +4127,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.4679431713</v>
+        <v>46188.63460983796</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.51043608796</v>
+        <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4190,11 +4190,11 @@
         <v>177</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.46794728009</v>
+        <v>46188.634613946764</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46188.51039945602</v>
+        <v>46188.677066122684</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>178</v>
@@ -4243,11 +4243,11 @@
         <v>181</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.46795173611</v>
+        <v>46188.63461840278</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46188.51039618056</v>
+        <v>46188.67706284722</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4296,11 +4296,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.46800628472</v>
+        <v>46188.63467295139</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.493675011574</v>
+        <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4343,11 +4343,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.468010972225</v>
+        <v>46188.63467763889</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46188.510564537035</v>
+        <v>46188.67723120371</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4406,11 +4406,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.46801827547</v>
+        <v>46188.634684942124</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.51065322917</v>
+        <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4469,11 +4469,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.468026296294</v>
+        <v>46188.634692962965</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46188.510561331015</v>
+        <v>46188.67722799769</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4532,11 +4532,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.468032881945</v>
+        <v>46188.63469954861</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.51065034722</v>
+        <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4595,11 +4595,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.468038935185</v>
+        <v>46188.63470560186</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46188.51055827546</v>
+        <v>46188.677224942134</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4658,11 +4658,11 @@
         <v>202</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.468044884256</v>
+        <v>46188.63471155093</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.51064685185</v>
+        <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4721,11 +4721,11 @@
         <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.46805064815</v>
+        <v>46188.63471731481</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.49599372685</v>
+        <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -4768,11 +4768,11 @@
         <v>206</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.46805440972</v>
+        <v>46188.63472107639</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.51107644676</v>
+        <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>207</v>
@@ -4831,11 +4831,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.46806591435</v>
+        <v>46188.63473258102</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.51079777778</v>
+        <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>178</v>
@@ -4884,11 +4884,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.46807454861</v>
+        <v>46188.63474121528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.510794421294</v>
+        <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>178</v>
@@ -4937,11 +4937,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.46810618056</v>
+        <v>46188.63477284722</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.511072685185</v>
+        <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5000,11 +5000,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.46811210648</v>
+        <v>46188.63477877315</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46198.3413091088</v>
+        <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>178</v>
@@ -5053,11 +5053,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.46811938657</v>
+        <v>46188.63478605324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.341309641204</v>
+        <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>178</v>
@@ -5106,11 +5106,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.4681887037</v>
+        <v>46188.63485537037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.511136747686</v>
+        <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5169,11 +5169,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.46819513889</v>
+        <v>46188.634861805556</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46198.3413070949</v>
+        <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>178</v>
@@ -5222,11 +5222,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.46820215278</v>
+        <v>46188.63486881944</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46198.341296388884</v>
+        <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>178</v>
@@ -5275,11 +5275,11 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.46822664352</v>
+        <v>46188.63489331018</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46188.49781223379</v>
+        <v>46188.664478900464</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>183</v>
@@ -5322,11 +5322,11 @@
         <v>229</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.46823672454</v>
+        <v>46188.634903391205</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46198.00186423611</v>
+        <v>46198.16853090278</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5385,11 +5385,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.468243379626</v>
+        <v>46188.6349100463</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.41989109953</v>
+        <v>46197.586557766204</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5448,11 +5448,11 @@
         <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.46824984954</v>
+        <v>46188.6349165162</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.41995064815</v>
+        <v>46197.58661731481</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>
@@ -5511,11 +5511,11 @@
         <v>235</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.468256249995</v>
+        <v>46188.634922916666</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46188.51123265046</v>
+        <v>46188.67789931713</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5574,11 +5574,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.468261284725</v>
+        <v>46188.63492795139</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.42039136574</v>
+        <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>239</v>
@@ -5621,11 +5621,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.46826486111</v>
+        <v>46188.63493152778</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.51135721065</v>
+        <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5684,11 +5684,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.468273680555</v>
+        <v>46188.63494034723</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.51131699074</v>
+        <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>178</v>
@@ -5737,11 +5737,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.46827848379</v>
+        <v>46188.634945150465</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.51131390047</v>
+        <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>178</v>
@@ -5790,13 +5790,13 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.46829700231</v>
+        <v>46188.634963668985</v>
       </c>
       <c r="C75" s="9">
-        <v>46197.42038163195</v>
+        <v>46197.58704829861</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.42039403935</v>
+        <v>46197.58706070602</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5855,13 +5855,13 @@
         <v>249</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.46830221065</v>
+        <v>46188.63496887732</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.42028853009</v>
+        <v>46197.58695519676</v>
       </c>
       <c r="D76" s="5">
-        <v>46198.34130777778</v>
+        <v>46198.507974444445</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>178</v>
@@ -5910,13 +5910,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.46831445602</v>
+        <v>46188.63498112268</v>
       </c>
       <c r="C77" s="9">
-        <v>46197.42036866898</v>
+        <v>46197.587035335644</v>
       </c>
       <c r="D77" s="9">
-        <v>46198.341311435186</v>
+        <v>46198.50797810185</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>178</v>
@@ -5965,11 +5965,11 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.46837962963</v>
+        <v>46188.635046296295</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.51228384259</v>
+        <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6028,11 +6028,11 @@
         <v>256</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.46838737269</v>
+        <v>46188.63505403935</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.341310358795</v>
+        <v>46198.50797702547</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>178</v>
@@ -6081,11 +6081,11 @@
         <v>258</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.46840146991</v>
+        <v>46188.63506813657</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.34130849537</v>
+        <v>46198.507975162036</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>178</v>
@@ -6134,11 +6134,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.468430381945</v>
+        <v>46188.63509704861</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.51239336806</v>
+        <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6197,11 +6197,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.46843627315</v>
+        <v>46188.635102939814</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.34131092593</v>
+        <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>178</v>
@@ -6250,11 +6250,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.46844325231</v>
+        <v>46188.63510991898</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46198.34129537037</v>
+        <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>178</v>
@@ -6303,11 +6303,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.468469363426</v>
+        <v>46188.63513603009</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.51254302083</v>
+        <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6366,11 +6366,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.468475057874</v>
+        <v>46188.63514172454</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46188.51249291666</v>
+        <v>46188.679159583335</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>179</v>
@@ -6417,11 +6417,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.46848186343</v>
+        <v>46188.63514853009</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46188.512489988425</v>
+        <v>46188.6791566551</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>178</v>
@@ -6468,11 +6468,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.46854449074</v>
+        <v>46188.63521115741</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46188.51396326389</v>
+        <v>46188.68062993056</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6531,11 +6531,11 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.46855128472</v>
+        <v>46188.63521795139</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46188.51403880787</v>
+        <v>46188.68070547454</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>178</v>
@@ -6584,11 +6584,11 @@
         <v>278</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.46855625</v>
+        <v>46188.635222916666</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.51403582176</v>
+        <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>178</v>
@@ -6637,11 +6637,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.46858053241</v>
+        <v>46188.635247199076</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.50343700231</v>
+        <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -6684,11 +6684,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.46858417824</v>
+        <v>46188.635250844905</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.514185381944</v>
+        <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>283</v>
@@ -6747,11 +6747,11 @@
         <v>287</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.468590069446</v>
+        <v>46188.63525673611</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46188.51413481482</v>
+        <v>46188.68080148148</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>178</v>
@@ -6800,11 +6800,11 @@
         <v>289</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.46859502315</v>
+        <v>46188.635261689815</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46188.514131261574</v>
+        <v>46188.680797928246</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>178</v>
@@ -6853,11 +6853,11 @@
         <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.46861270833</v>
+        <v>46188.635279375</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.514514305556</v>
+        <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -6916,11 +6916,11 @@
         <v>292</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.46861780093</v>
+        <v>46188.63528446759</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46188.51446038194</v>
+        <v>46188.68112704861</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>178</v>
@@ -6967,11 +6967,11 @@
         <v>294</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.46862275463</v>
+        <v>46188.6352894213</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46188.514457592595</v>
+        <v>46188.68112425926</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>178</v>
@@ -7018,11 +7018,11 @@
         <v>296</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.46864255787</v>
+        <v>46188.63530922454</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.51468978009</v>
+        <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>297</v>
@@ -7081,11 +7081,11 @@
         <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.4686474537</v>
+        <v>46188.63531412037</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46188.51464789352</v>
+        <v>46188.681314560185</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>178</v>
@@ -7132,11 +7132,11 @@
         <v>300</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.46865572917</v>
+        <v>46188.63532239583</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46188.51464486111</v>
+        <v>46188.68131152778</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>178</v>
@@ -7183,11 +7183,11 @@
         <v>301</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.4687140162</v>
+        <v>46188.63538068287</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.514829004635</v>
+        <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>302</v>
@@ -7246,11 +7246,11 @@
         <v>304</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.46872078704</v>
+        <v>46188.6353874537</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46188.514782199076</v>
+        <v>46188.68144886574</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>178</v>
@@ -7299,11 +7299,11 @@
         <v>305</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.46872539352</v>
+        <v>46188.63539206018</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46188.51477896991</v>
+        <v>46188.681445636576</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>178</v>
@@ -7352,11 +7352,11 @@
         <v>306</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.46874401621</v>
+        <v>46188.635410682866</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.50457228009</v>
+        <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>307</v>
@@ -7399,11 +7399,11 @@
         <v>309</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.46874732639</v>
+        <v>46188.635413993055</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.514947986114</v>
+        <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>310</v>
@@ -7462,11 +7462,11 @@
         <v>313</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.46875277778</v>
+        <v>46188.63541944444</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.753907175924</v>
+        <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>314</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -4003,7 +4003,7 @@
         <v>46198.50789115741</v>
       </c>
       <c r="D44" s="5">
-        <v>46198.50791363426</v>
+        <v>46202.17234546297</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>166</v>
@@ -4047,8 +4047,8 @@
       <c r="R44" s="5">
         <v>46209</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>93</v>
+      <c r="S44" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -4194,7 +4194,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46188.677066122684</v>
+        <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>178</v>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46188.67706284722</v>
+        <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46188.679159583335</v>
+        <v>46202.95697799769</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>179</v>
@@ -6384,7 +6384,9 @@
       <c r="H85" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I85" s="10"/>
+      <c r="I85" s="9">
+        <v>46258</v>
+      </c>
       <c r="J85" s="9">
         <v>46258</v>
       </c>
@@ -6421,7 +6423,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46188.6791566551</v>
+        <v>46202.95697554398</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>178</v>
@@ -6435,7 +6437,9 @@
       <c r="H86" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I86" s="6"/>
+      <c r="I86" s="5">
+        <v>46258</v>
+      </c>
       <c r="J86" s="5">
         <v>46258</v>
       </c>
@@ -6472,7 +6476,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46188.68062993056</v>
+        <v>46202.95705052083</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6535,7 +6539,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46188.68070547454</v>
+        <v>46202.957050694444</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>178</v>
@@ -6550,10 +6554,10 @@
         <v>72</v>
       </c>
       <c r="I88" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="J88" s="5">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
@@ -6751,7 +6755,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46188.68080148148</v>
+        <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>178</v>
@@ -6804,7 +6808,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46188.680797928246</v>
+        <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>178</v>
@@ -6920,7 +6924,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46188.68112704861</v>
+        <v>46202.956975532405</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>178</v>
@@ -6934,7 +6938,9 @@
       <c r="H95" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="I95" s="10"/>
+      <c r="I95" s="9">
+        <v>46262</v>
+      </c>
       <c r="J95" s="9">
         <v>46262</v>
       </c>
@@ -6971,7 +6977,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46188.68112425926</v>
+        <v>46202.956975497684</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>178</v>
@@ -6985,7 +6991,9 @@
       <c r="H96" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I96" s="6"/>
+      <c r="I96" s="5">
+        <v>46262</v>
+      </c>
       <c r="J96" s="5">
         <v>46262</v>
       </c>
@@ -7085,7 +7093,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46188.681314560185</v>
+        <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>178</v>
@@ -7099,7 +7107,9 @@
       <c r="H98" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="I98" s="6"/>
+      <c r="I98" s="5">
+        <v>46265</v>
+      </c>
       <c r="J98" s="5">
         <v>46265</v>
       </c>
@@ -7136,7 +7146,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46188.68131152778</v>
+        <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>178</v>
@@ -7150,7 +7160,9 @@
       <c r="H99" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="I99" s="10"/>
+      <c r="I99" s="9">
+        <v>46265</v>
+      </c>
       <c r="J99" s="9">
         <v>46265</v>
       </c>
@@ -7250,7 +7262,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46188.68144886574</v>
+        <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>178</v>
@@ -7303,7 +7315,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46188.681445636576</v>
+        <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>178</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -4068,7 +4068,7 @@
         <v>46198.50795378472</v>
       </c>
       <c r="D45" s="9">
-        <v>46198.50797135416</v>
+        <v>46203.17655171297</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4112,8 +4112,8 @@
       <c r="R45" s="9">
         <v>46210</v>
       </c>
-      <c r="S45" s="7" t="s">
-        <v>93</v>
+      <c r="S45" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="T45" s="10">
         <v>1</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -256,7 +256,7 @@
     <t>benjamin.bustos@zitron.com</t>
   </si>
   <si>
-    <t>Propuesta compras:,Generación OC Rodete OT 4316</t>
+    <t>Propuesta compras:,Generación OC Rodete OT 4360</t>
   </si>
   <si>
     <t>1215728035784447</t>
@@ -325,7 +325,7 @@
     <t>motor ot 4360</t>
   </si>
   <si>
-    <t>Reserva producción,Recepcionx motor</t>
+    <t>Reserva producción,Recepcion motor</t>
   </si>
   <si>
     <t>1215771707606685</t>
@@ -334,7 +334,7 @@
     <t>Alabe  ot 4360</t>
   </si>
   <si>
-    <t>Reserva producción,Recepcionx Alabe</t>
+    <t>Reserva producción,Recepcion Alabe</t>
   </si>
   <si>
     <t>1215727332551586</t>
@@ -358,7 +358,7 @@
     <t>ecarico@zitron.com</t>
   </si>
   <si>
-    <t>Generación OC Rodete OT 4316,Fabricación Rodete OT 4316</t>
+    <t>Generación OC Rodete OT 4360,Fabricación Rodete OT 4360</t>
   </si>
   <si>
     <t>Media</t>
@@ -370,16 +370,16 @@
     <t>1215728035819308</t>
   </si>
   <si>
-    <t>Generación OC Rodete OT 4316</t>
-  </si>
-  <si>
-    <t>rodete OT 4360,Fabricación Rodete OT 4316</t>
+    <t>Generación OC Rodete OT 4360</t>
+  </si>
+  <si>
+    <t>rodete OT 4360,Fabricación Rodete OT 4360</t>
   </si>
   <si>
     <t>1215728035829709</t>
   </si>
   <si>
-    <t>Fabricación Rodete OT 4316</t>
+    <t>Fabricación Rodete OT 4360</t>
   </si>
   <si>
     <t>Recepcion Rodete,rodete OT 4360</t>
@@ -721,7 +721,7 @@
     <t>1215727940067011</t>
   </si>
   <si>
-    <t>Recepcionx Alabe,Recepcionx motor,Recepcion Rodete</t>
+    <t>Recepcion Alabe,Recepcion motor,Recepcion Rodete</t>
   </si>
   <si>
     <t>1215727940078553</t>
@@ -733,13 +733,13 @@
     <t>1215727940078575</t>
   </si>
   <si>
-    <t>Recepcionx Alabe</t>
+    <t>Recepcion Alabe</t>
   </si>
   <si>
     <t>1215727793148813</t>
   </si>
   <si>
-    <t>Recepcionx motor</t>
+    <t>Recepcion motor</t>
   </si>
   <si>
     <t>1215728036191110</t>
@@ -787,7 +787,7 @@
     <t>1215727940112407</t>
   </si>
   <si>
-    <t>Recepcionx Alabe,check planos</t>
+    <t>Recepcion Alabe,check planos</t>
   </si>
   <si>
     <t>Montaje Alabe,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
@@ -826,7 +826,7 @@
     <t>1215728008590051</t>
   </si>
   <si>
-    <t>Recepcionx motor,check planos</t>
+    <t>Recepcion motor,check planos</t>
   </si>
   <si>
     <t>Montaje motor,OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46197.586468877314</v>
+        <v>46203.550629606485</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46188.67377366898</v>
+        <v>46203.55067265047</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46188.664478900464</v>
+        <v>46203.55043523148</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>183</v>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46197.586557766204</v>
+        <v>46203.55044364583</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46197.58661731481</v>
+        <v>46203.550511388894</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -2965,7 +2965,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46197.177845300925</v>
+        <v>46204.17206540509</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46203.55067265047</v>
+        <v>46204.172067569445</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -218,7 +218,7 @@
     <t>Propuesta compras:</t>
   </si>
   <si>
-    <t>propuesta motor,propuesta alabes,propuesta Corte Laser OT 43164360,propuesta nucleo rodeteOT 4360</t>
+    <t>propuesta motor,propuesta alabes,propuesta Corte Laser OT 4360,propuesta nucleo rodeteOT 4360</t>
   </si>
   <si>
     <t>1215727792562799</t>
@@ -262,7 +262,7 @@
     <t>1215728035784447</t>
   </si>
   <si>
-    <t>propuesta Corte Laser OT 43164360</t>
+    <t>propuesta Corte Laser OT 4360</t>
   </si>
   <si>
     <t>hugo isla martinez</t>
@@ -550,7 +550,7 @@
     <t>hgutierrez@zitron.com</t>
   </si>
   <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 43164360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 4360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215727939821604</t>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46198.50798766204</v>
+        <v>46204.903678159724</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -277,6 +277,9 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4360</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
@@ -359,9 +362,6 @@
   </si>
   <si>
     <t>Generación OC Rodete OT 4360,Fabricación Rodete OT 4360</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -1609,13 +1609,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46188.634159629626</v>
+        <v>46188.46749296296</v>
       </c>
       <c r="C4" s="5">
-        <v>46188.91968755787</v>
+        <v>46188.75302089121</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.91970172454</v>
+        <v>46188.753035057875</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1662,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46188.634310856476</v>
+        <v>46188.46764418982</v>
       </c>
       <c r="C5" s="9">
-        <v>46188.919674178236</v>
+        <v>46188.75300751158</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.91968832176</v>
+        <v>46188.753021655095</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1727,13 +1727,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46188.63431648148</v>
+        <v>46188.46764981482</v>
       </c>
       <c r="C6" s="5">
-        <v>46188.919543298616</v>
+        <v>46188.752876631945</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.91956144676</v>
+        <v>46188.75289478009</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1792,13 +1792,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="9">
-        <v>46188.63432182871</v>
+        <v>46188.467655162036</v>
       </c>
       <c r="C7" s="9">
-        <v>46188.91959428241</v>
+        <v>46188.752927615744</v>
       </c>
       <c r="D7" s="9">
-        <v>46188.9196094213</v>
+        <v>46188.752942754625</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>36</v>
@@ -1857,13 +1857,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46188.634326643514</v>
+        <v>46188.46765997686</v>
       </c>
       <c r="C8" s="5">
-        <v>46188.919635115744</v>
+        <v>46188.75296844907</v>
       </c>
       <c r="D8" s="5">
-        <v>46188.91965210648</v>
+        <v>46188.752985439816</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1922,13 +1922,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46188.634165474534</v>
+        <v>46188.46749880787</v>
       </c>
       <c r="C9" s="9">
-        <v>46188.92057981482</v>
+        <v>46188.753913148146</v>
       </c>
       <c r="D9" s="9">
-        <v>46188.92059026621</v>
+        <v>46188.753923599535</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -1975,13 +1975,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46188.63433173611</v>
+        <v>46188.467665069446</v>
       </c>
       <c r="C10" s="5">
-        <v>46188.920111388885</v>
+        <v>46188.75344472222</v>
       </c>
       <c r="D10" s="5">
-        <v>46188.920113182874</v>
+        <v>46188.7534465162</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2040,13 +2040,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46188.63434310185</v>
+        <v>46188.46767643519</v>
       </c>
       <c r="C11" s="9">
-        <v>46188.91974537037</v>
+        <v>46188.7530787037</v>
       </c>
       <c r="D11" s="9">
-        <v>46188.92032122685</v>
+        <v>46188.75365456019</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2105,13 +2105,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46188.63435032408</v>
+        <v>46188.46768365741</v>
       </c>
       <c r="C12" s="5">
-        <v>46188.92048497685</v>
+        <v>46188.753818310186</v>
       </c>
       <c r="D12" s="5">
-        <v>46188.92050125</v>
+        <v>46188.75383458333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2170,13 +2170,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="9">
-        <v>46188.634356759256</v>
+        <v>46188.46769009259</v>
       </c>
       <c r="C13" s="9">
-        <v>46188.920564201384</v>
+        <v>46188.75389753473</v>
       </c>
       <c r="D13" s="9">
-        <v>46188.92057991898</v>
+        <v>46188.753913252316</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2235,11 +2235,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46188.634170000005</v>
+        <v>46188.46750333333</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.58646723379</v>
+        <v>46197.41980056713</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2282,13 +2282,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46188.63436615741</v>
+        <v>46188.46769949074</v>
       </c>
       <c r="C15" s="9">
-        <v>46188.92065792824</v>
+        <v>46188.753991261576</v>
       </c>
       <c r="D15" s="9">
-        <v>46189.814397685186</v>
+        <v>46189.647731018515</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2347,13 +2347,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46188.63437259259</v>
+        <v>46188.46770592593</v>
       </c>
       <c r="C16" s="5">
-        <v>46188.9213359375</v>
+        <v>46188.754669270835</v>
       </c>
       <c r="D16" s="5">
-        <v>46189.814421944444</v>
+        <v>46189.64775527778</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2412,13 +2412,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46188.63437929398</v>
+        <v>46188.467712627316</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.58646039352</v>
+        <v>46197.41979372685</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.586479687496</v>
+        <v>46197.41981302084</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2477,11 +2477,11 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46188.63438636574</v>
+        <v>46188.467719699074</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46204.903678159724</v>
+        <v>46205.025704155094</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2525,29 +2525,29 @@
       <c r="R18" s="5">
         <v>46212</v>
       </c>
-      <c r="S18" s="11" t="s">
-        <v>32</v>
+      <c r="S18" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
       <c r="U18" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46188.634392708336</v>
+        <v>46188.467726041665</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46198.507987627316</v>
+        <v>46205.02570414352</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2580,7 +2580,7 @@
         <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="9">
         <v>46211</v>
@@ -2588,29 +2588,29 @@
       <c r="R19" s="9">
         <v>46212</v>
       </c>
-      <c r="S19" s="11" t="s">
-        <v>32</v>
+      <c r="S19" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="T19" s="10">
         <v>0</v>
       </c>
       <c r="U19" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46188.63439828704</v>
+        <v>46188.467731620374</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46198.50798822917</v>
+        <v>46205.02570416666</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2643,7 +2643,7 @@
         <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46211</v>
@@ -2651,29 +2651,29 @@
       <c r="R20" s="5">
         <v>46212</v>
       </c>
-      <c r="S20" s="11" t="s">
-        <v>32</v>
+      <c r="S20" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
       <c r="U20" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46188.634403055556</v>
+        <v>46188.46773638889</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46198.50798766204</v>
+        <v>46205.02570409722</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2706,7 +2706,7 @@
         <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="9">
         <v>46211</v>
@@ -2714,31 +2714,31 @@
       <c r="R21" s="9">
         <v>46212</v>
       </c>
-      <c r="S21" s="11" t="s">
-        <v>32</v>
+      <c r="S21" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="T21" s="10">
         <v>0</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46189.78075929398</v>
+        <v>46189.614092627315</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.58662379629</v>
+        <v>46197.419957129634</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.58663670139</v>
+        <v>46197.41997003472</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2762,7 +2762,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2770,7 +2770,7 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2781,19 +2781,19 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46189.81187604167</v>
+        <v>46189.645209375</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.586606770834</v>
+        <v>46197.41994010417</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.586624143514</v>
+        <v>46197.41995747686</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2820,13 +2820,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>64</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q23" s="9">
         <v>46183</v>
@@ -2846,19 +2846,19 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46189.8120440162</v>
+        <v>46189.64537734954</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.58654909722</v>
+        <v>46197.41988243056</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.586567060185</v>
+        <v>46197.41990039352</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2885,13 +2885,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="5">
         <v>46183</v>
@@ -2911,17 +2911,17 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.634174861116</v>
+        <v>46188.467508194444</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46189.78281247686</v>
+        <v>46189.616145810185</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -2945,7 +2945,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -2958,26 +2958,26 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46188.63442598379</v>
+        <v>46188.46775931713</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46204.17206540509</v>
+        <v>46205.016595671295</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -2995,13 +2995,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q26" s="5">
         <v>46183</v>
@@ -3009,8 +3009,8 @@
       <c r="R26" s="5">
         <v>46204</v>
       </c>
-      <c r="S26" s="12" t="s">
-        <v>108</v>
+      <c r="S26" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -3024,11 +3024,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46188.634431805556</v>
+        <v>46188.46776513889</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46203.550629606485</v>
+        <v>46203.38396293981</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3037,10 +3037,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3058,7 +3058,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>71</v>
@@ -3069,7 +3069,7 @@
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
@@ -3083,11 +3083,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46188.63443740741</v>
+        <v>46188.46777074074</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46204.172067569445</v>
+        <v>46204.00540090278</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3096,10 +3096,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3117,7 +3117,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>111</v>
@@ -3128,7 +3128,7 @@
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
@@ -3142,11 +3142,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.63451584491</v>
+        <v>46188.46784917824</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46188.674114560185</v>
+        <v>46188.50744789352</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3176,13 +3176,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>120</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q29" s="9">
         <v>46213</v>
@@ -3191,7 +3191,7 @@
         <v>46225</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
@@ -3205,11 +3205,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.63452219908</v>
+        <v>46188.467855532406</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.67407226852</v>
+        <v>46188.50740560185</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3250,7 +3250,7 @@
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3264,11 +3264,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.634528194445</v>
+        <v>46188.46786152778</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46188.6740696412</v>
+        <v>46188.50740297454</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3309,7 +3309,7 @@
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
@@ -3323,11 +3323,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.63453408565</v>
+        <v>46188.46786741898</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46188.67423875</v>
+        <v>46188.507572083334</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3357,7 +3357,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>129</v>
@@ -3372,7 +3372,7 @@
         <v>46225</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -3386,14 +3386,14 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.634538252314</v>
+        <v>46188.46787158565</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46188.674186689816</v>
+        <v>46188.50752002315</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3423,7 +3423,7 @@
         <v>128</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>131</v>
@@ -3439,11 +3439,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.63454329861</v>
+        <v>46188.46787663194</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46188.674183877316</v>
+        <v>46188.507517210644</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3476,7 +3476,7 @@
         <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>134</v>
@@ -3492,11 +3492,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.63454804398</v>
+        <v>46188.46788137731</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46188.674703854165</v>
+        <v>46188.5080371875</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -3526,7 +3526,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>139</v>
@@ -3541,7 +3541,7 @@
         <v>46253</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
@@ -3555,14 +3555,14 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.63455278936</v>
+        <v>46188.467886122686</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46188.67435018519</v>
+        <v>46188.50768351852</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3592,7 +3592,7 @@
         <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>141</v>
@@ -3608,11 +3608,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.63455811342</v>
+        <v>46188.46789144676</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46188.67434657407</v>
+        <v>46188.50767990741</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3645,7 +3645,7 @@
         <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>144</v>
@@ -3661,11 +3661,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.63456381945</v>
+        <v>46188.467897152776</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46188.674648472224</v>
+        <v>46188.50798180555</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3714,11 +3714,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.63456738426</v>
+        <v>46188.46790071759</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46188.67687303241</v>
+        <v>46188.51020636574</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3748,7 +3748,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O39" s="10" t="s">
         <v>151</v>
@@ -3763,7 +3763,7 @@
         <v>46225</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
@@ -3777,14 +3777,14 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.63457166667</v>
+        <v>46188.467905</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46188.67683644676</v>
+        <v>46188.51016978009</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -3814,7 +3814,7 @@
         <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>153</v>
@@ -3830,11 +3830,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.634576701385</v>
+        <v>46188.46791003473</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46188.67683361111</v>
+        <v>46188.51016694444</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -3867,7 +3867,7 @@
         <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>156</v>
@@ -3883,11 +3883,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.63417921297</v>
+        <v>46188.467512546296</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46198.5079131713</v>
+        <v>46198.34124650463</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3924,7 +3924,7 @@
       <c r="S42" s="6"/>
       <c r="T42" s="6"/>
       <c r="U42" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -3932,13 +3932,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.63458247685</v>
+        <v>46188.467915810186</v>
       </c>
       <c r="C43" s="9">
-        <v>46196.52481820602</v>
+        <v>46196.35815153935</v>
       </c>
       <c r="D43" s="9">
-        <v>46197.71623851852</v>
+        <v>46197.54957185185</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -3997,13 +3997,13 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.634588587964</v>
+        <v>46188.4679219213</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.50789115741</v>
+        <v>46198.34122449074</v>
       </c>
       <c r="D44" s="5">
-        <v>46202.17234546297</v>
+        <v>46202.0056787963</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>166</v>
@@ -4048,7 +4048,7 @@
         <v>46209</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4062,13 +4062,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.63459497685</v>
+        <v>46188.46792831019</v>
       </c>
       <c r="C45" s="9">
-        <v>46198.50795378472</v>
+        <v>46198.341287118055</v>
       </c>
       <c r="D45" s="9">
-        <v>46203.17655171297</v>
+        <v>46203.0098850463</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4113,7 +4113,7 @@
         <v>46210</v>
       </c>
       <c r="S45" s="12" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="T45" s="10">
         <v>1</v>
@@ -4127,11 +4127,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.63460983796</v>
+        <v>46188.4679431713</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.677102754635</v>
+        <v>46188.51043608796</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4176,7 +4176,7 @@
         <v>46259</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4190,11 +4190,11 @@
         <v>177</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.634613946764</v>
+        <v>46188.46794728009</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46202.95705038194</v>
+        <v>46202.79038371528</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>178</v>
@@ -4243,11 +4243,11 @@
         <v>181</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.63461840278</v>
+        <v>46188.46795173611</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46202.957206238425</v>
+        <v>46202.79053957176</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4296,11 +4296,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.63467295139</v>
+        <v>46188.46800628472</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.660341678245</v>
+        <v>46188.493675011574</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4343,11 +4343,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.63467763889</v>
+        <v>46188.468010972225</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46188.67723120371</v>
+        <v>46188.510564537035</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4392,7 +4392,7 @@
         <v>46227</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4406,11 +4406,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.634684942124</v>
+        <v>46188.46801827547</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.67731989583</v>
+        <v>46188.51065322917</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4455,7 +4455,7 @@
         <v>46231</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4469,11 +4469,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.634692962965</v>
+        <v>46188.468026296294</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46188.67722799769</v>
+        <v>46188.510561331015</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4518,7 +4518,7 @@
         <v>46227</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4532,11 +4532,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.63469954861</v>
+        <v>46188.468032881945</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.67731701389</v>
+        <v>46188.51065034722</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4581,7 +4581,7 @@
         <v>46231</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4595,11 +4595,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.63470560186</v>
+        <v>46188.468038935185</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46188.677224942134</v>
+        <v>46188.51055827546</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4644,7 +4644,7 @@
         <v>46227</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4658,11 +4658,11 @@
         <v>202</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.63471155093</v>
+        <v>46188.468044884256</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.67731351852</v>
+        <v>46188.51064685185</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4707,7 +4707,7 @@
         <v>46231</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4721,11 +4721,11 @@
         <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.63471731481</v>
+        <v>46188.46805064815</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.662660393515</v>
+        <v>46188.49599372685</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -4768,11 +4768,11 @@
         <v>206</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.63472107639</v>
+        <v>46188.46805440972</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.677743113425</v>
+        <v>46188.51107644676</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>207</v>
@@ -4817,7 +4817,7 @@
         <v>46234</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
@@ -4831,11 +4831,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.63473258102</v>
+        <v>46188.46806591435</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.677464444445</v>
+        <v>46188.51079777778</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>178</v>
@@ -4884,11 +4884,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.63474121528</v>
+        <v>46188.46807454861</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.677461087966</v>
+        <v>46188.510794421294</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>178</v>
@@ -4937,11 +4937,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.63477284722</v>
+        <v>46188.46810618056</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.67773935186</v>
+        <v>46188.511072685185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -4986,7 +4986,7 @@
         <v>46241</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5000,11 +5000,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.63477877315</v>
+        <v>46188.46811210648</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46198.507975775465</v>
+        <v>46198.3413091088</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>178</v>
@@ -5053,11 +5053,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.63478605324</v>
+        <v>46188.46811938657</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.50797630787</v>
+        <v>46198.341309641204</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>178</v>
@@ -5106,11 +5106,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.63485537037</v>
+        <v>46188.4681887037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.67780341435</v>
+        <v>46188.511136747686</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5155,7 +5155,7 @@
         <v>46244</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
@@ -5169,11 +5169,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.634861805556</v>
+        <v>46188.46819513889</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46198.507973761574</v>
+        <v>46198.3413070949</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>178</v>
@@ -5222,11 +5222,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.63486881944</v>
+        <v>46188.46820215278</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46198.507963055556</v>
+        <v>46198.341296388884</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>178</v>
@@ -5275,11 +5275,11 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.63489331018</v>
+        <v>46188.46822664352</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46203.55043523148</v>
+        <v>46203.38376856482</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>183</v>
@@ -5322,11 +5322,11 @@
         <v>229</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.634903391205</v>
+        <v>46188.46823672454</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46198.16853090278</v>
+        <v>46205.00355140046</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5371,7 +5371,7 @@
         <v>46205</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
@@ -5385,11 +5385,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.6349100463</v>
+        <v>46188.468243379626</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46203.55044364583</v>
+        <v>46203.38377697917</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5422,7 +5422,7 @@
         <v>183</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>193</v>
@@ -5440,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5448,11 +5448,11 @@
         <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.6349165162</v>
+        <v>46188.46824984954</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46203.550511388894</v>
+        <v>46203.38384472222</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>
@@ -5485,7 +5485,7 @@
         <v>183</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>193</v>
@@ -5497,13 +5497,13 @@
         <v>46223</v>
       </c>
       <c r="S69" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5511,11 +5511,11 @@
         <v>235</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.634922916666</v>
+        <v>46188.468256249995</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46188.67789931713</v>
+        <v>46188.51123265046</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5560,7 +5560,7 @@
         <v>46254</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
@@ -5574,11 +5574,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.63492795139</v>
+        <v>46188.468261284725</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.58705803241</v>
+        <v>46197.42039136574</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>239</v>
@@ -5621,11 +5621,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.63493152778</v>
+        <v>46188.46826486111</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.67802387731</v>
+        <v>46188.51135721065</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5670,7 +5670,7 @@
         <v>46251</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5684,11 +5684,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.63494034723</v>
+        <v>46188.468273680555</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.677983657406</v>
+        <v>46188.51131699074</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>178</v>
@@ -5737,11 +5737,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.634945150465</v>
+        <v>46188.46827848379</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.677980567125</v>
+        <v>46188.51131390047</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>178</v>
@@ -5790,13 +5790,13 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.634963668985</v>
+        <v>46188.46829700231</v>
       </c>
       <c r="C75" s="9">
-        <v>46197.58704829861</v>
+        <v>46197.42038163195</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.58706070602</v>
+        <v>46197.42039403935</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5841,7 +5841,7 @@
         <v>46252</v>
       </c>
       <c r="S75" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -5855,13 +5855,13 @@
         <v>249</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.63496887732</v>
+        <v>46188.46830221065</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.58695519676</v>
+        <v>46197.42028853009</v>
       </c>
       <c r="D76" s="5">
-        <v>46198.507974444445</v>
+        <v>46198.34130777778</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>178</v>
@@ -5910,13 +5910,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.63498112268</v>
+        <v>46188.46831445602</v>
       </c>
       <c r="C77" s="9">
-        <v>46197.587035335644</v>
+        <v>46197.42036866898</v>
       </c>
       <c r="D77" s="9">
-        <v>46198.50797810185</v>
+        <v>46198.341311435186</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>178</v>
@@ -5965,11 +5965,11 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.635046296295</v>
+        <v>46188.46837962963</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.67895050926</v>
+        <v>46188.51228384259</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6014,7 +6014,7 @@
         <v>46253</v>
       </c>
       <c r="S78" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
@@ -6028,11 +6028,11 @@
         <v>256</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.63505403935</v>
+        <v>46188.46838737269</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.50797702547</v>
+        <v>46198.341310358795</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>178</v>
@@ -6081,11 +6081,11 @@
         <v>258</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.63506813657</v>
+        <v>46188.46840146991</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.507975162036</v>
+        <v>46198.34130849537</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>178</v>
@@ -6134,11 +6134,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.63509704861</v>
+        <v>46188.468430381945</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.67906003472</v>
+        <v>46188.51239336806</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6183,7 +6183,7 @@
         <v>46224</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
@@ -6197,11 +6197,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.635102939814</v>
+        <v>46188.46843627315</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.50797759259</v>
+        <v>46198.34131092593</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>178</v>
@@ -6250,11 +6250,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.63510991898</v>
+        <v>46188.46844325231</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46198.50796203704</v>
+        <v>46198.34129537037</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>178</v>
@@ -6303,11 +6303,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.63513603009</v>
+        <v>46188.468469363426</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.6792096875</v>
+        <v>46188.51254302083</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6352,7 +6352,7 @@
         <v>46258</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6366,11 +6366,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.63514172454</v>
+        <v>46188.468475057874</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46202.95697799769</v>
+        <v>46202.79031133102</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>179</v>
@@ -6419,11 +6419,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.63514853009</v>
+        <v>46188.46848186343</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46202.95697554398</v>
+        <v>46202.79030887732</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>178</v>
@@ -6472,11 +6472,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.63521115741</v>
+        <v>46188.46854449074</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46202.95705052083</v>
+        <v>46202.79038385417</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6521,7 +6521,7 @@
         <v>46260</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
@@ -6535,11 +6535,11 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.63521795139</v>
+        <v>46188.46855128472</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46202.957050694444</v>
+        <v>46202.79038402778</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>178</v>
@@ -6588,11 +6588,11 @@
         <v>278</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.635222916666</v>
+        <v>46188.46855625</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.680702488426</v>
+        <v>46188.51403582176</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>178</v>
@@ -6641,11 +6641,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.635247199076</v>
+        <v>46188.46858053241</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.67010366898</v>
+        <v>46188.50343700231</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -6688,11 +6688,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.635250844905</v>
+        <v>46188.46858417824</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.68085204861</v>
+        <v>46188.514185381944</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>283</v>
@@ -6737,7 +6737,7 @@
         <v>46261</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
@@ -6751,11 +6751,11 @@
         <v>287</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.63525673611</v>
+        <v>46188.468590069446</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46202.95704981481</v>
+        <v>46202.79038314815</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>178</v>
@@ -6804,11 +6804,11 @@
         <v>289</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.635261689815</v>
+        <v>46188.46859502315</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46202.95697837963</v>
+        <v>46202.79031171296</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>178</v>
@@ -6857,11 +6857,11 @@
         <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.635279375</v>
+        <v>46188.46861270833</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.68118097223</v>
+        <v>46188.514514305556</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -6906,7 +6906,7 @@
         <v>46262</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -6920,11 +6920,11 @@
         <v>292</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.63528446759</v>
+        <v>46188.46861780093</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46202.956975532405</v>
+        <v>46202.79030886574</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>178</v>
@@ -6973,11 +6973,11 @@
         <v>294</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.6352894213</v>
+        <v>46188.46862275463</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46202.956975497684</v>
+        <v>46202.79030883102</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>178</v>
@@ -7026,11 +7026,11 @@
         <v>296</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.63530922454</v>
+        <v>46188.46864255787</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.68135644676</v>
+        <v>46188.51468978009</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>297</v>
@@ -7075,7 +7075,7 @@
         <v>46265</v>
       </c>
       <c r="S97" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -7089,11 +7089,11 @@
         <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.63531412037</v>
+        <v>46188.4686474537</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46202.956975532405</v>
+        <v>46202.79030886574</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>178</v>
@@ -7142,11 +7142,11 @@
         <v>300</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.63532239583</v>
+        <v>46188.46865572917</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46202.956975532405</v>
+        <v>46202.79030886574</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>178</v>
@@ -7195,11 +7195,11 @@
         <v>301</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.63538068287</v>
+        <v>46188.4687140162</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.68149567129</v>
+        <v>46188.514829004635</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>302</v>
@@ -7244,7 +7244,7 @@
         <v>46266</v>
       </c>
       <c r="S100" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7258,11 +7258,11 @@
         <v>304</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.6353874537</v>
+        <v>46188.46872078704</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46202.95697842592</v>
+        <v>46202.79031175926</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>178</v>
@@ -7311,11 +7311,11 @@
         <v>305</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.63539206018</v>
+        <v>46188.46872539352</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46202.95697895833</v>
+        <v>46202.79031229166</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>178</v>
@@ -7364,11 +7364,11 @@
         <v>306</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.635410682866</v>
+        <v>46188.46874401621</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.67123894676</v>
+        <v>46188.50457228009</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>307</v>
@@ -7411,11 +7411,11 @@
         <v>309</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.635413993055</v>
+        <v>46188.46874732639</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.68161465278</v>
+        <v>46188.514947986114</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>310</v>
@@ -7460,7 +7460,7 @@
         <v>46275</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
@@ -7474,11 +7474,11 @@
         <v>313</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.63541944444</v>
+        <v>46188.46875277778</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.920573842595</v>
+        <v>46188.753907175924</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>314</v>
@@ -7523,7 +7523,7 @@
         <v>46275</v>
       </c>
       <c r="S105" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -1609,13 +1609,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46188.46749296296</v>
+        <v>46188.634159629626</v>
       </c>
       <c r="C4" s="5">
-        <v>46188.75302089121</v>
+        <v>46188.91968755787</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.753035057875</v>
+        <v>46188.91970172454</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1662,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46188.46764418982</v>
+        <v>46188.634310856476</v>
       </c>
       <c r="C5" s="9">
-        <v>46188.75300751158</v>
+        <v>46188.919674178236</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.753021655095</v>
+        <v>46188.91968832176</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1727,13 +1727,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46188.46764981482</v>
+        <v>46188.63431648148</v>
       </c>
       <c r="C6" s="5">
-        <v>46188.752876631945</v>
+        <v>46188.919543298616</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.75289478009</v>
+        <v>46188.91956144676</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1792,13 +1792,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="9">
-        <v>46188.467655162036</v>
+        <v>46188.63432182871</v>
       </c>
       <c r="C7" s="9">
-        <v>46188.752927615744</v>
+        <v>46188.91959428241</v>
       </c>
       <c r="D7" s="9">
-        <v>46188.752942754625</v>
+        <v>46188.9196094213</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>36</v>
@@ -1857,13 +1857,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46188.46765997686</v>
+        <v>46188.634326643514</v>
       </c>
       <c r="C8" s="5">
-        <v>46188.75296844907</v>
+        <v>46188.919635115744</v>
       </c>
       <c r="D8" s="5">
-        <v>46188.752985439816</v>
+        <v>46188.91965210648</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1922,13 +1922,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46188.46749880787</v>
+        <v>46188.634165474534</v>
       </c>
       <c r="C9" s="9">
-        <v>46188.753913148146</v>
+        <v>46188.92057981482</v>
       </c>
       <c r="D9" s="9">
-        <v>46188.753923599535</v>
+        <v>46188.92059026621</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -1975,13 +1975,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46188.467665069446</v>
+        <v>46188.63433173611</v>
       </c>
       <c r="C10" s="5">
-        <v>46188.75344472222</v>
+        <v>46188.920111388885</v>
       </c>
       <c r="D10" s="5">
-        <v>46188.7534465162</v>
+        <v>46188.920113182874</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2040,13 +2040,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46188.46767643519</v>
+        <v>46188.63434310185</v>
       </c>
       <c r="C11" s="9">
-        <v>46188.7530787037</v>
+        <v>46188.91974537037</v>
       </c>
       <c r="D11" s="9">
-        <v>46188.75365456019</v>
+        <v>46188.92032122685</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2105,13 +2105,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46188.46768365741</v>
+        <v>46188.63435032408</v>
       </c>
       <c r="C12" s="5">
-        <v>46188.753818310186</v>
+        <v>46188.92048497685</v>
       </c>
       <c r="D12" s="5">
-        <v>46188.75383458333</v>
+        <v>46188.92050125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2170,13 +2170,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="9">
-        <v>46188.46769009259</v>
+        <v>46188.634356759256</v>
       </c>
       <c r="C13" s="9">
-        <v>46188.75389753473</v>
+        <v>46188.920564201384</v>
       </c>
       <c r="D13" s="9">
-        <v>46188.753913252316</v>
+        <v>46188.92057991898</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2235,11 +2235,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46188.46750333333</v>
+        <v>46188.634170000005</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46197.41980056713</v>
+        <v>46197.58646723379</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2282,13 +2282,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46188.46769949074</v>
+        <v>46188.63436615741</v>
       </c>
       <c r="C15" s="9">
-        <v>46188.753991261576</v>
+        <v>46188.92065792824</v>
       </c>
       <c r="D15" s="9">
-        <v>46189.647731018515</v>
+        <v>46189.814397685186</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2347,13 +2347,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46188.46770592593</v>
+        <v>46188.63437259259</v>
       </c>
       <c r="C16" s="5">
-        <v>46188.754669270835</v>
+        <v>46188.9213359375</v>
       </c>
       <c r="D16" s="5">
-        <v>46189.64775527778</v>
+        <v>46189.814421944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2412,13 +2412,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46188.467712627316</v>
+        <v>46188.63437929398</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.41979372685</v>
+        <v>46197.58646039352</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.41981302084</v>
+        <v>46197.586479687496</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2477,11 +2477,11 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46188.467719699074</v>
+        <v>46188.63438636574</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46205.025704155094</v>
+        <v>46205.19237082176</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2540,11 +2540,11 @@
         <v>82</v>
       </c>
       <c r="B19" s="9">
-        <v>46188.467726041665</v>
+        <v>46188.634392708336</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46205.02570414352</v>
+        <v>46205.19237081018</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>83</v>
@@ -2603,11 +2603,11 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46188.467731620374</v>
+        <v>46188.63439828704</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46205.02570416666</v>
+        <v>46205.192370833334</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2666,11 +2666,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="9">
-        <v>46188.46773638889</v>
+        <v>46188.634403055556</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="9">
-        <v>46205.02570409722</v>
+        <v>46205.19237076389</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>89</v>
@@ -2729,13 +2729,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46189.614092627315</v>
+        <v>46189.78075929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.419957129634</v>
+        <v>46197.58662379629</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.41997003472</v>
+        <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2784,13 +2784,13 @@
         <v>95</v>
       </c>
       <c r="B23" s="9">
-        <v>46189.645209375</v>
+        <v>46189.81187604167</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.41994010417</v>
+        <v>46197.586606770834</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.41995747686</v>
+        <v>46197.586624143514</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>96</v>
@@ -2849,13 +2849,13 @@
         <v>98</v>
       </c>
       <c r="B24" s="5">
-        <v>46189.64537734954</v>
+        <v>46189.8120440162</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.41988243056</v>
+        <v>46197.58654909722</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.41990039352</v>
+        <v>46197.586567060185</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>99</v>
@@ -2914,11 +2914,11 @@
         <v>101</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.467508194444</v>
+        <v>46188.634174861116</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46189.616145810185</v>
+        <v>46189.78281247686</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>102</v>
@@ -2961,11 +2961,11 @@
         <v>104</v>
       </c>
       <c r="B26" s="5">
-        <v>46188.46775931713</v>
+        <v>46188.63442598379</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46205.016595671295</v>
+        <v>46205.18326233796</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>105</v>
@@ -3024,11 +3024,11 @@
         <v>110</v>
       </c>
       <c r="B27" s="9">
-        <v>46188.46776513889</v>
+        <v>46188.634431805556</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46203.38396293981</v>
+        <v>46203.550629606485</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>111</v>
@@ -3083,11 +3083,11 @@
         <v>113</v>
       </c>
       <c r="B28" s="5">
-        <v>46188.46777074074</v>
+        <v>46188.63443740741</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46204.00540090278</v>
+        <v>46204.172067569445</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>114</v>
@@ -3142,11 +3142,11 @@
         <v>116</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.46784917824</v>
+        <v>46188.63451584491</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46188.50744789352</v>
+        <v>46188.674114560185</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>117</v>
@@ -3205,11 +3205,11 @@
         <v>121</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.467855532406</v>
+        <v>46188.63452219908</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.50740560185</v>
+        <v>46188.67407226852</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>122</v>
@@ -3264,11 +3264,11 @@
         <v>124</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.46786152778</v>
+        <v>46188.634528194445</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46188.50740297454</v>
+        <v>46188.6740696412</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>125</v>
@@ -3323,11 +3323,11 @@
         <v>127</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.46786741898</v>
+        <v>46188.63453408565</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46188.507572083334</v>
+        <v>46188.67423875</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>128</v>
@@ -3386,11 +3386,11 @@
         <v>130</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.46787158565</v>
+        <v>46188.634538252314</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46188.50752002315</v>
+        <v>46188.674186689816</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>84</v>
@@ -3439,11 +3439,11 @@
         <v>132</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.46787663194</v>
+        <v>46188.63454329861</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46188.507517210644</v>
+        <v>46188.674183877316</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>133</v>
@@ -3492,11 +3492,11 @@
         <v>135</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.46788137731</v>
+        <v>46188.63454804398</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46188.5080371875</v>
+        <v>46188.674703854165</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>136</v>
@@ -3555,11 +3555,11 @@
         <v>140</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.467886122686</v>
+        <v>46188.63455278936</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46188.50768351852</v>
+        <v>46188.67435018519</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>90</v>
@@ -3608,11 +3608,11 @@
         <v>142</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.46789144676</v>
+        <v>46188.63455811342</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46188.50767990741</v>
+        <v>46188.67434657407</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>143</v>
@@ -3661,11 +3661,11 @@
         <v>145</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.467897152776</v>
+        <v>46188.63456381945</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46188.50798180555</v>
+        <v>46188.674648472224</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>146</v>
@@ -3714,11 +3714,11 @@
         <v>149</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.46790071759</v>
+        <v>46188.63456738426</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46188.51020636574</v>
+        <v>46188.67687303241</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>150</v>
@@ -3777,11 +3777,11 @@
         <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.467905</v>
+        <v>46188.63457166667</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46188.51016978009</v>
+        <v>46188.67683644676</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>87</v>
@@ -3830,11 +3830,11 @@
         <v>154</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.46791003473</v>
+        <v>46188.634576701385</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46188.51016694444</v>
+        <v>46188.67683361111</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>155</v>
@@ -3883,11 +3883,11 @@
         <v>157</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.467512546296</v>
+        <v>46188.63417921297</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46198.34124650463</v>
+        <v>46198.5079131713</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>158</v>
@@ -3932,13 +3932,13 @@
         <v>160</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.467915810186</v>
+        <v>46188.63458247685</v>
       </c>
       <c r="C43" s="9">
-        <v>46196.35815153935</v>
+        <v>46196.52481820602</v>
       </c>
       <c r="D43" s="9">
-        <v>46197.54957185185</v>
+        <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>161</v>
@@ -3997,13 +3997,13 @@
         <v>165</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.4679219213</v>
+        <v>46188.634588587964</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.34122449074</v>
+        <v>46198.50789115741</v>
       </c>
       <c r="D44" s="5">
-        <v>46202.0056787963</v>
+        <v>46202.17234546297</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>166</v>
@@ -4062,13 +4062,13 @@
         <v>168</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.46792831019</v>
+        <v>46188.63459497685</v>
       </c>
       <c r="C45" s="9">
-        <v>46198.341287118055</v>
+        <v>46198.50795378472</v>
       </c>
       <c r="D45" s="9">
-        <v>46203.0098850463</v>
+        <v>46203.17655171297</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4127,11 +4127,11 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.4679431713</v>
+        <v>46188.63460983796</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.51043608796</v>
+        <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4190,11 +4190,11 @@
         <v>177</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.46794728009</v>
+        <v>46188.634613946764</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46202.79038371528</v>
+        <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>178</v>
@@ -4243,11 +4243,11 @@
         <v>181</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.46795173611</v>
+        <v>46188.63461840278</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46202.79053957176</v>
+        <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>178</v>
@@ -4296,11 +4296,11 @@
         <v>182</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.46800628472</v>
+        <v>46188.63467295139</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.493675011574</v>
+        <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>183</v>
@@ -4343,11 +4343,11 @@
         <v>185</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.468010972225</v>
+        <v>46188.63467763889</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46188.510564537035</v>
+        <v>46188.67723120371</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4406,11 +4406,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.46801827547</v>
+        <v>46188.634684942124</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.51065322917</v>
+        <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4469,11 +4469,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.468026296294</v>
+        <v>46188.634692962965</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46188.510561331015</v>
+        <v>46188.67722799769</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4532,11 +4532,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.468032881945</v>
+        <v>46188.63469954861</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.51065034722</v>
+        <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4595,11 +4595,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.468038935185</v>
+        <v>46188.63470560186</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46188.51055827546</v>
+        <v>46188.677224942134</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4658,11 +4658,11 @@
         <v>202</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.468044884256</v>
+        <v>46188.63471155093</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.51064685185</v>
+        <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4721,11 +4721,11 @@
         <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.46805064815</v>
+        <v>46188.63471731481</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.49599372685</v>
+        <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -4768,11 +4768,11 @@
         <v>206</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.46805440972</v>
+        <v>46188.63472107639</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.51107644676</v>
+        <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>207</v>
@@ -4831,11 +4831,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.46806591435</v>
+        <v>46188.63473258102</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.51079777778</v>
+        <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>178</v>
@@ -4884,11 +4884,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.46807454861</v>
+        <v>46188.63474121528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.510794421294</v>
+        <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>178</v>
@@ -4937,11 +4937,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.46810618056</v>
+        <v>46188.63477284722</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.511072685185</v>
+        <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5000,11 +5000,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.46811210648</v>
+        <v>46188.63477877315</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46198.3413091088</v>
+        <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>178</v>
@@ -5053,11 +5053,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.46811938657</v>
+        <v>46188.63478605324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.341309641204</v>
+        <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>178</v>
@@ -5106,11 +5106,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.4681887037</v>
+        <v>46188.63485537037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.511136747686</v>
+        <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5169,11 +5169,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.46819513889</v>
+        <v>46188.634861805556</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46198.3413070949</v>
+        <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>178</v>
@@ -5222,11 +5222,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.46820215278</v>
+        <v>46188.63486881944</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46198.341296388884</v>
+        <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>178</v>
@@ -5275,11 +5275,11 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.46822664352</v>
+        <v>46188.63489331018</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46203.38376856482</v>
+        <v>46203.55043523148</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>183</v>
@@ -5322,11 +5322,11 @@
         <v>229</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.46823672454</v>
+        <v>46188.634903391205</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46205.00355140046</v>
+        <v>46205.17021806713</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5385,11 +5385,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.468243379626</v>
+        <v>46188.6349100463</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46203.38377697917</v>
+        <v>46203.55044364583</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5448,11 +5448,11 @@
         <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.46824984954</v>
+        <v>46188.6349165162</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46203.38384472222</v>
+        <v>46203.550511388894</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>
@@ -5511,11 +5511,11 @@
         <v>235</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.468256249995</v>
+        <v>46188.634922916666</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46188.51123265046</v>
+        <v>46188.67789931713</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5574,11 +5574,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.468261284725</v>
+        <v>46188.63492795139</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.42039136574</v>
+        <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>239</v>
@@ -5621,11 +5621,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.46826486111</v>
+        <v>46188.63493152778</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.51135721065</v>
+        <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5684,11 +5684,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.468273680555</v>
+        <v>46188.63494034723</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.51131699074</v>
+        <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>178</v>
@@ -5737,11 +5737,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.46827848379</v>
+        <v>46188.634945150465</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.51131390047</v>
+        <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>178</v>
@@ -5790,13 +5790,13 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.46829700231</v>
+        <v>46188.634963668985</v>
       </c>
       <c r="C75" s="9">
-        <v>46197.42038163195</v>
+        <v>46197.58704829861</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.42039403935</v>
+        <v>46197.58706070602</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5855,13 +5855,13 @@
         <v>249</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.46830221065</v>
+        <v>46188.63496887732</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.42028853009</v>
+        <v>46197.58695519676</v>
       </c>
       <c r="D76" s="5">
-        <v>46198.34130777778</v>
+        <v>46198.507974444445</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>178</v>
@@ -5910,13 +5910,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.46831445602</v>
+        <v>46188.63498112268</v>
       </c>
       <c r="C77" s="9">
-        <v>46197.42036866898</v>
+        <v>46197.587035335644</v>
       </c>
       <c r="D77" s="9">
-        <v>46198.341311435186</v>
+        <v>46198.50797810185</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>178</v>
@@ -5965,11 +5965,11 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.46837962963</v>
+        <v>46188.635046296295</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.51228384259</v>
+        <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6028,11 +6028,11 @@
         <v>256</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.46838737269</v>
+        <v>46188.63505403935</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.341310358795</v>
+        <v>46198.50797702547</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>178</v>
@@ -6081,11 +6081,11 @@
         <v>258</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.46840146991</v>
+        <v>46188.63506813657</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.34130849537</v>
+        <v>46198.507975162036</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>178</v>
@@ -6134,11 +6134,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.468430381945</v>
+        <v>46188.63509704861</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.51239336806</v>
+        <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6197,11 +6197,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.46843627315</v>
+        <v>46188.635102939814</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.34131092593</v>
+        <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>178</v>
@@ -6250,11 +6250,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.46844325231</v>
+        <v>46188.63510991898</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46198.34129537037</v>
+        <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>178</v>
@@ -6303,11 +6303,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.468469363426</v>
+        <v>46188.63513603009</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.51254302083</v>
+        <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6366,11 +6366,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.468475057874</v>
+        <v>46188.63514172454</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46202.79031133102</v>
+        <v>46202.95697799769</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>179</v>
@@ -6419,11 +6419,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.46848186343</v>
+        <v>46188.63514853009</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46202.79030887732</v>
+        <v>46202.95697554398</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>178</v>
@@ -6472,11 +6472,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.46854449074</v>
+        <v>46188.63521115741</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46202.79038385417</v>
+        <v>46202.95705052083</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6535,11 +6535,11 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.46855128472</v>
+        <v>46188.63521795139</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46202.79038402778</v>
+        <v>46202.957050694444</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>178</v>
@@ -6588,11 +6588,11 @@
         <v>278</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.46855625</v>
+        <v>46188.635222916666</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.51403582176</v>
+        <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>178</v>
@@ -6641,11 +6641,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.46858053241</v>
+        <v>46188.635247199076</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.50343700231</v>
+        <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -6688,11 +6688,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.46858417824</v>
+        <v>46188.635250844905</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.514185381944</v>
+        <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>283</v>
@@ -6751,11 +6751,11 @@
         <v>287</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.468590069446</v>
+        <v>46188.63525673611</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46202.79038314815</v>
+        <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>178</v>
@@ -6804,11 +6804,11 @@
         <v>289</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.46859502315</v>
+        <v>46188.635261689815</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46202.79031171296</v>
+        <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>178</v>
@@ -6857,11 +6857,11 @@
         <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.46861270833</v>
+        <v>46188.635279375</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.514514305556</v>
+        <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -6920,11 +6920,11 @@
         <v>292</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.46861780093</v>
+        <v>46188.63528446759</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46202.79030886574</v>
+        <v>46202.956975532405</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>178</v>
@@ -6973,11 +6973,11 @@
         <v>294</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.46862275463</v>
+        <v>46188.6352894213</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46202.79030883102</v>
+        <v>46202.956975497684</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>178</v>
@@ -7026,11 +7026,11 @@
         <v>296</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.46864255787</v>
+        <v>46188.63530922454</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.51468978009</v>
+        <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>297</v>
@@ -7089,11 +7089,11 @@
         <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.4686474537</v>
+        <v>46188.63531412037</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46202.79030886574</v>
+        <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>178</v>
@@ -7142,11 +7142,11 @@
         <v>300</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.46865572917</v>
+        <v>46188.63532239583</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46202.79030886574</v>
+        <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>178</v>
@@ -7195,11 +7195,11 @@
         <v>301</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.4687140162</v>
+        <v>46188.63538068287</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.514829004635</v>
+        <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>302</v>
@@ -7258,11 +7258,11 @@
         <v>304</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.46872078704</v>
+        <v>46188.6353874537</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46202.79031175926</v>
+        <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>178</v>
@@ -7311,11 +7311,11 @@
         <v>305</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.46872539352</v>
+        <v>46188.63539206018</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46202.79031229166</v>
+        <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>178</v>
@@ -7364,11 +7364,11 @@
         <v>306</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.46874401621</v>
+        <v>46188.635410682866</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.50457228009</v>
+        <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>307</v>
@@ -7411,11 +7411,11 @@
         <v>309</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.46874732639</v>
+        <v>46188.635413993055</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.514947986114</v>
+        <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>310</v>
@@ -7474,11 +7474,11 @@
         <v>313</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.46875277778</v>
+        <v>46188.63541944444</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.753907175924</v>
+        <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>314</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="316">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -280,241 +280,241 @@
     <t>Media</t>
   </si>
   <si>
+    <t>1215727831264658</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4360</t>
+  </si>
+  <si>
+    <t>1215727831264670</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215728035806401</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4360</t>
+  </si>
+  <si>
+    <t>1215771707606671</t>
+  </si>
+  <si>
+    <t>Reserva producción</t>
+  </si>
+  <si>
+    <t>motor ot 4360,Alabe  ot 4360</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>1215771707606683</t>
+  </si>
+  <si>
+    <t>motor ot 4360</t>
+  </si>
+  <si>
+    <t>Reserva producción,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215771707606685</t>
+  </si>
+  <si>
+    <t>Alabe  ot 4360</t>
+  </si>
+  <si>
+    <t>Reserva producción,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215727332551586</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4360,rodete OT 4360</t>
+  </si>
+  <si>
+    <t>1215728035819291</t>
+  </si>
+  <si>
+    <t>rodete OT 4360</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4360,Fabricación Rodete OT 4360</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1215728035819308</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4360</t>
+  </si>
+  <si>
+    <t>rodete OT 4360,Fabricación Rodete OT 4360</t>
+  </si>
+  <si>
+    <t>1215728035829709</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4360</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,rodete OT 4360</t>
+  </si>
+  <si>
+    <t>1215727723568477</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4360</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>1215727831363866</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>1215727831363886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4360,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215727831373407</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>1215727831373419</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>1215727723641751</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1215727723641768</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4360,Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t>1215727939764035</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4360,Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t>1215727939764052</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4360,Control de calidad fabricación externa  OT 4360,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215727939776448</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215727939776460</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215727792775028</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215727792775045</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1215727332551588</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215727831264658</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4360</t>
-  </si>
-  <si>
-    <t>1215727831264670</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215728035806401</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4360</t>
-  </si>
-  <si>
-    <t>1215771707606671</t>
-  </si>
-  <si>
-    <t>Reserva producción</t>
-  </si>
-  <si>
-    <t>motor ot 4360,Alabe  ot 4360</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>1215771707606683</t>
-  </si>
-  <si>
-    <t>motor ot 4360</t>
-  </si>
-  <si>
-    <t>Reserva producción,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215771707606685</t>
-  </si>
-  <si>
-    <t>Alabe  ot 4360</t>
-  </si>
-  <si>
-    <t>Reserva producción,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215727332551586</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4360,rodete OT 4360</t>
-  </si>
-  <si>
-    <t>1215728035819291</t>
-  </si>
-  <si>
-    <t>rodete OT 4360</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4360,Fabricación Rodete OT 4360</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215728035819308</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4360</t>
-  </si>
-  <si>
-    <t>rodete OT 4360,Fabricación Rodete OT 4360</t>
-  </si>
-  <si>
-    <t>1215728035829709</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4360</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,rodete OT 4360</t>
-  </si>
-  <si>
-    <t>1215727723568477</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4360</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>1215727831363866</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>1215727831363886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4360,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215727831373407</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>1215727831373419</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>1215727723641751</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1215727723641768</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4360,Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t>1215727939764035</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4360,Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t>1215727939764052</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4360,Control de calidad fabricación externa  OT 4360,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215727939776448</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215727939776460</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792775028</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792775045</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1215727332551588</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
   </si>
   <si>
     <t>1215727939795692</t>
@@ -2237,9 +2237,11 @@
       <c r="B14" s="5">
         <v>46188.634170000005</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46206.50378961806</v>
+      </c>
       <c r="D14" s="5">
-        <v>46197.58646723379</v>
+        <v>46206.50380298611</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2274,8 +2276,12 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
@@ -2479,9 +2485,11 @@
       <c r="B18" s="5">
         <v>46188.63438636574</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46206.502370312504</v>
+      </c>
       <c r="D18" s="5">
-        <v>46205.19237082176</v>
+        <v>46206.502387430555</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2529,25 +2537,27 @@
         <v>80</v>
       </c>
       <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46188.634392708336</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46206.50354868056</v>
+      </c>
       <c r="D19" s="9">
-        <v>46205.19237081018</v>
+        <v>46206.503564328705</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2580,7 +2590,7 @@
         <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="9">
         <v>46211</v>
@@ -2592,25 +2602,27 @@
         <v>80</v>
       </c>
       <c r="T19" s="10">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46188.63439828704</v>
       </c>
-      <c r="C20" s="6"/>
+      <c r="C20" s="5">
+        <v>46206.50323137731</v>
+      </c>
       <c r="D20" s="5">
-        <v>46205.192370833334</v>
+        <v>46206.50324875</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2643,7 +2655,7 @@
         <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46211</v>
@@ -2655,25 +2667,27 @@
         <v>80</v>
       </c>
       <c r="T20" s="6">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U20" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
         <v>46188.634403055556</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9">
+        <v>46206.5037743287</v>
+      </c>
       <c r="D21" s="9">
-        <v>46205.19237076389</v>
+        <v>46206.5037896412</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2706,7 +2720,7 @@
         <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="9">
         <v>46211</v>
@@ -2718,15 +2732,15 @@
         <v>80</v>
       </c>
       <c r="T21" s="10">
-        <v>0</v>
-      </c>
-      <c r="U21" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U21" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46189.78075929398</v>
@@ -2738,7 +2752,7 @@
         <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2762,7 +2776,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2770,7 +2784,7 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2781,7 +2795,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46189.81187604167</v>
@@ -2793,7 +2807,7 @@
         <v>46197.586624143514</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2820,13 +2834,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>64</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="9">
         <v>46183</v>
@@ -2846,7 +2860,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46189.8120440162</v>
@@ -2858,7 +2872,7 @@
         <v>46197.586567060185</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2885,13 +2899,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="5">
         <v>46183</v>
@@ -2911,7 +2925,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25" s="9">
         <v>46188.634174861116</v>
@@ -2921,7 +2935,7 @@
         <v>46189.78281247686</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -2945,7 +2959,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -2958,7 +2972,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
@@ -2968,16 +2982,16 @@
         <v>46205.18326233796</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -2995,13 +3009,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q26" s="5">
         <v>46183</v>
@@ -3016,12 +3030,12 @@
         <v>0</v>
       </c>
       <c r="U26" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" s="9">
         <v>46188.634431805556</v>
@@ -3031,16 +3045,16 @@
         <v>46203.550629606485</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>107</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3058,29 +3072,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3090,16 +3104,16 @@
         <v>46204.172067569445</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3117,29 +3131,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3149,16 +3163,16 @@
         <v>46188.674114560185</v>
       </c>
       <c r="E29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="10" t="s">
+      <c r="H29" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3176,13 +3190,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q29" s="9">
         <v>46213</v>
@@ -3191,37 +3205,37 @@
         <v>46225</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T29" s="10">
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46188.67407226852</v>
+        <v>46206.502381377315</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3239,29 +3253,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3271,16 +3285,16 @@
         <v>46188.6740696412</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3298,29 +3312,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3330,16 +3344,16 @@
         <v>46188.67423875</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3357,10 +3371,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3372,37 +3386,37 @@
         <v>46225</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46188.674186689816</v>
+        <v>46206.50355516204</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3420,13 +3434,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3436,7 +3450,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3446,16 +3460,16 @@
         <v>46188.674183877316</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3473,13 +3487,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3489,7 +3503,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3499,16 +3513,16 @@
         <v>46188.674703854165</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3526,10 +3540,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3541,37 +3555,37 @@
         <v>46253</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T35" s="10">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46188.67435018519</v>
+        <v>46206.50378075232</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3589,13 +3603,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3605,7 +3619,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3615,16 +3629,16 @@
         <v>46188.67434657407</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3642,13 +3656,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3658,7 +3672,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3668,16 +3682,16 @@
         <v>46188.674648472224</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3695,10 +3709,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3711,7 +3725,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3721,16 +3735,16 @@
         <v>46188.67687303241</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3748,10 +3762,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3763,37 +3777,37 @@
         <v>46225</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T39" s="10">
         <v>0</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46188.67683644676</v>
+        <v>46206.50323967593</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3811,13 +3825,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3827,7 +3841,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3837,16 +3851,16 @@
         <v>46188.67683361111</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3864,13 +3878,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3880,7 +3894,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3890,7 +3904,7 @@
         <v>46198.5079131713</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3914,7 +3928,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3924,7 +3938,7 @@
       <c r="S42" s="6"/>
       <c r="T42" s="6"/>
       <c r="U42" s="12" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -3968,7 +3982,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>54</v>
@@ -4033,7 +4047,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>161</v>
@@ -4098,7 +4112,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>166</v>
@@ -4161,7 +4175,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>176</v>
@@ -4176,13 +4190,13 @@
         <v>46259</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4380,7 +4394,7 @@
         <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>189</v>
@@ -4392,13 +4406,13 @@
         <v>46227</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4419,10 +4433,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4455,13 +4469,13 @@
         <v>46231</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4506,7 +4520,7 @@
         <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>196</v>
@@ -4518,13 +4532,13 @@
         <v>46227</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4545,10 +4559,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4581,13 +4595,13 @@
         <v>46231</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4632,7 +4646,7 @@
         <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>201</v>
@@ -4644,13 +4658,13 @@
         <v>46227</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4671,10 +4685,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4707,13 +4721,13 @@
         <v>46231</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4817,13 +4831,13 @@
         <v>46234</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4986,13 +5000,13 @@
         <v>46241</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5119,10 +5133,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5155,13 +5169,13 @@
         <v>46244</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5182,10 +5196,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5235,10 +5249,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5326,7 +5340,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46205.17021806713</v>
+        <v>46206.20793023148</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5359,7 +5373,7 @@
         <v>183</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>193</v>
@@ -5370,14 +5384,14 @@
       <c r="R67" s="9">
         <v>46205</v>
       </c>
-      <c r="S67" s="12" t="s">
-        <v>80</v>
+      <c r="S67" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T67" s="10">
         <v>0</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5422,7 +5436,7 @@
         <v>183</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>193</v>
@@ -5440,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5485,7 +5499,7 @@
         <v>183</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>193</v>
@@ -5497,13 +5511,13 @@
         <v>46223</v>
       </c>
       <c r="S69" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5548,7 +5562,7 @@
         <v>183</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>237</v>
@@ -5560,13 +5574,13 @@
         <v>46254</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5670,13 +5684,13 @@
         <v>46251</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5841,7 +5855,7 @@
         <v>46252</v>
       </c>
       <c r="S75" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -6014,13 +6028,13 @@
         <v>46253</v>
       </c>
       <c r="S78" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6183,13 +6197,13 @@
         <v>46224</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6352,13 +6366,13 @@
         <v>46258</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6521,13 +6535,13 @@
         <v>46260</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6737,13 +6751,13 @@
         <v>46261</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6906,13 +6920,13 @@
         <v>46262</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7075,13 +7089,13 @@
         <v>46265</v>
       </c>
       <c r="S97" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7244,13 +7258,13 @@
         <v>46266</v>
       </c>
       <c r="S100" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7460,13 +7474,13 @@
         <v>46275</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7523,13 +7537,13 @@
         <v>46275</v>
       </c>
       <c r="S105" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -3508,9 +3508,11 @@
       <c r="B35" s="9">
         <v>46188.63454804398</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9">
+        <v>46209.62074709491</v>
+      </c>
       <c r="D35" s="9">
-        <v>46188.674703854165</v>
+        <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>135</v>
@@ -3558,10 +3560,10 @@
         <v>93</v>
       </c>
       <c r="T35" s="10">
-        <v>0</v>
-      </c>
-      <c r="U35" s="11" t="s">
-        <v>108</v>
+        <v>1</v>
+      </c>
+      <c r="U35" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3571,9 +3573,11 @@
       <c r="B36" s="5">
         <v>46188.63455278936</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46209.62002465277</v>
+      </c>
       <c r="D36" s="5">
-        <v>46206.50378075232</v>
+        <v>46209.62002645833</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>89</v>
@@ -3624,9 +3628,11 @@
       <c r="B37" s="9">
         <v>46188.63455811342</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="9">
+        <v>46209.62070212963</v>
+      </c>
       <c r="D37" s="9">
-        <v>46188.67434657407</v>
+        <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3679,7 +3685,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46188.674648472224</v>
+        <v>46209.62071325231</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -5529,7 +5535,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46188.67789931713</v>
+        <v>46209.620722314816</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5579,8 +5585,8 @@
       <c r="T70" s="6">
         <v>0</v>
       </c>
-      <c r="U70" s="11" t="s">
-        <v>108</v>
+      <c r="U70" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46189.78281247686</v>
+        <v>46209.81875638889</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -3158,9 +3158,11 @@
       <c r="B29" s="9">
         <v>46188.63451584491</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9">
+        <v>46209.81873614583</v>
+      </c>
       <c r="D29" s="9">
-        <v>46188.674114560185</v>
+        <v>46209.818759456015</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3208,10 +3210,10 @@
         <v>93</v>
       </c>
       <c r="T29" s="10">
-        <v>0</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>108</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3221,9 +3223,11 @@
       <c r="B30" s="5">
         <v>46188.63452219908</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46209.818676319446</v>
+      </c>
       <c r="D30" s="5">
-        <v>46206.502381377315</v>
+        <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3280,9 +3284,11 @@
       <c r="B31" s="9">
         <v>46188.634528194445</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9">
+        <v>46209.818722615746</v>
+      </c>
       <c r="D31" s="9">
-        <v>46188.6740696412</v>
+        <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3339,9 +3345,11 @@
       <c r="B32" s="5">
         <v>46188.63453408565</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46209.819314988425</v>
+      </c>
       <c r="D32" s="5">
-        <v>46188.67423875</v>
+        <v>46209.81933853009</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3389,10 +3397,10 @@
         <v>93</v>
       </c>
       <c r="T32" s="6">
-        <v>0</v>
-      </c>
-      <c r="U32" s="11" t="s">
-        <v>108</v>
+        <v>1</v>
+      </c>
+      <c r="U32" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3402,9 +3410,11 @@
       <c r="B33" s="9">
         <v>46188.634538252314</v>
       </c>
-      <c r="C33" s="10"/>
+      <c r="C33" s="9">
+        <v>46209.819259537035</v>
+      </c>
       <c r="D33" s="9">
-        <v>46206.50355516204</v>
+        <v>46209.81926089121</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>83</v>
@@ -3455,9 +3465,11 @@
       <c r="B34" s="5">
         <v>46188.63454329861</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46209.8193018287</v>
+      </c>
       <c r="D34" s="5">
-        <v>46188.674183877316</v>
+        <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -4367,7 +4379,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46188.67723120371</v>
+        <v>46209.818739016206</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>186</v>
@@ -4417,8 +4429,8 @@
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="11" t="s">
-        <v>108</v>
+      <c r="U50" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4493,7 +4505,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46188.67722799769</v>
+        <v>46209.819318298614</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4543,8 +4555,8 @@
       <c r="T52" s="6">
         <v>0</v>
       </c>
-      <c r="U52" s="11" t="s">
-        <v>108</v>
+      <c r="U52" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -3748,9 +3748,11 @@
       <c r="B39" s="9">
         <v>46188.63456738426</v>
       </c>
-      <c r="C39" s="10"/>
+      <c r="C39" s="9">
+        <v>46209.81975005787</v>
+      </c>
       <c r="D39" s="9">
-        <v>46188.67687303241</v>
+        <v>46209.81975170139</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3798,10 +3800,10 @@
         <v>93</v>
       </c>
       <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>108</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -3811,9 +3813,11 @@
       <c r="B40" s="5">
         <v>46188.63457166667</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46209.8196269676</v>
+      </c>
       <c r="D40" s="5">
-        <v>46206.50323967593</v>
+        <v>46209.81962844907</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>86</v>
@@ -3864,9 +3868,11 @@
       <c r="B41" s="9">
         <v>46188.634576701385</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="9">
+        <v>46209.819662615744</v>
+      </c>
       <c r="D41" s="9">
-        <v>46188.67683361111</v>
+        <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -4631,7 +4637,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46188.677224942134</v>
+        <v>46209.8196808912</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4681,8 +4687,8 @@
       <c r="T54" s="6">
         <v>0</v>
       </c>
-      <c r="U54" s="11" t="s">
-        <v>108</v>
+      <c r="U54" s="12" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -514,97 +514,97 @@
     <t>Planos definitivos,Planos preliminar</t>
   </si>
   <si>
+    <t>1215727939795692</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1215727939795714</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1215727792809496</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 4360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727939821604</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728035964722</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728035964734</t>
+  </si>
+  <si>
+    <t>1215727939892842</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215727939892854</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Bodega:</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215727939795692</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1215727939795714</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1215727792809496</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 4360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727939821604</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728035964722</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728035964734</t>
-  </si>
-  <si>
-    <t>1215727939892842</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215727939892854</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Bodega:</t>
   </si>
   <si>
     <t>1215727723755882</t>
@@ -3923,9 +3923,11 @@
       <c r="B42" s="5">
         <v>46188.63417921297</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46210.52949314815</v>
+      </c>
       <c r="D42" s="5">
-        <v>46198.5079131713</v>
+        <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3960,14 +3962,16 @@
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="12" t="s">
-        <v>159</v>
+      <c r="T42" s="6">
+        <v>1</v>
+      </c>
+      <c r="U42" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -3979,16 +3983,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4012,7 +4016,7 @@
         <v>54</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4032,7 +4036,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4041,19 +4045,19 @@
         <v>46198.50789115741</v>
       </c>
       <c r="D44" s="5">
-        <v>46202.17234546297</v>
+        <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4074,10 +4078,10 @@
         <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4085,8 +4089,8 @@
       <c r="R44" s="5">
         <v>46209</v>
       </c>
-      <c r="S44" s="12" t="s">
-        <v>80</v>
+      <c r="S44" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4097,7 +4101,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4115,10 +4119,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>170</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4139,10 +4143,10 @@
         <v>157</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4162,7 +4166,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4172,16 +4176,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4202,7 +4206,7 @@
         <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4225,7 +4229,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4235,16 +4239,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4262,13 +4266,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4278,7 +4282,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4288,16 +4292,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4315,13 +4319,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4331,7 +4335,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4341,7 +4345,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4365,7 +4369,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4378,7 +4382,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4388,16 +4392,16 @@
         <v>46209.818739016206</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4415,13 +4419,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>124</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4436,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4478,7 +4482,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>192</v>
@@ -4520,10 +4524,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4541,7 +4545,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>132</v>
@@ -4562,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4604,13 +4608,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4646,10 +4650,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4667,7 +4671,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>154</v>
@@ -4688,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4730,13 +4734,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>200</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4843,7 +4847,7 @@
         <v>204</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>204</v>
@@ -4876,7 +4880,7 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4929,7 +4933,7 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5012,7 +5016,7 @@
         <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>204</v>
@@ -5045,7 +5049,7 @@
         <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5098,7 +5102,7 @@
         <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5181,7 +5185,7 @@
         <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>204</v>
@@ -5214,7 +5218,7 @@
         <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5267,7 +5271,7 @@
         <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5320,7 +5324,7 @@
         <v>46203.55043523148</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5373,10 +5377,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5394,7 +5398,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>113</v>
@@ -5436,10 +5440,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5457,7 +5461,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>98</v>
@@ -5478,7 +5482,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="12" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5499,10 +5503,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5520,7 +5524,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>95</v>
@@ -5541,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5562,10 +5566,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5583,7 +5587,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>142</v>
@@ -5604,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5729,7 +5733,7 @@
         <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5782,7 +5786,7 @@
         <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5867,7 +5871,7 @@
         <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>239</v>
@@ -5902,7 +5906,7 @@
         <v>46198.507974444445</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5957,7 +5961,7 @@
         <v>46198.50797810185</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6040,7 +6044,7 @@
         <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>239</v>
@@ -6073,7 +6077,7 @@
         <v>46198.50797702547</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6126,7 +6130,7 @@
         <v>46198.507975162036</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6209,7 +6213,7 @@
         <v>239</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>239</v>
@@ -6242,7 +6246,7 @@
         <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6295,7 +6299,7 @@
         <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6411,7 +6415,7 @@
         <v>46202.95697799769</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6441,7 +6445,7 @@
         <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>271</v>
@@ -6464,7 +6468,7 @@
         <v>46202.95697554398</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6494,7 +6498,7 @@
         <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>271</v>
@@ -6547,7 +6551,7 @@
         <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>275</v>
@@ -6580,7 +6584,7 @@
         <v>46202.957050694444</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6610,7 +6614,7 @@
         <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>277</v>
@@ -6633,7 +6637,7 @@
         <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6663,7 +6667,7 @@
         <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>277</v>
@@ -6796,7 +6800,7 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6826,7 +6830,7 @@
         <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>288</v>
@@ -6849,7 +6853,7 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6879,7 +6883,7 @@
         <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>288</v>
@@ -6932,7 +6936,7 @@
         <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>280</v>
@@ -6965,7 +6969,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6995,7 +6999,7 @@
         <v>291</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>293</v>
@@ -7018,7 +7022,7 @@
         <v>46202.956975497684</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7048,7 +7052,7 @@
         <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>295</v>
@@ -7101,7 +7105,7 @@
         <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>280</v>
@@ -7134,7 +7138,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7164,7 +7168,7 @@
         <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>299</v>
@@ -7187,7 +7191,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7217,7 +7221,7 @@
         <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>299</v>
@@ -7270,7 +7274,7 @@
         <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>303</v>
@@ -7303,7 +7307,7 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7333,7 +7337,7 @@
         <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>302</v>
@@ -7356,7 +7360,7 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7386,7 +7390,7 @@
         <v>302</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>302</v>
@@ -7525,10 +7529,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -4110,7 +4110,7 @@
         <v>46198.50795378472</v>
       </c>
       <c r="D45" s="9">
-        <v>46203.17655171297</v>
+        <v>46211.17038164352</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4154,8 +4154,8 @@
       <c r="R45" s="9">
         <v>46210</v>
       </c>
-      <c r="S45" s="12" t="s">
-        <v>80</v>
+      <c r="S45" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T45" s="10">
         <v>1</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -1609,13 +1609,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46188.634159629626</v>
+        <v>46188.46749296296</v>
       </c>
       <c r="C4" s="5">
-        <v>46188.91968755787</v>
+        <v>46188.75302089121</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.91970172454</v>
+        <v>46188.753035057875</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1662,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46188.634310856476</v>
+        <v>46188.46764418982</v>
       </c>
       <c r="C5" s="9">
-        <v>46188.919674178236</v>
+        <v>46188.75300751158</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.91968832176</v>
+        <v>46188.753021655095</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1727,13 +1727,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46188.63431648148</v>
+        <v>46188.46764981482</v>
       </c>
       <c r="C6" s="5">
-        <v>46188.919543298616</v>
+        <v>46188.752876631945</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.91956144676</v>
+        <v>46188.75289478009</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1792,13 +1792,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="9">
-        <v>46188.63432182871</v>
+        <v>46188.467655162036</v>
       </c>
       <c r="C7" s="9">
-        <v>46188.91959428241</v>
+        <v>46188.752927615744</v>
       </c>
       <c r="D7" s="9">
-        <v>46188.9196094213</v>
+        <v>46188.752942754625</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>36</v>
@@ -1857,13 +1857,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46188.634326643514</v>
+        <v>46188.46765997686</v>
       </c>
       <c r="C8" s="5">
-        <v>46188.919635115744</v>
+        <v>46188.75296844907</v>
       </c>
       <c r="D8" s="5">
-        <v>46188.91965210648</v>
+        <v>46188.752985439816</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1922,13 +1922,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46188.634165474534</v>
+        <v>46188.46749880787</v>
       </c>
       <c r="C9" s="9">
-        <v>46188.92057981482</v>
+        <v>46188.753913148146</v>
       </c>
       <c r="D9" s="9">
-        <v>46188.92059026621</v>
+        <v>46188.753923599535</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -1975,13 +1975,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46188.63433173611</v>
+        <v>46188.467665069446</v>
       </c>
       <c r="C10" s="5">
-        <v>46188.920111388885</v>
+        <v>46188.75344472222</v>
       </c>
       <c r="D10" s="5">
-        <v>46188.920113182874</v>
+        <v>46188.7534465162</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2040,13 +2040,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46188.63434310185</v>
+        <v>46188.46767643519</v>
       </c>
       <c r="C11" s="9">
-        <v>46188.91974537037</v>
+        <v>46188.7530787037</v>
       </c>
       <c r="D11" s="9">
-        <v>46188.92032122685</v>
+        <v>46188.75365456019</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2105,13 +2105,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46188.63435032408</v>
+        <v>46188.46768365741</v>
       </c>
       <c r="C12" s="5">
-        <v>46188.92048497685</v>
+        <v>46188.753818310186</v>
       </c>
       <c r="D12" s="5">
-        <v>46188.92050125</v>
+        <v>46188.75383458333</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2170,13 +2170,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="9">
-        <v>46188.634356759256</v>
+        <v>46188.46769009259</v>
       </c>
       <c r="C13" s="9">
-        <v>46188.920564201384</v>
+        <v>46188.75389753473</v>
       </c>
       <c r="D13" s="9">
-        <v>46188.92057991898</v>
+        <v>46188.753913252316</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2235,13 +2235,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46188.634170000005</v>
+        <v>46188.46750333333</v>
       </c>
       <c r="C14" s="5">
-        <v>46206.50378961806</v>
+        <v>46206.33712295139</v>
       </c>
       <c r="D14" s="5">
-        <v>46206.50380298611</v>
+        <v>46206.337136319446</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2288,13 +2288,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46188.63436615741</v>
+        <v>46188.46769949074</v>
       </c>
       <c r="C15" s="9">
-        <v>46188.92065792824</v>
+        <v>46188.753991261576</v>
       </c>
       <c r="D15" s="9">
-        <v>46189.814397685186</v>
+        <v>46189.647731018515</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2353,13 +2353,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46188.63437259259</v>
+        <v>46188.46770592593</v>
       </c>
       <c r="C16" s="5">
-        <v>46188.9213359375</v>
+        <v>46188.754669270835</v>
       </c>
       <c r="D16" s="5">
-        <v>46189.814421944444</v>
+        <v>46189.64775527778</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2418,13 +2418,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46188.63437929398</v>
+        <v>46188.467712627316</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.58646039352</v>
+        <v>46197.41979372685</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.586479687496</v>
+        <v>46197.41981302084</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2483,13 +2483,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46188.63438636574</v>
+        <v>46188.467719699074</v>
       </c>
       <c r="C18" s="5">
-        <v>46206.502370312504</v>
+        <v>46206.33570364583</v>
       </c>
       <c r="D18" s="5">
-        <v>46206.502387430555</v>
+        <v>46206.33572076389</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2548,13 +2548,13 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46188.634392708336</v>
+        <v>46188.467726041665</v>
       </c>
       <c r="C19" s="9">
-        <v>46206.50354868056</v>
+        <v>46206.336882013886</v>
       </c>
       <c r="D19" s="9">
-        <v>46206.503564328705</v>
+        <v>46206.33689766204</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2613,13 +2613,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46188.63439828704</v>
+        <v>46188.467731620374</v>
       </c>
       <c r="C20" s="5">
-        <v>46206.50323137731</v>
+        <v>46206.33656471065</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.50324875</v>
+        <v>46206.336582083335</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2678,13 +2678,13 @@
         <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46188.634403055556</v>
+        <v>46188.46773638889</v>
       </c>
       <c r="C21" s="9">
-        <v>46206.5037743287</v>
+        <v>46206.33710766204</v>
       </c>
       <c r="D21" s="9">
-        <v>46206.5037896412</v>
+        <v>46206.33712297454</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2743,13 +2743,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46189.78075929398</v>
+        <v>46189.614092627315</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.58662379629</v>
+        <v>46197.419957129634</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.58663670139</v>
+        <v>46197.41997003472</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2798,13 +2798,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46189.81187604167</v>
+        <v>46189.645209375</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.586606770834</v>
+        <v>46197.41994010417</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.586624143514</v>
+        <v>46197.41995747686</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -2863,13 +2863,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46189.8120440162</v>
+        <v>46189.64537734954</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.58654909722</v>
+        <v>46197.41988243056</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.586567060185</v>
+        <v>46197.41990039352</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2928,11 +2928,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.634174861116</v>
+        <v>46188.467508194444</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46209.81875638889</v>
+        <v>46209.65208972222</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -2975,11 +2975,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46188.63442598379</v>
+        <v>46188.46775931713</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46205.18326233796</v>
+        <v>46205.016595671295</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -3038,11 +3038,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46188.634431805556</v>
+        <v>46188.46776513889</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46203.550629606485</v>
+        <v>46203.38396293981</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3097,11 +3097,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46188.63443740741</v>
+        <v>46188.46777074074</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46204.172067569445</v>
+        <v>46204.00540090278</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3156,13 +3156,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.63451584491</v>
+        <v>46188.46784917824</v>
       </c>
       <c r="C29" s="9">
-        <v>46209.81873614583</v>
+        <v>46209.65206947917</v>
       </c>
       <c r="D29" s="9">
-        <v>46209.818759456015</v>
+        <v>46209.65209278935</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3221,13 +3221,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.63452219908</v>
+        <v>46188.467855532406</v>
       </c>
       <c r="C30" s="5">
-        <v>46209.818676319446</v>
+        <v>46209.65200965278</v>
       </c>
       <c r="D30" s="5">
-        <v>46209.81867788194</v>
+        <v>46209.65201121528</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3282,13 +3282,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.634528194445</v>
+        <v>46188.46786152778</v>
       </c>
       <c r="C31" s="9">
-        <v>46209.818722615746</v>
+        <v>46209.652055949075</v>
       </c>
       <c r="D31" s="9">
-        <v>46209.8187240625</v>
+        <v>46209.65205739583</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3343,13 +3343,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.63453408565</v>
+        <v>46188.46786741898</v>
       </c>
       <c r="C32" s="5">
-        <v>46209.819314988425</v>
+        <v>46209.65264832176</v>
       </c>
       <c r="D32" s="5">
-        <v>46209.81933853009</v>
+        <v>46209.65267186343</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3408,13 +3408,13 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.634538252314</v>
+        <v>46188.46787158565</v>
       </c>
       <c r="C33" s="9">
-        <v>46209.819259537035</v>
+        <v>46209.65259287037</v>
       </c>
       <c r="D33" s="9">
-        <v>46209.81926089121</v>
+        <v>46209.652594224535</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>83</v>
@@ -3463,13 +3463,13 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.63454329861</v>
+        <v>46188.46787663194</v>
       </c>
       <c r="C34" s="5">
-        <v>46209.8193018287</v>
+        <v>46209.65263516204</v>
       </c>
       <c r="D34" s="5">
-        <v>46209.81930329862</v>
+        <v>46209.652636631945</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3518,13 +3518,13 @@
         <v>134</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.63454804398</v>
+        <v>46188.46788137731</v>
       </c>
       <c r="C35" s="9">
-        <v>46209.62074709491</v>
+        <v>46209.454080428244</v>
       </c>
       <c r="D35" s="9">
-        <v>46209.62077068287</v>
+        <v>46209.4541040162</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>135</v>
@@ -3583,13 +3583,13 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.63455278936</v>
+        <v>46188.467886122686</v>
       </c>
       <c r="C36" s="5">
-        <v>46209.62002465277</v>
+        <v>46209.453357986116</v>
       </c>
       <c r="D36" s="5">
-        <v>46209.62002645833</v>
+        <v>46209.45335979167</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>89</v>
@@ -3638,13 +3638,13 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.63455811342</v>
+        <v>46188.46789144676</v>
       </c>
       <c r="C37" s="9">
-        <v>46209.62070212963</v>
+        <v>46209.454035462964</v>
       </c>
       <c r="D37" s="9">
-        <v>46209.620703761575</v>
+        <v>46209.45403709491</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3693,11 +3693,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.63456381945</v>
+        <v>46188.467897152776</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46209.62071325231</v>
+        <v>46209.45404658565</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3746,13 +3746,13 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.63456738426</v>
+        <v>46188.46790071759</v>
       </c>
       <c r="C39" s="9">
-        <v>46209.81975005787</v>
+        <v>46209.653083391204</v>
       </c>
       <c r="D39" s="9">
-        <v>46209.81975170139</v>
+        <v>46209.65308503472</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3811,13 +3811,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.63457166667</v>
+        <v>46188.467905</v>
       </c>
       <c r="C40" s="5">
-        <v>46209.8196269676</v>
+        <v>46209.652960300926</v>
       </c>
       <c r="D40" s="5">
-        <v>46209.81962844907</v>
+        <v>46209.65296178241</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>86</v>
@@ -3866,13 +3866,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.634576701385</v>
+        <v>46188.46791003473</v>
       </c>
       <c r="C41" s="9">
-        <v>46209.819662615744</v>
+        <v>46209.65299594907</v>
       </c>
       <c r="D41" s="9">
-        <v>46209.81966414352</v>
+        <v>46209.65299747685</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -3921,13 +3921,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.63417921297</v>
+        <v>46188.467512546296</v>
       </c>
       <c r="C42" s="5">
-        <v>46210.52949314815</v>
+        <v>46210.362826481476</v>
       </c>
       <c r="D42" s="5">
-        <v>46210.52951039352</v>
+        <v>46210.36284372685</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3974,13 +3974,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.63458247685</v>
+        <v>46188.467915810186</v>
       </c>
       <c r="C43" s="9">
-        <v>46196.52481820602</v>
+        <v>46196.35815153935</v>
       </c>
       <c r="D43" s="9">
-        <v>46197.71623851852</v>
+        <v>46197.54957185185</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -4039,13 +4039,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.634588587964</v>
+        <v>46188.4679219213</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.50789115741</v>
+        <v>46198.34122449074</v>
       </c>
       <c r="D44" s="5">
-        <v>46210.20534939815</v>
+        <v>46210.03868273148</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4104,13 +4104,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.63459497685</v>
+        <v>46188.46792831019</v>
       </c>
       <c r="C45" s="9">
-        <v>46198.50795378472</v>
+        <v>46198.341287118055</v>
       </c>
       <c r="D45" s="9">
-        <v>46211.17038164352</v>
+        <v>46211.00371497685</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4169,11 +4169,11 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.63460983796</v>
+        <v>46188.4679431713</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.677102754635</v>
+        <v>46188.51043608796</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4232,11 +4232,11 @@
         <v>176</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.634613946764</v>
+        <v>46188.46794728009</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46202.95705038194</v>
+        <v>46202.79038371528</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>177</v>
@@ -4285,11 +4285,11 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.63461840278</v>
+        <v>46188.46795173611</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46202.957206238425</v>
+        <v>46202.79053957176</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4338,11 +4338,11 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.63467295139</v>
+        <v>46188.46800628472</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.660341678245</v>
+        <v>46188.493675011574</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4385,11 +4385,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.63467763889</v>
+        <v>46188.468010972225</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46209.818739016206</v>
+        <v>46209.652072349534</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4448,11 +4448,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.634684942124</v>
+        <v>46188.46801827547</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.67731989583</v>
+        <v>46188.51065322917</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4511,11 +4511,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.634692962965</v>
+        <v>46188.468026296294</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46209.819318298614</v>
+        <v>46209.65265163194</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4574,11 +4574,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.63469954861</v>
+        <v>46188.468032881945</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.67731701389</v>
+        <v>46188.51065034722</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4637,11 +4637,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.63470560186</v>
+        <v>46188.468038935185</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46209.8196808912</v>
+        <v>46209.65301422453</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4700,11 +4700,11 @@
         <v>202</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.63471155093</v>
+        <v>46188.468044884256</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.67731351852</v>
+        <v>46188.51064685185</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4763,11 +4763,11 @@
         <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.63471731481</v>
+        <v>46188.46805064815</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.662660393515</v>
+        <v>46188.49599372685</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -4810,11 +4810,11 @@
         <v>206</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.63472107639</v>
+        <v>46188.46805440972</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.677743113425</v>
+        <v>46188.51107644676</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>207</v>
@@ -4873,11 +4873,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.63473258102</v>
+        <v>46188.46806591435</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.677464444445</v>
+        <v>46188.51079777778</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>177</v>
@@ -4926,11 +4926,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.63474121528</v>
+        <v>46188.46807454861</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.677461087966</v>
+        <v>46188.510794421294</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>177</v>
@@ -4979,11 +4979,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.63477284722</v>
+        <v>46188.46810618056</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.67773935186</v>
+        <v>46188.511072685185</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5042,11 +5042,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.63477877315</v>
+        <v>46188.46811210648</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46198.507975775465</v>
+        <v>46198.3413091088</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>177</v>
@@ -5095,11 +5095,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.63478605324</v>
+        <v>46188.46811938657</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.50797630787</v>
+        <v>46198.341309641204</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>177</v>
@@ -5148,11 +5148,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.63485537037</v>
+        <v>46188.4681887037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.67780341435</v>
+        <v>46188.511136747686</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5211,11 +5211,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.634861805556</v>
+        <v>46188.46819513889</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46198.507973761574</v>
+        <v>46198.3413070949</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>177</v>
@@ -5264,11 +5264,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.63486881944</v>
+        <v>46188.46820215278</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46198.507963055556</v>
+        <v>46198.341296388884</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>177</v>
@@ -5317,11 +5317,11 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.63489331018</v>
+        <v>46188.46822664352</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46203.55043523148</v>
+        <v>46203.38376856482</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>182</v>
@@ -5364,11 +5364,11 @@
         <v>229</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.634903391205</v>
+        <v>46188.46823672454</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46206.20793023148</v>
+        <v>46206.04126356481</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5427,11 +5427,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.6349100463</v>
+        <v>46188.468243379626</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46203.55044364583</v>
+        <v>46203.38377697917</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5490,11 +5490,11 @@
         <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.6349165162</v>
+        <v>46188.46824984954</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46203.550511388894</v>
+        <v>46203.38384472222</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>
@@ -5553,11 +5553,11 @@
         <v>235</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.634922916666</v>
+        <v>46188.468256249995</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46209.620722314816</v>
+        <v>46209.45405564815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5616,11 +5616,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.63492795139</v>
+        <v>46188.468261284725</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.58705803241</v>
+        <v>46197.42039136574</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>239</v>
@@ -5663,11 +5663,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.63493152778</v>
+        <v>46188.46826486111</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.67802387731</v>
+        <v>46188.51135721065</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5726,11 +5726,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.63494034723</v>
+        <v>46188.468273680555</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.677983657406</v>
+        <v>46188.51131699074</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>177</v>
@@ -5779,11 +5779,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.634945150465</v>
+        <v>46188.46827848379</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.677980567125</v>
+        <v>46188.51131390047</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>177</v>
@@ -5832,13 +5832,13 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.634963668985</v>
+        <v>46188.46829700231</v>
       </c>
       <c r="C75" s="9">
-        <v>46197.58704829861</v>
+        <v>46197.42038163195</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.58706070602</v>
+        <v>46197.42039403935</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5897,13 +5897,13 @@
         <v>249</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.63496887732</v>
+        <v>46188.46830221065</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.58695519676</v>
+        <v>46197.42028853009</v>
       </c>
       <c r="D76" s="5">
-        <v>46198.507974444445</v>
+        <v>46198.34130777778</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>177</v>
@@ -5952,13 +5952,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.63498112268</v>
+        <v>46188.46831445602</v>
       </c>
       <c r="C77" s="9">
-        <v>46197.587035335644</v>
+        <v>46197.42036866898</v>
       </c>
       <c r="D77" s="9">
-        <v>46198.50797810185</v>
+        <v>46198.341311435186</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>177</v>
@@ -6007,11 +6007,11 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.635046296295</v>
+        <v>46188.46837962963</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.67895050926</v>
+        <v>46188.51228384259</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6070,11 +6070,11 @@
         <v>256</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.63505403935</v>
+        <v>46188.46838737269</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.50797702547</v>
+        <v>46198.341310358795</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>177</v>
@@ -6123,11 +6123,11 @@
         <v>258</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.63506813657</v>
+        <v>46188.46840146991</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.507975162036</v>
+        <v>46198.34130849537</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>177</v>
@@ -6176,11 +6176,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.63509704861</v>
+        <v>46188.468430381945</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.67906003472</v>
+        <v>46188.51239336806</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6239,11 +6239,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.635102939814</v>
+        <v>46188.46843627315</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.50797759259</v>
+        <v>46198.34131092593</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>177</v>
@@ -6292,11 +6292,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.63510991898</v>
+        <v>46188.46844325231</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46198.50796203704</v>
+        <v>46198.34129537037</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>177</v>
@@ -6345,11 +6345,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.63513603009</v>
+        <v>46188.468469363426</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.6792096875</v>
+        <v>46188.51254302083</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6408,11 +6408,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.63514172454</v>
+        <v>46188.468475057874</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46202.95697799769</v>
+        <v>46202.79031133102</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>178</v>
@@ -6461,11 +6461,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.63514853009</v>
+        <v>46188.46848186343</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46202.95697554398</v>
+        <v>46202.79030887732</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>177</v>
@@ -6514,11 +6514,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.63521115741</v>
+        <v>46188.46854449074</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46202.95705052083</v>
+        <v>46202.79038385417</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6577,11 +6577,11 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.63521795139</v>
+        <v>46188.46855128472</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46202.957050694444</v>
+        <v>46202.79038402778</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>177</v>
@@ -6630,11 +6630,11 @@
         <v>278</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.635222916666</v>
+        <v>46188.46855625</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.680702488426</v>
+        <v>46188.51403582176</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>177</v>
@@ -6683,11 +6683,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.635247199076</v>
+        <v>46188.46858053241</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.67010366898</v>
+        <v>46188.50343700231</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -6730,11 +6730,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.635250844905</v>
+        <v>46188.46858417824</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.68085204861</v>
+        <v>46188.514185381944</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>283</v>
@@ -6793,11 +6793,11 @@
         <v>287</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.63525673611</v>
+        <v>46188.468590069446</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46202.95704981481</v>
+        <v>46202.79038314815</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>177</v>
@@ -6846,11 +6846,11 @@
         <v>289</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.635261689815</v>
+        <v>46188.46859502315</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46202.95697837963</v>
+        <v>46202.79031171296</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>177</v>
@@ -6899,11 +6899,11 @@
         <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.635279375</v>
+        <v>46188.46861270833</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.68118097223</v>
+        <v>46188.514514305556</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -6962,11 +6962,11 @@
         <v>292</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.63528446759</v>
+        <v>46188.46861780093</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46202.956975532405</v>
+        <v>46202.79030886574</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>177</v>
@@ -7015,11 +7015,11 @@
         <v>294</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.6352894213</v>
+        <v>46188.46862275463</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46202.956975497684</v>
+        <v>46202.79030883102</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>177</v>
@@ -7068,11 +7068,11 @@
         <v>296</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.63530922454</v>
+        <v>46188.46864255787</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.68135644676</v>
+        <v>46188.51468978009</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>297</v>
@@ -7131,11 +7131,11 @@
         <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.63531412037</v>
+        <v>46188.4686474537</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46202.956975532405</v>
+        <v>46202.79030886574</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>177</v>
@@ -7184,11 +7184,11 @@
         <v>300</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.63532239583</v>
+        <v>46188.46865572917</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46202.956975532405</v>
+        <v>46202.79030886574</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>177</v>
@@ -7237,11 +7237,11 @@
         <v>301</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.63538068287</v>
+        <v>46188.4687140162</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.68149567129</v>
+        <v>46188.514829004635</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>302</v>
@@ -7300,11 +7300,11 @@
         <v>304</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.6353874537</v>
+        <v>46188.46872078704</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46202.95697842592</v>
+        <v>46202.79031175926</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>177</v>
@@ -7353,11 +7353,11 @@
         <v>305</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.63539206018</v>
+        <v>46188.46872539352</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46202.95697895833</v>
+        <v>46202.79031229166</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>177</v>
@@ -7406,11 +7406,11 @@
         <v>306</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.635410682866</v>
+        <v>46188.46874401621</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.67123894676</v>
+        <v>46188.50457228009</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>307</v>
@@ -7453,11 +7453,11 @@
         <v>309</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.635413993055</v>
+        <v>46188.46874732639</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.68161465278</v>
+        <v>46188.514947986114</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>310</v>
@@ -7516,11 +7516,11 @@
         <v>313</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.63541944444</v>
+        <v>46188.46875277778</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.920573842595</v>
+        <v>46188.753907175924</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>314</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -1609,13 +1609,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46188.46749296296</v>
+        <v>46188.634159629626</v>
       </c>
       <c r="C4" s="5">
-        <v>46188.75302089121</v>
+        <v>46188.91968755787</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.753035057875</v>
+        <v>46188.91970172454</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1662,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46188.46764418982</v>
+        <v>46188.634310856476</v>
       </c>
       <c r="C5" s="9">
-        <v>46188.75300751158</v>
+        <v>46188.919674178236</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.753021655095</v>
+        <v>46188.91968832176</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1727,13 +1727,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46188.46764981482</v>
+        <v>46188.63431648148</v>
       </c>
       <c r="C6" s="5">
-        <v>46188.752876631945</v>
+        <v>46188.919543298616</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.75289478009</v>
+        <v>46188.91956144676</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1792,13 +1792,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="9">
-        <v>46188.467655162036</v>
+        <v>46188.63432182871</v>
       </c>
       <c r="C7" s="9">
-        <v>46188.752927615744</v>
+        <v>46188.91959428241</v>
       </c>
       <c r="D7" s="9">
-        <v>46188.752942754625</v>
+        <v>46188.9196094213</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>36</v>
@@ -1857,13 +1857,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46188.46765997686</v>
+        <v>46188.634326643514</v>
       </c>
       <c r="C8" s="5">
-        <v>46188.75296844907</v>
+        <v>46188.919635115744</v>
       </c>
       <c r="D8" s="5">
-        <v>46188.752985439816</v>
+        <v>46188.91965210648</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1922,13 +1922,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46188.46749880787</v>
+        <v>46188.634165474534</v>
       </c>
       <c r="C9" s="9">
-        <v>46188.753913148146</v>
+        <v>46188.92057981482</v>
       </c>
       <c r="D9" s="9">
-        <v>46188.753923599535</v>
+        <v>46188.92059026621</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -1975,13 +1975,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="5">
-        <v>46188.467665069446</v>
+        <v>46188.63433173611</v>
       </c>
       <c r="C10" s="5">
-        <v>46188.75344472222</v>
+        <v>46188.920111388885</v>
       </c>
       <c r="D10" s="5">
-        <v>46188.7534465162</v>
+        <v>46188.920113182874</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>46</v>
@@ -2040,13 +2040,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="9">
-        <v>46188.46767643519</v>
+        <v>46188.63434310185</v>
       </c>
       <c r="C11" s="9">
-        <v>46188.7530787037</v>
+        <v>46188.91974537037</v>
       </c>
       <c r="D11" s="9">
-        <v>46188.75365456019</v>
+        <v>46188.92032122685</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>50</v>
@@ -2105,13 +2105,13 @@
         <v>53</v>
       </c>
       <c r="B12" s="5">
-        <v>46188.46768365741</v>
+        <v>46188.63435032408</v>
       </c>
       <c r="C12" s="5">
-        <v>46188.753818310186</v>
+        <v>46188.92048497685</v>
       </c>
       <c r="D12" s="5">
-        <v>46188.75383458333</v>
+        <v>46188.92050125</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>54</v>
@@ -2170,13 +2170,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="9">
-        <v>46188.46769009259</v>
+        <v>46188.634356759256</v>
       </c>
       <c r="C13" s="9">
-        <v>46188.75389753473</v>
+        <v>46188.920564201384</v>
       </c>
       <c r="D13" s="9">
-        <v>46188.753913252316</v>
+        <v>46188.92057991898</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>57</v>
@@ -2235,13 +2235,13 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46188.46750333333</v>
+        <v>46188.634170000005</v>
       </c>
       <c r="C14" s="5">
-        <v>46206.33712295139</v>
+        <v>46206.50378961806</v>
       </c>
       <c r="D14" s="5">
-        <v>46206.337136319446</v>
+        <v>46206.50380298611</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2288,13 +2288,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46188.46769949074</v>
+        <v>46188.63436615741</v>
       </c>
       <c r="C15" s="9">
-        <v>46188.753991261576</v>
+        <v>46188.92065792824</v>
       </c>
       <c r="D15" s="9">
-        <v>46189.647731018515</v>
+        <v>46189.814397685186</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>64</v>
@@ -2353,13 +2353,13 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46188.46770592593</v>
+        <v>46188.63437259259</v>
       </c>
       <c r="C16" s="5">
-        <v>46188.754669270835</v>
+        <v>46188.9213359375</v>
       </c>
       <c r="D16" s="5">
-        <v>46189.64775527778</v>
+        <v>46189.814421944444</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2418,13 +2418,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="9">
-        <v>46188.467712627316</v>
+        <v>46188.63437929398</v>
       </c>
       <c r="C17" s="9">
-        <v>46197.41979372685</v>
+        <v>46197.58646039352</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.41981302084</v>
+        <v>46197.586479687496</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>71</v>
@@ -2483,13 +2483,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46188.467719699074</v>
+        <v>46188.63438636574</v>
       </c>
       <c r="C18" s="5">
-        <v>46206.33570364583</v>
+        <v>46206.502370312504</v>
       </c>
       <c r="D18" s="5">
-        <v>46206.33572076389</v>
+        <v>46206.502387430555</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2548,13 +2548,13 @@
         <v>81</v>
       </c>
       <c r="B19" s="9">
-        <v>46188.467726041665</v>
+        <v>46188.634392708336</v>
       </c>
       <c r="C19" s="9">
-        <v>46206.336882013886</v>
+        <v>46206.50354868056</v>
       </c>
       <c r="D19" s="9">
-        <v>46206.33689766204</v>
+        <v>46206.503564328705</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>82</v>
@@ -2613,13 +2613,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46188.467731620374</v>
+        <v>46188.63439828704</v>
       </c>
       <c r="C20" s="5">
-        <v>46206.33656471065</v>
+        <v>46206.50323137731</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.336582083335</v>
+        <v>46206.50324875</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2678,13 +2678,13 @@
         <v>87</v>
       </c>
       <c r="B21" s="9">
-        <v>46188.46773638889</v>
+        <v>46188.634403055556</v>
       </c>
       <c r="C21" s="9">
-        <v>46206.33710766204</v>
+        <v>46206.5037743287</v>
       </c>
       <c r="D21" s="9">
-        <v>46206.33712297454</v>
+        <v>46206.5037896412</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>88</v>
@@ -2743,13 +2743,13 @@
         <v>90</v>
       </c>
       <c r="B22" s="5">
-        <v>46189.614092627315</v>
+        <v>46189.78075929398</v>
       </c>
       <c r="C22" s="5">
-        <v>46197.419957129634</v>
+        <v>46197.58662379629</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.41997003472</v>
+        <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>91</v>
@@ -2798,13 +2798,13 @@
         <v>94</v>
       </c>
       <c r="B23" s="9">
-        <v>46189.645209375</v>
+        <v>46189.81187604167</v>
       </c>
       <c r="C23" s="9">
-        <v>46197.41994010417</v>
+        <v>46197.586606770834</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.41995747686</v>
+        <v>46197.586624143514</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>95</v>
@@ -2863,13 +2863,13 @@
         <v>97</v>
       </c>
       <c r="B24" s="5">
-        <v>46189.64537734954</v>
+        <v>46189.8120440162</v>
       </c>
       <c r="C24" s="5">
-        <v>46197.41988243056</v>
+        <v>46197.58654909722</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.41990039352</v>
+        <v>46197.586567060185</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>98</v>
@@ -2928,11 +2928,11 @@
         <v>100</v>
       </c>
       <c r="B25" s="9">
-        <v>46188.467508194444</v>
+        <v>46188.634174861116</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46209.65208972222</v>
+        <v>46209.81875638889</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -2975,11 +2975,11 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46188.46775931713</v>
+        <v>46188.63442598379</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46205.016595671295</v>
+        <v>46205.18326233796</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -3038,11 +3038,11 @@
         <v>109</v>
       </c>
       <c r="B27" s="9">
-        <v>46188.46776513889</v>
+        <v>46188.634431805556</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46203.38396293981</v>
+        <v>46203.550629606485</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3097,11 +3097,11 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46188.46777074074</v>
+        <v>46188.63443740741</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46204.00540090278</v>
+        <v>46204.172067569445</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3156,13 +3156,13 @@
         <v>115</v>
       </c>
       <c r="B29" s="9">
-        <v>46188.46784917824</v>
+        <v>46188.63451584491</v>
       </c>
       <c r="C29" s="9">
-        <v>46209.65206947917</v>
+        <v>46209.81873614583</v>
       </c>
       <c r="D29" s="9">
-        <v>46209.65209278935</v>
+        <v>46209.818759456015</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3221,13 +3221,13 @@
         <v>120</v>
       </c>
       <c r="B30" s="5">
-        <v>46188.467855532406</v>
+        <v>46188.63452219908</v>
       </c>
       <c r="C30" s="5">
-        <v>46209.65200965278</v>
+        <v>46209.818676319446</v>
       </c>
       <c r="D30" s="5">
-        <v>46209.65201121528</v>
+        <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>121</v>
@@ -3282,13 +3282,13 @@
         <v>123</v>
       </c>
       <c r="B31" s="9">
-        <v>46188.46786152778</v>
+        <v>46188.634528194445</v>
       </c>
       <c r="C31" s="9">
-        <v>46209.652055949075</v>
+        <v>46209.818722615746</v>
       </c>
       <c r="D31" s="9">
-        <v>46209.65205739583</v>
+        <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>124</v>
@@ -3343,13 +3343,13 @@
         <v>126</v>
       </c>
       <c r="B32" s="5">
-        <v>46188.46786741898</v>
+        <v>46188.63453408565</v>
       </c>
       <c r="C32" s="5">
-        <v>46209.65264832176</v>
+        <v>46209.819314988425</v>
       </c>
       <c r="D32" s="5">
-        <v>46209.65267186343</v>
+        <v>46209.81933853009</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>127</v>
@@ -3408,13 +3408,13 @@
         <v>129</v>
       </c>
       <c r="B33" s="9">
-        <v>46188.46787158565</v>
+        <v>46188.634538252314</v>
       </c>
       <c r="C33" s="9">
-        <v>46209.65259287037</v>
+        <v>46209.819259537035</v>
       </c>
       <c r="D33" s="9">
-        <v>46209.652594224535</v>
+        <v>46209.81926089121</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>83</v>
@@ -3463,13 +3463,13 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46188.46787663194</v>
+        <v>46188.63454329861</v>
       </c>
       <c r="C34" s="5">
-        <v>46209.65263516204</v>
+        <v>46209.8193018287</v>
       </c>
       <c r="D34" s="5">
-        <v>46209.652636631945</v>
+        <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3518,13 +3518,13 @@
         <v>134</v>
       </c>
       <c r="B35" s="9">
-        <v>46188.46788137731</v>
+        <v>46188.63454804398</v>
       </c>
       <c r="C35" s="9">
-        <v>46209.454080428244</v>
+        <v>46209.62074709491</v>
       </c>
       <c r="D35" s="9">
-        <v>46209.4541040162</v>
+        <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>135</v>
@@ -3583,13 +3583,13 @@
         <v>139</v>
       </c>
       <c r="B36" s="5">
-        <v>46188.467886122686</v>
+        <v>46188.63455278936</v>
       </c>
       <c r="C36" s="5">
-        <v>46209.453357986116</v>
+        <v>46209.62002465277</v>
       </c>
       <c r="D36" s="5">
-        <v>46209.45335979167</v>
+        <v>46209.62002645833</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>89</v>
@@ -3638,13 +3638,13 @@
         <v>141</v>
       </c>
       <c r="B37" s="9">
-        <v>46188.46789144676</v>
+        <v>46188.63455811342</v>
       </c>
       <c r="C37" s="9">
-        <v>46209.454035462964</v>
+        <v>46209.62070212963</v>
       </c>
       <c r="D37" s="9">
-        <v>46209.45403709491</v>
+        <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>142</v>
@@ -3693,11 +3693,11 @@
         <v>144</v>
       </c>
       <c r="B38" s="5">
-        <v>46188.467897152776</v>
+        <v>46188.63456381945</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46209.45404658565</v>
+        <v>46209.62071325231</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>145</v>
@@ -3746,13 +3746,13 @@
         <v>148</v>
       </c>
       <c r="B39" s="9">
-        <v>46188.46790071759</v>
+        <v>46188.63456738426</v>
       </c>
       <c r="C39" s="9">
-        <v>46209.653083391204</v>
+        <v>46209.81975005787</v>
       </c>
       <c r="D39" s="9">
-        <v>46209.65308503472</v>
+        <v>46209.81975170139</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>149</v>
@@ -3811,13 +3811,13 @@
         <v>151</v>
       </c>
       <c r="B40" s="5">
-        <v>46188.467905</v>
+        <v>46188.63457166667</v>
       </c>
       <c r="C40" s="5">
-        <v>46209.652960300926</v>
+        <v>46209.8196269676</v>
       </c>
       <c r="D40" s="5">
-        <v>46209.65296178241</v>
+        <v>46209.81962844907</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>86</v>
@@ -3866,13 +3866,13 @@
         <v>153</v>
       </c>
       <c r="B41" s="9">
-        <v>46188.46791003473</v>
+        <v>46188.634576701385</v>
       </c>
       <c r="C41" s="9">
-        <v>46209.65299594907</v>
+        <v>46209.819662615744</v>
       </c>
       <c r="D41" s="9">
-        <v>46209.65299747685</v>
+        <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>154</v>
@@ -3921,13 +3921,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="5">
-        <v>46188.467512546296</v>
+        <v>46188.63417921297</v>
       </c>
       <c r="C42" s="5">
-        <v>46210.362826481476</v>
+        <v>46210.52949314815</v>
       </c>
       <c r="D42" s="5">
-        <v>46210.36284372685</v>
+        <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>157</v>
@@ -3974,13 +3974,13 @@
         <v>159</v>
       </c>
       <c r="B43" s="9">
-        <v>46188.467915810186</v>
+        <v>46188.63458247685</v>
       </c>
       <c r="C43" s="9">
-        <v>46196.35815153935</v>
+        <v>46196.52481820602</v>
       </c>
       <c r="D43" s="9">
-        <v>46197.54957185185</v>
+        <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>160</v>
@@ -4039,13 +4039,13 @@
         <v>164</v>
       </c>
       <c r="B44" s="5">
-        <v>46188.4679219213</v>
+        <v>46188.634588587964</v>
       </c>
       <c r="C44" s="5">
-        <v>46198.34122449074</v>
+        <v>46198.50789115741</v>
       </c>
       <c r="D44" s="5">
-        <v>46210.03868273148</v>
+        <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>165</v>
@@ -4104,13 +4104,13 @@
         <v>167</v>
       </c>
       <c r="B45" s="9">
-        <v>46188.46792831019</v>
+        <v>46188.63459497685</v>
       </c>
       <c r="C45" s="9">
-        <v>46198.341287118055</v>
+        <v>46198.50795378472</v>
       </c>
       <c r="D45" s="9">
-        <v>46211.00371497685</v>
+        <v>46211.17038164352</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>78</v>
@@ -4169,11 +4169,11 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46188.4679431713</v>
+        <v>46188.63460983796</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.51043608796</v>
+        <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4232,11 +4232,11 @@
         <v>176</v>
       </c>
       <c r="B47" s="9">
-        <v>46188.46794728009</v>
+        <v>46188.634613946764</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46202.79038371528</v>
+        <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>177</v>
@@ -4285,11 +4285,11 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46188.46795173611</v>
+        <v>46188.63461840278</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46202.79053957176</v>
+        <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>177</v>
@@ -4338,11 +4338,11 @@
         <v>181</v>
       </c>
       <c r="B49" s="9">
-        <v>46188.46800628472</v>
+        <v>46188.63467295139</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46188.493675011574</v>
+        <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>182</v>
@@ -4385,11 +4385,11 @@
         <v>184</v>
       </c>
       <c r="B50" s="5">
-        <v>46188.468010972225</v>
+        <v>46188.63467763889</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46209.652072349534</v>
+        <v>46209.818739016206</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>185</v>
@@ -4448,11 +4448,11 @@
         <v>190</v>
       </c>
       <c r="B51" s="9">
-        <v>46188.46801827547</v>
+        <v>46188.634684942124</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.51065322917</v>
+        <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4511,11 +4511,11 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46188.468026296294</v>
+        <v>46188.634692962965</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46209.65265163194</v>
+        <v>46209.819318298614</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4574,11 +4574,11 @@
         <v>197</v>
       </c>
       <c r="B53" s="9">
-        <v>46188.468032881945</v>
+        <v>46188.63469954861</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.51065034722</v>
+        <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4637,11 +4637,11 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46188.468038935185</v>
+        <v>46188.63470560186</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46209.65301422453</v>
+        <v>46209.8196808912</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4700,11 +4700,11 @@
         <v>202</v>
       </c>
       <c r="B55" s="9">
-        <v>46188.468044884256</v>
+        <v>46188.63471155093</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.51064685185</v>
+        <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4763,11 +4763,11 @@
         <v>203</v>
       </c>
       <c r="B56" s="5">
-        <v>46188.46805064815</v>
+        <v>46188.63471731481</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46188.49599372685</v>
+        <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -4810,11 +4810,11 @@
         <v>206</v>
       </c>
       <c r="B57" s="9">
-        <v>46188.46805440972</v>
+        <v>46188.63472107639</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.51107644676</v>
+        <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>207</v>
@@ -4873,11 +4873,11 @@
         <v>210</v>
       </c>
       <c r="B58" s="5">
-        <v>46188.46806591435</v>
+        <v>46188.63473258102</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.51079777778</v>
+        <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>177</v>
@@ -4926,11 +4926,11 @@
         <v>213</v>
       </c>
       <c r="B59" s="9">
-        <v>46188.46807454861</v>
+        <v>46188.63474121528</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.510794421294</v>
+        <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>177</v>
@@ -4979,11 +4979,11 @@
         <v>216</v>
       </c>
       <c r="B60" s="5">
-        <v>46188.46810618056</v>
+        <v>46188.63477284722</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.511072685185</v>
+        <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5042,11 +5042,11 @@
         <v>218</v>
       </c>
       <c r="B61" s="9">
-        <v>46188.46811210648</v>
+        <v>46188.63477877315</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46198.3413091088</v>
+        <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>177</v>
@@ -5095,11 +5095,11 @@
         <v>221</v>
       </c>
       <c r="B62" s="5">
-        <v>46188.46811938657</v>
+        <v>46188.63478605324</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.341309641204</v>
+        <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>177</v>
@@ -5148,11 +5148,11 @@
         <v>222</v>
       </c>
       <c r="B63" s="9">
-        <v>46188.4681887037</v>
+        <v>46188.63485537037</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.511136747686</v>
+        <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5211,11 +5211,11 @@
         <v>224</v>
       </c>
       <c r="B64" s="5">
-        <v>46188.46819513889</v>
+        <v>46188.634861805556</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46198.3413070949</v>
+        <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>177</v>
@@ -5264,11 +5264,11 @@
         <v>226</v>
       </c>
       <c r="B65" s="9">
-        <v>46188.46820215278</v>
+        <v>46188.63486881944</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46198.341296388884</v>
+        <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>177</v>
@@ -5317,11 +5317,11 @@
         <v>227</v>
       </c>
       <c r="B66" s="5">
-        <v>46188.46822664352</v>
+        <v>46188.63489331018</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46203.38376856482</v>
+        <v>46203.55043523148</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>182</v>
@@ -5364,11 +5364,11 @@
         <v>229</v>
       </c>
       <c r="B67" s="9">
-        <v>46188.46823672454</v>
+        <v>46188.634903391205</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46206.04126356481</v>
+        <v>46206.20793023148</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5427,11 +5427,11 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46188.468243379626</v>
+        <v>46188.6349100463</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46203.38377697917</v>
+        <v>46203.55044364583</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5490,11 +5490,11 @@
         <v>233</v>
       </c>
       <c r="B69" s="9">
-        <v>46188.46824984954</v>
+        <v>46188.6349165162</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46203.38384472222</v>
+        <v>46203.550511388894</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>
@@ -5553,11 +5553,11 @@
         <v>235</v>
       </c>
       <c r="B70" s="5">
-        <v>46188.468256249995</v>
+        <v>46188.634922916666</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46209.45405564815</v>
+        <v>46209.620722314816</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5616,11 +5616,11 @@
         <v>238</v>
       </c>
       <c r="B71" s="9">
-        <v>46188.468261284725</v>
+        <v>46188.63492795139</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.42039136574</v>
+        <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>239</v>
@@ -5663,11 +5663,11 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46188.46826486111</v>
+        <v>46188.63493152778</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.51135721065</v>
+        <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5726,11 +5726,11 @@
         <v>244</v>
       </c>
       <c r="B73" s="9">
-        <v>46188.468273680555</v>
+        <v>46188.63494034723</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.51131699074</v>
+        <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>177</v>
@@ -5779,11 +5779,11 @@
         <v>246</v>
       </c>
       <c r="B74" s="5">
-        <v>46188.46827848379</v>
+        <v>46188.634945150465</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.51131390047</v>
+        <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>177</v>
@@ -5832,13 +5832,13 @@
         <v>247</v>
       </c>
       <c r="B75" s="9">
-        <v>46188.46829700231</v>
+        <v>46188.634963668985</v>
       </c>
       <c r="C75" s="9">
-        <v>46197.42038163195</v>
+        <v>46197.58704829861</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.42039403935</v>
+        <v>46197.58706070602</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5897,13 +5897,13 @@
         <v>249</v>
       </c>
       <c r="B76" s="5">
-        <v>46188.46830221065</v>
+        <v>46188.63496887732</v>
       </c>
       <c r="C76" s="5">
-        <v>46197.42028853009</v>
+        <v>46197.58695519676</v>
       </c>
       <c r="D76" s="5">
-        <v>46198.34130777778</v>
+        <v>46198.507974444445</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>177</v>
@@ -5952,13 +5952,13 @@
         <v>252</v>
       </c>
       <c r="B77" s="9">
-        <v>46188.46831445602</v>
+        <v>46188.63498112268</v>
       </c>
       <c r="C77" s="9">
-        <v>46197.42036866898</v>
+        <v>46197.587035335644</v>
       </c>
       <c r="D77" s="9">
-        <v>46198.341311435186</v>
+        <v>46198.50797810185</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>177</v>
@@ -6007,11 +6007,11 @@
         <v>254</v>
       </c>
       <c r="B78" s="5">
-        <v>46188.46837962963</v>
+        <v>46188.635046296295</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.51228384259</v>
+        <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6070,11 +6070,11 @@
         <v>256</v>
       </c>
       <c r="B79" s="9">
-        <v>46188.46838737269</v>
+        <v>46188.63505403935</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.341310358795</v>
+        <v>46198.50797702547</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>177</v>
@@ -6123,11 +6123,11 @@
         <v>258</v>
       </c>
       <c r="B80" s="5">
-        <v>46188.46840146991</v>
+        <v>46188.63506813657</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.34130849537</v>
+        <v>46198.507975162036</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>177</v>
@@ -6176,11 +6176,11 @@
         <v>260</v>
       </c>
       <c r="B81" s="9">
-        <v>46188.468430381945</v>
+        <v>46188.63509704861</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.51239336806</v>
+        <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6239,11 +6239,11 @@
         <v>262</v>
       </c>
       <c r="B82" s="5">
-        <v>46188.46843627315</v>
+        <v>46188.635102939814</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.34131092593</v>
+        <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>177</v>
@@ -6292,11 +6292,11 @@
         <v>265</v>
       </c>
       <c r="B83" s="9">
-        <v>46188.46844325231</v>
+        <v>46188.63510991898</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46198.34129537037</v>
+        <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>177</v>
@@ -6345,11 +6345,11 @@
         <v>267</v>
       </c>
       <c r="B84" s="5">
-        <v>46188.468469363426</v>
+        <v>46188.63513603009</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.51254302083</v>
+        <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6408,11 +6408,11 @@
         <v>270</v>
       </c>
       <c r="B85" s="9">
-        <v>46188.468475057874</v>
+        <v>46188.63514172454</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46202.79031133102</v>
+        <v>46202.95697799769</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>178</v>
@@ -6461,11 +6461,11 @@
         <v>272</v>
       </c>
       <c r="B86" s="5">
-        <v>46188.46848186343</v>
+        <v>46188.63514853009</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46202.79030887732</v>
+        <v>46202.95697554398</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>177</v>
@@ -6514,11 +6514,11 @@
         <v>273</v>
       </c>
       <c r="B87" s="9">
-        <v>46188.46854449074</v>
+        <v>46188.63521115741</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46202.79038385417</v>
+        <v>46202.95705052083</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6577,11 +6577,11 @@
         <v>276</v>
       </c>
       <c r="B88" s="5">
-        <v>46188.46855128472</v>
+        <v>46188.63521795139</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46202.79038402778</v>
+        <v>46202.957050694444</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>177</v>
@@ -6630,11 +6630,11 @@
         <v>278</v>
       </c>
       <c r="B89" s="9">
-        <v>46188.46855625</v>
+        <v>46188.635222916666</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.51403582176</v>
+        <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>177</v>
@@ -6683,11 +6683,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46188.46858053241</v>
+        <v>46188.635247199076</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.50343700231</v>
+        <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -6730,11 +6730,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="9">
-        <v>46188.46858417824</v>
+        <v>46188.635250844905</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.514185381944</v>
+        <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>283</v>
@@ -6793,11 +6793,11 @@
         <v>287</v>
       </c>
       <c r="B92" s="5">
-        <v>46188.468590069446</v>
+        <v>46188.63525673611</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46202.79038314815</v>
+        <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>177</v>
@@ -6846,11 +6846,11 @@
         <v>289</v>
       </c>
       <c r="B93" s="9">
-        <v>46188.46859502315</v>
+        <v>46188.635261689815</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46202.79031171296</v>
+        <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>177</v>
@@ -6899,11 +6899,11 @@
         <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46188.46861270833</v>
+        <v>46188.635279375</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.514514305556</v>
+        <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -6962,11 +6962,11 @@
         <v>292</v>
       </c>
       <c r="B95" s="9">
-        <v>46188.46861780093</v>
+        <v>46188.63528446759</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46202.79030886574</v>
+        <v>46202.956975532405</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>177</v>
@@ -7015,11 +7015,11 @@
         <v>294</v>
       </c>
       <c r="B96" s="5">
-        <v>46188.46862275463</v>
+        <v>46188.6352894213</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46202.79030883102</v>
+        <v>46202.956975497684</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>177</v>
@@ -7068,11 +7068,11 @@
         <v>296</v>
       </c>
       <c r="B97" s="9">
-        <v>46188.46864255787</v>
+        <v>46188.63530922454</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.51468978009</v>
+        <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>297</v>
@@ -7131,11 +7131,11 @@
         <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46188.4686474537</v>
+        <v>46188.63531412037</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46202.79030886574</v>
+        <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>177</v>
@@ -7184,11 +7184,11 @@
         <v>300</v>
       </c>
       <c r="B99" s="9">
-        <v>46188.46865572917</v>
+        <v>46188.63532239583</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46202.79030886574</v>
+        <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>177</v>
@@ -7237,11 +7237,11 @@
         <v>301</v>
       </c>
       <c r="B100" s="5">
-        <v>46188.4687140162</v>
+        <v>46188.63538068287</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.514829004635</v>
+        <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>302</v>
@@ -7300,11 +7300,11 @@
         <v>304</v>
       </c>
       <c r="B101" s="9">
-        <v>46188.46872078704</v>
+        <v>46188.6353874537</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46202.79031175926</v>
+        <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>177</v>
@@ -7353,11 +7353,11 @@
         <v>305</v>
       </c>
       <c r="B102" s="5">
-        <v>46188.46872539352</v>
+        <v>46188.63539206018</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46202.79031229166</v>
+        <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>177</v>
@@ -7406,11 +7406,11 @@
         <v>306</v>
       </c>
       <c r="B103" s="9">
-        <v>46188.46874401621</v>
+        <v>46188.635410682866</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46188.50457228009</v>
+        <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>307</v>
@@ -7453,11 +7453,11 @@
         <v>309</v>
       </c>
       <c r="B104" s="5">
-        <v>46188.46874732639</v>
+        <v>46188.635413993055</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.514947986114</v>
+        <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>310</v>
@@ -7516,11 +7516,11 @@
         <v>313</v>
       </c>
       <c r="B105" s="9">
-        <v>46188.46875277778</v>
+        <v>46188.63541944444</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.753907175924</v>
+        <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>314</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="316">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -346,6 +346,9 @@
     <t>Materiales corte Laser OT 4360,rodete OT 4360</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1215728035819291</t>
   </si>
   <si>
@@ -361,18 +364,18 @@
     <t>Generación OC Rodete OT 4360,Fabricación Rodete OT 4360</t>
   </si>
   <si>
+    <t>1215728035819308</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4360</t>
+  </si>
+  <si>
+    <t>rodete OT 4360,Fabricación Rodete OT 4360</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
-    <t>1215728035819308</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4360</t>
-  </si>
-  <si>
-    <t>rodete OT 4360,Fabricación Rodete OT 4360</t>
-  </si>
-  <si>
     <t>1215728035829709</t>
   </si>
   <si>
@@ -602,9 +605,6 @@
   </si>
   <si>
     <t>Control de calidad corte laser ,Bodega:</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215727723755882</t>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46209.81875638889</v>
+        <v>46212.65353668982</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -2968,30 +2968,34 @@
       <c r="R25" s="10"/>
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
+      <c r="U25" s="12" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46212.653515659724</v>
+      </c>
       <c r="D26" s="5">
-        <v>46205.18326233796</v>
+        <v>46212.653841203704</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -3012,7 +3016,7 @@
         <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>101</v>
@@ -3027,10 +3031,10 @@
         <v>32</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="11" t="s">
-        <v>108</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3040,9 +3044,11 @@
       <c r="B27" s="9">
         <v>46188.634431805556</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46212.653463124996</v>
+      </c>
       <c r="D27" s="9">
-        <v>46203.550629606485</v>
+        <v>46212.65346519676</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>110</v>
@@ -3051,10 +3057,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3072,7 +3078,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>71</v>
@@ -3089,31 +3095,33 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46212.653502280096</v>
+      </c>
       <c r="D28" s="5">
-        <v>46204.172067569445</v>
+        <v>46212.65350395833</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3131,13 +3139,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3148,12 +3156,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3165,16 +3173,16 @@
         <v>46209.818759456015</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3195,7 +3203,7 @@
         <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>101</v>
@@ -3218,7 +3226,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3230,16 +3238,16 @@
         <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3257,13 +3265,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3274,12 +3282,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3291,16 +3299,16 @@
         <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3318,13 +3326,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3335,12 +3343,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3352,16 +3360,16 @@
         <v>46209.81933853009</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3382,7 +3390,7 @@
         <v>101</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3405,7 +3413,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3423,10 +3431,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3444,13 +3452,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3460,7 +3468,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3472,16 +3480,16 @@
         <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3499,13 +3507,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3515,7 +3523,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3527,16 +3535,16 @@
         <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3557,7 +3565,7 @@
         <v>101</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3580,7 +3588,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3598,10 +3606,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3619,13 +3627,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3635,7 +3643,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3647,16 +3655,16 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3674,13 +3682,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3690,7 +3698,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3700,16 +3708,16 @@
         <v>46209.62071325231</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3727,10 +3735,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3743,7 +3751,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3755,16 +3763,16 @@
         <v>46209.81975170139</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3785,7 +3793,7 @@
         <v>101</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3808,7 +3816,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3826,10 +3834,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3847,13 +3855,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3863,7 +3871,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3875,16 +3883,16 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3902,13 +3910,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3918,7 +3926,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3930,7 +3938,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3954,7 +3962,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3971,7 +3979,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -3983,16 +3991,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4010,13 +4018,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>54</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4036,7 +4044,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4048,16 +4056,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4075,13 +4083,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4101,7 +4109,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4119,10 +4127,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4140,13 +4148,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4166,7 +4174,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4176,16 +4184,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4203,10 +4211,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4224,12 +4232,12 @@
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4239,16 +4247,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4266,13 +4274,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4282,7 +4290,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4292,16 +4300,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4319,13 +4327,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4335,7 +4343,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4345,7 +4353,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4369,7 +4377,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4382,7 +4390,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4392,16 +4400,16 @@
         <v>46209.818739016206</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4419,13 +4427,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4440,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4461,10 +4469,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4482,7 +4490,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>192</v>
@@ -4503,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4524,10 +4532,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4545,10 +4553,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>196</v>
@@ -4566,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4587,10 +4595,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4608,13 +4616,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4629,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4650,10 +4658,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4671,10 +4679,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>201</v>
@@ -4692,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4713,10 +4721,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4734,13 +4742,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>200</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4755,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4847,7 +4855,7 @@
         <v>204</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>204</v>
@@ -4865,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4880,7 +4888,7 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4933,7 +4941,7 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5016,7 +5024,7 @@
         <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>204</v>
@@ -5034,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5049,7 +5057,7 @@
         <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5102,7 +5110,7 @@
         <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5161,10 +5169,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5185,7 +5193,7 @@
         <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>204</v>
@@ -5203,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5218,16 +5226,16 @@
         <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5271,16 +5279,16 @@
         <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5321,10 +5329,10 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46203.55043523148</v>
+        <v>46212.654024166666</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5366,9 +5374,11 @@
       <c r="B67" s="9">
         <v>46188.634903391205</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="9">
+        <v>46212.65378395833</v>
+      </c>
       <c r="D67" s="9">
-        <v>46206.20793023148</v>
+        <v>46212.65419707176</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>230</v>
@@ -5377,10 +5387,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5398,10 +5408,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>193</v>
@@ -5416,10 +5426,10 @@
         <v>32</v>
       </c>
       <c r="T67" s="10">
-        <v>0</v>
-      </c>
-      <c r="U67" s="11" t="s">
-        <v>108</v>
+        <v>1</v>
+      </c>
+      <c r="U67" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5429,9 +5439,11 @@
       <c r="B68" s="5">
         <v>46188.6349100463</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46212.654018402776</v>
+      </c>
       <c r="D68" s="5">
-        <v>46203.55044364583</v>
+        <v>46212.65411137731</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5440,10 +5452,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5461,7 +5473,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>98</v>
@@ -5479,10 +5491,10 @@
         <v>32</v>
       </c>
       <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="12" t="s">
-        <v>189</v>
+        <v>1</v>
+      </c>
+      <c r="U68" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5503,10 +5515,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5524,7 +5536,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>95</v>
@@ -5545,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5566,10 +5578,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5587,10 +5599,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>237</v>
@@ -5608,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5718,7 +5730,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5733,7 +5745,7 @@
         <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5786,7 +5798,7 @@
         <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5871,7 +5883,7 @@
         <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>239</v>
@@ -5903,10 +5915,10 @@
         <v>46197.58695519676</v>
       </c>
       <c r="D76" s="5">
-        <v>46198.507974444445</v>
+        <v>46212.65402488426</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5958,10 +5970,10 @@
         <v>46197.587035335644</v>
       </c>
       <c r="D77" s="9">
-        <v>46198.50797810185</v>
+        <v>46212.65402556713</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6044,7 +6056,7 @@
         <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>239</v>
@@ -6062,7 +6074,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6074,10 +6086,10 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46198.50797702547</v>
+        <v>46212.65379315973</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6127,10 +6139,10 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46198.507975162036</v>
+        <v>46212.65379201389</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6213,7 +6225,7 @@
         <v>239</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>239</v>
@@ -6231,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6246,7 +6258,7 @@
         <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6299,7 +6311,7 @@
         <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6400,7 +6412,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6415,7 +6427,7 @@
         <v>46202.95697799769</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6445,7 +6457,7 @@
         <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>271</v>
@@ -6468,7 +6480,7 @@
         <v>46202.95697554398</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6498,7 +6510,7 @@
         <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>271</v>
@@ -6551,7 +6563,7 @@
         <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>275</v>
@@ -6569,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6584,7 +6596,7 @@
         <v>46202.957050694444</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6614,7 +6626,7 @@
         <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>277</v>
@@ -6637,7 +6649,7 @@
         <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6667,7 +6679,7 @@
         <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>277</v>
@@ -6785,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6800,7 +6812,7 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6830,7 +6842,7 @@
         <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>288</v>
@@ -6853,7 +6865,7 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6883,7 +6895,7 @@
         <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>288</v>
@@ -6936,7 +6948,7 @@
         <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>280</v>
@@ -6954,7 +6966,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -6969,7 +6981,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6999,7 +7011,7 @@
         <v>291</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>293</v>
@@ -7022,7 +7034,7 @@
         <v>46202.956975497684</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7052,7 +7064,7 @@
         <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>295</v>
@@ -7105,7 +7117,7 @@
         <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>280</v>
@@ -7123,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7138,7 +7150,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7168,7 +7180,7 @@
         <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>299</v>
@@ -7191,7 +7203,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7221,7 +7233,7 @@
         <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>299</v>
@@ -7274,7 +7286,7 @@
         <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>303</v>
@@ -7292,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7307,7 +7319,7 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7337,7 +7349,7 @@
         <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>302</v>
@@ -7360,7 +7372,7 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7390,7 +7402,7 @@
         <v>302</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>302</v>
@@ -7508,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7529,10 +7541,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>
@@ -7571,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -346,265 +346,265 @@
     <t>Materiales corte Laser OT 4360,rodete OT 4360</t>
   </si>
   <si>
+    <t>1215728035819291</t>
+  </si>
+  <si>
+    <t>rodete OT 4360</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4360,Fabricación Rodete OT 4360</t>
+  </si>
+  <si>
+    <t>1215728035819308</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete OT 4360</t>
+  </si>
+  <si>
+    <t>rodete OT 4360,Fabricación Rodete OT 4360</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1215728035829709</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete OT 4360</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,rodete OT 4360</t>
+  </si>
+  <si>
+    <t>1215727723568477</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4360</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>1215727831363866</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>1215727831363886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4360,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215727831373407</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>1215727831373419</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>1215727723641751</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1215727723641768</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4360,Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t>1215727939764035</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4360,Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t>1215727939764052</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4360,Control de calidad fabricación externa  OT 4360,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215727939776448</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215727939776460</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215727792775028</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215727792775045</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1215727332551588</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215727939795692</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1215727939795714</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1215727792809496</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 4360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727939821604</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728035964722</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728035964734</t>
+  </si>
+  <si>
+    <t>1215727939892842</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215727939892854</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Bodega:</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215728035819291</t>
-  </si>
-  <si>
-    <t>rodete OT 4360</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4360,Fabricación Rodete OT 4360</t>
-  </si>
-  <si>
-    <t>1215728035819308</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete OT 4360</t>
-  </si>
-  <si>
-    <t>rodete OT 4360,Fabricación Rodete OT 4360</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1215728035829709</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete OT 4360</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,rodete OT 4360</t>
-  </si>
-  <si>
-    <t>1215727723568477</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4360</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>1215727831363866</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>1215727831363886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4360,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215727831373407</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>1215727831373419</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>1215727723641751</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1215727723641768</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4360,Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t>1215727939764035</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4360,Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t>1215727939764052</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4360,Control de calidad fabricación externa  OT 4360,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215727939776448</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215727939776460</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792775028</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792775045</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1215727332551588</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215727939795692</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1215727939795714</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1215727792809496</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 4360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727939821604</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728035964722</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728035964734</t>
-  </si>
-  <si>
-    <t>1215727939892842</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215727939892854</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Bodega:</t>
   </si>
   <si>
     <t>1215727723755882</t>
@@ -2930,9 +2930,11 @@
       <c r="B25" s="9">
         <v>46188.634174861116</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46212.85334166666</v>
+      </c>
       <c r="D25" s="9">
-        <v>46212.65353668982</v>
+        <v>46212.85336304398</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>101</v>
@@ -2967,14 +2969,16 @@
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-      <c r="U25" s="12" t="s">
-        <v>103</v>
+      <c r="T25" s="10">
+        <v>1</v>
+      </c>
+      <c r="U25" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
@@ -2986,16 +2990,16 @@
         <v>46212.653841203704</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -3016,7 +3020,7 @@
         <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>101</v>
@@ -3039,7 +3043,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46188.634431805556</v>
@@ -3051,16 +3055,16 @@
         <v>46212.65346519676</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>107</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3078,13 +3082,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3095,12 +3099,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3112,16 +3116,16 @@
         <v>46212.65350395833</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3139,13 +3143,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3156,12 +3160,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3173,16 +3177,16 @@
         <v>46209.818759456015</v>
       </c>
       <c r="E29" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="10" t="s">
+      <c r="H29" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3203,7 +3207,7 @@
         <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>101</v>
@@ -3226,7 +3230,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3238,16 +3242,16 @@
         <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3265,13 +3269,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3282,12 +3286,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3299,16 +3303,16 @@
         <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3326,13 +3330,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3343,12 +3347,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3360,16 +3364,16 @@
         <v>46209.81933853009</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3390,7 +3394,7 @@
         <v>101</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3413,7 +3417,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3431,10 +3435,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3452,13 +3456,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3468,7 +3472,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3480,16 +3484,16 @@
         <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3507,13 +3511,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3523,7 +3527,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3535,16 +3539,16 @@
         <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3565,7 +3569,7 @@
         <v>101</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3588,7 +3592,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3606,10 +3610,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3627,13 +3631,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3643,7 +3647,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3655,16 +3659,16 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3682,13 +3686,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3698,7 +3702,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3708,16 +3712,16 @@
         <v>46209.62071325231</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3735,10 +3739,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3751,7 +3755,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3763,16 +3767,16 @@
         <v>46209.81975170139</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3793,7 +3797,7 @@
         <v>101</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3816,7 +3820,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3834,10 +3838,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3855,13 +3859,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3871,7 +3875,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3883,16 +3887,16 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>119</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3910,13 +3914,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3926,7 +3930,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3938,7 +3942,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3962,7 +3966,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3979,7 +3983,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -3991,16 +3995,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>162</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4018,13 +4022,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>54</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4044,7 +4048,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4056,16 +4060,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4083,13 +4087,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4109,7 +4113,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4127,10 +4131,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>170</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4148,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4174,7 +4178,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4184,16 +4188,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4211,10 +4215,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4232,12 +4236,12 @@
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4247,16 +4251,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4274,13 +4278,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4290,7 +4294,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4300,16 +4304,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4327,13 +4331,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4343,7 +4347,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4353,7 +4357,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4377,7 +4381,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4390,7 +4394,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4400,16 +4404,16 @@
         <v>46209.818739016206</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4427,13 +4431,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4448,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4469,10 +4473,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4490,7 +4494,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>192</v>
@@ -4511,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4532,10 +4536,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4553,10 +4557,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>196</v>
@@ -4574,7 +4578,7 @@
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4595,10 +4599,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4616,13 +4620,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4637,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4658,10 +4662,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4679,10 +4683,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>201</v>
@@ -4700,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4721,10 +4725,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4742,13 +4746,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>200</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4763,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4855,7 +4859,7 @@
         <v>204</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>204</v>
@@ -4873,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4888,7 +4892,7 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4941,7 +4945,7 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5024,7 +5028,7 @@
         <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>204</v>
@@ -5042,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5057,7 +5061,7 @@
         <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5110,7 +5114,7 @@
         <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5169,10 +5173,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5193,7 +5197,7 @@
         <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>204</v>
@@ -5211,7 +5215,7 @@
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5226,16 +5230,16 @@
         <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5279,16 +5283,16 @@
         <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5332,7 +5336,7 @@
         <v>46212.654024166666</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5387,10 +5391,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5408,10 +5412,10 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P67" s="10" t="s">
         <v>193</v>
@@ -5452,10 +5456,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5473,7 +5477,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>98</v>
@@ -5515,10 +5519,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5536,7 +5540,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>95</v>
@@ -5557,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5578,10 +5582,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5599,10 +5603,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>237</v>
@@ -5620,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5730,7 +5734,7 @@
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5745,7 +5749,7 @@
         <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5798,7 +5802,7 @@
         <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5883,7 +5887,7 @@
         <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>239</v>
@@ -5918,7 +5922,7 @@
         <v>46212.65402488426</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5973,7 +5977,7 @@
         <v>46212.65402556713</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6056,7 +6060,7 @@
         <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>239</v>
@@ -6074,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6089,7 +6093,7 @@
         <v>46212.65379315973</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6142,7 +6146,7 @@
         <v>46212.65379201389</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6225,7 +6229,7 @@
         <v>239</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>239</v>
@@ -6243,7 +6247,7 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6258,7 +6262,7 @@
         <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6311,7 +6315,7 @@
         <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6412,7 +6416,7 @@
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6427,7 +6431,7 @@
         <v>46202.95697799769</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6457,7 +6461,7 @@
         <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>271</v>
@@ -6480,7 +6484,7 @@
         <v>46202.95697554398</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6510,7 +6514,7 @@
         <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>271</v>
@@ -6563,7 +6567,7 @@
         <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>275</v>
@@ -6581,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6596,7 +6600,7 @@
         <v>46202.957050694444</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6626,7 +6630,7 @@
         <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>277</v>
@@ -6649,7 +6653,7 @@
         <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6679,7 +6683,7 @@
         <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>277</v>
@@ -6797,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -6812,7 +6816,7 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6842,7 +6846,7 @@
         <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>288</v>
@@ -6865,7 +6869,7 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6895,7 +6899,7 @@
         <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>288</v>
@@ -6948,7 +6952,7 @@
         <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>280</v>
@@ -6966,7 +6970,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -6981,7 +6985,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7011,7 +7015,7 @@
         <v>291</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>293</v>
@@ -7034,7 +7038,7 @@
         <v>46202.956975497684</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7064,7 +7068,7 @@
         <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>295</v>
@@ -7117,7 +7121,7 @@
         <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>280</v>
@@ -7135,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7150,7 +7154,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7180,7 +7184,7 @@
         <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>299</v>
@@ -7203,7 +7207,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7233,7 +7237,7 @@
         <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>299</v>
@@ -7286,7 +7290,7 @@
         <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>303</v>
@@ -7304,7 +7308,7 @@
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7319,7 +7323,7 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7349,7 +7353,7 @@
         <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>302</v>
@@ -7372,7 +7376,7 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7402,7 +7406,7 @@
         <v>302</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>302</v>
@@ -7520,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -7541,10 +7545,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>
@@ -7583,7 +7587,7 @@
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="315">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -275,9 +275,6 @@
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales corte Laser OT 4360</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215727831264658</t>
@@ -2489,7 +2486,7 @@
         <v>46206.502370312504</v>
       </c>
       <c r="D18" s="5">
-        <v>46206.502387430555</v>
+        <v>46213.191536909726</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2533,8 +2530,8 @@
       <c r="R18" s="5">
         <v>46212</v>
       </c>
-      <c r="S18" s="12" t="s">
-        <v>80</v>
+      <c r="S18" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T18" s="6">
         <v>1</v>
@@ -2545,7 +2542,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="9">
         <v>46188.634392708336</v>
@@ -2554,10 +2551,10 @@
         <v>46206.50354868056</v>
       </c>
       <c r="D19" s="9">
-        <v>46206.503564328705</v>
+        <v>46213.19154050926</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2590,7 +2587,7 @@
         <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="9">
         <v>46211</v>
@@ -2598,8 +2595,8 @@
       <c r="R19" s="9">
         <v>46212</v>
       </c>
-      <c r="S19" s="12" t="s">
-        <v>80</v>
+      <c r="S19" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T19" s="10">
         <v>1</v>
@@ -2610,7 +2607,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46188.63439828704</v>
@@ -2619,10 +2616,10 @@
         <v>46206.50323137731</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.50324875</v>
+        <v>46213.191536875005</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2655,7 +2652,7 @@
         <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46211</v>
@@ -2663,8 +2660,8 @@
       <c r="R20" s="5">
         <v>46212</v>
       </c>
-      <c r="S20" s="12" t="s">
-        <v>80</v>
+      <c r="S20" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
@@ -2675,7 +2672,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="9">
         <v>46188.634403055556</v>
@@ -2684,10 +2681,10 @@
         <v>46206.5037743287</v>
       </c>
       <c r="D21" s="9">
-        <v>46206.5037896412</v>
+        <v>46213.19153681713</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2720,7 +2717,7 @@
         <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="9">
         <v>46211</v>
@@ -2728,8 +2725,8 @@
       <c r="R21" s="9">
         <v>46212</v>
       </c>
-      <c r="S21" s="12" t="s">
-        <v>80</v>
+      <c r="S21" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T21" s="10">
         <v>1</v>
@@ -2740,7 +2737,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46189.78075929398</v>
@@ -2752,7 +2749,7 @@
         <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2776,7 +2773,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2784,7 +2781,7 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2795,7 +2792,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="9">
         <v>46189.81187604167</v>
@@ -2807,7 +2804,7 @@
         <v>46197.586624143514</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2834,13 +2831,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>64</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="9">
         <v>46183</v>
@@ -2860,7 +2857,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46189.8120440162</v>
@@ -2872,7 +2869,7 @@
         <v>46197.586567060185</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2899,13 +2896,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>46183</v>
@@ -2925,7 +2922,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B25" s="9">
         <v>46188.634174861116</v>
@@ -2937,7 +2934,7 @@
         <v>46212.85336304398</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -2961,7 +2958,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -2978,7 +2975,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
@@ -2990,16 +2987,16 @@
         <v>46212.653841203704</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
+      <c r="H26" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -3017,13 +3014,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="5">
         <v>46183</v>
@@ -3043,7 +3040,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" s="9">
         <v>46188.634431805556</v>
@@ -3055,16 +3052,16 @@
         <v>46212.65346519676</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="10" t="s">
         <v>105</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>106</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3082,29 +3079,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>71</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3116,16 +3113,16 @@
         <v>46212.65350395833</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3143,29 +3140,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3177,16 +3174,16 @@
         <v>46209.818759456015</v>
       </c>
       <c r="E29" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="10" t="s">
+      <c r="H29" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3204,13 +3201,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q29" s="9">
         <v>46213</v>
@@ -3219,7 +3216,7 @@
         <v>46225</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3230,7 +3227,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3242,16 +3239,16 @@
         <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3269,29 +3266,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3303,16 +3300,16 @@
         <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3330,29 +3327,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3364,16 +3361,16 @@
         <v>46209.81933853009</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3391,10 +3388,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3406,7 +3403,7 @@
         <v>46225</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3417,7 +3414,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3429,16 +3426,16 @@
         <v>46209.81926089121</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3456,13 +3453,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3472,7 +3469,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3484,16 +3481,16 @@
         <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3511,13 +3508,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3527,7 +3524,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3539,16 +3536,16 @@
         <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3566,10 +3563,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3581,7 +3578,7 @@
         <v>46253</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3592,7 +3589,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3604,16 +3601,16 @@
         <v>46209.62002645833</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3631,13 +3628,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3647,7 +3644,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3659,16 +3656,16 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3686,13 +3683,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3702,7 +3699,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3712,16 +3709,16 @@
         <v>46209.62071325231</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3739,10 +3736,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3755,7 +3752,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3767,16 +3764,16 @@
         <v>46209.81975170139</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3794,10 +3791,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3809,7 +3806,7 @@
         <v>46225</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3820,7 +3817,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3832,16 +3829,16 @@
         <v>46209.81962844907</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3859,13 +3856,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3875,7 +3872,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3887,16 +3884,16 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>117</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>118</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3914,13 +3911,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3930,7 +3927,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3942,7 +3939,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3966,7 +3963,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3983,7 +3980,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -3995,16 +3992,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4022,13 +4019,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>54</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4048,7 +4045,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4060,16 +4057,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4087,13 +4084,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4113,7 +4110,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4131,10 +4128,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4152,13 +4149,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4178,7 +4175,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4188,16 +4185,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4215,10 +4212,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4230,18 +4227,18 @@
         <v>46259</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4251,16 +4248,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4278,13 +4275,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4294,7 +4291,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4304,16 +4301,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4331,13 +4328,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4347,7 +4344,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4357,7 +4354,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4381,7 +4378,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4394,7 +4391,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4404,16 +4401,16 @@
         <v>46209.818739016206</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4431,13 +4428,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4446,18 +4443,18 @@
         <v>46227</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46188.634684942124</v>
@@ -4467,16 +4464,16 @@
         <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4494,13 +4491,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4509,18 +4506,18 @@
         <v>46231</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46188.634692962965</v>
@@ -4530,16 +4527,16 @@
         <v>46209.819318298614</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4557,13 +4554,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4572,18 +4569,18 @@
         <v>46227</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46188.63469954861</v>
@@ -4593,16 +4590,16 @@
         <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4620,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4635,18 +4632,18 @@
         <v>46231</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63470560186</v>
@@ -4656,16 +4653,16 @@
         <v>46209.8196808912</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4683,13 +4680,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4698,18 +4695,18 @@
         <v>46227</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9">
         <v>46188.63471155093</v>
@@ -4719,16 +4716,16 @@
         <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4746,13 +4743,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4761,18 +4758,18 @@
         <v>46231</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46188.63471731481</v>
@@ -4782,7 +4779,7 @@
         <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4806,7 +4803,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4819,7 +4816,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
         <v>46188.63472107639</v>
@@ -4829,16 +4826,16 @@
         <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4856,13 +4853,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4871,18 +4868,18 @@
         <v>46234</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63473258102</v>
@@ -4892,16 +4889,16 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4919,13 +4916,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4935,7 +4932,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B59" s="9">
         <v>46188.63474121528</v>
@@ -4945,16 +4942,16 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -4972,13 +4969,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>214</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>215</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4988,7 +4985,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63477284722</v>
@@ -4998,16 +4995,16 @@
         <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -5025,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -5040,18 +5037,18 @@
         <v>46241</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46188.63477877315</v>
@@ -5061,16 +5058,16 @@
         <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5088,13 +5085,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5104,7 +5101,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63478605324</v>
@@ -5114,16 +5111,16 @@
         <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5141,13 +5138,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5157,7 +5154,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46188.63485537037</v>
@@ -5167,16 +5164,16 @@
         <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5194,13 +5191,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5209,18 +5206,18 @@
         <v>46244</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46188.634861805556</v>
@@ -5230,16 +5227,16 @@
         <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5257,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5273,7 +5270,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46188.63486881944</v>
@@ -5283,16 +5280,16 @@
         <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5310,13 +5307,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5326,7 +5323,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63489331018</v>
@@ -5336,7 +5333,7 @@
         <v>46212.654024166666</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5360,7 +5357,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5373,7 +5370,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B67" s="9">
         <v>46188.634903391205</v>
@@ -5385,16 +5382,16 @@
         <v>46212.65419707176</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5412,13 +5409,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5438,7 +5435,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46188.6349100463</v>
@@ -5450,16 +5447,16 @@
         <v>46212.65411137731</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5477,13 +5474,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5503,7 +5500,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
@@ -5513,16 +5510,16 @@
         <v>46203.550511388894</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5540,13 +5537,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5555,18 +5552,18 @@
         <v>46223</v>
       </c>
       <c r="S69" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5576,16 +5573,16 @@
         <v>46209.620722314816</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5603,13 +5600,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5618,18 +5615,18 @@
         <v>46254</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5639,7 +5636,7 @@
         <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5663,7 +5660,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5676,7 +5673,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
@@ -5686,7 +5683,7 @@
         <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5713,13 +5710,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5728,18 +5725,18 @@
         <v>46251</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B73" s="9">
         <v>46188.63494034723</v>
@@ -5749,7 +5746,7 @@
         <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5776,10 +5773,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5792,7 +5789,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46188.634945150465</v>
@@ -5802,7 +5799,7 @@
         <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5829,10 +5826,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5845,7 +5842,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B75" s="9">
         <v>46188.634963668985</v>
@@ -5857,7 +5854,7 @@
         <v>46197.58706070602</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5884,13 +5881,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5899,7 +5896,7 @@
         <v>46252</v>
       </c>
       <c r="S75" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -5910,7 +5907,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46188.63496887732</v>
@@ -5922,7 +5919,7 @@
         <v>46212.65402488426</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5949,13 +5946,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5965,7 +5962,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B77" s="9">
         <v>46188.63498112268</v>
@@ -5977,7 +5974,7 @@
         <v>46212.65402556713</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6004,13 +6001,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6020,7 +6017,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B78" s="5">
         <v>46188.635046296295</v>
@@ -6030,7 +6027,7 @@
         <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6057,13 +6054,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -6072,18 +6069,18 @@
         <v>46253</v>
       </c>
       <c r="S78" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B79" s="9">
         <v>46188.63505403935</v>
@@ -6093,7 +6090,7 @@
         <v>46212.65379315973</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6120,13 +6117,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6136,7 +6133,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46188.63506813657</v>
@@ -6146,7 +6143,7 @@
         <v>46212.65379201389</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6173,13 +6170,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6189,7 +6186,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
         <v>46188.63509704861</v>
@@ -6199,7 +6196,7 @@
         <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6226,13 +6223,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6241,18 +6238,18 @@
         <v>46224</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46188.635102939814</v>
@@ -6262,7 +6259,7 @@
         <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6289,13 +6286,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>263</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>264</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6305,7 +6302,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
         <v>46188.63510991898</v>
@@ -6315,7 +6312,7 @@
         <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6342,13 +6339,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6358,7 +6355,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46188.63513603009</v>
@@ -6368,7 +6365,7 @@
         <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6395,13 +6392,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6410,18 +6407,18 @@
         <v>46258</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
         <v>46188.63514172454</v>
@@ -6431,7 +6428,7 @@
         <v>46202.95697799769</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6458,13 +6455,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6474,7 +6471,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B86" s="5">
         <v>46188.63514853009</v>
@@ -6484,7 +6481,7 @@
         <v>46202.95697554398</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6511,13 +6508,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6527,7 +6524,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46188.63521115741</v>
@@ -6537,7 +6534,7 @@
         <v>46202.95705052083</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6564,13 +6561,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q87" s="9">
         <v>46260</v>
@@ -6579,18 +6576,18 @@
         <v>46260</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B88" s="5">
         <v>46188.63521795139</v>
@@ -6600,7 +6597,7 @@
         <v>46202.957050694444</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6627,13 +6624,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6643,7 +6640,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B89" s="9">
         <v>46188.635222916666</v>
@@ -6653,7 +6650,7 @@
         <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6680,13 +6677,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6696,7 +6693,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46188.635247199076</v>
@@ -6706,7 +6703,7 @@
         <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6730,7 +6727,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6743,7 +6740,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B91" s="9">
         <v>46188.635250844905</v>
@@ -6753,16 +6750,16 @@
         <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="10" t="s">
+      <c r="H91" s="10" t="s">
         <v>284</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>285</v>
       </c>
       <c r="I91" s="9">
         <v>46261</v>
@@ -6780,13 +6777,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q91" s="9">
         <v>46261</v>
@@ -6795,18 +6792,18 @@
         <v>46261</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B92" s="5">
         <v>46188.63525673611</v>
@@ -6816,16 +6813,16 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I92" s="5">
         <v>46261</v>
@@ -6843,13 +6840,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6859,7 +6856,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B93" s="9">
         <v>46188.635261689815</v>
@@ -6869,16 +6866,16 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>284</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>285</v>
       </c>
       <c r="I93" s="9">
         <v>46261</v>
@@ -6896,13 +6893,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6912,7 +6909,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B94" s="5">
         <v>46188.635279375</v>
@@ -6922,7 +6919,7 @@
         <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6949,13 +6946,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q94" s="5">
         <v>46262</v>
@@ -6964,18 +6961,18 @@
         <v>46262</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B95" s="9">
         <v>46188.63528446759</v>
@@ -6985,7 +6982,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7012,13 +7009,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7028,7 +7025,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B96" s="5">
         <v>46188.6352894213</v>
@@ -7038,7 +7035,7 @@
         <v>46202.956975497684</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7065,13 +7062,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7081,7 +7078,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B97" s="9">
         <v>46188.63530922454</v>
@@ -7091,16 +7088,16 @@
         <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7118,13 +7115,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q97" s="9">
         <v>46265</v>
@@ -7133,18 +7130,18 @@
         <v>46265</v>
       </c>
       <c r="S97" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B98" s="5">
         <v>46188.63531412037</v>
@@ -7154,16 +7151,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I98" s="5">
         <v>46265</v>
@@ -7181,13 +7178,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7197,7 +7194,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B99" s="9">
         <v>46188.63532239583</v>
@@ -7207,16 +7204,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I99" s="9">
         <v>46265</v>
@@ -7234,13 +7231,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7250,7 +7247,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B100" s="5">
         <v>46188.63538068287</v>
@@ -7260,16 +7257,16 @@
         <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7287,13 +7284,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q100" s="5">
         <v>46266</v>
@@ -7302,18 +7299,18 @@
         <v>46266</v>
       </c>
       <c r="S100" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B101" s="9">
         <v>46188.6353874537</v>
@@ -7323,16 +7320,16 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7350,13 +7347,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7366,7 +7363,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B102" s="5">
         <v>46188.63539206018</v>
@@ -7376,16 +7373,16 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>
@@ -7403,13 +7400,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7419,7 +7416,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B103" s="9">
         <v>46188.635410682866</v>
@@ -7429,7 +7426,7 @@
         <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7453,7 +7450,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7466,7 +7463,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B104" s="5">
         <v>46188.635413993055</v>
@@ -7476,16 +7473,16 @@
         <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G104" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="F104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G104" s="6" t="s">
+      <c r="H104" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>312</v>
       </c>
       <c r="I104" s="5">
         <v>46267</v>
@@ -7503,13 +7500,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q104" s="5">
         <v>46267</v>
@@ -7518,18 +7515,18 @@
         <v>46275</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
@@ -7539,16 +7536,16 @@
         <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>
@@ -7566,13 +7563,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q105" s="9">
         <v>46267</v>
@@ -7581,13 +7578,13 @@
         <v>46275</v>
       </c>
       <c r="S105" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="316">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -116,6 +116,30 @@
   </si>
   <si>
     <t>Alcance del proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para el pedido 50001563, se tienen 2 ventiladores ZVN 1-9-90/2 para Zitrón Colombia (ANTIOQUIA GOLD):
+Alcance: TOBERA + REJILLA + FAR 90/100 + VENT + FAR 90/100 + TIPO C
+    Plano para fabricación:
+        Ventilador ZVN 1-9-90/2 con motor OMEG
+        Alcance Chile: TOBERA + REJILLA + VENT
+        Alcance Colombia: 2FAR 90/100 + TIPO C (900 a 800 mm)
+        Carpeta de Planos. hgutierrez@zitron.com por favor tu apoyo.
+    Definición Rodete ZVN 1-9:
+        Alabe s/ plano 4999.01
+        Código 300000
+        Rodete de placas s/plano 4999.00
+        Z8 N590
+        Calaje y consumo: hgutierrez@zitron.com por favor tu apoyo.
+    Datos eléctricos motor 90KW:
+        90 kW, 460 V, 60 Hz, IE3, IP-55, f.s 1,15
+        Sistema de monitoreo WEG Motorscan 100
+    Tratamiento superficial estándar Zitrón:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Fecha de Entrega Proyecto: 09-07-2026
+</t>
   </si>
   <si>
     <t>1215727723447853</t>
@@ -1730,7 +1754,7 @@
         <v>46188.919543298616</v>
       </c>
       <c r="D6" s="5">
-        <v>46188.91956144676</v>
+        <v>46213.76143587963</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1754,7 +1778,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1786,7 +1810,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="9">
         <v>46188.63432182871</v>
@@ -1798,7 +1822,7 @@
         <v>46188.9196094213</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>26</v>
@@ -1819,7 +1843,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>26</v>
@@ -1831,7 +1855,7 @@
         <v>26</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q7" s="9">
         <v>46176</v>
@@ -1851,7 +1875,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5">
         <v>46188.634326643514</v>
@@ -1863,7 +1887,7 @@
         <v>46188.91965210648</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -1884,7 +1908,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -1916,7 +1940,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="9">
         <v>46188.634165474534</v>
@@ -1928,7 +1952,7 @@
         <v>46188.92059026621</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>25</v>
@@ -1952,7 +1976,7 @@
         <v>26</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P9" s="10" t="s">
         <v>26</v>
@@ -1969,7 +1993,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="5">
         <v>46188.63433173611</v>
@@ -1981,7 +2005,7 @@
         <v>46188.920113182874</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>26</v>
@@ -2002,19 +2026,19 @@
         <v>26</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q10" s="5">
         <v>46177</v>
@@ -2034,7 +2058,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="9">
         <v>46188.63434310185</v>
@@ -2046,7 +2070,7 @@
         <v>46188.92032122685</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
@@ -2067,19 +2091,19 @@
         <v>26</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="9">
         <v>46177</v>
@@ -2099,7 +2123,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46188.63435032408</v>
@@ -2111,7 +2135,7 @@
         <v>46188.92050125</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2138,13 +2162,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q12" s="5">
         <v>46177</v>
@@ -2164,7 +2188,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="9">
         <v>46188.634356759256</v>
@@ -2176,7 +2200,7 @@
         <v>46188.92057991898</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
@@ -2203,13 +2227,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="9">
         <v>46177</v>
@@ -2229,7 +2253,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5">
         <v>46188.634170000005</v>
@@ -2241,7 +2265,7 @@
         <v>46206.50380298611</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2265,7 +2289,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2282,7 +2306,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="9">
         <v>46188.63436615741</v>
@@ -2294,7 +2318,7 @@
         <v>46189.814397685186</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
@@ -2321,13 +2345,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q15" s="9">
         <v>46181</v>
@@ -2347,7 +2371,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5">
         <v>46188.63437259259</v>
@@ -2359,7 +2383,7 @@
         <v>46189.814421944444</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2380,19 +2404,19 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="5">
         <v>46181</v>
@@ -2412,7 +2436,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="9">
         <v>46188.63437929398</v>
@@ -2424,16 +2448,16 @@
         <v>46197.586479687496</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" s="9">
         <v>46181</v>
@@ -2451,13 +2475,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="9">
         <v>46211</v>
@@ -2477,7 +2501,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46188.63438636574</v>
@@ -2489,16 +2513,16 @@
         <v>46213.191536909726</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" s="5">
         <v>46211</v>
@@ -2516,13 +2540,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q18" s="5">
         <v>46211</v>
@@ -2542,7 +2566,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B19" s="9">
         <v>46188.634392708336</v>
@@ -2554,16 +2578,16 @@
         <v>46213.19154050926</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" s="9">
         <v>46211</v>
@@ -2581,13 +2605,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="9">
         <v>46211</v>
@@ -2607,7 +2631,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46188.63439828704</v>
@@ -2619,16 +2643,16 @@
         <v>46213.191536875005</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46211</v>
@@ -2646,13 +2670,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46211</v>
@@ -2672,7 +2696,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9">
         <v>46188.634403055556</v>
@@ -2684,16 +2708,16 @@
         <v>46213.19153681713</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" s="9">
         <v>46211</v>
@@ -2711,13 +2735,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q21" s="9">
         <v>46211</v>
@@ -2737,7 +2761,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" s="5">
         <v>46189.78075929398</v>
@@ -2749,7 +2773,7 @@
         <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2773,7 +2797,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2781,7 +2805,7 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2792,7 +2816,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B23" s="9">
         <v>46189.81187604167</v>
@@ -2804,16 +2828,16 @@
         <v>46197.586624143514</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I23" s="9">
         <v>46183</v>
@@ -2831,13 +2855,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q23" s="9">
         <v>46183</v>
@@ -2857,7 +2881,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B24" s="5">
         <v>46189.8120440162</v>
@@ -2869,16 +2893,16 @@
         <v>46197.586567060185</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I24" s="5">
         <v>46183</v>
@@ -2896,13 +2920,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q24" s="5">
         <v>46183</v>
@@ -2922,7 +2946,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="9">
         <v>46188.634174861116</v>
@@ -2934,7 +2958,7 @@
         <v>46212.85336304398</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -2958,7 +2982,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -2975,7 +2999,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
@@ -2987,16 +3011,16 @@
         <v>46212.653841203704</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -3014,13 +3038,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q26" s="5">
         <v>46183</v>
@@ -3040,7 +3064,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="9">
         <v>46188.634431805556</v>
@@ -3052,16 +3076,16 @@
         <v>46212.65346519676</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3079,29 +3103,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3113,16 +3137,16 @@
         <v>46212.65350395833</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3140,29 +3164,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3174,16 +3198,16 @@
         <v>46209.818759456015</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3201,13 +3225,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q29" s="9">
         <v>46213</v>
@@ -3216,7 +3240,7 @@
         <v>46225</v>
       </c>
       <c r="S29" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3227,7 +3251,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3239,16 +3263,16 @@
         <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3266,29 +3290,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3300,16 +3324,16 @@
         <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3327,29 +3351,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3361,16 +3385,16 @@
         <v>46209.81933853009</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3388,10 +3412,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3403,7 +3427,7 @@
         <v>46225</v>
       </c>
       <c r="S32" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3414,7 +3438,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3426,16 +3450,16 @@
         <v>46209.81926089121</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3453,13 +3477,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3469,7 +3493,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3481,16 +3505,16 @@
         <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3508,13 +3532,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3524,7 +3548,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3536,16 +3560,16 @@
         <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3563,10 +3587,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3578,7 +3602,7 @@
         <v>46253</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3589,7 +3613,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3601,16 +3625,16 @@
         <v>46209.62002645833</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3628,13 +3652,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3644,7 +3668,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3656,16 +3680,16 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3683,13 +3707,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3699,7 +3723,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3709,16 +3733,16 @@
         <v>46209.62071325231</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3736,10 +3760,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3752,7 +3776,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3764,16 +3788,16 @@
         <v>46209.81975170139</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3791,10 +3815,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3806,7 +3830,7 @@
         <v>46225</v>
       </c>
       <c r="S39" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3817,7 +3841,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3829,16 +3853,16 @@
         <v>46209.81962844907</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3856,13 +3880,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3872,7 +3896,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3884,16 +3908,16 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3911,13 +3935,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3927,7 +3951,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3939,7 +3963,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3963,7 +3987,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3980,7 +4004,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -3992,16 +4016,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4019,13 +4043,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4045,7 +4069,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4057,16 +4081,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4084,13 +4108,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4110,7 +4134,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4122,16 +4146,16 @@
         <v>46211.17038164352</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4149,13 +4173,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4175,7 +4199,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4185,16 +4209,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4212,10 +4236,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4227,18 +4251,18 @@
         <v>46259</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4248,16 +4272,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4275,13 +4299,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4291,7 +4315,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4301,16 +4325,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4328,13 +4352,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4344,7 +4368,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4354,7 +4378,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4378,7 +4402,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4391,7 +4415,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4401,16 +4425,16 @@
         <v>46209.818739016206</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4428,13 +4452,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4443,18 +4467,18 @@
         <v>46227</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46188.634684942124</v>
@@ -4464,16 +4488,16 @@
         <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4491,13 +4515,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4506,18 +4530,18 @@
         <v>46231</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46188.634692962965</v>
@@ -4527,16 +4551,16 @@
         <v>46209.819318298614</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4554,13 +4578,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4569,18 +4593,18 @@
         <v>46227</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B53" s="9">
         <v>46188.63469954861</v>
@@ -4590,16 +4614,16 @@
         <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4617,13 +4641,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4632,18 +4656,18 @@
         <v>46231</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63470560186</v>
@@ -4653,16 +4677,16 @@
         <v>46209.8196808912</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4680,13 +4704,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4695,18 +4719,18 @@
         <v>46227</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="9">
         <v>46188.63471155093</v>
@@ -4716,16 +4740,16 @@
         <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4743,13 +4767,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4758,18 +4782,18 @@
         <v>46231</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5">
         <v>46188.63471731481</v>
@@ -4779,7 +4803,7 @@
         <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4803,7 +4827,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4816,7 +4840,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B57" s="9">
         <v>46188.63472107639</v>
@@ -4826,16 +4850,16 @@
         <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4853,13 +4877,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4868,18 +4892,18 @@
         <v>46234</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63473258102</v>
@@ -4889,16 +4913,16 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4916,13 +4940,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4932,7 +4956,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
         <v>46188.63474121528</v>
@@ -4942,16 +4966,16 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -4969,13 +4993,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4985,7 +5009,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63477284722</v>
@@ -4995,16 +5019,16 @@
         <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -5022,13 +5046,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -5037,18 +5061,18 @@
         <v>46241</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B61" s="9">
         <v>46188.63477877315</v>
@@ -5058,16 +5082,16 @@
         <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5085,13 +5109,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5101,7 +5125,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63478605324</v>
@@ -5111,16 +5135,16 @@
         <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5138,13 +5162,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5154,7 +5178,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B63" s="9">
         <v>46188.63485537037</v>
@@ -5164,16 +5188,16 @@
         <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5191,13 +5215,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5206,18 +5230,18 @@
         <v>46244</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46188.634861805556</v>
@@ -5227,16 +5251,16 @@
         <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5254,13 +5278,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5270,7 +5294,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>46188.63486881944</v>
@@ -5280,16 +5304,16 @@
         <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5307,13 +5331,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5323,7 +5347,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63489331018</v>
@@ -5333,7 +5357,7 @@
         <v>46212.654024166666</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5357,7 +5381,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5370,7 +5394,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B67" s="9">
         <v>46188.634903391205</v>
@@ -5382,16 +5406,16 @@
         <v>46212.65419707176</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5409,13 +5433,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5435,7 +5459,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46188.6349100463</v>
@@ -5447,16 +5471,16 @@
         <v>46212.65411137731</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5474,13 +5498,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5500,7 +5524,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
@@ -5510,16 +5534,16 @@
         <v>46203.550511388894</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5537,13 +5561,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5552,18 +5576,18 @@
         <v>46223</v>
       </c>
       <c r="S69" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5573,16 +5597,16 @@
         <v>46209.620722314816</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5600,13 +5624,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5615,18 +5639,18 @@
         <v>46254</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5636,7 +5660,7 @@
         <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5660,7 +5684,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5673,7 +5697,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
@@ -5683,16 +5707,16 @@
         <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I72" s="5">
         <v>46245</v>
@@ -5710,13 +5734,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5725,18 +5749,18 @@
         <v>46251</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="9">
         <v>46188.63494034723</v>
@@ -5746,16 +5770,16 @@
         <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I73" s="9">
         <v>46245</v>
@@ -5773,10 +5797,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5789,7 +5813,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46188.634945150465</v>
@@ -5799,16 +5823,16 @@
         <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I74" s="5">
         <v>46245</v>
@@ -5826,10 +5850,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5842,7 +5866,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" s="9">
         <v>46188.634963668985</v>
@@ -5854,16 +5878,16 @@
         <v>46197.58706070602</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" s="9">
         <v>46252</v>
@@ -5881,13 +5905,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5896,7 +5920,7 @@
         <v>46252</v>
       </c>
       <c r="S75" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -5907,7 +5931,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" s="5">
         <v>46188.63496887732</v>
@@ -5919,16 +5943,16 @@
         <v>46212.65402488426</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" s="5">
         <v>46252</v>
@@ -5946,13 +5970,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5962,7 +5986,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B77" s="9">
         <v>46188.63498112268</v>
@@ -5974,16 +5998,16 @@
         <v>46212.65402556713</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I77" s="9">
         <v>46252</v>
@@ -6001,13 +6025,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6017,7 +6041,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B78" s="5">
         <v>46188.635046296295</v>
@@ -6027,16 +6051,16 @@
         <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I78" s="5">
         <v>46253</v>
@@ -6054,13 +6078,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -6069,18 +6093,18 @@
         <v>46253</v>
       </c>
       <c r="S78" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B79" s="9">
         <v>46188.63505403935</v>
@@ -6090,16 +6114,16 @@
         <v>46212.65379315973</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" s="9">
         <v>46253</v>
@@ -6117,13 +6141,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6133,7 +6157,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B80" s="5">
         <v>46188.63506813657</v>
@@ -6143,16 +6167,16 @@
         <v>46212.65379201389</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6170,13 +6194,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6186,7 +6210,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B81" s="9">
         <v>46188.63509704861</v>
@@ -6196,16 +6220,16 @@
         <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I81" s="9">
         <v>46224</v>
@@ -6223,13 +6247,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6238,18 +6262,18 @@
         <v>46224</v>
       </c>
       <c r="S81" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B82" s="5">
         <v>46188.635102939814</v>
@@ -6259,16 +6283,16 @@
         <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I82" s="5">
         <v>46224</v>
@@ -6286,13 +6310,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6302,7 +6326,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B83" s="9">
         <v>46188.63510991898</v>
@@ -6312,16 +6336,16 @@
         <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" s="9">
         <v>46224</v>
@@ -6339,13 +6363,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6355,7 +6379,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B84" s="5">
         <v>46188.63513603009</v>
@@ -6365,16 +6389,16 @@
         <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I84" s="5">
         <v>46258</v>
@@ -6392,13 +6416,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6407,18 +6431,18 @@
         <v>46258</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B85" s="9">
         <v>46188.63514172454</v>
@@ -6428,16 +6452,16 @@
         <v>46202.95697799769</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I85" s="9">
         <v>46258</v>
@@ -6455,13 +6479,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6471,7 +6495,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B86" s="5">
         <v>46188.63514853009</v>
@@ -6481,16 +6505,16 @@
         <v>46202.95697554398</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I86" s="5">
         <v>46258</v>
@@ -6508,13 +6532,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6524,7 +6548,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B87" s="9">
         <v>46188.63521115741</v>
@@ -6534,16 +6558,16 @@
         <v>46202.95705052083</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" s="9">
         <v>46260</v>
@@ -6561,13 +6585,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="9">
         <v>46260</v>
@@ -6576,18 +6600,18 @@
         <v>46260</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B88" s="5">
         <v>46188.63521795139</v>
@@ -6597,16 +6621,16 @@
         <v>46202.957050694444</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" s="5">
         <v>46261</v>
@@ -6624,13 +6648,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6640,7 +6664,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B89" s="9">
         <v>46188.635222916666</v>
@@ -6650,16 +6674,16 @@
         <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" s="9">
         <v>46260</v>
@@ -6677,13 +6701,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6693,7 +6717,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46188.635247199076</v>
@@ -6703,7 +6727,7 @@
         <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6727,7 +6751,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6740,7 +6764,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B91" s="9">
         <v>46188.635250844905</v>
@@ -6750,16 +6774,16 @@
         <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I91" s="9">
         <v>46261</v>
@@ -6777,13 +6801,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q91" s="9">
         <v>46261</v>
@@ -6792,18 +6816,18 @@
         <v>46261</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B92" s="5">
         <v>46188.63525673611</v>
@@ -6813,16 +6837,16 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I92" s="5">
         <v>46261</v>
@@ -6840,13 +6864,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6856,7 +6880,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B93" s="9">
         <v>46188.635261689815</v>
@@ -6866,16 +6890,16 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I93" s="9">
         <v>46261</v>
@@ -6893,13 +6917,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6909,7 +6933,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B94" s="5">
         <v>46188.635279375</v>
@@ -6919,16 +6943,16 @@
         <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I94" s="5">
         <v>46262</v>
@@ -6946,13 +6970,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q94" s="5">
         <v>46262</v>
@@ -6961,18 +6985,18 @@
         <v>46262</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B95" s="9">
         <v>46188.63528446759</v>
@@ -6982,16 +7006,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I95" s="9">
         <v>46262</v>
@@ -7009,13 +7033,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7025,7 +7049,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B96" s="5">
         <v>46188.6352894213</v>
@@ -7035,16 +7059,16 @@
         <v>46202.956975497684</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I96" s="5">
         <v>46262</v>
@@ -7062,13 +7086,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7078,7 +7102,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B97" s="9">
         <v>46188.63530922454</v>
@@ -7088,16 +7112,16 @@
         <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7115,13 +7139,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q97" s="9">
         <v>46265</v>
@@ -7130,18 +7154,18 @@
         <v>46265</v>
       </c>
       <c r="S97" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B98" s="5">
         <v>46188.63531412037</v>
@@ -7151,16 +7175,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I98" s="5">
         <v>46265</v>
@@ -7178,13 +7202,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7194,7 +7218,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B99" s="9">
         <v>46188.63532239583</v>
@@ -7204,16 +7228,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I99" s="9">
         <v>46265</v>
@@ -7231,13 +7255,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7247,7 +7271,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B100" s="5">
         <v>46188.63538068287</v>
@@ -7257,16 +7281,16 @@
         <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7284,13 +7308,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q100" s="5">
         <v>46266</v>
@@ -7299,18 +7323,18 @@
         <v>46266</v>
       </c>
       <c r="S100" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B101" s="9">
         <v>46188.6353874537</v>
@@ -7320,16 +7344,16 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7347,13 +7371,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7363,7 +7387,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B102" s="5">
         <v>46188.63539206018</v>
@@ -7373,16 +7397,16 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>
@@ -7400,13 +7424,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7416,7 +7440,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" s="9">
         <v>46188.635410682866</v>
@@ -7426,7 +7450,7 @@
         <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7450,7 +7474,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7463,7 +7487,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B104" s="5">
         <v>46188.635413993055</v>
@@ -7473,16 +7497,16 @@
         <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I104" s="5">
         <v>46267</v>
@@ -7500,13 +7524,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q104" s="5">
         <v>46267</v>
@@ -7515,18 +7539,18 @@
         <v>46275</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
@@ -7536,16 +7560,16 @@
         <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>
@@ -7563,13 +7587,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q105" s="9">
         <v>46267</v>
@@ -7578,13 +7602,13 @@
         <v>46275</v>
       </c>
       <c r="S105" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="317">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -761,6 +761,9 @@
   </si>
   <si>
     <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215728036191110</t>
@@ -5531,7 +5534,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46203.550511388894</v>
+        <v>46216.1786388426</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>
@@ -5575,8 +5578,8 @@
       <c r="R69" s="9">
         <v>46223</v>
       </c>
-      <c r="S69" s="7" t="s">
-        <v>93</v>
+      <c r="S69" s="12" t="s">
+        <v>235</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -5587,7 +5590,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5597,7 +5600,7 @@
         <v>46209.620722314816</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5630,7 +5633,7 @@
         <v>142</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5650,7 +5653,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5660,7 +5663,7 @@
         <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5684,7 +5687,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5697,7 +5700,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
@@ -5707,7 +5710,7 @@
         <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5734,13 +5737,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5760,7 +5763,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B73" s="9">
         <v>46188.63494034723</v>
@@ -5797,10 +5800,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5813,7 +5816,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
         <v>46188.634945150465</v>
@@ -5850,10 +5853,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5866,7 +5869,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B75" s="9">
         <v>46188.634963668985</v>
@@ -5878,7 +5881,7 @@
         <v>46197.58706070602</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5905,13 +5908,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>175</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5931,7 +5934,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B76" s="5">
         <v>46188.63496887732</v>
@@ -5970,13 +5973,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5986,7 +5989,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B77" s="9">
         <v>46188.63498112268</v>
@@ -6025,13 +6028,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6041,7 +6044,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B78" s="5">
         <v>46188.635046296295</v>
@@ -6051,7 +6054,7 @@
         <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6078,13 +6081,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -6104,7 +6107,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B79" s="9">
         <v>46188.63505403935</v>
@@ -6141,13 +6144,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6157,7 +6160,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B80" s="5">
         <v>46188.63506813657</v>
@@ -6194,13 +6197,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6210,7 +6213,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B81" s="9">
         <v>46188.63509704861</v>
@@ -6220,7 +6223,7 @@
         <v>46188.67906003472</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6247,13 +6250,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>175</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6273,7 +6276,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B82" s="5">
         <v>46188.635102939814</v>
@@ -6310,13 +6313,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6326,7 +6329,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B83" s="9">
         <v>46188.63510991898</v>
@@ -6363,13 +6366,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6379,7 +6382,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B84" s="5">
         <v>46188.63513603009</v>
@@ -6389,7 +6392,7 @@
         <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6416,13 +6419,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6442,7 +6445,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B85" s="9">
         <v>46188.63514172454</v>
@@ -6479,13 +6482,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>177</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6495,7 +6498,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B86" s="5">
         <v>46188.63514853009</v>
@@ -6532,13 +6535,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>177</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6548,7 +6551,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B87" s="9">
         <v>46188.63521115741</v>
@@ -6558,7 +6561,7 @@
         <v>46202.95705052083</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6585,13 +6588,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>175</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q87" s="9">
         <v>46260</v>
@@ -6611,7 +6614,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B88" s="5">
         <v>46188.63521795139</v>
@@ -6648,13 +6651,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>177</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6664,7 +6667,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B89" s="9">
         <v>46188.635222916666</v>
@@ -6701,13 +6704,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>177</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6717,7 +6720,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B90" s="5">
         <v>46188.635247199076</v>
@@ -6727,7 +6730,7 @@
         <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6751,7 +6754,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6764,7 +6767,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B91" s="9">
         <v>46188.635250844905</v>
@@ -6774,16 +6777,16 @@
         <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I91" s="9">
         <v>46261</v>
@@ -6801,13 +6804,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q91" s="9">
         <v>46261</v>
@@ -6827,7 +6830,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B92" s="5">
         <v>46188.63525673611</v>
@@ -6843,10 +6846,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I92" s="5">
         <v>46261</v>
@@ -6864,13 +6867,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>177</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6880,7 +6883,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B93" s="9">
         <v>46188.635261689815</v>
@@ -6896,10 +6899,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I93" s="9">
         <v>46261</v>
@@ -6917,13 +6920,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>177</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6933,7 +6936,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B94" s="5">
         <v>46188.635279375</v>
@@ -6943,7 +6946,7 @@
         <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6970,13 +6973,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q94" s="5">
         <v>46262</v>
@@ -6996,7 +6999,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B95" s="9">
         <v>46188.63528446759</v>
@@ -7033,13 +7036,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>177</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7049,7 +7052,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B96" s="5">
         <v>46188.6352894213</v>
@@ -7086,13 +7089,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>177</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7102,7 +7105,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B97" s="9">
         <v>46188.63530922454</v>
@@ -7112,7 +7115,7 @@
         <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7139,13 +7142,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>175</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q97" s="9">
         <v>46265</v>
@@ -7165,7 +7168,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B98" s="5">
         <v>46188.63531412037</v>
@@ -7202,13 +7205,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>177</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7218,7 +7221,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B99" s="9">
         <v>46188.63532239583</v>
@@ -7255,13 +7258,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>177</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7271,7 +7274,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B100" s="5">
         <v>46188.63538068287</v>
@@ -7281,7 +7284,7 @@
         <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7308,13 +7311,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q100" s="5">
         <v>46266</v>
@@ -7334,7 +7337,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B101" s="9">
         <v>46188.6353874537</v>
@@ -7371,13 +7374,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>177</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7387,7 +7390,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B102" s="5">
         <v>46188.63539206018</v>
@@ -7424,13 +7427,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>177</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7440,7 +7443,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B103" s="9">
         <v>46188.635410682866</v>
@@ -7450,7 +7453,7 @@
         <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7474,7 +7477,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7487,7 +7490,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B104" s="5">
         <v>46188.635413993055</v>
@@ -7497,16 +7500,16 @@
         <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I104" s="5">
         <v>46267</v>
@@ -7524,13 +7527,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q104" s="5">
         <v>46267</v>
@@ -7550,7 +7553,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
@@ -7560,7 +7563,7 @@
         <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7587,13 +7590,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q105" s="9">
         <v>46267</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -6220,7 +6220,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46188.67906003472</v>
+        <v>46217.19090564815</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>262</v>
@@ -6264,8 +6264,8 @@
       <c r="R81" s="9">
         <v>46224</v>
       </c>
-      <c r="S81" s="7" t="s">
-        <v>93</v>
+      <c r="S81" s="12" t="s">
+        <v>235</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -418,6 +418,9 @@
     <t xml:space="preserve">Generación OC materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215727831363866</t>
   </si>
   <si>
@@ -761,9 +764,6 @@
   </si>
   <si>
     <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215728036191110</t>
@@ -3198,7 +3198,7 @@
         <v>46209.81873614583</v>
       </c>
       <c r="D29" s="9">
-        <v>46209.818759456015</v>
+        <v>46218.189632430556</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>116</v>
@@ -3242,8 +3242,8 @@
       <c r="R29" s="9">
         <v>46225</v>
       </c>
-      <c r="S29" s="7" t="s">
-        <v>93</v>
+      <c r="S29" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3266,7 +3266,7 @@
         <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3299,7 +3299,7 @@
         <v>76</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3327,7 +3327,7 @@
         <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3357,10 +3357,10 @@
         <v>116</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3385,10 +3385,10 @@
         <v>46209.819314988425</v>
       </c>
       <c r="D32" s="5">
-        <v>46209.81933853009</v>
+        <v>46218.18963260417</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3418,7 +3418,7 @@
         <v>101</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3429,8 +3429,8 @@
       <c r="R32" s="5">
         <v>46225</v>
       </c>
-      <c r="S32" s="7" t="s">
-        <v>93</v>
+      <c r="S32" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3480,13 +3480,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>82</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3508,7 +3508,7 @@
         <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3535,13 +3535,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3563,16 +3563,16 @@
         <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3593,7 +3593,7 @@
         <v>101</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3616,7 +3616,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3634,10 +3634,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3655,13 +3655,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3683,16 +3683,16 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3710,13 +3710,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3736,16 +3736,16 @@
         <v>46209.62071325231</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3763,10 +3763,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3788,10 +3788,10 @@
         <v>46209.81975005787</v>
       </c>
       <c r="D39" s="9">
-        <v>46209.81975170139</v>
+        <v>46218.18963259259</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
@@ -3821,7 +3821,7 @@
         <v>101</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3832,8 +3832,8 @@
       <c r="R39" s="9">
         <v>46225</v>
       </c>
-      <c r="S39" s="7" t="s">
-        <v>93</v>
+      <c r="S39" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3883,13 +3883,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3911,7 +3911,7 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -3938,13 +3938,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3966,7 +3966,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3990,7 +3990,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4007,7 +4007,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -4019,16 +4019,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4046,13 +4046,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4072,7 +4072,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4084,16 +4084,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4111,13 +4111,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4155,10 +4155,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4176,13 +4176,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4202,7 +4202,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4212,16 +4212,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4239,10 +4239,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4275,16 +4275,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4302,13 +4302,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4318,7 +4318,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4328,16 +4328,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4355,13 +4355,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4381,7 +4381,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4405,7 +4405,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4418,7 +4418,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4428,16 +4428,16 @@
         <v>46209.818739016206</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4455,13 +4455,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4476,12 +4476,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="9">
         <v>46188.634684942124</v>
@@ -4491,16 +4491,16 @@
         <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4518,13 +4518,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4544,7 +4544,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B52" s="5">
         <v>46188.634692962965</v>
@@ -4554,16 +4554,16 @@
         <v>46209.819318298614</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4581,13 +4581,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4602,12 +4602,12 @@
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B53" s="9">
         <v>46188.63469954861</v>
@@ -4617,16 +4617,16 @@
         <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4644,13 +4644,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4670,7 +4670,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63470560186</v>
@@ -4680,16 +4680,16 @@
         <v>46209.8196808912</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4707,13 +4707,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4728,12 +4728,12 @@
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="9">
         <v>46188.63471155093</v>
@@ -4743,16 +4743,16 @@
         <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4770,13 +4770,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4796,7 +4796,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46188.63471731481</v>
@@ -4806,7 +4806,7 @@
         <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4830,7 +4830,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4843,7 +4843,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B57" s="9">
         <v>46188.63472107639</v>
@@ -4853,16 +4853,16 @@
         <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4880,13 +4880,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63473258102</v>
@@ -4916,16 +4916,16 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4943,13 +4943,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B59" s="9">
         <v>46188.63474121528</v>
@@ -4969,16 +4969,16 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -4996,13 +4996,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5012,7 +5012,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63477284722</v>
@@ -5022,16 +5022,16 @@
         <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -5049,13 +5049,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -5075,7 +5075,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B61" s="9">
         <v>46188.63477877315</v>
@@ -5085,16 +5085,16 @@
         <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5112,13 +5112,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5128,7 +5128,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63478605324</v>
@@ -5138,16 +5138,16 @@
         <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5165,13 +5165,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5181,7 +5181,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B63" s="9">
         <v>46188.63485537037</v>
@@ -5191,16 +5191,16 @@
         <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5218,13 +5218,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5244,7 +5244,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B64" s="5">
         <v>46188.634861805556</v>
@@ -5254,16 +5254,16 @@
         <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5281,13 +5281,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B65" s="9">
         <v>46188.63486881944</v>
@@ -5307,16 +5307,16 @@
         <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5334,13 +5334,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5350,7 +5350,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63489331018</v>
@@ -5360,7 +5360,7 @@
         <v>46212.654024166666</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5384,7 +5384,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="9">
         <v>46188.634903391205</v>
@@ -5409,16 +5409,16 @@
         <v>46212.65419707176</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5436,13 +5436,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>113</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5462,7 +5462,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46188.6349100463</v>
@@ -5474,16 +5474,16 @@
         <v>46212.65411137731</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5501,13 +5501,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
@@ -5537,16 +5537,16 @@
         <v>46216.1786388426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5564,13 +5564,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>95</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5579,13 +5579,13 @@
         <v>46223</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>235</v>
+        <v>120</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5606,10 +5606,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5627,10 +5627,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>238</v>
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5773,7 +5773,7 @@
         <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5826,7 +5826,7 @@
         <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5911,7 +5911,7 @@
         <v>240</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>240</v>
@@ -5946,7 +5946,7 @@
         <v>46212.65402488426</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6001,7 +6001,7 @@
         <v>46212.65402556713</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6084,7 +6084,7 @@
         <v>240</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>240</v>
@@ -6117,7 +6117,7 @@
         <v>46212.65379315973</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6170,7 +6170,7 @@
         <v>46212.65379201389</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6253,7 +6253,7 @@
         <v>240</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>240</v>
@@ -6265,7 +6265,7 @@
         <v>46224</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>235</v>
+        <v>120</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
@@ -6286,7 +6286,7 @@
         <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6339,7 +6339,7 @@
         <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6455,7 +6455,7 @@
         <v>46202.95697799769</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6485,7 +6485,7 @@
         <v>269</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>272</v>
@@ -6508,7 +6508,7 @@
         <v>46202.95697554398</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6538,7 +6538,7 @@
         <v>269</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>272</v>
@@ -6591,7 +6591,7 @@
         <v>240</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>276</v>
@@ -6624,7 +6624,7 @@
         <v>46202.957050694444</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6654,7 +6654,7 @@
         <v>275</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>278</v>
@@ -6677,7 +6677,7 @@
         <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6707,7 +6707,7 @@
         <v>275</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>278</v>
@@ -6840,7 +6840,7 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6870,7 +6870,7 @@
         <v>284</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>289</v>
@@ -6893,7 +6893,7 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6923,7 +6923,7 @@
         <v>284</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>289</v>
@@ -6976,7 +6976,7 @@
         <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>281</v>
@@ -7009,7 +7009,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7039,7 +7039,7 @@
         <v>292</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>294</v>
@@ -7062,7 +7062,7 @@
         <v>46202.956975497684</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7092,7 +7092,7 @@
         <v>292</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>296</v>
@@ -7121,10 +7121,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7145,7 +7145,7 @@
         <v>281</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>281</v>
@@ -7178,16 +7178,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I98" s="5">
         <v>46265</v>
@@ -7208,7 +7208,7 @@
         <v>298</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>300</v>
@@ -7231,16 +7231,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I99" s="9">
         <v>46265</v>
@@ -7261,7 +7261,7 @@
         <v>298</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>300</v>
@@ -7290,10 +7290,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7314,7 +7314,7 @@
         <v>281</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>304</v>
@@ -7347,16 +7347,16 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7377,7 +7377,7 @@
         <v>303</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>303</v>
@@ -7400,16 +7400,16 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>
@@ -7430,7 +7430,7 @@
         <v>303</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>303</v>
@@ -7569,10 +7569,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="314">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -277,9 +277,6 @@
     <t>propuesta nucleo rodeteOT 4360</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete OT 4360</t>
   </si>
   <si>
@@ -287,12 +284,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser OT 4360</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2457,11 +2448,9 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="10"/>
       <c r="I17" s="9">
         <v>46181</v>
       </c>
@@ -2484,7 +2473,7 @@
         <v>51</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q17" s="9">
         <v>46211</v>
@@ -2504,7 +2493,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46188.63438636574</v>
@@ -2516,17 +2505,15 @@
         <v>46213.191536909726</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
       <c r="I18" s="5">
         <v>46211</v>
       </c>
@@ -2546,10 +2533,10 @@
         <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="Q18" s="5">
         <v>46211</v>
@@ -2569,7 +2556,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B19" s="9">
         <v>46188.634392708336</v>
@@ -2581,17 +2568,15 @@
         <v>46213.19154050926</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H19" s="10"/>
       <c r="I19" s="9">
         <v>46211</v>
       </c>
@@ -2611,10 +2596,10 @@
         <v>62</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="9">
         <v>46211</v>
@@ -2634,7 +2619,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B20" s="5">
         <v>46188.63439828704</v>
@@ -2646,17 +2631,15 @@
         <v>46213.191536875005</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46211</v>
       </c>
@@ -2676,10 +2659,10 @@
         <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="Q20" s="5">
         <v>46211</v>
@@ -2699,7 +2682,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B21" s="9">
         <v>46188.634403055556</v>
@@ -2711,17 +2694,15 @@
         <v>46213.19153681713</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="10"/>
       <c r="I21" s="9">
         <v>46211</v>
       </c>
@@ -2741,10 +2722,10 @@
         <v>62</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Q21" s="9">
         <v>46211</v>
@@ -2764,7 +2745,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46189.78075929398</v>
@@ -2776,7 +2757,7 @@
         <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2800,7 +2781,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2808,7 +2789,7 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2819,7 +2800,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B23" s="9">
         <v>46189.81187604167</v>
@@ -2831,17 +2812,15 @@
         <v>46197.586624143514</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="10"/>
       <c r="I23" s="9">
         <v>46183</v>
       </c>
@@ -2858,13 +2837,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="9">
         <v>46183</v>
@@ -2884,7 +2863,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46189.8120440162</v>
@@ -2896,17 +2875,15 @@
         <v>46197.586567060185</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46183</v>
       </c>
@@ -2923,13 +2900,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Q24" s="5">
         <v>46183</v>
@@ -2949,7 +2926,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B25" s="9">
         <v>46188.634174861116</v>
@@ -2961,7 +2938,7 @@
         <v>46212.85336304398</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -2985,7 +2962,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -3002,7 +2979,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
@@ -3014,16 +2991,16 @@
         <v>46212.653841203704</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -3041,13 +3018,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="5">
         <v>46183</v>
@@ -3067,7 +3044,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B27" s="9">
         <v>46188.634431805556</v>
@@ -3079,16 +3056,16 @@
         <v>46212.65346519676</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3106,29 +3083,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3140,16 +3117,16 @@
         <v>46212.65350395833</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3167,29 +3144,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3201,16 +3178,16 @@
         <v>46218.189632430556</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3228,13 +3205,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q29" s="9">
         <v>46213</v>
@@ -3243,7 +3220,7 @@
         <v>46225</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3254,7 +3231,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3266,16 +3243,16 @@
         <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3293,29 +3270,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3327,16 +3304,16 @@
         <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3354,29 +3331,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3388,16 +3365,16 @@
         <v>46218.18963260417</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3415,10 +3392,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3430,7 +3407,7 @@
         <v>46225</v>
       </c>
       <c r="S32" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3441,7 +3418,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3453,16 +3430,16 @@
         <v>46209.81926089121</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3480,13 +3457,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="O33" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P33" s="10" t="s">
         <v>128</v>
-      </c>
-      <c r="O33" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="P33" s="10" t="s">
-        <v>131</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3496,7 +3473,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3508,16 +3485,16 @@
         <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3535,13 +3512,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3551,7 +3528,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3563,16 +3540,16 @@
         <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3590,10 +3567,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3605,7 +3582,7 @@
         <v>46253</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3616,7 +3593,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3628,16 +3605,16 @@
         <v>46209.62002645833</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3655,13 +3632,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3671,7 +3648,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3683,16 +3660,16 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3710,13 +3687,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3726,7 +3703,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3736,16 +3713,16 @@
         <v>46209.62071325231</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3763,10 +3740,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3779,7 +3756,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3791,16 +3768,16 @@
         <v>46218.18963259259</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3818,10 +3795,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3833,7 +3810,7 @@
         <v>46225</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3844,7 +3821,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3856,16 +3833,16 @@
         <v>46209.81962844907</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3883,13 +3860,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P40" s="6" t="s">
         <v>150</v>
-      </c>
-      <c r="O40" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>153</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3899,7 +3876,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3911,16 +3888,16 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3938,13 +3915,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3954,7 +3931,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3966,7 +3943,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3990,7 +3967,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4007,7 +3984,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -4019,16 +3996,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4046,13 +4023,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4072,7 +4049,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4084,16 +4061,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4111,13 +4088,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="O44" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="O44" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4137,7 +4114,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4149,16 +4126,16 @@
         <v>46211.17038164352</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4176,13 +4153,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4202,7 +4179,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4212,16 +4189,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4239,10 +4216,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4254,18 +4231,18 @@
         <v>46259</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4275,16 +4252,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4302,13 +4279,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4318,7 +4295,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4328,16 +4305,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4355,13 +4332,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4371,7 +4348,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4381,7 +4358,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4405,7 +4382,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4418,7 +4395,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4428,16 +4405,16 @@
         <v>46209.818739016206</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4455,13 +4432,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4470,18 +4447,18 @@
         <v>46227</v>
       </c>
       <c r="S50" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B51" s="9">
         <v>46188.634684942124</v>
@@ -4491,16 +4468,16 @@
         <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4518,13 +4495,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4533,18 +4510,18 @@
         <v>46231</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46188.634692962965</v>
@@ -4554,16 +4531,16 @@
         <v>46209.819318298614</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4581,13 +4558,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4596,18 +4573,18 @@
         <v>46227</v>
       </c>
       <c r="S52" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B53" s="9">
         <v>46188.63469954861</v>
@@ -4617,16 +4594,16 @@
         <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4644,13 +4621,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4659,18 +4636,18 @@
         <v>46231</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63470560186</v>
@@ -4680,16 +4657,16 @@
         <v>46209.8196808912</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4707,13 +4684,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4722,18 +4699,18 @@
         <v>46227</v>
       </c>
       <c r="S54" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B55" s="9">
         <v>46188.63471155093</v>
@@ -4743,16 +4720,16 @@
         <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4770,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4785,18 +4762,18 @@
         <v>46231</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B56" s="5">
         <v>46188.63471731481</v>
@@ -4806,7 +4783,7 @@
         <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4830,7 +4807,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4843,7 +4820,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B57" s="9">
         <v>46188.63472107639</v>
@@ -4853,16 +4830,16 @@
         <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4880,13 +4857,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4895,18 +4872,18 @@
         <v>46234</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63473258102</v>
@@ -4916,16 +4893,16 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4943,13 +4920,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4959,7 +4936,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B59" s="9">
         <v>46188.63474121528</v>
@@ -4969,16 +4946,16 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -4996,13 +4973,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5012,7 +4989,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63477284722</v>
@@ -5022,16 +4999,16 @@
         <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -5049,13 +5026,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -5064,18 +5041,18 @@
         <v>46241</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B61" s="9">
         <v>46188.63477877315</v>
@@ -5085,16 +5062,16 @@
         <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5112,13 +5089,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="O61" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="O61" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>221</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5128,7 +5105,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63478605324</v>
@@ -5138,16 +5115,16 @@
         <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5165,13 +5142,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5181,7 +5158,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B63" s="9">
         <v>46188.63485537037</v>
@@ -5191,16 +5168,16 @@
         <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5218,13 +5195,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5233,18 +5210,18 @@
         <v>46244</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46188.634861805556</v>
@@ -5254,16 +5231,16 @@
         <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5281,13 +5258,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5297,7 +5274,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B65" s="9">
         <v>46188.63486881944</v>
@@ -5307,16 +5284,16 @@
         <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5334,13 +5311,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5350,7 +5327,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63489331018</v>
@@ -5360,7 +5337,7 @@
         <v>46212.654024166666</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5384,7 +5361,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5397,7 +5374,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B67" s="9">
         <v>46188.634903391205</v>
@@ -5409,16 +5386,16 @@
         <v>46212.65419707176</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5436,13 +5413,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5462,7 +5439,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B68" s="5">
         <v>46188.6349100463</v>
@@ -5474,16 +5451,16 @@
         <v>46212.65411137731</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5501,13 +5478,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5527,7 +5504,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
@@ -5537,16 +5514,16 @@
         <v>46216.1786388426</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5564,13 +5541,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5579,18 +5556,18 @@
         <v>46223</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5600,16 +5577,16 @@
         <v>46209.620722314816</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5627,13 +5604,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5642,18 +5619,18 @@
         <v>46254</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5663,7 +5640,7 @@
         <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5687,7 +5664,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5700,7 +5677,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
@@ -5710,17 +5687,15 @@
         <v>46188.67802387731</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H72" s="6"/>
       <c r="I72" s="5">
         <v>46245</v>
       </c>
@@ -5737,13 +5712,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5752,18 +5727,18 @@
         <v>46251</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B73" s="9">
         <v>46188.63494034723</v>
@@ -5773,17 +5748,15 @@
         <v>46188.677983657406</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H73" s="10"/>
       <c r="I73" s="9">
         <v>46245</v>
       </c>
@@ -5800,10 +5773,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="O73" s="10" t="s">
         <v>243</v>
-      </c>
-      <c r="O73" s="10" t="s">
-        <v>246</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5816,7 +5789,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B74" s="5">
         <v>46188.634945150465</v>
@@ -5826,17 +5799,15 @@
         <v>46188.677980567125</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H74" s="6"/>
       <c r="I74" s="5">
         <v>46245</v>
       </c>
@@ -5853,10 +5824,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="O74" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>246</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5869,7 +5840,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B75" s="9">
         <v>46188.634963668985</v>
@@ -5881,17 +5852,15 @@
         <v>46197.58706070602</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H75" s="10"/>
       <c r="I75" s="9">
         <v>46252</v>
       </c>
@@ -5908,13 +5877,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5923,7 +5892,7 @@
         <v>46252</v>
       </c>
       <c r="S75" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -5934,7 +5903,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B76" s="5">
         <v>46188.63496887732</v>
@@ -5946,17 +5915,15 @@
         <v>46212.65402488426</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H76" s="6"/>
       <c r="I76" s="5">
         <v>46252</v>
       </c>
@@ -5973,13 +5940,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="O76" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5989,7 +5956,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B77" s="9">
         <v>46188.63498112268</v>
@@ -6001,17 +5968,15 @@
         <v>46212.65402556713</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H77" s="10"/>
       <c r="I77" s="9">
         <v>46252</v>
       </c>
@@ -6028,13 +5993,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O77" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="P77" s="10" t="s">
         <v>251</v>
-      </c>
-      <c r="P77" s="10" t="s">
-        <v>254</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6044,7 +6009,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B78" s="5">
         <v>46188.635046296295</v>
@@ -6054,17 +6019,15 @@
         <v>46188.67895050926</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H78" s="6"/>
       <c r="I78" s="5">
         <v>46253</v>
       </c>
@@ -6081,13 +6044,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -6096,18 +6059,18 @@
         <v>46253</v>
       </c>
       <c r="S78" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B79" s="9">
         <v>46188.63505403935</v>
@@ -6117,17 +6080,15 @@
         <v>46212.65379315973</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H79" s="10"/>
       <c r="I79" s="9">
         <v>46253</v>
       </c>
@@ -6144,13 +6105,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6160,7 +6121,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46188.63506813657</v>
@@ -6170,17 +6131,15 @@
         <v>46212.65379201389</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
       <c r="I80" s="5">
         <v>46253</v>
       </c>
@@ -6197,13 +6156,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6213,7 +6172,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46188.63509704861</v>
@@ -6223,17 +6182,15 @@
         <v>46217.19090564815</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H81" s="10"/>
       <c r="I81" s="9">
         <v>46224</v>
       </c>
@@ -6250,13 +6207,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6265,18 +6222,18 @@
         <v>46224</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B82" s="5">
         <v>46188.635102939814</v>
@@ -6286,17 +6243,15 @@
         <v>46198.50797759259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H82" s="6"/>
       <c r="I82" s="5">
         <v>46224</v>
       </c>
@@ -6313,13 +6268,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="O82" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6329,7 +6284,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B83" s="9">
         <v>46188.63510991898</v>
@@ -6339,17 +6294,15 @@
         <v>46198.50796203704</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="10"/>
       <c r="I83" s="9">
         <v>46224</v>
       </c>
@@ -6366,13 +6319,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O83" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="P83" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>267</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6382,7 +6335,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B84" s="5">
         <v>46188.63513603009</v>
@@ -6392,17 +6345,15 @@
         <v>46188.6792096875</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
       <c r="I84" s="5">
         <v>46258</v>
       </c>
@@ -6419,13 +6370,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6434,18 +6385,18 @@
         <v>46258</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B85" s="9">
         <v>46188.63514172454</v>
@@ -6455,17 +6406,15 @@
         <v>46202.95697799769</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H85" s="10"/>
       <c r="I85" s="9">
         <v>46258</v>
       </c>
@@ -6482,13 +6431,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="O85" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="P85" s="10" t="s">
         <v>269</v>
-      </c>
-      <c r="O85" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="P85" s="10" t="s">
-        <v>272</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6498,7 +6447,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B86" s="5">
         <v>46188.63514853009</v>
@@ -6508,17 +6457,15 @@
         <v>46202.95697554398</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H86" s="6"/>
       <c r="I86" s="5">
         <v>46258</v>
       </c>
@@ -6535,13 +6482,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>272</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6551,7 +6498,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B87" s="9">
         <v>46188.63521115741</v>
@@ -6561,17 +6508,15 @@
         <v>46202.95705052083</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="10"/>
       <c r="I87" s="9">
         <v>46260</v>
       </c>
@@ -6588,13 +6533,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q87" s="9">
         <v>46260</v>
@@ -6603,18 +6548,18 @@
         <v>46260</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B88" s="5">
         <v>46188.63521795139</v>
@@ -6624,17 +6569,15 @@
         <v>46202.957050694444</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="5">
         <v>46261</v>
       </c>
@@ -6651,13 +6594,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6667,7 +6610,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B89" s="9">
         <v>46188.635222916666</v>
@@ -6677,17 +6620,15 @@
         <v>46188.680702488426</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="10"/>
       <c r="I89" s="9">
         <v>46260</v>
       </c>
@@ -6704,13 +6645,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>275</v>
-      </c>
-      <c r="O89" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6720,7 +6661,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46188.635247199076</v>
@@ -6730,7 +6671,7 @@
         <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6754,7 +6695,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6767,7 +6708,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B91" s="9">
         <v>46188.635250844905</v>
@@ -6777,16 +6718,16 @@
         <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I91" s="9">
         <v>46261</v>
@@ -6804,13 +6745,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q91" s="9">
         <v>46261</v>
@@ -6819,18 +6760,18 @@
         <v>46261</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B92" s="5">
         <v>46188.63525673611</v>
@@ -6840,16 +6781,16 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I92" s="5">
         <v>46261</v>
@@ -6867,13 +6808,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6883,7 +6824,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B93" s="9">
         <v>46188.635261689815</v>
@@ -6893,16 +6834,16 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I93" s="9">
         <v>46261</v>
@@ -6920,13 +6861,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6936,7 +6877,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B94" s="5">
         <v>46188.635279375</v>
@@ -6946,17 +6887,15 @@
         <v>46188.68118097223</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="5">
         <v>46262</v>
       </c>
@@ -6973,13 +6912,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q94" s="5">
         <v>46262</v>
@@ -6988,18 +6927,18 @@
         <v>46262</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B95" s="9">
         <v>46188.63528446759</v>
@@ -7009,17 +6948,15 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H95" s="10"/>
       <c r="I95" s="9">
         <v>46262</v>
       </c>
@@ -7036,13 +6973,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7052,7 +6989,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B96" s="5">
         <v>46188.6352894213</v>
@@ -7062,17 +6999,15 @@
         <v>46202.956975497684</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
       <c r="I96" s="5">
         <v>46262</v>
       </c>
@@ -7089,13 +7024,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7105,7 +7040,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B97" s="9">
         <v>46188.63530922454</v>
@@ -7115,16 +7050,16 @@
         <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7142,13 +7077,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q97" s="9">
         <v>46265</v>
@@ -7157,18 +7092,18 @@
         <v>46265</v>
       </c>
       <c r="S97" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B98" s="5">
         <v>46188.63531412037</v>
@@ -7178,16 +7113,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I98" s="5">
         <v>46265</v>
@@ -7205,13 +7140,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7221,7 +7156,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B99" s="9">
         <v>46188.63532239583</v>
@@ -7231,16 +7166,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I99" s="9">
         <v>46265</v>
@@ -7258,13 +7193,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7274,7 +7209,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
         <v>46188.63538068287</v>
@@ -7284,16 +7219,16 @@
         <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7311,13 +7246,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q100" s="5">
         <v>46266</v>
@@ -7326,18 +7261,18 @@
         <v>46266</v>
       </c>
       <c r="S100" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B101" s="9">
         <v>46188.6353874537</v>
@@ -7347,16 +7282,16 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7374,13 +7309,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7390,7 +7325,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B102" s="5">
         <v>46188.63539206018</v>
@@ -7400,16 +7335,16 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>
@@ -7427,13 +7362,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7443,7 +7378,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B103" s="9">
         <v>46188.635410682866</v>
@@ -7453,7 +7388,7 @@
         <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7477,7 +7412,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7490,7 +7425,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B104" s="5">
         <v>46188.635413993055</v>
@@ -7500,16 +7435,16 @@
         <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I104" s="5">
         <v>46267</v>
@@ -7527,13 +7462,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q104" s="5">
         <v>46267</v>
@@ -7542,18 +7477,18 @@
         <v>46275</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
@@ -7563,16 +7498,16 @@
         <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>
@@ -7590,13 +7525,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q105" s="9">
         <v>46267</v>
@@ -7605,13 +7540,13 @@
         <v>46275</v>
       </c>
       <c r="S105" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46209.818739016206</v>
+        <v>46220.168184317125</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>183</v>
@@ -4446,8 +4446,8 @@
       <c r="R50" s="5">
         <v>46227</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>90</v>
+      <c r="S50" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46209.819318298614</v>
+        <v>46220.16818357639</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4572,8 +4572,8 @@
       <c r="R52" s="5">
         <v>46227</v>
       </c>
-      <c r="S52" s="7" t="s">
-        <v>90</v>
+      <c r="S52" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46209.8196808912</v>
+        <v>46220.16818925926</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>198</v>
@@ -4698,8 +4698,8 @@
       <c r="R54" s="5">
         <v>46227</v>
       </c>
-      <c r="S54" s="7" t="s">
-        <v>90</v>
+      <c r="S54" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -1683,7 +1683,7 @@
         <v>46188.919674178236</v>
       </c>
       <c r="D5" s="9">
-        <v>46188.91968832176</v>
+        <v>46222.63597420139</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -1748,7 +1748,7 @@
         <v>46188.919543298616</v>
       </c>
       <c r="D6" s="5">
-        <v>46213.76143587963</v>
+        <v>46222.635976273144</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="315">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodeteOT 4360</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete OT 4360</t>
@@ -2439,7 +2442,7 @@
         <v>46197.58646039352</v>
       </c>
       <c r="D17" s="9">
-        <v>46197.586479687496</v>
+        <v>46223.56356081019</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>72</v>
@@ -2448,9 +2451,11 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I17" s="9">
         <v>46181</v>
       </c>
@@ -2473,7 +2478,7 @@
         <v>51</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="9">
         <v>46211</v>
@@ -2493,7 +2498,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="5">
         <v>46188.63438636574</v>
@@ -2502,18 +2507,20 @@
         <v>46206.502370312504</v>
       </c>
       <c r="D18" s="5">
-        <v>46213.191536909726</v>
+        <v>46223.56355663194</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I18" s="5">
         <v>46211</v>
       </c>
@@ -2533,10 +2540,10 @@
         <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="5">
         <v>46211</v>
@@ -2556,7 +2563,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" s="9">
         <v>46188.634392708336</v>
@@ -2565,18 +2572,20 @@
         <v>46206.50354868056</v>
       </c>
       <c r="D19" s="9">
-        <v>46213.19154050926</v>
+        <v>46223.56355248843</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I19" s="9">
         <v>46211</v>
       </c>
@@ -2596,10 +2605,10 @@
         <v>62</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q19" s="9">
         <v>46211</v>
@@ -2619,7 +2628,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="5">
         <v>46188.63439828704</v>
@@ -2628,18 +2637,20 @@
         <v>46206.50323137731</v>
       </c>
       <c r="D20" s="5">
-        <v>46213.191536875005</v>
+        <v>46223.56354857639</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I20" s="5">
         <v>46211</v>
       </c>
@@ -2659,10 +2670,10 @@
         <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q20" s="5">
         <v>46211</v>
@@ -2682,7 +2693,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" s="9">
         <v>46188.634403055556</v>
@@ -2691,18 +2702,20 @@
         <v>46206.5037743287</v>
       </c>
       <c r="D21" s="9">
-        <v>46213.19153681713</v>
+        <v>46223.5635421412</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I21" s="9">
         <v>46211</v>
       </c>
@@ -2722,10 +2735,10 @@
         <v>62</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q21" s="9">
         <v>46211</v>
@@ -2745,7 +2758,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="5">
         <v>46189.78075929398</v>
@@ -2757,7 +2770,7 @@
         <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2781,7 +2794,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2789,7 +2802,7 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2800,7 +2813,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="9">
         <v>46189.81187604167</v>
@@ -2809,18 +2822,20 @@
         <v>46197.586606770834</v>
       </c>
       <c r="D23" s="9">
-        <v>46197.586624143514</v>
+        <v>46223.563613356484</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I23" s="9">
         <v>46183</v>
       </c>
@@ -2837,13 +2852,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q23" s="9">
         <v>46183</v>
@@ -2863,7 +2878,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B24" s="5">
         <v>46189.8120440162</v>
@@ -2872,18 +2887,20 @@
         <v>46197.58654909722</v>
       </c>
       <c r="D24" s="5">
-        <v>46197.586567060185</v>
+        <v>46223.563609467594</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I24" s="5">
         <v>46183</v>
       </c>
@@ -2900,13 +2917,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q24" s="5">
         <v>46183</v>
@@ -2926,7 +2943,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" s="9">
         <v>46188.634174861116</v>
@@ -2938,7 +2955,7 @@
         <v>46212.85336304398</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -2962,7 +2979,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -2979,7 +2996,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
@@ -2991,16 +3008,16 @@
         <v>46212.653841203704</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -3018,13 +3035,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46183</v>
@@ -3044,7 +3061,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" s="9">
         <v>46188.634431805556</v>
@@ -3056,16 +3073,16 @@
         <v>46212.65346519676</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3083,29 +3100,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3117,16 +3134,16 @@
         <v>46212.65350395833</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3144,29 +3161,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3178,16 +3195,16 @@
         <v>46218.189632430556</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3205,13 +3222,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q29" s="9">
         <v>46213</v>
@@ -3220,7 +3237,7 @@
         <v>46225</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3231,7 +3248,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3243,16 +3260,16 @@
         <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3270,29 +3287,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3304,16 +3321,16 @@
         <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3331,29 +3348,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3365,16 +3382,16 @@
         <v>46218.18963260417</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3392,10 +3409,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3407,7 +3424,7 @@
         <v>46225</v>
       </c>
       <c r="S32" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3418,7 +3435,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3430,16 +3447,16 @@
         <v>46209.81926089121</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3457,13 +3474,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3473,7 +3490,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3485,16 +3502,16 @@
         <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3512,13 +3529,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3528,7 +3545,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3540,16 +3557,16 @@
         <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3567,10 +3584,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3582,7 +3599,7 @@
         <v>46253</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3593,7 +3610,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3605,16 +3622,16 @@
         <v>46209.62002645833</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3632,13 +3649,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3648,7 +3665,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3660,16 +3677,16 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3687,13 +3704,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3703,7 +3720,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3713,16 +3730,16 @@
         <v>46209.62071325231</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3740,10 +3757,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3756,7 +3773,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3768,16 +3785,16 @@
         <v>46218.18963259259</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3795,10 +3812,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3810,7 +3827,7 @@
         <v>46225</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3821,7 +3838,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3833,16 +3850,16 @@
         <v>46209.81962844907</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3860,13 +3877,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3876,7 +3893,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3888,16 +3905,16 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3915,13 +3932,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3931,7 +3948,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3943,7 +3960,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3967,7 +3984,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3984,7 +4001,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -3996,16 +4013,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4023,13 +4040,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4049,7 +4066,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4061,16 +4078,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4088,13 +4105,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4114,7 +4131,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4126,16 +4143,16 @@
         <v>46211.17038164352</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4153,13 +4170,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4179,7 +4196,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4189,16 +4206,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4216,10 +4233,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4231,18 +4248,18 @@
         <v>46259</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4252,16 +4269,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4279,13 +4296,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4295,7 +4312,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4305,16 +4322,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4332,13 +4349,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4348,7 +4365,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4358,7 +4375,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4382,7 +4399,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4395,7 +4412,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4405,16 +4422,16 @@
         <v>46220.168184317125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4432,13 +4449,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4447,18 +4464,18 @@
         <v>46227</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46188.634684942124</v>
@@ -4468,16 +4485,16 @@
         <v>46188.67731989583</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4495,13 +4512,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4510,18 +4527,18 @@
         <v>46231</v>
       </c>
       <c r="S51" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46188.634692962965</v>
@@ -4531,16 +4548,16 @@
         <v>46220.16818357639</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4558,13 +4575,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4573,18 +4590,18 @@
         <v>46227</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46188.63469954861</v>
@@ -4594,16 +4611,16 @@
         <v>46188.67731701389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4621,13 +4638,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4636,18 +4653,18 @@
         <v>46231</v>
       </c>
       <c r="S53" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63470560186</v>
@@ -4657,16 +4674,16 @@
         <v>46220.16818925926</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4684,13 +4701,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4699,18 +4716,18 @@
         <v>46227</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9">
         <v>46188.63471155093</v>
@@ -4720,16 +4737,16 @@
         <v>46188.67731351852</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4747,13 +4764,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4762,18 +4779,18 @@
         <v>46231</v>
       </c>
       <c r="S55" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46188.63471731481</v>
@@ -4783,7 +4800,7 @@
         <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4807,7 +4824,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4820,7 +4837,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
         <v>46188.63472107639</v>
@@ -4830,16 +4847,16 @@
         <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4857,13 +4874,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4872,18 +4889,18 @@
         <v>46234</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63473258102</v>
@@ -4893,16 +4910,16 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4920,13 +4937,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4936,7 +4953,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B59" s="9">
         <v>46188.63474121528</v>
@@ -4946,16 +4963,16 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -4973,13 +4990,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4989,7 +5006,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63477284722</v>
@@ -4999,16 +5016,16 @@
         <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -5026,13 +5043,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -5041,18 +5058,18 @@
         <v>46241</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46188.63477877315</v>
@@ -5062,16 +5079,16 @@
         <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5089,13 +5106,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5105,7 +5122,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63478605324</v>
@@ -5115,16 +5132,16 @@
         <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5142,13 +5159,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5158,7 +5175,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46188.63485537037</v>
@@ -5168,16 +5185,16 @@
         <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5195,13 +5212,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5210,18 +5227,18 @@
         <v>46244</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46188.634861805556</v>
@@ -5231,16 +5248,16 @@
         <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5258,13 +5275,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5274,7 +5291,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46188.63486881944</v>
@@ -5284,16 +5301,16 @@
         <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5311,13 +5328,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5327,7 +5344,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63489331018</v>
@@ -5337,7 +5354,7 @@
         <v>46212.654024166666</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5361,7 +5378,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5374,7 +5391,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B67" s="9">
         <v>46188.634903391205</v>
@@ -5386,16 +5403,16 @@
         <v>46212.65419707176</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5413,13 +5430,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5439,7 +5456,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46188.6349100463</v>
@@ -5451,16 +5468,16 @@
         <v>46212.65411137731</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5478,13 +5495,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5504,26 +5521,26 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46216.1786388426</v>
+        <v>46223.169957499995</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5541,13 +5558,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5556,18 +5573,18 @@
         <v>46223</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5577,16 +5594,16 @@
         <v>46209.620722314816</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5604,13 +5621,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5619,18 +5636,18 @@
         <v>46254</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5640,7 +5657,7 @@
         <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5664,7 +5681,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5677,25 +5694,27 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46188.67802387731</v>
+        <v>46223.56503278935</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H72" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I72" s="5">
         <v>46245</v>
       </c>
@@ -5712,13 +5731,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5727,36 +5746,38 @@
         <v>46251</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B73" s="9">
         <v>46188.63494034723</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46188.677983657406</v>
+        <v>46223.56372924769</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I73" s="9">
         <v>46245</v>
       </c>
@@ -5773,10 +5794,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5789,25 +5810,27 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46188.634945150465</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46188.677980567125</v>
+        <v>46223.563728611116</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H74" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I74" s="5">
         <v>46245</v>
       </c>
@@ -5824,10 +5847,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5840,7 +5863,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B75" s="9">
         <v>46188.634963668985</v>
@@ -5849,18 +5872,20 @@
         <v>46197.58704829861</v>
       </c>
       <c r="D75" s="9">
-        <v>46197.58706070602</v>
+        <v>46223.56504700231</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I75" s="9">
         <v>46252</v>
       </c>
@@ -5877,13 +5902,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5892,7 +5917,7 @@
         <v>46252</v>
       </c>
       <c r="S75" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -5903,7 +5928,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46188.63496887732</v>
@@ -5912,18 +5937,20 @@
         <v>46197.58695519676</v>
       </c>
       <c r="D76" s="5">
-        <v>46212.65402488426</v>
+        <v>46223.56383306713</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I76" s="5">
         <v>46252</v>
       </c>
@@ -5940,13 +5967,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5956,7 +5983,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B77" s="9">
         <v>46188.63498112268</v>
@@ -5965,18 +5992,20 @@
         <v>46197.587035335644</v>
       </c>
       <c r="D77" s="9">
-        <v>46212.65402556713</v>
+        <v>46223.563828865736</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I77" s="9">
         <v>46252</v>
       </c>
@@ -5993,13 +6022,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6009,25 +6038,27 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B78" s="5">
         <v>46188.635046296295</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46188.67895050926</v>
+        <v>46223.56503155093</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I78" s="5">
         <v>46253</v>
       </c>
@@ -6044,13 +6075,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -6059,36 +6090,38 @@
         <v>46253</v>
       </c>
       <c r="S78" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B79" s="9">
         <v>46188.63505403935</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46212.65379315973</v>
+        <v>46223.56391444444</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I79" s="9">
         <v>46253</v>
       </c>
@@ -6105,13 +6138,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6121,25 +6154,27 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46188.63506813657</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46212.65379201389</v>
+        <v>46223.56391378472</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I80" s="5">
         <v>46253</v>
       </c>
@@ -6156,13 +6191,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6172,25 +6207,27 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
         <v>46188.63509704861</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46217.19090564815</v>
+        <v>46223.565030949074</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I81" s="9">
         <v>46224</v>
       </c>
@@ -6207,13 +6244,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6222,36 +6259,38 @@
         <v>46224</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46188.635102939814</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.50797759259</v>
+        <v>46223.56401104167</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I82" s="5">
         <v>46224</v>
       </c>
@@ -6268,13 +6307,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6284,25 +6323,27 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
         <v>46188.63510991898</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46198.50796203704</v>
+        <v>46223.56401016204</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I83" s="9">
         <v>46224</v>
       </c>
@@ -6319,13 +6360,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6335,25 +6376,27 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46188.63513603009</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46188.6792096875</v>
+        <v>46223.5650303125</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I84" s="5">
         <v>46258</v>
       </c>
@@ -6370,13 +6413,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6385,36 +6428,38 @@
         <v>46258</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
         <v>46188.63514172454</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46202.95697799769</v>
+        <v>46223.5648503125</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I85" s="9">
         <v>46258</v>
       </c>
@@ -6431,13 +6476,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6447,25 +6492,27 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B86" s="5">
         <v>46188.63514853009</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46202.95697554398</v>
+        <v>46223.564849629634</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I86" s="5">
         <v>46258</v>
       </c>
@@ -6482,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6498,25 +6545,27 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46188.63521115741</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46202.95705052083</v>
+        <v>46223.565029606485</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I87" s="9">
         <v>46260</v>
       </c>
@@ -6533,13 +6582,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q87" s="9">
         <v>46260</v>
@@ -6548,36 +6597,38 @@
         <v>46260</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B88" s="5">
         <v>46188.63521795139</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46202.957050694444</v>
+        <v>46223.564933078706</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I88" s="5">
         <v>46261</v>
       </c>
@@ -6594,13 +6645,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6610,25 +6661,27 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B89" s="9">
         <v>46188.635222916666</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46188.680702488426</v>
+        <v>46223.5649325</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I89" s="9">
         <v>46260</v>
       </c>
@@ -6645,13 +6698,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6661,7 +6714,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46188.635247199076</v>
@@ -6671,7 +6724,7 @@
         <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6695,7 +6748,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6708,7 +6761,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B91" s="9">
         <v>46188.635250844905</v>
@@ -6718,16 +6771,16 @@
         <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I91" s="9">
         <v>46261</v>
@@ -6745,13 +6798,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q91" s="9">
         <v>46261</v>
@@ -6760,18 +6813,18 @@
         <v>46261</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B92" s="5">
         <v>46188.63525673611</v>
@@ -6781,16 +6834,16 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I92" s="5">
         <v>46261</v>
@@ -6808,13 +6861,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6824,7 +6877,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B93" s="9">
         <v>46188.635261689815</v>
@@ -6834,16 +6887,16 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I93" s="9">
         <v>46261</v>
@@ -6861,13 +6914,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6877,25 +6930,27 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B94" s="5">
         <v>46188.635279375</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46188.68118097223</v>
+        <v>46223.56517429398</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I94" s="5">
         <v>46262</v>
       </c>
@@ -6912,13 +6967,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q94" s="5">
         <v>46262</v>
@@ -6927,36 +6982,38 @@
         <v>46262</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B95" s="9">
         <v>46188.63528446759</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46202.956975532405</v>
+        <v>46223.56512299769</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="10"/>
+        <v>73</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>73</v>
+      </c>
       <c r="I95" s="9">
         <v>46262</v>
       </c>
@@ -6973,13 +7030,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6989,25 +7046,27 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B96" s="5">
         <v>46188.6352894213</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46202.956975497684</v>
+        <v>46223.565122395834</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>73</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="I96" s="5">
         <v>46262</v>
       </c>
@@ -7024,13 +7083,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7040,7 +7099,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B97" s="9">
         <v>46188.63530922454</v>
@@ -7050,16 +7109,16 @@
         <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7077,13 +7136,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q97" s="9">
         <v>46265</v>
@@ -7092,18 +7151,18 @@
         <v>46265</v>
       </c>
       <c r="S97" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B98" s="5">
         <v>46188.63531412037</v>
@@ -7113,16 +7172,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I98" s="5">
         <v>46265</v>
@@ -7140,13 +7199,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7156,7 +7215,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B99" s="9">
         <v>46188.63532239583</v>
@@ -7166,16 +7225,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I99" s="9">
         <v>46265</v>
@@ -7193,13 +7252,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7209,7 +7268,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B100" s="5">
         <v>46188.63538068287</v>
@@ -7219,16 +7278,16 @@
         <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7246,13 +7305,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q100" s="5">
         <v>46266</v>
@@ -7261,18 +7320,18 @@
         <v>46266</v>
       </c>
       <c r="S100" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B101" s="9">
         <v>46188.6353874537</v>
@@ -7282,16 +7341,16 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7309,13 +7368,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7325,7 +7384,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B102" s="5">
         <v>46188.63539206018</v>
@@ -7335,16 +7394,16 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>
@@ -7362,13 +7421,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7378,7 +7437,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B103" s="9">
         <v>46188.635410682866</v>
@@ -7388,7 +7447,7 @@
         <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7412,7 +7471,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7425,7 +7484,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B104" s="5">
         <v>46188.635413993055</v>
@@ -7435,16 +7494,16 @@
         <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I104" s="5">
         <v>46267</v>
@@ -7462,13 +7521,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q104" s="5">
         <v>46267</v>
@@ -7477,18 +7536,18 @@
         <v>46275</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
@@ -7498,16 +7557,16 @@
         <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>
@@ -7525,13 +7584,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q105" s="9">
         <v>46267</v>
@@ -7540,13 +7599,13 @@
         <v>46275</v>
       </c>
       <c r="S105" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -4482,7 +4482,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46188.67731989583</v>
+        <v>46224.19878961805</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4526,8 +4526,8 @@
       <c r="R51" s="9">
         <v>46231</v>
       </c>
-      <c r="S51" s="7" t="s">
-        <v>91</v>
+      <c r="S51" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46188.67731701389</v>
+        <v>46224.19878951389</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>197</v>
@@ -4652,8 +4652,8 @@
       <c r="R53" s="9">
         <v>46231</v>
       </c>
-      <c r="S53" s="7" t="s">
-        <v>91</v>
+      <c r="S53" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46188.67731351852</v>
+        <v>46224.19878923611</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>200</v>
@@ -4778,8 +4778,8 @@
       <c r="R55" s="9">
         <v>46231</v>
       </c>
-      <c r="S55" s="7" t="s">
-        <v>91</v>
+      <c r="S55" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46223.169957499995</v>
+        <v>46224.20394021991</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>233</v>
@@ -5572,8 +5572,8 @@
       <c r="R69" s="9">
         <v>46223</v>
       </c>
-      <c r="S69" s="12" t="s">
-        <v>118</v>
+      <c r="S69" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T69" s="10">
         <v>0</v>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46223.565030949074</v>
+        <v>46224.250663321756</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46223.56401104167</v>
+        <v>46224.25060195602</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>176</v>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46223.56401016204</v>
+        <v>46224.25066554398</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>176</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -3725,9 +3725,11 @@
       <c r="B38" s="5">
         <v>46188.63456381945</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46225.54980681713</v>
+      </c>
       <c r="D38" s="5">
-        <v>46209.62071325231</v>
+        <v>46225.54980878472</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -5589,9 +5591,11 @@
       <c r="B70" s="5">
         <v>46188.634922916666</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46225.549930995374</v>
+      </c>
       <c r="D70" s="5">
-        <v>46209.620722314816</v>
+        <v>46225.54995010416</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>235</v>
@@ -5639,10 +5643,10 @@
         <v>91</v>
       </c>
       <c r="T70" s="6">
-        <v>0</v>
-      </c>
-      <c r="U70" s="12" t="s">
-        <v>188</v>
+        <v>1</v>
+      </c>
+      <c r="U70" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5701,7 +5705,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46223.56503278935</v>
+        <v>46225.54993601852</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>241</v>
@@ -5764,7 +5768,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46223.56372924769</v>
+        <v>46225.549936979165</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>176</v>
@@ -5817,7 +5821,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46223.563728611116</v>
+        <v>46225.549937523145</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>176</v>
@@ -6214,7 +6218,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46224.250663321756</v>
+        <v>46225.19365898149</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>260</v>
@@ -6258,8 +6262,8 @@
       <c r="R81" s="9">
         <v>46224</v>
       </c>
-      <c r="S81" s="12" t="s">
-        <v>118</v>
+      <c r="S81" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T81" s="10">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="316">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodeteOT 4360</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2454,7 +2457,7 @@
         <v>73</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I17" s="9">
         <v>46181</v>
@@ -2478,7 +2481,7 @@
         <v>51</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="9">
         <v>46211</v>
@@ -2498,7 +2501,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" s="5">
         <v>46188.63438636574</v>
@@ -2510,7 +2513,7 @@
         <v>46223.56355663194</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2519,7 +2522,7 @@
         <v>73</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I18" s="5">
         <v>46211</v>
@@ -2540,10 +2543,10 @@
         <v>62</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q18" s="5">
         <v>46211</v>
@@ -2563,7 +2566,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="9">
         <v>46188.634392708336</v>
@@ -2575,7 +2578,7 @@
         <v>46223.56355248843</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
@@ -2584,7 +2587,7 @@
         <v>73</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I19" s="9">
         <v>46211</v>
@@ -2605,10 +2608,10 @@
         <v>62</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q19" s="9">
         <v>46211</v>
@@ -2628,7 +2631,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="5">
         <v>46188.63439828704</v>
@@ -2640,7 +2643,7 @@
         <v>46223.56354857639</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2649,7 +2652,7 @@
         <v>73</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I20" s="5">
         <v>46211</v>
@@ -2670,10 +2673,10 @@
         <v>62</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q20" s="5">
         <v>46211</v>
@@ -2693,7 +2696,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" s="9">
         <v>46188.634403055556</v>
@@ -2705,7 +2708,7 @@
         <v>46223.5635421412</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2714,7 +2717,7 @@
         <v>73</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I21" s="9">
         <v>46211</v>
@@ -2735,10 +2738,10 @@
         <v>62</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q21" s="9">
         <v>46211</v>
@@ -2758,7 +2761,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" s="5">
         <v>46189.78075929398</v>
@@ -2770,7 +2773,7 @@
         <v>46197.58663670139</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -2794,7 +2797,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -2802,7 +2805,7 @@
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2813,7 +2816,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" s="9">
         <v>46189.81187604167</v>
@@ -2825,7 +2828,7 @@
         <v>46223.563613356484</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2834,7 +2837,7 @@
         <v>73</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I23" s="9">
         <v>46183</v>
@@ -2852,13 +2855,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O23" s="10" t="s">
         <v>65</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q23" s="9">
         <v>46183</v>
@@ -2878,7 +2881,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" s="5">
         <v>46189.8120440162</v>
@@ -2890,7 +2893,7 @@
         <v>46223.563609467594</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -2899,7 +2902,7 @@
         <v>73</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I24" s="5">
         <v>46183</v>
@@ -2917,13 +2920,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q24" s="5">
         <v>46183</v>
@@ -2943,7 +2946,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B25" s="9">
         <v>46188.634174861116</v>
@@ -2955,7 +2958,7 @@
         <v>46212.85336304398</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -2979,7 +2982,7 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P25" s="10" t="s">
         <v>26</v>
@@ -2996,7 +2999,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46188.63442598379</v>
@@ -3008,16 +3011,16 @@
         <v>46212.653841203704</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I26" s="5">
         <v>46183</v>
@@ -3035,13 +3038,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="5">
         <v>46183</v>
@@ -3061,7 +3064,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="9">
         <v>46188.634431805556</v>
@@ -3073,16 +3076,16 @@
         <v>46212.65346519676</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I27" s="9">
         <v>46183</v>
@@ -3100,29 +3103,29 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>72</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
       <c r="S27" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46188.63443740741</v>
@@ -3134,16 +3137,16 @@
         <v>46212.65350395833</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I28" s="5">
         <v>46185</v>
@@ -3161,29 +3164,29 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
       <c r="S28" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
         <v>46188.63451584491</v>
@@ -3195,16 +3198,16 @@
         <v>46218.189632430556</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I29" s="9">
         <v>46213</v>
@@ -3222,13 +3225,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q29" s="9">
         <v>46213</v>
@@ -3237,7 +3240,7 @@
         <v>46225</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3248,7 +3251,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3260,16 +3263,16 @@
         <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I30" s="5">
         <v>46213</v>
@@ -3287,29 +3290,29 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
       <c r="S30" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3321,16 +3324,16 @@
         <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I31" s="9">
         <v>46217</v>
@@ -3348,29 +3351,29 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3382,16 +3385,16 @@
         <v>46218.18963260417</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I32" s="5">
         <v>46213</v>
@@ -3409,10 +3412,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3424,7 +3427,7 @@
         <v>46225</v>
       </c>
       <c r="S32" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3435,7 +3438,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3447,16 +3450,16 @@
         <v>46209.81926089121</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I33" s="9">
         <v>46213</v>
@@ -3474,13 +3477,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3490,7 +3493,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3502,16 +3505,16 @@
         <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I34" s="5">
         <v>46217</v>
@@ -3529,13 +3532,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3545,7 +3548,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3557,16 +3560,16 @@
         <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3584,10 +3587,10 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3599,7 +3602,7 @@
         <v>46253</v>
       </c>
       <c r="S35" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3610,7 +3613,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3622,16 +3625,16 @@
         <v>46209.62002645833</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3649,13 +3652,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3665,7 +3668,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3677,16 +3680,16 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3704,13 +3707,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3720,7 +3723,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3732,16 +3735,16 @@
         <v>46225.54980878472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3759,10 +3762,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3775,7 +3778,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3787,16 +3790,16 @@
         <v>46218.18963259259</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I39" s="9">
         <v>46213</v>
@@ -3814,10 +3817,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3829,7 +3832,7 @@
         <v>46225</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3840,7 +3843,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3852,16 +3855,16 @@
         <v>46209.81962844907</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I40" s="5">
         <v>46213</v>
@@ -3879,13 +3882,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3895,7 +3898,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3907,16 +3910,16 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I41" s="9">
         <v>46217</v>
@@ -3934,13 +3937,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3950,7 +3953,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3962,7 +3965,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3986,7 +3989,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4003,7 +4006,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -4015,16 +4018,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4042,13 +4045,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4068,7 +4071,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4080,16 +4083,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4107,13 +4110,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4133,7 +4136,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4145,16 +4148,16 @@
         <v>46211.17038164352</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4172,13 +4175,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4198,7 +4201,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4208,16 +4211,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4235,10 +4238,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4250,18 +4253,18 @@
         <v>46259</v>
       </c>
       <c r="S46" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4271,16 +4274,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4298,13 +4301,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4314,7 +4317,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4324,16 +4327,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4351,13 +4354,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4367,7 +4370,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4377,7 +4380,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4401,7 +4404,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4414,7 +4417,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4424,16 +4427,16 @@
         <v>46220.168184317125</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4451,13 +4454,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4466,18 +4469,18 @@
         <v>46227</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46188.634684942124</v>
@@ -4487,16 +4490,16 @@
         <v>46224.19878961805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4514,13 +4517,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4529,18 +4532,18 @@
         <v>46231</v>
       </c>
       <c r="S51" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
       </c>
       <c r="U51" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46188.634692962965</v>
@@ -4550,16 +4553,16 @@
         <v>46220.16818357639</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4577,13 +4580,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4592,18 +4595,18 @@
         <v>46227</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B53" s="9">
         <v>46188.63469954861</v>
@@ -4613,16 +4616,16 @@
         <v>46224.19878951389</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4640,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4655,18 +4658,18 @@
         <v>46231</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
       </c>
       <c r="U53" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63470560186</v>
@@ -4676,16 +4679,16 @@
         <v>46220.16818925926</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4703,13 +4706,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4718,18 +4721,18 @@
         <v>46227</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="9">
         <v>46188.63471155093</v>
@@ -4739,16 +4742,16 @@
         <v>46224.19878923611</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4766,13 +4769,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4781,18 +4784,18 @@
         <v>46231</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
       </c>
       <c r="U55" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5">
         <v>46188.63471731481</v>
@@ -4802,7 +4805,7 @@
         <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4826,7 +4829,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4839,7 +4842,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B57" s="9">
         <v>46188.63472107639</v>
@@ -4849,16 +4852,16 @@
         <v>46188.677743113425</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4876,13 +4879,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4891,18 +4894,18 @@
         <v>46234</v>
       </c>
       <c r="S57" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63473258102</v>
@@ -4912,16 +4915,16 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4939,13 +4942,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4955,7 +4958,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
         <v>46188.63474121528</v>
@@ -4965,16 +4968,16 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -4992,13 +4995,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5008,7 +5011,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63477284722</v>
@@ -5018,16 +5021,16 @@
         <v>46188.67773935186</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -5045,13 +5048,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -5060,18 +5063,18 @@
         <v>46241</v>
       </c>
       <c r="S60" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
       </c>
       <c r="U60" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B61" s="9">
         <v>46188.63477877315</v>
@@ -5081,16 +5084,16 @@
         <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5108,13 +5111,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5124,7 +5127,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63478605324</v>
@@ -5134,16 +5137,16 @@
         <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5161,13 +5164,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5177,7 +5180,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B63" s="9">
         <v>46188.63485537037</v>
@@ -5187,16 +5190,16 @@
         <v>46188.67780341435</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5214,13 +5217,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5229,18 +5232,18 @@
         <v>46244</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46188.634861805556</v>
@@ -5250,16 +5253,16 @@
         <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5277,13 +5280,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5293,7 +5296,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>46188.63486881944</v>
@@ -5303,16 +5306,16 @@
         <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5330,13 +5333,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5346,7 +5349,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63489331018</v>
@@ -5356,7 +5359,7 @@
         <v>46212.654024166666</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5380,7 +5383,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5393,7 +5396,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B67" s="9">
         <v>46188.634903391205</v>
@@ -5405,16 +5408,16 @@
         <v>46212.65419707176</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5432,13 +5435,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5458,7 +5461,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46188.6349100463</v>
@@ -5470,16 +5473,16 @@
         <v>46212.65411137731</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5497,13 +5500,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5523,7 +5526,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
@@ -5533,16 +5536,16 @@
         <v>46224.20394021991</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5560,13 +5563,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5581,12 +5584,12 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5598,16 +5601,16 @@
         <v>46225.54995010416</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5625,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5640,7 +5643,7 @@
         <v>46254</v>
       </c>
       <c r="S70" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5651,7 +5654,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5661,7 +5664,7 @@
         <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5685,7 +5688,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5698,7 +5701,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
@@ -5708,7 +5711,7 @@
         <v>46225.54993601852</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5717,7 +5720,7 @@
         <v>73</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I72" s="5">
         <v>46245</v>
@@ -5735,13 +5738,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5750,18 +5753,18 @@
         <v>46251</v>
       </c>
       <c r="S72" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
       </c>
       <c r="U72" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="9">
         <v>46188.63494034723</v>
@@ -5771,7 +5774,7 @@
         <v>46225.549936979165</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5780,7 +5783,7 @@
         <v>73</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I73" s="9">
         <v>46245</v>
@@ -5798,10 +5801,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5814,7 +5817,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B74" s="5">
         <v>46188.634945150465</v>
@@ -5824,7 +5827,7 @@
         <v>46225.549937523145</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5833,7 +5836,7 @@
         <v>73</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I74" s="5">
         <v>46245</v>
@@ -5851,10 +5854,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5867,7 +5870,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" s="9">
         <v>46188.634963668985</v>
@@ -5879,7 +5882,7 @@
         <v>46223.56504700231</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5888,7 +5891,7 @@
         <v>73</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I75" s="9">
         <v>46252</v>
@@ -5906,13 +5909,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5921,7 +5924,7 @@
         <v>46252</v>
       </c>
       <c r="S75" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -5932,7 +5935,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" s="5">
         <v>46188.63496887732</v>
@@ -5944,7 +5947,7 @@
         <v>46223.56383306713</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5953,7 +5956,7 @@
         <v>73</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I76" s="5">
         <v>46252</v>
@@ -5971,13 +5974,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -5987,7 +5990,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B77" s="9">
         <v>46188.63498112268</v>
@@ -5999,7 +6002,7 @@
         <v>46223.563828865736</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6008,7 +6011,7 @@
         <v>73</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I77" s="9">
         <v>46252</v>
@@ -6026,13 +6029,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6042,7 +6045,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B78" s="5">
         <v>46188.635046296295</v>
@@ -6052,7 +6055,7 @@
         <v>46223.56503155093</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6061,7 +6064,7 @@
         <v>73</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I78" s="5">
         <v>46253</v>
@@ -6079,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -6094,18 +6097,18 @@
         <v>46253</v>
       </c>
       <c r="S78" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
       </c>
       <c r="U78" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B79" s="9">
         <v>46188.63505403935</v>
@@ -6115,7 +6118,7 @@
         <v>46223.56391444444</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6124,7 +6127,7 @@
         <v>73</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I79" s="9">
         <v>46253</v>
@@ -6142,13 +6145,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6158,7 +6161,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B80" s="5">
         <v>46188.63506813657</v>
@@ -6168,7 +6171,7 @@
         <v>46223.56391378472</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6177,7 +6180,7 @@
         <v>73</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6195,13 +6198,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6211,7 +6214,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B81" s="9">
         <v>46188.63509704861</v>
@@ -6221,7 +6224,7 @@
         <v>46225.19365898149</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6230,7 +6233,7 @@
         <v>73</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I81" s="9">
         <v>46224</v>
@@ -6248,13 +6251,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6269,12 +6272,12 @@
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B82" s="5">
         <v>46188.635102939814</v>
@@ -6284,7 +6287,7 @@
         <v>46224.25060195602</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6293,7 +6296,7 @@
         <v>73</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I82" s="5">
         <v>46224</v>
@@ -6311,13 +6314,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6327,7 +6330,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B83" s="9">
         <v>46188.63510991898</v>
@@ -6337,7 +6340,7 @@
         <v>46224.25066554398</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6346,7 +6349,7 @@
         <v>73</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I83" s="9">
         <v>46224</v>
@@ -6364,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6380,7 +6383,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B84" s="5">
         <v>46188.63513603009</v>
@@ -6390,7 +6393,7 @@
         <v>46223.5650303125</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6399,7 +6402,7 @@
         <v>73</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I84" s="5">
         <v>46258</v>
@@ -6417,13 +6420,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6432,18 +6435,18 @@
         <v>46258</v>
       </c>
       <c r="S84" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B85" s="9">
         <v>46188.63514172454</v>
@@ -6453,7 +6456,7 @@
         <v>46223.5648503125</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6462,7 +6465,7 @@
         <v>73</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I85" s="9">
         <v>46258</v>
@@ -6480,13 +6483,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6496,7 +6499,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B86" s="5">
         <v>46188.63514853009</v>
@@ -6506,7 +6509,7 @@
         <v>46223.564849629634</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6515,7 +6518,7 @@
         <v>73</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I86" s="5">
         <v>46258</v>
@@ -6533,13 +6536,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6549,7 +6552,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B87" s="9">
         <v>46188.63521115741</v>
@@ -6559,7 +6562,7 @@
         <v>46223.565029606485</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6568,7 +6571,7 @@
         <v>73</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I87" s="9">
         <v>46260</v>
@@ -6586,13 +6589,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q87" s="9">
         <v>46260</v>
@@ -6601,18 +6604,18 @@
         <v>46260</v>
       </c>
       <c r="S87" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B88" s="5">
         <v>46188.63521795139</v>
@@ -6622,7 +6625,7 @@
         <v>46223.564933078706</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6631,7 +6634,7 @@
         <v>73</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I88" s="5">
         <v>46261</v>
@@ -6649,13 +6652,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6665,7 +6668,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B89" s="9">
         <v>46188.635222916666</v>
@@ -6675,7 +6678,7 @@
         <v>46223.5649325</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6684,7 +6687,7 @@
         <v>73</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I89" s="9">
         <v>46260</v>
@@ -6702,13 +6705,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6718,7 +6721,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46188.635247199076</v>
@@ -6728,7 +6731,7 @@
         <v>46188.67010366898</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6752,7 +6755,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6765,7 +6768,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B91" s="9">
         <v>46188.635250844905</v>
@@ -6775,16 +6778,16 @@
         <v>46188.68085204861</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I91" s="9">
         <v>46261</v>
@@ -6802,13 +6805,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q91" s="9">
         <v>46261</v>
@@ -6817,18 +6820,18 @@
         <v>46261</v>
       </c>
       <c r="S91" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B92" s="5">
         <v>46188.63525673611</v>
@@ -6838,16 +6841,16 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I92" s="5">
         <v>46261</v>
@@ -6865,13 +6868,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6881,7 +6884,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B93" s="9">
         <v>46188.635261689815</v>
@@ -6891,16 +6894,16 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I93" s="9">
         <v>46261</v>
@@ -6918,13 +6921,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6934,7 +6937,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B94" s="5">
         <v>46188.635279375</v>
@@ -6944,7 +6947,7 @@
         <v>46223.56517429398</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6953,7 +6956,7 @@
         <v>73</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I94" s="5">
         <v>46262</v>
@@ -6971,13 +6974,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q94" s="5">
         <v>46262</v>
@@ -6986,18 +6989,18 @@
         <v>46262</v>
       </c>
       <c r="S94" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B95" s="9">
         <v>46188.63528446759</v>
@@ -7007,7 +7010,7 @@
         <v>46223.56512299769</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7016,7 +7019,7 @@
         <v>73</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I95" s="9">
         <v>46262</v>
@@ -7034,13 +7037,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7050,7 +7053,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B96" s="5">
         <v>46188.6352894213</v>
@@ -7060,7 +7063,7 @@
         <v>46223.565122395834</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7069,7 +7072,7 @@
         <v>73</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I96" s="5">
         <v>46262</v>
@@ -7087,13 +7090,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7103,7 +7106,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B97" s="9">
         <v>46188.63530922454</v>
@@ -7113,16 +7116,16 @@
         <v>46188.68135644676</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7140,13 +7143,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q97" s="9">
         <v>46265</v>
@@ -7155,18 +7158,18 @@
         <v>46265</v>
       </c>
       <c r="S97" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B98" s="5">
         <v>46188.63531412037</v>
@@ -7176,16 +7179,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I98" s="5">
         <v>46265</v>
@@ -7203,13 +7206,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7219,7 +7222,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B99" s="9">
         <v>46188.63532239583</v>
@@ -7229,16 +7232,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I99" s="9">
         <v>46265</v>
@@ -7256,13 +7259,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7272,7 +7275,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B100" s="5">
         <v>46188.63538068287</v>
@@ -7282,16 +7285,16 @@
         <v>46188.68149567129</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7309,13 +7312,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q100" s="5">
         <v>46266</v>
@@ -7324,18 +7327,18 @@
         <v>46266</v>
       </c>
       <c r="S100" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B101" s="9">
         <v>46188.6353874537</v>
@@ -7345,16 +7348,16 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7372,13 +7375,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7388,7 +7391,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B102" s="5">
         <v>46188.63539206018</v>
@@ -7398,16 +7401,16 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>
@@ -7425,13 +7428,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7441,7 +7444,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" s="9">
         <v>46188.635410682866</v>
@@ -7451,7 +7454,7 @@
         <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7475,7 +7478,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7488,7 +7491,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B104" s="5">
         <v>46188.635413993055</v>
@@ -7498,16 +7501,16 @@
         <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I104" s="5">
         <v>46267</v>
@@ -7525,13 +7528,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q104" s="5">
         <v>46267</v>
@@ -7540,18 +7543,18 @@
         <v>46275</v>
       </c>
       <c r="S104" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
       </c>
       <c r="U104" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
@@ -7561,16 +7564,16 @@
         <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>
@@ -7588,13 +7591,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q105" s="9">
         <v>46267</v>
@@ -7603,13 +7606,13 @@
         <v>46275</v>
       </c>
       <c r="S105" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -415,214 +415,214 @@
     <t xml:space="preserve">Generación OC materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
   </si>
   <si>
+    <t>1215727831363866</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser OT 4360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>1215727831363886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser OT 4360 </t>
+  </si>
+  <si>
+    <t>Materiales corte Laser OT 4360,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215727831373407</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>1215727831373419</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>1215727723641751</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma OT 4360</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  OT 4360,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1215727723641768</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa OT 4360,Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t>1215727939764035</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4360,Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t>1215727939764052</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4360,Control de calidad fabricación externa  OT 4360,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215727939776448</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215727939776460</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215727792775028</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215727792775045</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1215727332551588</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215727939795692</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1215727939795714</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1215727792809496</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 4360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727939821604</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728035964722</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728035964734</t>
+  </si>
+  <si>
+    <t>1215727939892842</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215727939892854</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Bodega:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215727831363866</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser OT 4360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser OT 4360,Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>1215727831363886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser OT 4360 </t>
-  </si>
-  <si>
-    <t>Materiales corte Laser OT 4360,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215727831373407</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>1215727831373419</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360,Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>1215727723641751</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma OT 4360</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  OT 4360,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1215727723641768</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa OT 4360,Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t>1215727939764035</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4360,Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t>1215727939764052</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4360,Control de calidad fabricación externa  OT 4360,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215727939776448</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215727939776460</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792775028</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792775045</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1215727332551588</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215727939795692</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1215727939795714</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1215727792809496</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 4360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727939821604</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728035964722</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728035964734</t>
-  </si>
-  <si>
-    <t>1215727939892842</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215727939892854</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Bodega:</t>
   </si>
   <si>
     <t>Tarea en curso</t>
@@ -3195,7 +3195,7 @@
         <v>46209.81873614583</v>
       </c>
       <c r="D29" s="9">
-        <v>46218.189632430556</v>
+        <v>46226.19369722222</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>115</v>
@@ -3239,8 +3239,8 @@
       <c r="R29" s="9">
         <v>46225</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>119</v>
+      <c r="S29" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T29" s="10">
         <v>1</v>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B30" s="5">
         <v>46188.63452219908</v>
@@ -3263,7 +3263,7 @@
         <v>46209.81867788194</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3296,7 +3296,7 @@
         <v>77</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="9">
         <v>46188.634528194445</v>
@@ -3324,7 +3324,7 @@
         <v>46209.8187240625</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3354,10 +3354,10 @@
         <v>115</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B32" s="5">
         <v>46188.63453408565</v>
@@ -3382,10 +3382,10 @@
         <v>46209.819314988425</v>
       </c>
       <c r="D32" s="5">
-        <v>46218.18963260417</v>
+        <v>46226.19369837963</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3415,7 +3415,7 @@
         <v>100</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3426,8 +3426,8 @@
       <c r="R32" s="5">
         <v>46225</v>
       </c>
-      <c r="S32" s="12" t="s">
-        <v>119</v>
+      <c r="S32" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="9">
         <v>46188.634538252314</v>
@@ -3477,13 +3477,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O33" s="10" t="s">
         <v>81</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3493,7 +3493,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46188.63454329861</v>
@@ -3505,7 +3505,7 @@
         <v>46209.81930329862</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3532,13 +3532,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>82</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3548,7 +3548,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B35" s="9">
         <v>46188.63454804398</v>
@@ -3560,16 +3560,16 @@
         <v>46209.62077068287</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I35" s="9">
         <v>46213</v>
@@ -3590,7 +3590,7 @@
         <v>100</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3631,10 +3631,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3652,13 +3652,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3680,16 +3680,16 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>137</v>
       </c>
       <c r="I37" s="9">
         <v>46224</v>
@@ -3707,13 +3707,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>88</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3723,7 +3723,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3735,16 +3735,16 @@
         <v>46225.54980878472</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3762,10 +3762,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3787,10 +3787,10 @@
         <v>46209.81975005787</v>
       </c>
       <c r="D39" s="9">
-        <v>46218.18963259259</v>
+        <v>46226.19369717593</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
@@ -3820,7 +3820,7 @@
         <v>100</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3831,8 +3831,8 @@
       <c r="R39" s="9">
         <v>46225</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>119</v>
+      <c r="S39" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T39" s="10">
         <v>1</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3882,13 +3882,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3910,7 +3910,7 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -3937,13 +3937,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>85</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3965,7 +3965,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3989,7 +3989,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -4018,16 +4018,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4045,13 +4045,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4083,16 +4083,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4110,13 +4110,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4154,10 +4154,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4175,13 +4175,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4211,16 +4211,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4238,10 +4238,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4274,16 +4274,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4301,13 +4301,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>179</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4327,16 +4327,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4354,13 +4354,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4380,7 +4380,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4404,7 +4404,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4417,7 +4417,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4427,16 +4427,16 @@
         <v>46220.168184317125</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4454,13 +4454,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4469,7 +4469,7 @@
         <v>46227</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4496,10 +4496,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4517,7 +4517,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>192</v>
@@ -4532,7 +4532,7 @@
         <v>46231</v>
       </c>
       <c r="S51" s="12" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4559,10 +4559,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4580,10 +4580,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>196</v>
@@ -4595,7 +4595,7 @@
         <v>46227</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
@@ -4622,10 +4622,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4643,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4658,7 +4658,7 @@
         <v>46231</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4685,10 +4685,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4706,10 +4706,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>201</v>
@@ -4721,7 +4721,7 @@
         <v>46227</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
@@ -4748,10 +4748,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4769,13 +4769,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>200</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4784,7 +4784,7 @@
         <v>46231</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4882,7 +4882,7 @@
         <v>204</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>204</v>
@@ -4915,7 +4915,7 @@
         <v>46188.677464444445</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4968,7 +4968,7 @@
         <v>46188.677461087966</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5051,7 +5051,7 @@
         <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>204</v>
@@ -5084,7 +5084,7 @@
         <v>46198.507975775465</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5137,7 +5137,7 @@
         <v>46198.50797630787</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5196,10 +5196,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5220,7 +5220,7 @@
         <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>204</v>
@@ -5253,16 +5253,16 @@
         <v>46198.507973761574</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5306,16 +5306,16 @@
         <v>46198.507963055556</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5359,7 +5359,7 @@
         <v>46212.654024166666</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5414,10 +5414,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5435,7 +5435,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>112</v>
@@ -5479,10 +5479,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5500,7 +5500,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>97</v>
@@ -5542,10 +5542,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>186</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>187</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5563,7 +5563,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>94</v>
@@ -5607,10 +5607,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5628,10 +5628,10 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>237</v>
@@ -5774,7 +5774,7 @@
         <v>46225.549936979165</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5827,7 +5827,7 @@
         <v>46225.549937523145</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5912,7 +5912,7 @@
         <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>239</v>
@@ -5947,7 +5947,7 @@
         <v>46223.56383306713</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6002,7 +6002,7 @@
         <v>46223.563828865736</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6085,7 +6085,7 @@
         <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>239</v>
@@ -6118,7 +6118,7 @@
         <v>46223.56391444444</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6171,7 +6171,7 @@
         <v>46223.56391378472</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6254,7 +6254,7 @@
         <v>239</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>239</v>
@@ -6287,7 +6287,7 @@
         <v>46224.25060195602</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6340,7 +6340,7 @@
         <v>46224.25066554398</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6456,7 +6456,7 @@
         <v>46223.5648503125</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6486,7 +6486,7 @@
         <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>271</v>
@@ -6509,7 +6509,7 @@
         <v>46223.564849629634</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6539,7 +6539,7 @@
         <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>271</v>
@@ -6592,7 +6592,7 @@
         <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>275</v>
@@ -6625,7 +6625,7 @@
         <v>46223.564933078706</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6655,7 +6655,7 @@
         <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>277</v>
@@ -6678,7 +6678,7 @@
         <v>46223.5649325</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6708,7 +6708,7 @@
         <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>277</v>
@@ -6841,7 +6841,7 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6871,7 +6871,7 @@
         <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>288</v>
@@ -6894,7 +6894,7 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6924,7 +6924,7 @@
         <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>288</v>
@@ -6977,7 +6977,7 @@
         <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>280</v>
@@ -7010,7 +7010,7 @@
         <v>46223.56512299769</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7040,7 +7040,7 @@
         <v>291</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>293</v>
@@ -7063,7 +7063,7 @@
         <v>46223.565122395834</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7093,7 +7093,7 @@
         <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>295</v>
@@ -7146,7 +7146,7 @@
         <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>280</v>
@@ -7179,7 +7179,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7209,7 +7209,7 @@
         <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>299</v>
@@ -7232,7 +7232,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7262,7 +7262,7 @@
         <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>299</v>
@@ -7315,7 +7315,7 @@
         <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>303</v>
@@ -7348,7 +7348,7 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7378,7 +7378,7 @@
         <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>302</v>
@@ -7401,7 +7401,7 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7431,7 +7431,7 @@
         <v>302</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>302</v>
@@ -7570,10 +7570,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -622,22 +622,22 @@
     <t>Control de calidad corte laser ,Bodega:</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215727723755882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Bodega:,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215727723755882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Bodega:,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215727723755904</t>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46220.168184317125</v>
+        <v>46228.19350180555</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>184</v>
@@ -4468,19 +4468,19 @@
       <c r="R50" s="5">
         <v>46227</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>188</v>
+      <c r="S50" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46188.634684942124</v>
@@ -4490,7 +4490,7 @@
         <v>46224.19878961805</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4520,10 +4520,10 @@
         <v>181</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4532,7 +4532,7 @@
         <v>46231</v>
       </c>
       <c r="S51" s="12" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46220.16818357639</v>
+        <v>46228.19350177083</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4594,14 +4594,14 @@
       <c r="R52" s="5">
         <v>46227</v>
       </c>
-      <c r="S52" s="12" t="s">
-        <v>188</v>
+      <c r="S52" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T52" s="6">
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4658,7 +4658,7 @@
         <v>46231</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46220.16818925926</v>
+        <v>46228.193501863425</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4720,14 +4720,14 @@
       <c r="R54" s="5">
         <v>46227</v>
       </c>
-      <c r="S54" s="12" t="s">
-        <v>188</v>
+      <c r="S54" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T54" s="6">
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4784,7 +4784,7 @@
         <v>46231</v>
       </c>
       <c r="S55" s="12" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46188.677743113425</v>
+        <v>46227.19003516204</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>207</v>
@@ -4893,8 +4893,8 @@
       <c r="R57" s="9">
         <v>46234</v>
       </c>
-      <c r="S57" s="7" t="s">
-        <v>92</v>
+      <c r="S57" s="12" t="s">
+        <v>193</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
@@ -5441,7 +5441,7 @@
         <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5506,7 +5506,7 @@
         <v>97</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5569,7 +5569,7 @@
         <v>94</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5584,7 +5584,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46224.19878961805</v>
+        <v>46231.168843645835</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46224.19878951389</v>
+        <v>46231.16884633102</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46224.19878923611</v>
+        <v>46231.168848333335</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -637,55 +637,55 @@
     <t>Bodega:,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
   </si>
   <si>
+    <t>1215727723755904</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215727792922204</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215727939939908</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215727939939925</t>
+  </si>
+  <si>
+    <t>1215727792945512</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215727792945524</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215727723755904</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215727792922204</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215727939939908</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215727939939925</t>
-  </si>
-  <si>
-    <t>1215727792945512</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215727792945524</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
     <t>1215728008153046</t>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46231.168843645835</v>
+        <v>46232.18847476852</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>190</v>
@@ -4531,8 +4531,8 @@
       <c r="R51" s="9">
         <v>46231</v>
       </c>
-      <c r="S51" s="12" t="s">
-        <v>193</v>
+      <c r="S51" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T51" s="10">
         <v>0</v>
@@ -4543,7 +4543,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46188.634692962965</v>
@@ -4553,7 +4553,7 @@
         <v>46228.19350177083</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4586,7 +4586,7 @@
         <v>131</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4606,17 +4606,17 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46188.63469954861</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46231.16884633102</v>
+        <v>46232.1884746412</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4646,7 +4646,7 @@
         <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>174</v>
@@ -4657,8 +4657,8 @@
       <c r="R53" s="9">
         <v>46231</v>
       </c>
-      <c r="S53" s="12" t="s">
-        <v>193</v>
+      <c r="S53" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T53" s="10">
         <v>0</v>
@@ -4669,7 +4669,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63470560186</v>
@@ -4679,7 +4679,7 @@
         <v>46228.193501863425</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4712,7 +4712,7 @@
         <v>153</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4732,17 +4732,17 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9">
         <v>46188.63471155093</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46231.168848333335</v>
+        <v>46232.18847440972</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4772,7 +4772,7 @@
         <v>181</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>174</v>
@@ -4783,8 +4783,8 @@
       <c r="R55" s="9">
         <v>46231</v>
       </c>
-      <c r="S55" s="12" t="s">
-        <v>193</v>
+      <c r="S55" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T55" s="10">
         <v>0</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46188.63471731481</v>
@@ -4805,7 +4805,7 @@
         <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4829,7 +4829,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4842,7 +4842,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
         <v>46188.63472107639</v>
@@ -4852,16 +4852,16 @@
         <v>46227.19003516204</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4879,13 +4879,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4894,7 +4894,7 @@
         <v>46234</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
@@ -4921,10 +4921,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4942,7 +4942,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>211</v>
@@ -4974,10 +4974,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -4995,7 +4995,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>214</v>
@@ -5027,10 +5027,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -5048,13 +5048,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -5090,10 +5090,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5143,10 +5143,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5217,13 +5217,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -7122,10 +7122,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7185,10 +7185,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I98" s="5">
         <v>46265</v>
@@ -7238,10 +7238,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I99" s="9">
         <v>46265</v>
@@ -7291,10 +7291,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7354,10 +7354,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7407,10 +7407,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46227.19003516204</v>
+        <v>46234.170905798615</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46188.677464444445</v>
+        <v>46234.170908541666</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>176</v>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46188.677461087966</v>
+        <v>46234.17091030093</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>176</v>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46188.67773935186</v>
+        <v>46234.18878228009</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5062,8 +5062,8 @@
       <c r="R60" s="5">
         <v>46241</v>
       </c>
-      <c r="S60" s="7" t="s">
-        <v>92</v>
+      <c r="S60" s="12" t="s">
+        <v>209</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -685,31 +685,31 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
+    <t>1215728008153046</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1215728008153073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727831697337</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215728008153046</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1215728008153073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727831697337</t>
-  </si>
-  <si>
-    <t>Armado</t>
   </si>
   <si>
     <t>1215727831697354</t>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46234.170905798615</v>
+        <v>46235.18396792824</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>206</v>
@@ -4893,8 +4893,8 @@
       <c r="R57" s="9">
         <v>46234</v>
       </c>
-      <c r="S57" s="12" t="s">
-        <v>209</v>
+      <c r="S57" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T57" s="10">
         <v>0</v>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63473258102</v>
@@ -4945,10 +4945,10 @@
         <v>206</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4958,7 +4958,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B59" s="9">
         <v>46188.63474121528</v>
@@ -4998,10 +4998,10 @@
         <v>206</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>214</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>215</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63477284722</v>
@@ -5021,7 +5021,7 @@
         <v>46234.18878228009</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -5063,7 +5063,7 @@
         <v>46241</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>219</v>
@@ -5164,7 +5164,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>219</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -5187,7 +5187,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46188.67780341435</v>
+        <v>46237.19660862269</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5231,8 +5231,8 @@
       <c r="R63" s="9">
         <v>46244</v>
       </c>
-      <c r="S63" s="7" t="s">
-        <v>92</v>
+      <c r="S63" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -5018,7 +5018,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46234.18878228009</v>
+        <v>46241.16942939815</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>216</v>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46198.507975775465</v>
+        <v>46241.169431689814</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>176</v>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46198.50797630787</v>
+        <v>46241.16943283565</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>176</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -709,25 +709,25 @@
     <t>Armado</t>
   </si>
   <si>
+    <t>1215727831697354</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,check planos</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Armado</t>
+  </si>
+  <si>
+    <t>1215728008191848</t>
+  </si>
+  <si>
+    <t>1215727723738193</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215727831697354</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,check planos</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Armado</t>
-  </si>
-  <si>
-    <t>1215728008191848</t>
-  </si>
-  <si>
-    <t>1215727723738193</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
   </si>
   <si>
     <t>1215727940055152</t>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46241.16942939815</v>
+        <v>46242.18423770834</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>216</v>
@@ -5062,8 +5062,8 @@
       <c r="R60" s="5">
         <v>46241</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>217</v>
+      <c r="S60" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T60" s="6">
         <v>0</v>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46188.63477877315</v>
@@ -5114,10 +5114,10 @@
         <v>216</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5127,7 +5127,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63478605324</v>
@@ -5167,10 +5167,10 @@
         <v>216</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5180,7 +5180,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46188.63485537037</v>
@@ -5190,7 +5190,7 @@
         <v>46237.19660862269</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5232,7 +5232,7 @@
         <v>46244</v>
       </c>
       <c r="S63" s="12" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
@@ -5280,10 +5280,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>225</v>
@@ -5333,10 +5333,10 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>225</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -3502,7 +3502,7 @@
         <v>46209.8193018287</v>
       </c>
       <c r="D34" s="5">
-        <v>46209.81930329862</v>
+        <v>46243.82222765047</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>131</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -5187,7 +5187,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46237.19660862269</v>
+        <v>46244.16895025463</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>222</v>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46198.507973761574</v>
+        <v>46244.16895381945</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>176</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46198.507963055556</v>
+        <v>46244.16895252315</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>176</v>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46225.54993601852</v>
+        <v>46244.17375673611</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5752,8 +5752,8 @@
       <c r="R72" s="5">
         <v>46251</v>
       </c>
-      <c r="S72" s="7" t="s">
-        <v>92</v>
+      <c r="S72" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -727,67 +727,67 @@
     <t>Control de calidad Armado</t>
   </si>
   <si>
+    <t>1215727940055152</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Revestimiento,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727831792621</t>
+  </si>
+  <si>
+    <t>1215727940067011</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion motor,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215727940078553</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215727940078575</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215727793148813</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215728036191110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>Revestimiento,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728036191127</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje Alabe,Montaje motor,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1215727940098468</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Recepcion fabricación externa </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215727940055152</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Revestimiento,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727831792621</t>
-  </si>
-  <si>
-    <t>1215727940067011</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion motor,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215727940078553</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215727940078575</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215727793148813</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215728036191110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Revestimiento,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728036191127</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje Alabe,Montaje motor,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1215727940098468</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Recepcion fabricación externa </t>
   </si>
   <si>
     <t>1215728008352265</t>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46244.16895025463</v>
+        <v>46245.20140042824</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>222</v>
@@ -5231,8 +5231,8 @@
       <c r="R63" s="9">
         <v>46244</v>
       </c>
-      <c r="S63" s="12" t="s">
-        <v>223</v>
+      <c r="S63" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T63" s="10">
         <v>0</v>
@@ -5243,7 +5243,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46188.634861805556</v>
@@ -5286,7 +5286,7 @@
         <v>218</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46188.63486881944</v>
@@ -5339,7 +5339,7 @@
         <v>218</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63489331018</v>
@@ -5383,7 +5383,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5396,7 +5396,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B67" s="9">
         <v>46188.634903391205</v>
@@ -5408,7 +5408,7 @@
         <v>46212.65419707176</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5461,7 +5461,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46188.6349100463</v>
@@ -5473,7 +5473,7 @@
         <v>46212.65411137731</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
@@ -5536,7 +5536,7 @@
         <v>46224.20394021991</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5601,7 +5601,7 @@
         <v>46225.54995010416</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5634,7 +5634,7 @@
         <v>141</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5654,7 +5654,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5664,7 +5664,7 @@
         <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5688,7 +5688,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
@@ -5711,7 +5711,7 @@
         <v>46244.17375673611</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5738,13 +5738,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5753,7 +5753,7 @@
         <v>46251</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5801,7 +5801,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>245</v>
@@ -5854,7 +5854,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>245</v>
@@ -5879,7 +5879,7 @@
         <v>46197.58704829861</v>
       </c>
       <c r="D75" s="9">
-        <v>46223.56504700231</v>
+        <v>46245.17138105324</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5909,13 +5909,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5923,8 +5923,8 @@
       <c r="R75" s="9">
         <v>46252</v>
       </c>
-      <c r="S75" s="7" t="s">
-        <v>92</v>
+      <c r="S75" s="12" t="s">
+        <v>243</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -6082,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -6251,13 +6251,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6420,13 +6420,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>269</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6589,7 +6589,7 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>174</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -472,6 +472,9 @@
     <t>Generacion OC Fabricación Externa OT 4360,Fabricación estructura proveedor externo OT 4360</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215727939764035</t>
   </si>
   <si>
@@ -785,9 +788,6 @@
   </si>
   <si>
     <t xml:space="preserve">OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215728008352265</t>
@@ -3557,7 +3557,7 @@
         <v>46209.62074709491</v>
       </c>
       <c r="D35" s="9">
-        <v>46209.62077068287</v>
+        <v>46246.207784872684</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3601,8 +3601,8 @@
       <c r="R35" s="9">
         <v>46253</v>
       </c>
-      <c r="S35" s="7" t="s">
-        <v>92</v>
+      <c r="S35" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3658,7 +3658,7 @@
         <v>87</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3680,7 +3680,7 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3713,7 +3713,7 @@
         <v>88</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3723,7 +3723,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3735,16 +3735,16 @@
         <v>46225.54980878472</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3765,7 +3765,7 @@
         <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3790,7 +3790,7 @@
         <v>46226.19369717593</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
@@ -3820,7 +3820,7 @@
         <v>100</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3882,13 +3882,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3910,7 +3910,7 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -3937,13 +3937,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>85</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3965,7 +3965,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3989,7 +3989,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -4018,16 +4018,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4045,13 +4045,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4083,16 +4083,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4110,13 +4110,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4154,10 +4154,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4175,13 +4175,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4211,16 +4211,16 @@
         <v>46188.677102754635</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4238,10 +4238,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4274,16 +4274,16 @@
         <v>46202.95705038194</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4301,13 +4301,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4327,16 +4327,16 @@
         <v>46202.957206238425</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4354,13 +4354,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4380,7 +4380,7 @@
         <v>46188.660341678245</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4404,7 +4404,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4417,7 +4417,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4427,16 +4427,16 @@
         <v>46228.19350180555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4454,13 +4454,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>123</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4475,12 +4475,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="9">
         <v>46188.634684942124</v>
@@ -4490,16 +4490,16 @@
         <v>46232.18847476852</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4517,13 +4517,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4543,7 +4543,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46188.634692962965</v>
@@ -4553,16 +4553,16 @@
         <v>46228.19350177083</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4580,13 +4580,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>131</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4601,12 +4601,12 @@
         <v>0</v>
       </c>
       <c r="U52" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B53" s="9">
         <v>46188.63469954861</v>
@@ -4616,16 +4616,16 @@
         <v>46232.1884746412</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4643,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4669,7 +4669,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63470560186</v>
@@ -4679,16 +4679,16 @@
         <v>46228.193501863425</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4706,13 +4706,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4727,12 +4727,12 @@
         <v>0</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="9">
         <v>46188.63471155093</v>
@@ -4742,16 +4742,16 @@
         <v>46232.18847440972</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4769,13 +4769,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4795,7 +4795,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5">
         <v>46188.63471731481</v>
@@ -4805,7 +4805,7 @@
         <v>46188.662660393515</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4829,7 +4829,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4842,7 +4842,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B57" s="9">
         <v>46188.63472107639</v>
@@ -4852,16 +4852,16 @@
         <v>46235.18396792824</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4879,13 +4879,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63473258102</v>
@@ -4915,16 +4915,16 @@
         <v>46234.170908541666</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4942,13 +4942,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4958,7 +4958,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B59" s="9">
         <v>46188.63474121528</v>
@@ -4968,16 +4968,16 @@
         <v>46234.17091030093</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -4995,13 +4995,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63477284722</v>
@@ -5021,16 +5021,16 @@
         <v>46242.18423770834</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -5048,13 +5048,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B61" s="9">
         <v>46188.63477877315</v>
@@ -5084,16 +5084,16 @@
         <v>46241.169431689814</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5111,13 +5111,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5127,7 +5127,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63478605324</v>
@@ -5137,16 +5137,16 @@
         <v>46241.16943283565</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5164,13 +5164,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5180,7 +5180,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B63" s="9">
         <v>46188.63485537037</v>
@@ -5190,16 +5190,16 @@
         <v>46245.20140042824</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5217,13 +5217,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5243,7 +5243,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B64" s="5">
         <v>46188.634861805556</v>
@@ -5253,16 +5253,16 @@
         <v>46244.16895381945</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5280,13 +5280,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B65" s="9">
         <v>46188.63486881944</v>
@@ -5306,16 +5306,16 @@
         <v>46244.16895252315</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5333,13 +5333,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63489331018</v>
@@ -5359,7 +5359,7 @@
         <v>46212.654024166666</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5383,7 +5383,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5396,7 +5396,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B67" s="9">
         <v>46188.634903391205</v>
@@ -5408,16 +5408,16 @@
         <v>46212.65419707176</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5435,13 +5435,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5461,7 +5461,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46188.6349100463</v>
@@ -5473,16 +5473,16 @@
         <v>46212.65411137731</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5500,13 +5500,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
@@ -5536,16 +5536,16 @@
         <v>46224.20394021991</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5563,13 +5563,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>94</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5584,12 +5584,12 @@
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5601,16 +5601,16 @@
         <v>46225.54995010416</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5628,13 +5628,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5654,7 +5654,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5664,7 +5664,7 @@
         <v>46197.58705803241</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5688,7 +5688,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
@@ -5711,7 +5711,7 @@
         <v>46244.17375673611</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5738,13 +5738,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5753,7 +5753,7 @@
         <v>46251</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>243</v>
+        <v>138</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5774,7 +5774,7 @@
         <v>46225.549936979165</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5801,7 +5801,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>245</v>
@@ -5827,7 +5827,7 @@
         <v>46225.549937523145</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5854,7 +5854,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>245</v>
@@ -5909,13 +5909,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5924,7 +5924,7 @@
         <v>46252</v>
       </c>
       <c r="S75" s="12" t="s">
-        <v>243</v>
+        <v>138</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -5947,7 +5947,7 @@
         <v>46223.56383306713</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6002,7 +6002,7 @@
         <v>46223.563828865736</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46223.56503155093</v>
+        <v>46246.20778631944</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6082,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -6096,8 +6096,8 @@
       <c r="R78" s="5">
         <v>46253</v>
       </c>
-      <c r="S78" s="7" t="s">
-        <v>92</v>
+      <c r="S78" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
@@ -6118,7 +6118,7 @@
         <v>46223.56391444444</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6171,7 +6171,7 @@
         <v>46223.56391378472</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6251,13 +6251,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6287,7 +6287,7 @@
         <v>46224.25060195602</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6340,7 +6340,7 @@
         <v>46224.25066554398</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6420,13 +6420,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>269</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6456,7 +6456,7 @@
         <v>46223.5648503125</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6486,7 +6486,7 @@
         <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>271</v>
@@ -6509,7 +6509,7 @@
         <v>46223.564849629634</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6539,7 +6539,7 @@
         <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>271</v>
@@ -6589,10 +6589,10 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>275</v>
@@ -6625,7 +6625,7 @@
         <v>46223.564933078706</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6655,7 +6655,7 @@
         <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>277</v>
@@ -6678,7 +6678,7 @@
         <v>46223.5649325</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6708,7 +6708,7 @@
         <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>277</v>
@@ -6841,7 +6841,7 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6871,7 +6871,7 @@
         <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>288</v>
@@ -6894,7 +6894,7 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6924,7 +6924,7 @@
         <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>288</v>
@@ -6977,7 +6977,7 @@
         <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>280</v>
@@ -7010,7 +7010,7 @@
         <v>46223.56512299769</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7040,7 +7040,7 @@
         <v>291</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>293</v>
@@ -7063,7 +7063,7 @@
         <v>46223.565122395834</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7093,7 +7093,7 @@
         <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>295</v>
@@ -7122,10 +7122,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7146,7 +7146,7 @@
         <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>280</v>
@@ -7179,16 +7179,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I98" s="5">
         <v>46265</v>
@@ -7209,7 +7209,7 @@
         <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>299</v>
@@ -7232,16 +7232,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I99" s="9">
         <v>46265</v>
@@ -7262,7 +7262,7 @@
         <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>299</v>
@@ -7291,10 +7291,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7315,7 +7315,7 @@
         <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>303</v>
@@ -7348,16 +7348,16 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7378,7 +7378,7 @@
         <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>302</v>
@@ -7401,16 +7401,16 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>
@@ -7431,7 +7431,7 @@
         <v>302</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>302</v>
@@ -7570,10 +7570,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -5598,7 +5598,7 @@
         <v>46225.549930995374</v>
       </c>
       <c r="D70" s="5">
-        <v>46225.54995010416</v>
+        <v>46247.18171297453</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5642,8 +5642,8 @@
       <c r="R70" s="5">
         <v>46254</v>
       </c>
-      <c r="S70" s="7" t="s">
-        <v>92</v>
+      <c r="S70" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46244.17375673611</v>
+        <v>46251.16879708333</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46225.549936979165</v>
+        <v>46251.16880724537</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>177</v>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46225.549937523145</v>
+        <v>46251.16880950231</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>177</v>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46223.5650303125</v>
+        <v>46251.17314805556</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6434,8 +6434,8 @@
       <c r="R84" s="5">
         <v>46258</v>
       </c>
-      <c r="S84" s="7" t="s">
-        <v>92</v>
+      <c r="S84" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -4208,7 +4208,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46188.677102754635</v>
+        <v>46252.186730347225</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4252,8 +4252,8 @@
       <c r="R46" s="5">
         <v>46259</v>
       </c>
-      <c r="S46" s="7" t="s">
-        <v>92</v>
+      <c r="S46" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46251.16879708333</v>
+        <v>46252.19890878472</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5752,8 +5752,8 @@
       <c r="R72" s="5">
         <v>46251</v>
       </c>
-      <c r="S72" s="12" t="s">
-        <v>138</v>
+      <c r="S72" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -5879,7 +5879,7 @@
         <v>46197.58704829861</v>
       </c>
       <c r="D75" s="9">
-        <v>46245.17138105324</v>
+        <v>46253.17086679398</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5923,8 +5923,8 @@
       <c r="R75" s="9">
         <v>46252</v>
       </c>
-      <c r="S75" s="12" t="s">
-        <v>138</v>
+      <c r="S75" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T75" s="10">
         <v>1</v>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46246.20778631944</v>
+        <v>46253.16840084491</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46223.56391444444</v>
+        <v>46253.168402800926</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>177</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46223.56391378472</v>
+        <v>46253.16839918982</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>177</v>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46223.565029606485</v>
+        <v>46253.206614930554</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6603,8 +6603,8 @@
       <c r="R87" s="9">
         <v>46260</v>
       </c>
-      <c r="S87" s="7" t="s">
-        <v>92</v>
+      <c r="S87" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -472,118 +472,118 @@
     <t>Generacion OC Fabricación Externa OT 4360,Fabricación estructura proveedor externo OT 4360</t>
   </si>
   <si>
+    <t>1215727939764035</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  OT 4360,Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t>1215727939764052</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4360,Control de calidad fabricación externa  OT 4360,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215727939776448</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4360</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215727939776460</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215727792775028</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360,Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>1215727792775045</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4316</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4360,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1215727332551588</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215727939795692</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1215727939795714</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1215727792809496</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 4360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727939821604</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215727939764035</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  OT 4360,Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t>1215727939764052</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4360,Control de calidad fabricación externa  OT 4360,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215727939776448</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4360</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215727939776460</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado OT 4316,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792775028</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360,Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>1215727792775045</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4316</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4360,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1215727332551588</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215727939795692</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1215727939795714</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1215727792809496</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Propuesta Fabricación externa  OT 4360,propuesta Corte Laser OT 4360,Propuesta Corte plasma OT 4360,Propuesta Mecanizado OT 4360,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727939821604</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215728035964722</t>
@@ -3557,7 +3557,7 @@
         <v>46209.62074709491</v>
       </c>
       <c r="D35" s="9">
-        <v>46246.207784872684</v>
+        <v>46254.20243388889</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>134</v>
@@ -3601,8 +3601,8 @@
       <c r="R35" s="9">
         <v>46253</v>
       </c>
-      <c r="S35" s="12" t="s">
-        <v>138</v>
+      <c r="S35" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T35" s="10">
         <v>1</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46188.63455278936</v>
@@ -3658,7 +3658,7 @@
         <v>87</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="9">
         <v>46188.63455811342</v>
@@ -3680,7 +3680,7 @@
         <v>46209.620703761575</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3713,7 +3713,7 @@
         <v>88</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3723,7 +3723,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46188.63456381945</v>
@@ -3735,16 +3735,16 @@
         <v>46225.54980878472</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="H38" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="I38" s="5">
         <v>46253</v>
@@ -3765,7 +3765,7 @@
         <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B39" s="9">
         <v>46188.63456738426</v>
@@ -3790,7 +3790,7 @@
         <v>46226.19369717593</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
@@ -3820,7 +3820,7 @@
         <v>100</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P39" s="10" t="s">
         <v>26</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46188.63457166667</v>
@@ -3882,13 +3882,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3898,7 +3898,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="9">
         <v>46188.634576701385</v>
@@ -3910,7 +3910,7 @@
         <v>46209.81966414352</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -3937,13 +3937,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>85</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46188.63417921297</v>
@@ -3965,7 +3965,7 @@
         <v>46210.52951039352</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3989,7 +3989,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="9">
         <v>46188.63458247685</v>
@@ -4018,16 +4018,16 @@
         <v>46197.71623851852</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>161</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>162</v>
       </c>
       <c r="I43" s="9">
         <v>46188</v>
@@ -4045,13 +4045,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q43" s="9">
         <v>46188</v>
@@ -4071,7 +4071,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46188.634588587964</v>
@@ -4083,16 +4083,16 @@
         <v>46210.20534939815</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I44" s="5">
         <v>46203</v>
@@ -4110,13 +4110,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q44" s="5">
         <v>46203</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="9">
         <v>46188.63459497685</v>
@@ -4154,10 +4154,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="I45" s="9">
         <v>46210</v>
@@ -4175,13 +4175,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="9">
         <v>46210</v>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46188.63460983796</v>
@@ -4211,16 +4211,16 @@
         <v>46252.186730347225</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I46" s="5">
         <v>46259</v>
@@ -4238,10 +4238,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4253,7 +4253,7 @@
         <v>46259</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="9">
         <v>46259</v>
@@ -4301,7 +4301,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>178</v>
@@ -4333,10 +4333,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46259</v>
@@ -4354,7 +4354,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>177</v>
@@ -4496,10 +4496,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I51" s="9">
         <v>46230</v>
@@ -4622,10 +4622,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H53" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I53" s="9">
         <v>46230</v>
@@ -4649,7 +4649,7 @@
         <v>195</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q53" s="9">
         <v>46230</v>
@@ -4709,7 +4709,7 @@
         <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>201</v>
@@ -4748,10 +4748,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I55" s="9">
         <v>46230</v>
@@ -4775,7 +4775,7 @@
         <v>200</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q55" s="9">
         <v>46230</v>
@@ -4882,7 +4882,7 @@
         <v>204</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>204</v>
@@ -5051,7 +5051,7 @@
         <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>204</v>
@@ -5196,10 +5196,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I63" s="9">
         <v>46244</v>
@@ -5220,7 +5220,7 @@
         <v>204</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>204</v>
@@ -5259,10 +5259,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>147</v>
       </c>
       <c r="I64" s="5">
         <v>46244</v>
@@ -5312,10 +5312,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>146</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>147</v>
       </c>
       <c r="I65" s="9">
         <v>46244</v>
@@ -5631,7 +5631,7 @@
         <v>182</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>237</v>
@@ -5643,7 +5643,7 @@
         <v>46254</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -5912,7 +5912,7 @@
         <v>239</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>239</v>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46253.16840084491</v>
+        <v>46254.20243348379</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6085,7 +6085,7 @@
         <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>239</v>
@@ -6096,8 +6096,8 @@
       <c r="R78" s="5">
         <v>46253</v>
       </c>
-      <c r="S78" s="12" t="s">
-        <v>138</v>
+      <c r="S78" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
@@ -6254,7 +6254,7 @@
         <v>239</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>239</v>
@@ -6435,7 +6435,7 @@
         <v>46258</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="T84" s="6">
         <v>0</v>
@@ -6592,7 +6592,7 @@
         <v>239</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>275</v>
@@ -6604,7 +6604,7 @@
         <v>46260</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46188.68085204861</v>
+        <v>46254.19264275463</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>283</v>
@@ -6819,8 +6819,8 @@
       <c r="R91" s="9">
         <v>46261</v>
       </c>
-      <c r="S91" s="7" t="s">
-        <v>92</v>
+      <c r="S91" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
@@ -6977,7 +6977,7 @@
         <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>280</v>
@@ -7146,7 +7146,7 @@
         <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>280</v>
@@ -7315,7 +7315,7 @@
         <v>280</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>303</v>
@@ -7570,10 +7570,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H105" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I105" s="9">
         <v>46267</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -5598,7 +5598,7 @@
         <v>46225.549930995374</v>
       </c>
       <c r="D70" s="5">
-        <v>46247.18171297453</v>
+        <v>46255.20534878472</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>236</v>
@@ -5642,8 +5642,8 @@
       <c r="R70" s="5">
         <v>46254</v>
       </c>
-      <c r="S70" s="12" t="s">
-        <v>175</v>
+      <c r="S70" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46223.56517429398</v>
+        <v>46255.19699795139</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -6988,8 +6988,8 @@
       <c r="R94" s="5">
         <v>46262</v>
       </c>
-      <c r="S94" s="7" t="s">
-        <v>92</v>
+      <c r="S94" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="316">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -586,6 +586,9 @@
     <t>Media</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1215728035964722</t>
   </si>
   <si>
@@ -623,9 +626,6 @@
   </si>
   <si>
     <t>Control de calidad corte laser ,Bodega:</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215727723755882</t>
@@ -1636,7 +1636,7 @@
         <v>46188.91968755787</v>
       </c>
       <c r="D4" s="5">
-        <v>46188.91970172454</v>
+        <v>46258.16354357639</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -3962,7 +3962,7 @@
         <v>46210.52949314815</v>
       </c>
       <c r="D42" s="5">
-        <v>46210.52951039352</v>
+        <v>46258.1884375</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -4015,7 +4015,7 @@
         <v>46196.52481820602</v>
       </c>
       <c r="D43" s="9">
-        <v>46197.71623851852</v>
+        <v>46258.163839733796</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>159</v>
@@ -4080,7 +4080,7 @@
         <v>46198.50789115741</v>
       </c>
       <c r="D44" s="5">
-        <v>46210.20534939815</v>
+        <v>46258.163823379626</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>164</v>
@@ -4206,9 +4206,11 @@
       <c r="B46" s="5">
         <v>46188.63460983796</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46258.53859034722</v>
+      </c>
       <c r="D46" s="5">
-        <v>46252.186730347225</v>
+        <v>46258.57714934028</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4256,25 +4258,27 @@
         <v>175</v>
       </c>
       <c r="T46" s="6">
-        <v>0</v>
-      </c>
-      <c r="U46" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U46" s="12" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9">
+        <v>46258.57712081019</v>
+      </c>
       <c r="D47" s="9">
-        <v>46202.95705038194</v>
+        <v>46258.577122372684</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4304,10 +4308,10 @@
         <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4317,17 +4321,19 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46258.57713456018</v>
+      </c>
       <c r="D48" s="5">
-        <v>46202.957206238425</v>
+        <v>46258.57713605324</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4357,10 +4363,10 @@
         <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4370,17 +4376,19 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="9">
+        <v>46258.57499196759</v>
+      </c>
       <c r="D49" s="9">
-        <v>46188.660341678245</v>
+        <v>46258.57500517361</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4404,7 +4412,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4412,31 +4420,37 @@
       <c r="Q49" s="10"/>
       <c r="R49" s="10"/>
       <c r="S49" s="10"/>
-      <c r="T49" s="10"/>
-      <c r="U49" s="10"/>
+      <c r="T49" s="10">
+        <v>1</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46258.57488173612</v>
+      </c>
       <c r="D50" s="5">
-        <v>46228.19350180555</v>
+        <v>46258.57490248843</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4454,13 +4468,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>123</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4472,10 +4486,10 @@
         <v>32</v>
       </c>
       <c r="T50" s="6">
-        <v>0</v>
-      </c>
-      <c r="U50" s="12" t="s">
-        <v>189</v>
+        <v>1</v>
+      </c>
+      <c r="U50" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4485,9 +4499,11 @@
       <c r="B51" s="9">
         <v>46188.634684942124</v>
       </c>
-      <c r="C51" s="10"/>
+      <c r="C51" s="9">
+        <v>46258.57491376158</v>
+      </c>
       <c r="D51" s="9">
-        <v>46232.18847476852</v>
+        <v>46258.57493045139</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>191</v>
@@ -4517,7 +4533,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O51" s="10" t="s">
         <v>192</v>
@@ -4535,10 +4551,10 @@
         <v>32</v>
       </c>
       <c r="T51" s="10">
-        <v>0</v>
-      </c>
-      <c r="U51" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U51" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -4548,9 +4564,11 @@
       <c r="B52" s="5">
         <v>46188.634692962965</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46258.57489256945</v>
+      </c>
       <c r="D52" s="5">
-        <v>46228.19350177083</v>
+        <v>46258.57491056713</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>195</v>
@@ -4559,10 +4577,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4580,7 +4598,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>131</v>
@@ -4598,10 +4616,10 @@
         <v>32</v>
       </c>
       <c r="T52" s="6">
-        <v>0</v>
-      </c>
-      <c r="U52" s="12" t="s">
-        <v>189</v>
+        <v>1</v>
+      </c>
+      <c r="U52" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -4611,9 +4629,11 @@
       <c r="B53" s="9">
         <v>46188.63469954861</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="9">
+        <v>46258.57495891204</v>
+      </c>
       <c r="D53" s="9">
-        <v>46232.1884746412</v>
+        <v>46258.57497778935</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>198</v>
@@ -4643,7 +4663,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>195</v>
@@ -4661,10 +4681,10 @@
         <v>32</v>
       </c>
       <c r="T53" s="10">
-        <v>0</v>
-      </c>
-      <c r="U53" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U53" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -4674,9 +4694,11 @@
       <c r="B54" s="5">
         <v>46188.63470560186</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46258.57489766204</v>
+      </c>
       <c r="D54" s="5">
-        <v>46228.193501863425</v>
+        <v>46258.57491270833</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4685,10 +4707,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4706,7 +4728,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>153</v>
@@ -4724,10 +4746,10 @@
         <v>32</v>
       </c>
       <c r="T54" s="6">
-        <v>0</v>
-      </c>
-      <c r="U54" s="12" t="s">
-        <v>189</v>
+        <v>1</v>
+      </c>
+      <c r="U54" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4737,9 +4759,11 @@
       <c r="B55" s="9">
         <v>46188.63471155093</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46258.57497616898</v>
+      </c>
       <c r="D55" s="9">
-        <v>46232.18847440972</v>
+        <v>46258.574992256945</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>201</v>
@@ -4769,7 +4793,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>200</v>
@@ -4787,10 +4811,10 @@
         <v>32</v>
       </c>
       <c r="T55" s="10">
-        <v>0</v>
-      </c>
-      <c r="U55" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U55" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4800,9 +4824,11 @@
       <c r="B56" s="5">
         <v>46188.63471731481</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46258.57601996528</v>
+      </c>
       <c r="D56" s="5">
-        <v>46188.662660393515</v>
+        <v>46258.57603575231</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>204</v>
@@ -4837,8 +4863,12 @@
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
       <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
-      <c r="U56" s="6"/>
+      <c r="T56" s="6">
+        <v>1</v>
+      </c>
+      <c r="U56" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
@@ -4847,9 +4877,11 @@
       <c r="B57" s="9">
         <v>46188.63472107639</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46258.57506138889</v>
+      </c>
       <c r="D57" s="9">
-        <v>46235.18396792824</v>
+        <v>46258.5750800463</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>207</v>
@@ -4897,10 +4929,10 @@
         <v>32</v>
       </c>
       <c r="T57" s="10">
-        <v>0</v>
-      </c>
-      <c r="U57" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U57" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -4910,12 +4942,14 @@
       <c r="B58" s="5">
         <v>46188.63473258102</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46258.5750391551</v>
+      </c>
       <c r="D58" s="5">
-        <v>46234.170908541666</v>
+        <v>46258.57504092593</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -4963,12 +4997,14 @@
       <c r="B59" s="9">
         <v>46188.63474121528</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46258.57504487269</v>
+      </c>
       <c r="D59" s="9">
-        <v>46234.17091030093</v>
+        <v>46258.57504671296</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
@@ -5016,9 +5052,11 @@
       <c r="B60" s="5">
         <v>46188.63477284722</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46258.575111886574</v>
+      </c>
       <c r="D60" s="5">
-        <v>46242.18423770834</v>
+        <v>46258.57512483797</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5066,10 +5104,10 @@
         <v>32</v>
       </c>
       <c r="T60" s="6">
-        <v>0</v>
-      </c>
-      <c r="U60" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U60" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5079,12 +5117,14 @@
       <c r="B61" s="9">
         <v>46188.63477877315</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46258.575087881945</v>
+      </c>
       <c r="D61" s="9">
-        <v>46241.169431689814</v>
+        <v>46258.575089502316</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
@@ -5132,12 +5172,14 @@
       <c r="B62" s="5">
         <v>46188.63478605324</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46258.5750969213</v>
+      </c>
       <c r="D62" s="5">
-        <v>46241.16943283565</v>
+        <v>46258.57509857639</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5185,9 +5227,11 @@
       <c r="B63" s="9">
         <v>46188.63485537037</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9">
+        <v>46258.575180775464</v>
+      </c>
       <c r="D63" s="9">
-        <v>46245.20140042824</v>
+        <v>46258.57519108796</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>223</v>
@@ -5235,10 +5279,10 @@
         <v>32</v>
       </c>
       <c r="T63" s="10">
-        <v>0</v>
-      </c>
-      <c r="U63" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U63" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5248,12 +5292,14 @@
       <c r="B64" s="5">
         <v>46188.634861805556</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46258.57513146991</v>
+      </c>
       <c r="D64" s="5">
-        <v>46244.16895381945</v>
+        <v>46258.57513333333</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5301,12 +5347,14 @@
       <c r="B65" s="9">
         <v>46188.63486881944</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9">
+        <v>46258.575166423616</v>
+      </c>
       <c r="D65" s="9">
-        <v>46244.16895252315</v>
+        <v>46258.57516814815</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5354,12 +5402,14 @@
       <c r="B66" s="5">
         <v>46188.63489331018</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46258.57525863426</v>
+      </c>
       <c r="D66" s="5">
-        <v>46212.654024166666</v>
+        <v>46258.57527986111</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5391,8 +5441,12 @@
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
       <c r="S66" s="6"/>
-      <c r="T66" s="6"/>
-      <c r="U66" s="6"/>
+      <c r="T66" s="6">
+        <v>1</v>
+      </c>
+      <c r="U66" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
@@ -5414,10 +5468,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5435,7 +5489,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>112</v>
@@ -5479,10 +5533,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5500,7 +5554,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>97</v>
@@ -5531,9 +5585,11 @@
       <c r="B69" s="9">
         <v>46188.6349165162</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="9">
+        <v>46258.57524318287</v>
+      </c>
       <c r="D69" s="9">
-        <v>46224.20394021991</v>
+        <v>46258.575258171295</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>234</v>
@@ -5542,10 +5598,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5563,7 +5619,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>94</v>
@@ -5581,10 +5637,10 @@
         <v>32</v>
       </c>
       <c r="T69" s="10">
-        <v>0</v>
-      </c>
-      <c r="U69" s="12" t="s">
-        <v>189</v>
+        <v>1</v>
+      </c>
+      <c r="U69" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5607,10 +5663,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5628,7 +5684,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>141</v>
@@ -5661,7 +5717,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46197.58705803241</v>
+        <v>46258.57597358796</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>239</v>
@@ -5706,9 +5762,11 @@
       <c r="B72" s="5">
         <v>46188.63493152778</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46258.575706250005</v>
+      </c>
       <c r="D72" s="5">
-        <v>46252.19890878472</v>
+        <v>46258.57572197917</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>242</v>
@@ -5756,10 +5814,10 @@
         <v>32</v>
       </c>
       <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U72" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5771,10 +5829,10 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46251.16880724537</v>
+        <v>46258.57514153935</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5824,10 +5882,10 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46251.16880950231</v>
+        <v>46258.57517729167</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5879,7 +5937,7 @@
         <v>46197.58704829861</v>
       </c>
       <c r="D75" s="9">
-        <v>46253.17086679398</v>
+        <v>46258.16420450232</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>248</v>
@@ -5947,7 +6005,7 @@
         <v>46223.56383306713</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6002,7 +6060,7 @@
         <v>46223.563828865736</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6050,9 +6108,11 @@
       <c r="B78" s="5">
         <v>46188.635046296295</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46258.57588525463</v>
+      </c>
       <c r="D78" s="5">
-        <v>46254.20243348379</v>
+        <v>46258.57589622685</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>255</v>
@@ -6100,10 +6160,10 @@
         <v>32</v>
       </c>
       <c r="T78" s="6">
-        <v>0</v>
-      </c>
-      <c r="U78" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U78" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6113,12 +6173,14 @@
       <c r="B79" s="9">
         <v>46188.63505403935</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="9">
+        <v>46258.57586165509</v>
+      </c>
       <c r="D79" s="9">
-        <v>46253.168402800926</v>
+        <v>46258.57586484954</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6166,12 +6228,14 @@
       <c r="B80" s="5">
         <v>46188.63506813657</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46258.57587064814</v>
+      </c>
       <c r="D80" s="5">
-        <v>46253.16839918982</v>
+        <v>46258.57587212963</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6219,9 +6283,11 @@
       <c r="B81" s="9">
         <v>46188.63509704861</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="9">
+        <v>46258.57592091435</v>
+      </c>
       <c r="D81" s="9">
-        <v>46225.19365898149</v>
+        <v>46258.57593314815</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>261</v>
@@ -6269,10 +6335,10 @@
         <v>32</v>
       </c>
       <c r="T81" s="10">
-        <v>0</v>
-      </c>
-      <c r="U81" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U81" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6282,12 +6348,14 @@
       <c r="B82" s="5">
         <v>46188.635102939814</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46258.57590001158</v>
+      </c>
       <c r="D82" s="5">
-        <v>46224.25060195602</v>
+        <v>46258.575901539356</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6335,12 +6403,14 @@
       <c r="B83" s="9">
         <v>46188.63510991898</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="9">
+        <v>46258.57590351852</v>
+      </c>
       <c r="D83" s="9">
-        <v>46224.25066554398</v>
+        <v>46258.57590449074</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6388,9 +6458,11 @@
       <c r="B84" s="5">
         <v>46188.63513603009</v>
       </c>
-      <c r="C84" s="6"/>
+      <c r="C84" s="5">
+        <v>46258.57596667824</v>
+      </c>
       <c r="D84" s="5">
-        <v>46251.17314805556</v>
+        <v>46258.57597790509</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6438,10 +6510,10 @@
         <v>175</v>
       </c>
       <c r="T84" s="6">
-        <v>0</v>
-      </c>
-      <c r="U84" s="11" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="U84" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6451,12 +6523,14 @@
       <c r="B85" s="9">
         <v>46188.63514172454</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="9">
+        <v>46258.575944502314</v>
+      </c>
       <c r="D85" s="9">
-        <v>46223.5648503125</v>
+        <v>46258.57594594907</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6486,7 +6560,7 @@
         <v>268</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>271</v>
@@ -6504,12 +6578,14 @@
       <c r="B86" s="5">
         <v>46188.63514853009</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46258.575951631945</v>
+      </c>
       <c r="D86" s="5">
-        <v>46223.564849629634</v>
+        <v>46258.57595326389</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6539,7 +6615,7 @@
         <v>268</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>271</v>
@@ -6559,7 +6635,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46253.206614930554</v>
+        <v>46258.16445473379</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6622,10 +6698,10 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46223.564933078706</v>
+        <v>46258.577127094904</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6655,7 +6731,7 @@
         <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>277</v>
@@ -6675,10 +6751,10 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46223.5649325</v>
+        <v>46258.5771419213</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6708,7 +6784,7 @@
         <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>277</v>
@@ -6728,7 +6804,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46188.67010366898</v>
+        <v>46258.181910451385</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -6775,7 +6851,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46254.19264275463</v>
+        <v>46258.164585833336</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>283</v>
@@ -6841,7 +6917,7 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6871,7 +6947,7 @@
         <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>288</v>
@@ -6894,7 +6970,7 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6924,7 +7000,7 @@
         <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>288</v>
@@ -6944,7 +7020,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46255.19699795139</v>
+        <v>46258.16468540509</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -7010,7 +7086,7 @@
         <v>46223.56512299769</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7040,7 +7116,7 @@
         <v>291</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>293</v>
@@ -7063,7 +7139,7 @@
         <v>46223.565122395834</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7093,7 +7169,7 @@
         <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>295</v>
@@ -7113,7 +7189,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46188.68135644676</v>
+        <v>46258.18662144676</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>297</v>
@@ -7157,8 +7233,8 @@
       <c r="R97" s="9">
         <v>46265</v>
       </c>
-      <c r="S97" s="7" t="s">
-        <v>92</v>
+      <c r="S97" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -7179,7 +7255,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7209,7 +7285,7 @@
         <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>299</v>
@@ -7232,7 +7308,7 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7262,7 +7338,7 @@
         <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>299</v>
@@ -7282,7 +7358,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46188.68149567129</v>
+        <v>46258.16474872685</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>302</v>
@@ -7348,7 +7424,7 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7378,7 +7454,7 @@
         <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>302</v>
@@ -7401,7 +7477,7 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7431,7 +7507,7 @@
         <v>302</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>302</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -6462,7 +6462,7 @@
         <v>46258.57596667824</v>
       </c>
       <c r="D84" s="5">
-        <v>46258.57597790509</v>
+        <v>46259.17279440972</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>268</v>
@@ -6506,8 +6506,8 @@
       <c r="R84" s="5">
         <v>46258</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>175</v>
+      <c r="S84" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T84" s="6">
         <v>1</v>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46258.16474872685</v>
+        <v>46259.174705833335</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>302</v>
@@ -7402,8 +7402,8 @@
       <c r="R100" s="5">
         <v>46266</v>
       </c>
-      <c r="S100" s="7" t="s">
-        <v>92</v>
+      <c r="S100" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -583,307 +583,307 @@
     <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215728035964722</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728035964734</t>
+  </si>
+  <si>
+    <t>1215727939892842</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>1215727939892854</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Bodega:</t>
+  </si>
+  <si>
+    <t>1215727723755882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Bodega:,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727723755904</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215727792922204</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215727939939908</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215727939939925</t>
+  </si>
+  <si>
+    <t>1215727792945512</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215727792945524</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>1215728008153046</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1215728008153073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727831697337</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1215727831697354</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,check planos</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Armado</t>
+  </si>
+  <si>
+    <t>1215728008191848</t>
+  </si>
+  <si>
+    <t>1215727723738193</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215727940055152</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Revestimiento,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727831792621</t>
+  </si>
+  <si>
+    <t>1215727940067011</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion motor,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215727940078553</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215727940078575</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215727793148813</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215728036191110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>Revestimiento,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728036191127</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Montaje Alabe,Montaje motor,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1215727940098468</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215728008352265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215728008352282</t>
+  </si>
+  <si>
+    <t>1215728008391623</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1215727940112407</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727940112429</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1215728036181340</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1215728036181357</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>1215728008549824</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,check planos,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727793305863</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1215728008590051</t>
+  </si>
+  <si>
+    <t>Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>Montaje motor,OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
+  </si>
+  <si>
+    <t>1215727793316670</t>
+  </si>
+  <si>
+    <t>Montaje motor,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728137556075</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
+  </si>
+  <si>
+    <t>1215728137556092</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727940272095</t>
+  </si>
+  <si>
+    <t>1215727793206827</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Montaje:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215728035964722</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728035964734</t>
-  </si>
-  <si>
-    <t>1215727939892842</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>1215727939892854</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Bodega:</t>
-  </si>
-  <si>
-    <t>1215727723755882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Bodega:,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727723755904</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215727792922204</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215727939939908</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215727939939925</t>
-  </si>
-  <si>
-    <t>1215727792945512</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215727792945524</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>1215728008153046</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1215728008153073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727831697337</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1215727831697354</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,check planos</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Armado</t>
-  </si>
-  <si>
-    <t>1215728008191848</t>
-  </si>
-  <si>
-    <t>1215727723738193</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215727940055152</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Revestimiento,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727831792621</t>
-  </si>
-  <si>
-    <t>1215727940067011</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion motor,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215727940078553</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215727940078575</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215727793148813</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215728036191110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Revestimiento,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728036191127</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Montaje Alabe,Montaje motor,Montaje Rodete,Pruebas FAT,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1215727940098468</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215728008352265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215728008352282</t>
-  </si>
-  <si>
-    <t>1215728008391623</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1215727940112407</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727940112429</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1215728036181340</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1215728036181357</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>1215728008549824</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,check planos,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727793305863</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1215728008590051</t>
-  </si>
-  <si>
-    <t>Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
-  </si>
-  <si>
-    <t>1215727793316670</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728137556075</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ1-9-25/4</t>
-  </si>
-  <si>
-    <t>1215728137556092</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727940272095</t>
-  </si>
-  <si>
-    <t>1215727793206827</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
     <t>1215728137628840</t>
@@ -4210,7 +4210,7 @@
         <v>46258.53859034722</v>
       </c>
       <c r="D46" s="5">
-        <v>46258.57714934028</v>
+        <v>46260.18503548611</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>171</v>
@@ -4254,19 +4254,19 @@
       <c r="R46" s="5">
         <v>46259</v>
       </c>
-      <c r="S46" s="12" t="s">
-        <v>175</v>
+      <c r="S46" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
       </c>
       <c r="U46" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B47" s="9">
         <v>46188.634613946764</v>
@@ -4278,7 +4278,7 @@
         <v>46258.577122372684</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4308,10 +4308,10 @@
         <v>171</v>
       </c>
       <c r="O47" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="P47" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="P47" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46188.63461840278</v>
@@ -4333,7 +4333,7 @@
         <v>46258.57713605324</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4363,10 +4363,10 @@
         <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B49" s="9">
         <v>46188.63467295139</v>
@@ -4388,7 +4388,7 @@
         <v>46258.57500517361</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4412,7 +4412,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46188.63467763889</v>
@@ -4441,16 +4441,16 @@
         <v>46258.57490248843</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46226</v>
@@ -4468,13 +4468,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>123</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="5">
         <v>46226</v>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="9">
         <v>46188.634684942124</v>
@@ -4506,7 +4506,7 @@
         <v>46258.57493045139</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4533,13 +4533,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>192</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>193</v>
       </c>
       <c r="Q51" s="9">
         <v>46230</v>
@@ -4559,7 +4559,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46188.634692962965</v>
@@ -4571,16 +4571,16 @@
         <v>46258.57491056713</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I52" s="5">
         <v>46226</v>
@@ -4598,13 +4598,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>131</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46226</v>
@@ -4624,7 +4624,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B53" s="9">
         <v>46188.63469954861</v>
@@ -4636,7 +4636,7 @@
         <v>46258.57497778935</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
@@ -4663,10 +4663,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>174</v>
@@ -4689,7 +4689,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46188.63470560186</v>
@@ -4701,16 +4701,16 @@
         <v>46258.57491270833</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I54" s="5">
         <v>46226</v>
@@ -4728,13 +4728,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46226</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B55" s="9">
         <v>46188.63471155093</v>
@@ -4766,7 +4766,7 @@
         <v>46258.574992256945</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4793,10 +4793,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P55" s="10" t="s">
         <v>174</v>
@@ -4819,7 +4819,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B56" s="5">
         <v>46188.63471731481</v>
@@ -4831,7 +4831,7 @@
         <v>46258.57603575231</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>25</v>
@@ -4855,7 +4855,7 @@
         <v>26</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -4872,7 +4872,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B57" s="9">
         <v>46188.63472107639</v>
@@ -4884,16 +4884,16 @@
         <v>46258.5750800463</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I57" s="9">
         <v>46232</v>
@@ -4911,13 +4911,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="9">
         <v>46232</v>
@@ -4937,7 +4937,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46188.63473258102</v>
@@ -4949,16 +4949,16 @@
         <v>46258.57504092593</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I58" s="5">
         <v>46232</v>
@@ -4976,13 +4976,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4992,7 +4992,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B59" s="9">
         <v>46188.63474121528</v>
@@ -5004,16 +5004,16 @@
         <v>46258.57504671296</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I59" s="9">
         <v>46232</v>
@@ -5031,13 +5031,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O59" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="P59" s="10" t="s">
         <v>214</v>
-      </c>
-      <c r="P59" s="10" t="s">
-        <v>215</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46188.63477284722</v>
@@ -5059,16 +5059,16 @@
         <v>46258.57512483797</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46237</v>
@@ -5086,13 +5086,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="5">
         <v>46237</v>
@@ -5112,7 +5112,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B61" s="9">
         <v>46188.63477877315</v>
@@ -5124,16 +5124,16 @@
         <v>46258.575089502316</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I61" s="9">
         <v>46237</v>
@@ -5151,13 +5151,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O61" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="P61" s="10" t="s">
         <v>219</v>
-      </c>
-      <c r="P61" s="10" t="s">
-        <v>220</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5167,7 +5167,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B62" s="5">
         <v>46188.63478605324</v>
@@ -5179,16 +5179,16 @@
         <v>46258.57509857639</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46237</v>
@@ -5206,13 +5206,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B63" s="9">
         <v>46188.63485537037</v>
@@ -5234,7 +5234,7 @@
         <v>46258.57519108796</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5261,13 +5261,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q63" s="9">
         <v>46244</v>
@@ -5287,7 +5287,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B64" s="5">
         <v>46188.634861805556</v>
@@ -5299,7 +5299,7 @@
         <v>46258.57513333333</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5326,13 +5326,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5342,7 +5342,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B65" s="9">
         <v>46188.63486881944</v>
@@ -5354,7 +5354,7 @@
         <v>46258.57516814815</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5381,13 +5381,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5397,7 +5397,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46188.63489331018</v>
@@ -5409,7 +5409,7 @@
         <v>46258.57527986111</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>25</v>
@@ -5433,7 +5433,7 @@
         <v>26</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>26</v>
@@ -5450,7 +5450,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B67" s="9">
         <v>46188.634903391205</v>
@@ -5462,16 +5462,16 @@
         <v>46212.65419707176</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I67" s="9">
         <v>46205</v>
@@ -5489,13 +5489,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q67" s="9">
         <v>46205</v>
@@ -5515,7 +5515,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B68" s="5">
         <v>46188.6349100463</v>
@@ -5527,16 +5527,16 @@
         <v>46212.65411137731</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I68" s="5">
         <v>46189</v>
@@ -5554,13 +5554,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q68" s="5">
         <v>46189</v>
@@ -5580,7 +5580,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B69" s="9">
         <v>46188.6349165162</v>
@@ -5592,16 +5592,16 @@
         <v>46258.575258171295</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="I69" s="9">
         <v>46223</v>
@@ -5619,13 +5619,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>94</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q69" s="9">
         <v>46223</v>
@@ -5645,7 +5645,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B70" s="5">
         <v>46188.634922916666</v>
@@ -5657,16 +5657,16 @@
         <v>46255.20534878472</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I70" s="5">
         <v>46254</v>
@@ -5684,13 +5684,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>141</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q70" s="5">
         <v>46254</v>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B71" s="9">
         <v>46188.63492795139</v>
@@ -5720,7 +5720,7 @@
         <v>46258.57597358796</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>25</v>
@@ -5744,7 +5744,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P71" s="10" t="s">
         <v>26</v>
@@ -5757,7 +5757,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B72" s="5">
         <v>46188.63493152778</v>
@@ -5769,7 +5769,7 @@
         <v>46258.57572197917</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5796,13 +5796,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q72" s="5">
         <v>46245</v>
@@ -5822,7 +5822,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B73" s="9">
         <v>46188.63494034723</v>
@@ -5832,7 +5832,7 @@
         <v>46258.57514153935</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5859,10 +5859,10 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P73" s="10" t="s">
         <v>26</v>
@@ -5875,7 +5875,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B74" s="5">
         <v>46188.634945150465</v>
@@ -5885,7 +5885,7 @@
         <v>46258.57517729167</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5912,10 +5912,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5928,7 +5928,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B75" s="9">
         <v>46188.634963668985</v>
@@ -5940,7 +5940,7 @@
         <v>46258.16420450232</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5967,13 +5967,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O75" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q75" s="9">
         <v>46252</v>
@@ -5993,7 +5993,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B76" s="5">
         <v>46188.63496887732</v>
@@ -6005,7 +6005,7 @@
         <v>46223.56383306713</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6032,13 +6032,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>250</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>251</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6048,7 +6048,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B77" s="9">
         <v>46188.63498112268</v>
@@ -6060,7 +6060,7 @@
         <v>46223.563828865736</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6087,13 +6087,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B78" s="5">
         <v>46188.635046296295</v>
@@ -6115,7 +6115,7 @@
         <v>46258.57589622685</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6142,13 +6142,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q78" s="5">
         <v>46253</v>
@@ -6168,7 +6168,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B79" s="9">
         <v>46188.63505403935</v>
@@ -6180,7 +6180,7 @@
         <v>46258.57586484954</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -6207,13 +6207,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -6223,7 +6223,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B80" s="5">
         <v>46188.63506813657</v>
@@ -6235,7 +6235,7 @@
         <v>46258.57587212963</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6262,13 +6262,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6278,7 +6278,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B81" s="9">
         <v>46188.63509704861</v>
@@ -6290,7 +6290,7 @@
         <v>46258.57593314815</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6317,13 +6317,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q81" s="9">
         <v>46224</v>
@@ -6343,7 +6343,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B82" s="5">
         <v>46188.635102939814</v>
@@ -6355,7 +6355,7 @@
         <v>46258.575901539356</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6382,13 +6382,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>263</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>264</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B83" s="9">
         <v>46188.63510991898</v>
@@ -6410,7 +6410,7 @@
         <v>46258.57590449074</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6437,13 +6437,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B84" s="5">
         <v>46188.63513603009</v>
@@ -6465,7 +6465,7 @@
         <v>46259.17279440972</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6492,13 +6492,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q84" s="5">
         <v>46258</v>
@@ -6518,7 +6518,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B85" s="9">
         <v>46188.63514172454</v>
@@ -6530,7 +6530,7 @@
         <v>46258.57594594907</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6557,13 +6557,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6573,7 +6573,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B86" s="5">
         <v>46188.63514853009</v>
@@ -6585,7 +6585,7 @@
         <v>46258.57595326389</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6612,13 +6612,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6628,17 +6628,17 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B87" s="9">
         <v>46188.63521115741</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46258.16445473379</v>
+        <v>46260.16838396991</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6665,13 +6665,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q87" s="9">
         <v>46260</v>
@@ -6680,7 +6680,7 @@
         <v>46260</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
@@ -6701,7 +6701,7 @@
         <v>46258.577127094904</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6728,10 +6728,10 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>277</v>
@@ -6751,10 +6751,10 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46258.5771419213</v>
+        <v>46260.16838662037</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6781,10 +6781,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>277</v>
@@ -6896,7 +6896,7 @@
         <v>46261</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
@@ -6917,7 +6917,7 @@
         <v>46202.95704981481</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6947,7 +6947,7 @@
         <v>283</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>288</v>
@@ -6970,7 +6970,7 @@
         <v>46202.95697837963</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7000,7 +7000,7 @@
         <v>283</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>288</v>
@@ -7065,7 +7065,7 @@
         <v>46262</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7086,7 +7086,7 @@
         <v>46223.56512299769</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7116,7 +7116,7 @@
         <v>291</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>293</v>
@@ -7139,7 +7139,7 @@
         <v>46223.565122395834</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7169,7 +7169,7 @@
         <v>291</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>295</v>
@@ -7198,10 +7198,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H97" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I97" s="9">
         <v>46265</v>
@@ -7234,7 +7234,7 @@
         <v>46265</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -7255,16 +7255,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I98" s="5">
         <v>46265</v>
@@ -7285,7 +7285,7 @@
         <v>297</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>299</v>
@@ -7308,16 +7308,16 @@
         <v>46202.956975532405</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H99" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I99" s="9">
         <v>46265</v>
@@ -7338,7 +7338,7 @@
         <v>297</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P99" s="10" t="s">
         <v>299</v>
@@ -7367,10 +7367,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I100" s="5">
         <v>46266</v>
@@ -7403,7 +7403,7 @@
         <v>46266</v>
       </c>
       <c r="S100" s="12" t="s">
-        <v>175</v>
+        <v>275</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7424,16 +7424,16 @@
         <v>46202.95697842592</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="H101" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="I101" s="9">
         <v>46266</v>
@@ -7454,7 +7454,7 @@
         <v>302</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>302</v>
@@ -7477,16 +7477,16 @@
         <v>46202.95697895833</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I102" s="5">
         <v>46266</v>
@@ -7507,7 +7507,7 @@
         <v>302</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>302</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -6635,7 +6635,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46260.16838396991</v>
+        <v>46260.58957314814</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>273</v>
@@ -6685,8 +6685,8 @@
       <c r="T87" s="10">
         <v>0</v>
       </c>
-      <c r="U87" s="11" t="s">
-        <v>110</v>
+      <c r="U87" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46258.181910451385</v>
+        <v>46260.589834479164</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46258.16468540509</v>
+        <v>46260.58961618056</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -7070,8 +7070,8 @@
       <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="U94" s="11" t="s">
-        <v>110</v>
+      <c r="U94" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46258.18662144676</v>
+        <v>46260.5897877199</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>297</v>
@@ -7239,8 +7239,8 @@
       <c r="T97" s="10">
         <v>0</v>
       </c>
-      <c r="U97" s="11" t="s">
-        <v>110</v>
+      <c r="U97" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -883,40 +883,40 @@
     <t>Coordinacion Entrega con Cliente,Montaje:</t>
   </si>
   <si>
+    <t>1215728137628840</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1215728137628857</t>
+  </si>
+  <si>
+    <t>1215727793425699</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,PACKING LIST,Despacho,Embalaje</t>
+  </si>
+  <si>
+    <t>1215727793425711</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215728137628840</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1215728137628857</t>
-  </si>
-  <si>
-    <t>1215727793425699</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,PACKING LIST,Despacho,Embalaje</t>
-  </si>
-  <si>
-    <t>1215727793425711</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215727940307492</t>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46260.58957314814</v>
+        <v>46261.16823309028</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>273</v>
@@ -6679,8 +6679,8 @@
       <c r="R87" s="9">
         <v>46260</v>
       </c>
-      <c r="S87" s="12" t="s">
-        <v>275</v>
+      <c r="S87" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T87" s="10">
         <v>0</v>
@@ -6691,14 +6691,14 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B88" s="5">
         <v>46188.63521795139</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46258.577127094904</v>
+        <v>46261.16792226852</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>177</v>
@@ -6734,7 +6734,7 @@
         <v>177</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B89" s="9">
         <v>46188.635222916666</v>
@@ -6787,7 +6787,7 @@
         <v>177</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46188.635247199076</v>
@@ -6807,7 +6807,7 @@
         <v>46260.589834479164</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6831,7 +6831,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6844,26 +6844,26 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B91" s="9">
         <v>46188.635250844905</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46258.164585833336</v>
+        <v>46261.16796847222</v>
       </c>
       <c r="E91" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="10" t="s">
+      <c r="H91" s="10" t="s">
         <v>284</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>285</v>
       </c>
       <c r="I91" s="9">
         <v>46261</v>
@@ -6881,13 +6881,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q91" s="9">
         <v>46261</v>
@@ -6896,7 +6896,7 @@
         <v>46261</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46202.95704981481</v>
+        <v>46261.167970636576</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>177</v>
@@ -6923,10 +6923,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I92" s="5">
         <v>46261</v>
@@ -6944,7 +6944,7 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>177</v>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46202.95697837963</v>
+        <v>46261.16797177083</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>177</v>
@@ -6976,10 +6976,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="H93" s="10" t="s">
         <v>284</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>285</v>
       </c>
       <c r="I93" s="9">
         <v>46261</v>
@@ -6997,7 +6997,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O93" s="10" t="s">
         <v>177</v>
@@ -7050,13 +7050,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q94" s="5">
         <v>46262</v>
@@ -7065,7 +7065,7 @@
         <v>46262</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7219,13 +7219,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O97" s="10" t="s">
         <v>174</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q97" s="9">
         <v>46265</v>
@@ -7234,7 +7234,7 @@
         <v>46265</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -7388,7 +7388,7 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>174</v>
@@ -7403,7 +7403,7 @@
         <v>46266</v>
       </c>
       <c r="S100" s="12" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -7020,7 +7020,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46260.58961618056</v>
+        <v>46262.16906962963</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>291</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46223.56512299769</v>
+        <v>46262.169073287034</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>177</v>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46223.565122395834</v>
+        <v>46262.16907469908</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>177</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -916,22 +916,22 @@
     <t>RE-PINTADO,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
   </si>
   <si>
+    <t>1215727940307492</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215727940307509</t>
+  </si>
+  <si>
+    <t>1215727940311189</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215727940307492</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215727940307509</t>
-  </si>
-  <si>
-    <t>1215727940311189</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
   </si>
   <si>
     <t>1215728036487935</t>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46261.16796847222</v>
+        <v>46262.186115115735</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>282</v>
@@ -6895,8 +6895,8 @@
       <c r="R91" s="9">
         <v>46261</v>
       </c>
-      <c r="S91" s="12" t="s">
-        <v>286</v>
+      <c r="S91" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T91" s="10">
         <v>0</v>
@@ -6907,7 +6907,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B92" s="5">
         <v>46188.63525673611</v>
@@ -6950,7 +6950,7 @@
         <v>177</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6960,7 +6960,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B93" s="9">
         <v>46188.635261689815</v>
@@ -7003,7 +7003,7 @@
         <v>177</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7013,7 +7013,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B94" s="5">
         <v>46188.635279375</v>
@@ -7023,7 +7023,7 @@
         <v>46262.16906962963</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7065,7 +7065,7 @@
         <v>46262</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7113,7 +7113,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>177</v>
@@ -7166,7 +7166,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>177</v>
@@ -7234,7 +7234,7 @@
         <v>46265</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -7403,7 +7403,7 @@
         <v>46266</v>
       </c>
       <c r="S100" s="12" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -2770,7 +2770,7 @@
         <v>46197.58662379629</v>
       </c>
       <c r="D22" s="5">
-        <v>46197.58663670139</v>
+        <v>46262.9455846412</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>90</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -931,25 +931,25 @@
     <t>Embalaje</t>
   </si>
   <si>
+    <t>1215728036487935</t>
+  </si>
+  <si>
+    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Embalaje</t>
+  </si>
+  <si>
+    <t>1215728036487952</t>
+  </si>
+  <si>
+    <t>Embalaje,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728008768392</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215728036487935</t>
-  </si>
-  <si>
-    <t>OT4360 -  ZVN 1-9-90/2 + TOB + REJ,Embalaje</t>
-  </si>
-  <si>
-    <t>1215728036487952</t>
-  </si>
-  <si>
-    <t>Embalaje,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728008768392</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
   </si>
   <si>
     <t>1215727940331573</t>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46262.16906962963</v>
+        <v>46263.20301833333</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>290</v>
@@ -7064,8 +7064,8 @@
       <c r="R94" s="5">
         <v>46262</v>
       </c>
-      <c r="S94" s="12" t="s">
-        <v>291</v>
+      <c r="S94" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7076,7 +7076,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B95" s="9">
         <v>46188.63528446759</v>
@@ -7119,7 +7119,7 @@
         <v>177</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7129,7 +7129,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B96" s="5">
         <v>46188.6352894213</v>
@@ -7172,7 +7172,7 @@
         <v>177</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7182,7 +7182,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B97" s="9">
         <v>46188.63530922454</v>
@@ -7192,7 +7192,7 @@
         <v>46260.5897877199</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7234,7 +7234,7 @@
         <v>46265</v>
       </c>
       <c r="S97" s="12" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -7282,7 +7282,7 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>177</v>
@@ -7335,7 +7335,7 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O99" s="10" t="s">
         <v>177</v>
@@ -7403,7 +7403,7 @@
         <v>46266</v>
       </c>
       <c r="S100" s="12" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -5406,7 +5406,7 @@
         <v>46258.57525863426</v>
       </c>
       <c r="D66" s="5">
-        <v>46258.57527986111</v>
+        <v>46265.3437968287</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>182</v>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46260.5897877199</v>
+        <v>46265.16904971065</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>296</v>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46202.956975532405</v>
+        <v>46265.16904490741</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>177</v>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46202.956975532405</v>
+        <v>46265.1690515625</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>177</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -949,25 +949,25 @@
     <t>PACKING LIST</t>
   </si>
   <si>
+    <t>1215727940331573</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Planos Preliminar,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215728008769860</t>
+  </si>
+  <si>
+    <t>1215728008802770</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Costos,Logistica:,Gestion</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215727940331573</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Planos Preliminar,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215728008769860</t>
-  </si>
-  <si>
-    <t>1215728008802770</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Costos,Logistica:,Gestion</t>
   </si>
   <si>
     <t>1215728137775706</t>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46265.16904971065</v>
+        <v>46266.189001018516</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>296</v>
@@ -7233,8 +7233,8 @@
       <c r="R97" s="9">
         <v>46265</v>
       </c>
-      <c r="S97" s="12" t="s">
-        <v>297</v>
+      <c r="S97" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T97" s="10">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B98" s="5">
         <v>46188.63531412037</v>
@@ -7288,7 +7288,7 @@
         <v>177</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7298,7 +7298,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B99" s="9">
         <v>46188.63532239583</v>
@@ -7341,7 +7341,7 @@
         <v>177</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7351,17 +7351,17 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B100" s="5">
         <v>46188.63538068287</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46259.174705833335</v>
+        <v>46266.16857814815</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7394,7 +7394,7 @@
         <v>174</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q100" s="5">
         <v>46266</v>
@@ -7403,7 +7403,7 @@
         <v>46266</v>
       </c>
       <c r="S100" s="12" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46202.95697842592</v>
+        <v>46266.168580185185</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>177</v>
@@ -7451,13 +7451,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O101" s="10" t="s">
         <v>177</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46202.95697895833</v>
+        <v>46266.168581412036</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>177</v>
@@ -7504,13 +7504,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>177</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7607,7 +7607,7 @@
         <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>307</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="315">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -965,9 +965,6 @@
   </si>
   <si>
     <t>Costos,Logistica:,Gestion</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215728137775706</t>
@@ -7358,7 +7355,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46266.16857814815</v>
+        <v>46267.17007989583</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>301</v>
@@ -7402,8 +7399,8 @@
       <c r="R100" s="5">
         <v>46266</v>
       </c>
-      <c r="S100" s="12" t="s">
-        <v>303</v>
+      <c r="S100" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7414,7 +7411,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B101" s="9">
         <v>46188.6353874537</v>
@@ -7467,7 +7464,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B102" s="5">
         <v>46188.63539206018</v>
@@ -7520,7 +7517,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B103" s="9">
         <v>46188.635410682866</v>
@@ -7530,7 +7527,7 @@
         <v>46188.67123894676</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>25</v>
@@ -7554,7 +7551,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P103" s="10" t="s">
         <v>26</v>
@@ -7567,7 +7564,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B104" s="5">
         <v>46188.635413993055</v>
@@ -7577,16 +7574,16 @@
         <v>46188.68161465278</v>
       </c>
       <c r="E104" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G104" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="F104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G104" s="6" t="s">
+      <c r="H104" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>312</v>
       </c>
       <c r="I104" s="5">
         <v>46267</v>
@@ -7604,13 +7601,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>301</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q104" s="5">
         <v>46267</v>
@@ -7630,7 +7627,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
@@ -7640,7 +7637,7 @@
         <v>46188.920573842595</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7667,13 +7664,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q105" s="9">
         <v>46267</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="316">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -992,6 +992,9 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215728036640526</t>
@@ -7571,7 +7574,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46188.68161465278</v>
+        <v>46268.191007939815</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>309</v>
@@ -7615,8 +7618,8 @@
       <c r="R104" s="5">
         <v>46275</v>
       </c>
-      <c r="S104" s="7" t="s">
-        <v>92</v>
+      <c r="S104" s="12" t="s">
+        <v>312</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
@@ -7627,17 +7630,17 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46188.920573842595</v>
+        <v>46268.191008124995</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7667,7 +7670,7 @@
         <v>306</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>306</v>
@@ -7678,8 +7681,8 @@
       <c r="R105" s="9">
         <v>46275</v>
       </c>
-      <c r="S105" s="7" t="s">
-        <v>92</v>
+      <c r="S105" s="12" t="s">
+        <v>312</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46268.191007939815</v>
+        <v>46275.168045983795</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>309</v>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46268.191008124995</v>
+        <v>46275.16804815972</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>314</v>

--- a/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
+++ b/data/50001563 - ZITRON COLOMBIA ANTIOQUIA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="315">
   <si>
     <t>50001563 - "ZITRON COLOMBIA ANTIOQUIA"</t>
   </si>
@@ -992,9 +992,6 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215728036640526</t>
@@ -7574,7 +7571,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46275.168045983795</v>
+        <v>46276.13225435185</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>309</v>
@@ -7618,8 +7615,8 @@
       <c r="R104" s="5">
         <v>46275</v>
       </c>
-      <c r="S104" s="12" t="s">
-        <v>312</v>
+      <c r="S104" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T104" s="6">
         <v>0</v>
@@ -7630,17 +7627,17 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B105" s="9">
         <v>46188.63541944444</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46275.16804815972</v>
+        <v>46276.132254571756</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7670,7 +7667,7 @@
         <v>306</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>306</v>
@@ -7681,8 +7678,8 @@
       <c r="R105" s="9">
         <v>46275</v>
       </c>
-      <c r="S105" s="12" t="s">
-        <v>312</v>
+      <c r="S105" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T105" s="10">
         <v>0</v>
